--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,6 +772,1532 @@
         <is>
           <t>Odd_Corners_Under115</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>7948326</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>45871.45833333334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>7948334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>45871.45833333334</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>7948332</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>45871.45833333334</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7948335</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>45871.45833333334</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>['10', '30', '64']</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>7948330</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>45871.45833333334</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>['8', '41', '45+4']</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7948329</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>45871.45833333334</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>['22', '50']</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7948327</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>45871.45833333334</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP8"/>
+  <dimension ref="A1:BP13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,22 +926,22 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
         <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA2" t="n">
         <v>3</v>
@@ -997,7 +997,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>7948334</v>
+        <v>7948337</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -1038,10 +1038,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -1050,77 +1050,77 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U3" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="W3" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA3" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1144,70 +1144,70 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
         <v>4</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AZ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA3" t="n">
         <v>7</v>
       </c>
-      <c r="BA3" t="n">
-        <v>13</v>
-      </c>
       <c r="BB3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.65</v>
+        <v>8.85</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.35</v>
+        <v>3.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="BJ3" t="n">
-        <v>3.07</v>
+        <v>2.31</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="BL3" t="n">
-        <v>2.33</v>
+        <v>1.81</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.87</v>
+        <v>2.42</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.34</v>
+        <v>3.15</v>
       </c>
       <c r="BP3" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="4">
@@ -1215,7 +1215,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>7948332</v>
+        <v>7948336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1235,110 +1235,110 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="Q4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF4" t="n">
         <v>2.4</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>3.78</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1.76</v>
+        <v>2.37</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1362,70 +1362,70 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY4" t="n">
         <v>10</v>
       </c>
-      <c r="AX4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>13</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA4" t="n">
         <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BC4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.51</v>
+        <v>1.89</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.5</v>
+        <v>7.85</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.16</v>
+        <v>2.19</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="BJ4" t="n">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="BK4" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="BP4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="5">
@@ -1433,7 +1433,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>7948335</v>
+        <v>7948334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1453,197 +1453,197 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
         <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>['10', '30', '64']</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>8</v>
       </c>
       <c r="AV5" t="n">
         <v>2</v>
       </c>
       <c r="AW5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA5" t="n">
         <v>13</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BB5" t="n">
         <v>4</v>
       </c>
-      <c r="AY5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3</v>
-      </c>
       <c r="BC5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.1</v>
+        <v>8.65</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.47</v>
+        <v>2.92</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.48</v>
+        <v>4.35</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>2.53</v>
+        <v>3.07</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="BL5" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="BO5" t="n">
-        <v>2.77</v>
+        <v>2.34</v>
       </c>
       <c r="BP5" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="6">
@@ -1651,7 +1651,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>7948330</v>
+        <v>7948333</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1671,56 +1671,56 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="R6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U6" t="n">
         <v>3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>['16']</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>['8', '41', '45+4']</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.25</v>
       </c>
       <c r="V6" t="n">
         <v>2.63</v>
@@ -1729,37 +1729,37 @@
         <v>1.44</v>
       </c>
       <c r="X6" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.81</v>
+        <v>2.21</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.59</v>
+        <v>3.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.45</v>
+        <v>2.68</v>
       </c>
       <c r="AC6" t="n">
         <v>1.01</v>
       </c>
       <c r="AD6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF6" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AI6" t="n">
         <v>1.67</v>
@@ -1768,13 +1768,13 @@
         <v>2.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
@@ -1783,85 +1783,85 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV6" t="n">
         <v>3</v>
       </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>10</v>
-      </c>
       <c r="AW6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BC6" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.49</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="BJ6" t="n">
-        <v>2.28</v>
+        <v>2.83</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.34</v>
+        <v>2.48</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="7">
@@ -1869,7 +1869,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>7948329</v>
+        <v>7948332</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1889,110 +1889,110 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>['22', '50']</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
         <v>4.33</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U7" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="V7" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.26</v>
+        <v>3.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.47</v>
+        <v>3.75</v>
       </c>
       <c r="AC7" t="n">
         <v>1.01</v>
       </c>
       <c r="AD7" t="n">
-        <v>8.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AK7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL7" t="n">
         <v>1.27</v>
       </c>
-      <c r="AL7" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AM7" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2016,70 +2016,70 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AV7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA7" t="n">
         <v>4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>8</v>
       </c>
       <c r="BB7" t="n">
         <v>2</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.48</v>
+        <v>2.85</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="BJ7" t="n">
-        <v>2.53</v>
+        <v>2.19</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="BL7" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="BO7" t="n">
-        <v>2.77</v>
+        <v>3.38</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="8">
@@ -2087,7 +2087,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>7948327</v>
+        <v>7948335</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2107,35 +2107,35 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['10', '30', '64']</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2144,73 +2144,73 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="V8" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.61</v>
+        <v>3.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.5</v>
+        <v>3.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AD8" t="n">
-        <v>9.300000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.44</v>
+        <v>4.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
@@ -2234,70 +2234,1160 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX8" t="n">
         <v>4</v>
       </c>
-      <c r="AV8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>7</v>
-      </c>
       <c r="AY8" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
         <v>3</v>
       </c>
       <c r="BC8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7948330</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>45871.45833333334</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>['8', '41', '45+4']</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW9" t="n">
         <v>7</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="AX9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7948329</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>45871.45833333334</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>['22', '50']</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T10" t="n">
         <v>1.4</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="U10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX10" t="n">
         <v>9</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="AY10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>7948328</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>45871.45833333334</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>['8', '90+1']</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>7948327</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>45871.45833333334</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF12" t="n">
         <v>3.66</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BG12" t="n">
         <v>1.26</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BH12" t="n">
         <v>3.32</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BI12" t="n">
         <v>1.49</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BJ12" t="n">
         <v>2.44</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BK12" t="n">
         <v>1.82</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BL12" t="n">
         <v>1.93</v>
       </c>
-      <c r="BM8" t="n">
+      <c r="BM12" t="n">
         <v>2.29</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BN12" t="n">
         <v>1.58</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BO12" t="n">
         <v>2.9</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BP12" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7948331</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>45871.45833333334</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>45871.45833333334</v>
+        <v>45871.5</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -1819,10 +1819,10 @@
         <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD6" t="n">
         <v>1.77</v>
@@ -3345,10 +3345,10 @@
         <v>2</v>
       </c>
       <c r="BB13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD13" t="n">
         <v>4.04</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP13"/>
+  <dimension ref="A1:BP25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3388,6 +3388,2622 @@
       </c>
       <c r="BP13" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7948338</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>45878.35416666666</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>['19', '22', '74', '88']</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>7948341</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>45878.35416666666</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>['35', '58']</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>7948346</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>45878.45833333334</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>['58', '71', '76']</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>['68', '84', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X16" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>7948349</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>45878.45833333334</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>['36', '90+5']</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X17" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>7948348</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>45878.45833333334</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>7948347</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>45878.45833333334</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>['90+6']</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>['68', '70']</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X19" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>7948345</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>45878.45833333334</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>['32', '34', '53']</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>['4', '64']</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>7948340</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>45878.45833333334</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>['73', '81']</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X21" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>7948343</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>45878.45833333334</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>7948342</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>45878.45833333334</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>['18', '30']</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>7948339</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>45878.45833333334</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>['26', '34']</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X24" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>7948344</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>45878.45833333334</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>['47', '68']</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -4435,10 +4435,10 @@
         <v>8</v>
       </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD18" t="n">
         <v>2.32</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP25"/>
+  <dimension ref="A1:BP37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
         <v>1</v>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>3</v>
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>3</v>
@@ -5274,7 +5274,7 @@
         <v>3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -6004,6 +6004,2622 @@
       </c>
       <c r="BP25" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>7948354</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>45885.35416666666</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>['4', '19']</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V26" t="n">
+        <v>3</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X26" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>7948361</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>45885.35416666666</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>['41', '84', '88']</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X27" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>7948360</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>45885.45833333334</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>['57', '83']</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>7948359</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>45885.45833333334</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>['1', '90+4']</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>7948358</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>45885.45833333334</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X30" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>7948357</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>45885.45833333334</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>['30', '73']</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>['8', '90+3']</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X31" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>7948353</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>45885.45833333334</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>['23', '27']</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>7948355</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>45885.45833333334</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>['2', '22']</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X33" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>7948352</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>45885.45833333334</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>['18']</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V34" t="n">
+        <v>3</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X34" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>7948351</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>45885.45833333334</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>['32', '90+7']</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X35" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>7948350</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>45885.45833333334</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>5</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>['9', '15', '25', '60', '80']</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X36" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>7948356</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>45885.45833333334</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X37" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP37"/>
+  <dimension ref="A1:BP47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>1</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>2</v>
@@ -1786,7 +1786,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.5</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.5</v>
@@ -3963,10 +3963,10 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.5</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
         <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -8620,6 +8620,2186 @@
       </c>
       <c r="BP37" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>7948362</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>45888.64583333334</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X38" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>7948373</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>45888.65625</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>['45+7']</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
+      </c>
+      <c r="V39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X39" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>7948371</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>45888.65625</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X40" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>7948370</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>45888.65625</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>4</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>5</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>['28', '50', '56', '90+1']</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>7948369</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>45888.65625</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>['1', '22', '50', '55']</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X42" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>7948368</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>45888.65625</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>['45', '45+2']</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X43" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>7948365</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>45888.65625</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X44" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>7948364</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>45888.65625</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>['85', '90+10']</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
+      </c>
+      <c r="V45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X45" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>7948363</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>45888.65625</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>['14', '71']</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V46" t="n">
+        <v>3</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X46" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>7948366</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>45888.66666666666</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>3</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V47" t="n">
+        <v>3</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X47" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK47" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>1.82</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -8777,13 +8777,13 @@
         <v>2</v>
       </c>
       <c r="AV38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW38" t="n">
         <v>9</v>
       </c>
       <c r="AX38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY38" t="n">
         <v>11</v>
@@ -9213,13 +9213,13 @@
         <v>5</v>
       </c>
       <c r="AV40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW40" t="n">
         <v>17</v>
       </c>
       <c r="AX40" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY40" t="n">
         <v>22</v>
@@ -9428,13 +9428,13 @@
         <v>2.8</v>
       </c>
       <c r="AU41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV41" t="n">
         <v>3</v>
       </c>
       <c r="AW41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX41" t="n">
         <v>5</v>
@@ -9649,13 +9649,13 @@
         <v>3</v>
       </c>
       <c r="AV42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW42" t="n">
         <v>6</v>
       </c>
       <c r="AX42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY42" t="n">
         <v>9</v>
@@ -10082,13 +10082,13 @@
         <v>2.29</v>
       </c>
       <c r="AU44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV44" t="n">
         <v>1</v>
       </c>
       <c r="AW44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX44" t="n">
         <v>9</v>
@@ -10518,13 +10518,13 @@
         <v>2.24</v>
       </c>
       <c r="AU46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV46" t="n">
         <v>4</v>
       </c>
       <c r="AW46" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX46" t="n">
         <v>14</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -10518,13 +10518,13 @@
         <v>2.24</v>
       </c>
       <c r="AU46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV46" t="n">
         <v>4</v>
       </c>
       <c r="AW46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX46" t="n">
         <v>14</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP48"/>
+  <dimension ref="A1:BP50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.5</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.5</v>
@@ -3530,7 +3530,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -8759,10 +8759,10 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR38" t="n">
         <v>0.49</v>
@@ -8980,7 +8980,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR39" t="n">
         <v>1.5</v>
@@ -10721,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ47" t="n">
         <v>2</v>
@@ -11018,6 +11018,442 @@
       </c>
       <c r="BP48" t="n">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8217313</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>45892.35416666666</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>['45+1', '51']</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="V49" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X49" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>8217315</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>45892.35416666666</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="V50" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X50" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP50"/>
+  <dimension ref="A1:BP60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ3" t="n">
         <v>2</v>
@@ -2440,7 +2440,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ14" t="n">
         <v>2</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.5</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ23" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
         <v>2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -8977,7 +8977,7 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ39" t="n">
         <v>2.33</v>
@@ -9195,10 +9195,10 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR40" t="n">
         <v>1.1</v>
@@ -9416,7 +9416,7 @@
         <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR41" t="n">
         <v>0.76</v>
@@ -9631,7 +9631,7 @@
         <v>1</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ42" t="n">
         <v>1</v>
@@ -9849,10 +9849,10 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR43" t="n">
         <v>0.86</v>
@@ -10070,7 +10070,7 @@
         <v>3</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR44" t="n">
         <v>0.83</v>
@@ -10285,10 +10285,10 @@
         <v>3</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR45" t="n">
         <v>0.89</v>
@@ -10503,10 +10503,10 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR46" t="n">
         <v>0.93</v>
@@ -10724,7 +10724,7 @@
         <v>2</v>
       </c>
       <c r="AQ47" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR47" t="n">
         <v>0.87</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ48" t="n">
         <v>0</v>
@@ -11454,6 +11454,2186 @@
       </c>
       <c r="BP50" t="n">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>8217288</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>45892.45833333334</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>['56', '80']</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V51" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X51" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ51" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="n">
+        <v>8217308</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>45892.45833333334</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V52" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X52" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BJ52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="n">
+        <v>8217309</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>45892.45833333334</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>4</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X53" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="n">
+        <v>8217310</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>45892.45833333334</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>3</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X54" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ54" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK54" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BL54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>8217311</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>45892.45833333334</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>['9', '72']</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S55" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V55" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="n">
+        <v>8217316</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>45892.45833333334</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>['7', '90+3']</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S56" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V56" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X56" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ56" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="n">
+        <v>8217314</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>45892.45833333334</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>['6', '81']</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V57" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X57" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ57" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="n">
+        <v>8217312</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>45892.45833333334</v>
+      </c>
+      <c r="F58" t="n">
+        <v>5</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R58" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V58" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X58" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI58" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BJ58" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK58" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>8217294</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>45892.45833333334</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>2</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R59" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S59" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V59" t="n">
+        <v>3</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X59" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ59" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BK59" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL59" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="n">
+        <v>8217317</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>45892.45833333334</v>
+      </c>
+      <c r="F60" t="n">
+        <v>5</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>2</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>['11', '31']</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>['18', '83']</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="R60" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V60" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X60" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG60" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI60" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ60" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK60" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL60" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -932,16 +932,16 @@
         <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AY2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BA2" t="n">
         <v>4</v>
@@ -1150,16 +1150,16 @@
         <v>2</v>
       </c>
       <c r="AW3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AX3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA3" t="n">
         <v>13</v>
@@ -1368,16 +1368,16 @@
         <v>2</v>
       </c>
       <c r="AW4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4</v>
       </c>
       <c r="BA4" t="n">
         <v>4</v>
@@ -1586,16 +1586,16 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BA5" t="n">
         <v>3</v>
@@ -1804,16 +1804,16 @@
         <v>1</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AX6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BA6" t="n">
         <v>10</v>
@@ -2022,16 +2022,16 @@
         <v>7</v>
       </c>
       <c r="AW7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX7" t="n">
         <v>5</v>
       </c>
-      <c r="AX7" t="n">
-        <v>2</v>
-      </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA7" t="n">
         <v>8</v>
@@ -2240,16 +2240,16 @@
         <v>5</v>
       </c>
       <c r="AW8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY8" t="n">
         <v>6</v>
       </c>
-      <c r="AY8" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
         <v>2</v>
@@ -2458,16 +2458,16 @@
         <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BA9" t="n">
         <v>7</v>
@@ -2676,16 +2676,16 @@
         <v>2</v>
       </c>
       <c r="AW10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AY10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
         <v>4</v>
@@ -2894,16 +2894,16 @@
         <v>2</v>
       </c>
       <c r="AW11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA11" t="n">
         <v>4</v>
@@ -3112,16 +3112,16 @@
         <v>1</v>
       </c>
       <c r="AW12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX12" t="n">
         <v>4</v>
       </c>
-      <c r="AX12" t="n">
-        <v>1</v>
-      </c>
       <c r="AY12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BA12" t="n">
         <v>7</v>
@@ -3333,13 +3333,13 @@
         <v>2</v>
       </c>
       <c r="AX13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AY13" t="n">
         <v>6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
         <v>1</v>
@@ -3548,16 +3548,16 @@
         <v>5</v>
       </c>
       <c r="AW14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
         <v>1</v>
@@ -3766,16 +3766,16 @@
         <v>3</v>
       </c>
       <c r="AW15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
         <v>2</v>
@@ -3984,16 +3984,16 @@
         <v>2</v>
       </c>
       <c r="AW16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX16" t="n">
         <v>4</v>
       </c>
-      <c r="AX16" t="n">
-        <v>1</v>
-      </c>
       <c r="AY16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>3</v>
       </c>
       <c r="BA16" t="n">
         <v>5</v>
@@ -4202,16 +4202,16 @@
         <v>6</v>
       </c>
       <c r="AW17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>1</v>
@@ -4420,16 +4420,16 @@
         <v>4</v>
       </c>
       <c r="AW18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA18" t="n">
         <v>2</v>
@@ -4638,16 +4638,16 @@
         <v>3</v>
       </c>
       <c r="AW19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AY19" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BA19" t="n">
         <v>6</v>
@@ -4856,16 +4856,16 @@
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BA20" t="n">
         <v>3</v>
@@ -5074,16 +5074,16 @@
         <v>8</v>
       </c>
       <c r="AW21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
         <v>2</v>
@@ -5292,16 +5292,16 @@
         <v>3</v>
       </c>
       <c r="AW22" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AX22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY22" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AZ22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA22" t="n">
         <v>8</v>
@@ -5513,13 +5513,13 @@
         <v>4</v>
       </c>
       <c r="AX23" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AY23" t="n">
         <v>7</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="BA23" t="n">
         <v>1</v>
@@ -5728,16 +5728,16 @@
         <v>3</v>
       </c>
       <c r="AW24" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>9</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>8</v>
@@ -5946,16 +5946,16 @@
         <v>2</v>
       </c>
       <c r="AW25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA25" t="n">
         <v>6</v>
@@ -6149,13 +6149,13 @@
         <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.91</v>
+        <v>1.04</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.13</v>
+        <v>1.62</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.04</v>
+        <v>2.66</v>
       </c>
       <c r="AU26" t="n">
         <v>10</v>
@@ -6164,16 +6164,16 @@
         <v>3</v>
       </c>
       <c r="AW26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY26" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA26" t="n">
         <v>4</v>
@@ -6367,13 +6367,13 @@
         <v>1.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.46</v>
+        <v>4.15</v>
       </c>
       <c r="AU27" t="n">
         <v>5</v>
@@ -6382,16 +6382,16 @@
         <v>3</v>
       </c>
       <c r="AW27" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AY27" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AZ27" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BA27" t="n">
         <v>4</v>
@@ -6585,13 +6585,13 @@
         <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -6600,16 +6600,16 @@
         <v>4</v>
       </c>
       <c r="AW28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX28" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ28" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BA28" t="n">
         <v>7</v>
@@ -6803,13 +6803,13 @@
         <v>1.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.44</v>
+        <v>3.12</v>
       </c>
       <c r="AU29" t="n">
         <v>6</v>
@@ -6818,16 +6818,16 @@
         <v>3</v>
       </c>
       <c r="AW29" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AX29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AY29" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BA29" t="n">
         <v>12</v>
@@ -7021,13 +7021,13 @@
         <v>2</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -7036,16 +7036,16 @@
         <v>4</v>
       </c>
       <c r="AW30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX30" t="n">
         <v>5</v>
       </c>
-      <c r="AX30" t="n">
-        <v>3</v>
-      </c>
       <c r="AY30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA30" t="n">
         <v>6</v>
@@ -7239,13 +7239,13 @@
         <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AU31" t="n">
         <v>8</v>
@@ -7254,16 +7254,16 @@
         <v>2</v>
       </c>
       <c r="AW31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY31" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AZ31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA31" t="n">
         <v>3</v>
@@ -7457,13 +7457,13 @@
         <v>2</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="AU32" t="n">
         <v>5</v>
@@ -7472,16 +7472,16 @@
         <v>4</v>
       </c>
       <c r="AW32" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AX32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AY32" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AZ32" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="BA32" t="n">
         <v>7</v>
@@ -7675,13 +7675,13 @@
         <v>2</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.13</v>
+        <v>2.31</v>
       </c>
       <c r="AU33" t="n">
         <v>5</v>
@@ -7690,16 +7690,16 @@
         <v>1</v>
       </c>
       <c r="AW33" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY33" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AZ33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA33" t="n">
         <v>9</v>
@@ -7893,13 +7893,13 @@
         <v>1</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.49</v>
+        <v>0.8</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.78</v>
+        <v>2.21</v>
       </c>
       <c r="AU34" t="n">
         <v>2</v>
@@ -7908,16 +7908,16 @@
         <v>1</v>
       </c>
       <c r="AW34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AX34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AY34" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ34" t="n">
         <v>6</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>2</v>
       </c>
       <c r="BA34" t="n">
         <v>3</v>
@@ -8111,13 +8111,13 @@
         <v>1.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.33</v>
+        <v>3.02</v>
       </c>
       <c r="AU35" t="n">
         <v>3</v>
@@ -8126,16 +8126,16 @@
         <v>2</v>
       </c>
       <c r="AW35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA35" t="n">
         <v>7</v>
@@ -8329,13 +8329,13 @@
         <v>0.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AU36" t="n">
         <v>6</v>
@@ -8344,16 +8344,16 @@
         <v>3</v>
       </c>
       <c r="AW36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY36" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA36" t="n">
         <v>3</v>
@@ -8547,13 +8547,13 @@
         <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.86</v>
+        <v>0.99</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="AU37" t="n">
         <v>3</v>
@@ -8562,16 +8562,16 @@
         <v>4</v>
       </c>
       <c r="AW37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ37" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA37" t="n">
         <v>5</v>
@@ -8765,13 +8765,13 @@
         <v>2</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.49</v>
+        <v>0.62</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="AU38" t="n">
         <v>2</v>
@@ -8780,16 +8780,16 @@
         <v>3</v>
       </c>
       <c r="AW38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX38" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ38" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA38" t="n">
         <v>5</v>
@@ -8983,31 +8983,31 @@
         <v>2.33</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AU39" t="n">
         <v>6</v>
       </c>
       <c r="AV39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW39" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX39" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AY39" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ39" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BA39" t="n">
         <v>8</v>
@@ -9201,13 +9201,13 @@
         <v>2</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="AU40" t="n">
         <v>4</v>
@@ -9216,16 +9216,16 @@
         <v>5</v>
       </c>
       <c r="AW40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA40" t="n">
         <v>6</v>
@@ -9419,13 +9419,13 @@
         <v>1.67</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.86</v>
+        <v>2.36</v>
       </c>
       <c r="AU41" t="n">
         <v>5</v>
@@ -9434,16 +9434,16 @@
         <v>4</v>
       </c>
       <c r="AW41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX41" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AY41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ41" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BA41" t="n">
         <v>12</v>
@@ -9637,13 +9637,13 @@
         <v>1</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.52</v>
+        <v>0.7</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.8</v>
+        <v>2.36</v>
       </c>
       <c r="AU42" t="n">
         <v>4</v>
@@ -9652,16 +9652,16 @@
         <v>1</v>
       </c>
       <c r="AW42" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX42" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY42" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AZ42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA42" t="n">
         <v>4</v>
@@ -9855,13 +9855,13 @@
         <v>1</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.86</v>
+        <v>1.11</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.99</v>
+        <v>2.43</v>
       </c>
       <c r="AU43" t="n">
         <v>3</v>
@@ -9870,16 +9870,16 @@
         <v>4</v>
       </c>
       <c r="AW43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AY43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ43" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA43" t="n">
         <v>2</v>
@@ -10073,13 +10073,13 @@
         <v>2</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="AU44" t="n">
         <v>6</v>
@@ -10088,13 +10088,13 @@
         <v>3</v>
       </c>
       <c r="AW44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX44" t="n">
         <v>4</v>
       </c>
       <c r="AY44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ44" t="n">
         <v>7</v>
@@ -10294,10 +10294,10 @@
         <v>0.89</v>
       </c>
       <c r="AS45" t="n">
-        <v>2.03</v>
+        <v>2.46</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="AU45" t="n">
         <v>3</v>
@@ -10306,16 +10306,16 @@
         <v>10</v>
       </c>
       <c r="AW45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY45" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AZ45" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA45" t="n">
         <v>2</v>
@@ -10509,13 +10509,13 @@
         <v>1</v>
       </c>
       <c r="AR46" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AS46" t="n">
         <v>0.93</v>
       </c>
-      <c r="AS46" t="n">
-        <v>0.55</v>
-      </c>
       <c r="AT46" t="n">
-        <v>1.48</v>
+        <v>1.99</v>
       </c>
       <c r="AU46" t="n">
         <v>5</v>
@@ -10524,16 +10524,16 @@
         <v>1</v>
       </c>
       <c r="AW46" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AX46" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AY46" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AZ46" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="BA46" t="n">
         <v>4</v>
@@ -10730,10 +10730,10 @@
         <v>0.87</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="AU47" t="n">
         <v>2</v>
@@ -10742,16 +10742,16 @@
         <v>5</v>
       </c>
       <c r="AW47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX47" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AY47" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ47" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BA47" t="n">
         <v>4</v>
@@ -10945,13 +10945,13 @@
         <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.76</v>
+        <v>1.01</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AU48" t="n">
         <v>8</v>
@@ -10960,16 +10960,16 @@
         <v>2</v>
       </c>
       <c r="AW48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY48" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA48" t="n">
         <v>4</v>
@@ -11163,13 +11163,13 @@
         <v>2.33</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.23</v>
+        <v>2.53</v>
       </c>
       <c r="AU49" t="n">
         <v>3</v>
@@ -11381,13 +11381,13 @@
         <v>2</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="AU50" t="n">
         <v>6</v>
@@ -11599,13 +11599,13 @@
         <v>2</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.37</v>
+        <v>1.68</v>
       </c>
       <c r="AS51" t="n">
-        <v>0.84</v>
+        <v>1.02</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="AU51" t="n">
         <v>4</v>
@@ -11817,13 +11817,13 @@
         <v>1</v>
       </c>
       <c r="AR52" t="n">
-        <v>0.96</v>
+        <v>1.05</v>
       </c>
       <c r="AS52" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AU52" t="n">
         <v>3</v>
@@ -12035,13 +12035,13 @@
         <v>2</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="AU53" t="n">
         <v>1</v>
@@ -12253,13 +12253,13 @@
         <v>1</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.52</v>
+        <v>3.08</v>
       </c>
       <c r="AU54" t="n">
         <v>3</v>
@@ -12471,13 +12471,13 @@
         <v>1</v>
       </c>
       <c r="AR55" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="AS55" t="n">
-        <v>0.76</v>
+        <v>1.26</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="AU55" t="n">
         <v>6</v>
@@ -12689,13 +12689,13 @@
         <v>0</v>
       </c>
       <c r="AR56" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AS56" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="AU56" t="n">
         <v>7</v>
@@ -12907,13 +12907,13 @@
         <v>2</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AT57" t="n">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="AU57" t="n">
         <v>3</v>
@@ -13125,13 +13125,13 @@
         <v>2</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="AT58" t="n">
-        <v>3.11</v>
+        <v>3.51</v>
       </c>
       <c r="AU58" t="n">
         <v>5</v>
@@ -13343,13 +13343,13 @@
         <v>1.67</v>
       </c>
       <c r="AR59" t="n">
-        <v>0.95</v>
+        <v>1.14</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="AT59" t="n">
-        <v>2.18</v>
+        <v>2.65</v>
       </c>
       <c r="AU59" t="n">
         <v>3</v>
@@ -13561,13 +13561,13 @@
         <v>1.67</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="AT60" t="n">
-        <v>2.26</v>
+        <v>2.91</v>
       </c>
       <c r="AU60" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -11181,13 +11181,13 @@
         <v>7</v>
       </c>
       <c r="AX49" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY49" t="n">
         <v>10</v>
       </c>
       <c r="AZ49" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA49" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -11608,7 +11608,7 @@
         <v>2.7</v>
       </c>
       <c r="AU51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV51" t="n">
         <v>2</v>
@@ -11620,7 +11620,7 @@
         <v>8</v>
       </c>
       <c r="AY51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ51" t="n">
         <v>10</v>
@@ -11826,19 +11826,19 @@
         <v>1.9</v>
       </c>
       <c r="AU52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV52" t="n">
         <v>3</v>
       </c>
       <c r="AW52" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX52" t="n">
         <v>19</v>
       </c>
       <c r="AY52" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AZ52" t="n">
         <v>22</v>
@@ -12050,16 +12050,16 @@
         <v>6</v>
       </c>
       <c r="AW53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ53" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA53" t="n">
         <v>1</v>
@@ -12486,13 +12486,13 @@
         <v>4</v>
       </c>
       <c r="AW55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX55" t="n">
         <v>5</v>
       </c>
       <c r="AY55" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ55" t="n">
         <v>9</v>
@@ -13140,16 +13140,16 @@
         <v>2</v>
       </c>
       <c r="AW58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA58" t="n">
         <v>4</v>
@@ -13579,13 +13579,13 @@
         <v>5</v>
       </c>
       <c r="AX60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY60" t="n">
         <v>8</v>
       </c>
       <c r="AZ60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA60" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -11172,13 +11172,13 @@
         <v>2.53</v>
       </c>
       <c r="AU49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV49" t="n">
         <v>4</v>
       </c>
       <c r="AW49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX49" t="n">
         <v>13</v>
@@ -11617,13 +11617,13 @@
         <v>17</v>
       </c>
       <c r="AX51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY51" t="n">
         <v>20</v>
       </c>
       <c r="AZ51" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA51" t="n">
         <v>8</v>
@@ -12922,13 +12922,13 @@
         <v>5</v>
       </c>
       <c r="AW57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX57" t="n">
         <v>8</v>
       </c>
       <c r="AY57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ57" t="n">
         <v>13</v>
@@ -13573,7 +13573,7 @@
         <v>3</v>
       </c>
       <c r="AV60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW60" t="n">
         <v>5</v>
@@ -13585,7 +13585,7 @@
         <v>8</v>
       </c>
       <c r="AZ60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA60" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -11617,13 +11617,13 @@
         <v>17</v>
       </c>
       <c r="AX51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY51" t="n">
         <v>20</v>
       </c>
       <c r="AZ51" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA51" t="n">
         <v>8</v>
@@ -11832,13 +11832,13 @@
         <v>3</v>
       </c>
       <c r="AW52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX52" t="n">
         <v>19</v>
       </c>
       <c r="AY52" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ52" t="n">
         <v>22</v>
@@ -13140,13 +13140,13 @@
         <v>2</v>
       </c>
       <c r="AW58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX58" t="n">
         <v>5</v>
       </c>
       <c r="AY58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ58" t="n">
         <v>7</v>
@@ -13352,19 +13352,19 @@
         <v>2.65</v>
       </c>
       <c r="AU59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV59" t="n">
         <v>4</v>
       </c>
       <c r="AW59" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX59" t="n">
         <v>9</v>
       </c>
       <c r="AY59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ59" t="n">
         <v>13</v>
@@ -13570,7 +13570,7 @@
         <v>2.91</v>
       </c>
       <c r="AU60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV60" t="n">
         <v>2</v>
@@ -13582,7 +13582,7 @@
         <v>6</v>
       </c>
       <c r="AY60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ60" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP60"/>
+  <dimension ref="A1:BP61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9" t="n">
         <v>2</v>
@@ -7236,7 +7236,7 @@
         <v>2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR31" t="n">
         <v>0.73</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ37" t="n">
         <v>0</v>
@@ -13634,6 +13634,224 @@
       </c>
       <c r="BP60" t="n">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8217364</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>45898.65625</v>
+      </c>
+      <c r="F61" t="n">
+        <v>6</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R61" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="S61" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V61" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X61" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI61" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ61" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BK61" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL61" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP61"/>
+  <dimension ref="A1:BP72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ2" t="n">
         <v>1</v>
@@ -1132,7 +1132,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.33</v>
@@ -1568,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.67</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12" t="n">
         <v>1</v>
@@ -3312,7 +3312,7 @@
         <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ17" t="n">
         <v>2.33</v>
@@ -4620,7 +4620,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5271,10 +5271,10 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -5707,10 +5707,10 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ25" t="n">
         <v>2</v>
@@ -6143,10 +6143,10 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR26" t="n">
         <v>1.04</v>
@@ -6361,10 +6361,10 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR27" t="n">
         <v>2.21</v>
@@ -6579,10 +6579,10 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR28" t="n">
         <v>1.67</v>
@@ -6797,10 +6797,10 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR29" t="n">
         <v>2.14</v>
@@ -7015,10 +7015,10 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ30" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR30" t="n">
         <v>0.89</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.33</v>
@@ -7451,10 +7451,10 @@
         <v>3</v>
       </c>
       <c r="AP32" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR32" t="n">
         <v>1.09</v>
@@ -7669,10 +7669,10 @@
         <v>3</v>
       </c>
       <c r="AP33" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ33" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR33" t="n">
         <v>1.53</v>
@@ -7887,10 +7887,10 @@
         <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AR34" t="n">
         <v>1.41</v>
@@ -8105,10 +8105,10 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR35" t="n">
         <v>2.2</v>
@@ -8323,10 +8323,10 @@
         <v>1</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR36" t="n">
         <v>0.89</v>
@@ -8544,7 +8544,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR37" t="n">
         <v>1.35</v>
@@ -13852,6 +13852,2404 @@
       </c>
       <c r="BP61" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8217300</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>45899.35416666666</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>3</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>['8', '35', '41']</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R62" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S62" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V62" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X62" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG62" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH62" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI62" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ62" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK62" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL62" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM62" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BN62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO62" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP62" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8217327</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>45899.35416666666</v>
+      </c>
+      <c r="F63" t="n">
+        <v>6</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R63" t="n">
+        <v>2</v>
+      </c>
+      <c r="S63" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V63" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X63" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG63" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI63" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ63" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK63" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>8217373</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>45899.45833333334</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S64" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V64" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BG64" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BI64" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ64" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BK64" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BL64" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BM64" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BN64" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BO64" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP64" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8217374</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>45899.45833333334</v>
+      </c>
+      <c r="F65" t="n">
+        <v>6</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" t="n">
+        <v>2</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>['49', '62']</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V65" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X65" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI65" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ65" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK65" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BL65" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM65" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8217375</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>45899.45833333334</v>
+      </c>
+      <c r="F66" t="n">
+        <v>6</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V66" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X66" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG66" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BI66" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ66" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BK66" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL66" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM66" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="n">
+        <v>8217408</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>45899.45833333334</v>
+      </c>
+      <c r="F67" t="n">
+        <v>6</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S67" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V67" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X67" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI67" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ67" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM67" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="n">
+        <v>8217326</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>45899.45833333334</v>
+      </c>
+      <c r="F68" t="n">
+        <v>6</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>2</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>2</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>['74', '80']</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S68" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V68" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X68" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ68" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BK68" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL68" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="n">
+        <v>8217325</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>45899.45833333334</v>
+      </c>
+      <c r="F69" t="n">
+        <v>6</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" t="n">
+        <v>2</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>['38', '75']</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R69" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V69" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X69" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="n">
+        <v>8217365</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>45899.45833333334</v>
+      </c>
+      <c r="F70" t="n">
+        <v>6</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2</v>
+      </c>
+      <c r="L70" t="n">
+        <v>2</v>
+      </c>
+      <c r="M70" t="n">
+        <v>2</v>
+      </c>
+      <c r="N70" t="n">
+        <v>4</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>['56', '58']</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>['9', '36']</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R70" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V70" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X70" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BI70" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ70" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK70" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL70" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM70" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN70" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>8217366</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>45899.45833333334</v>
+      </c>
+      <c r="F71" t="n">
+        <v>6</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R71" t="n">
+        <v>2</v>
+      </c>
+      <c r="S71" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V71" t="n">
+        <v>3</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X71" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BI71" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ71" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BK71" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BL71" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM71" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BN71" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO71" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP71" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="n">
+        <v>8217393</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>45899.45833333334</v>
+      </c>
+      <c r="F72" t="n">
+        <v>6</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R72" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S72" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V72" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X72" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI72" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ72" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BK72" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL72" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM72" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN72" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO72" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP72" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -14448,13 +14448,13 @@
         <v>2</v>
       </c>
       <c r="AW64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX64" t="n">
         <v>6</v>
       </c>
       <c r="AY64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ64" t="n">
         <v>8</v>
@@ -14666,16 +14666,16 @@
         <v>4</v>
       </c>
       <c r="AW65" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA65" t="n">
         <v>8</v>
@@ -14878,19 +14878,19 @@
         <v>2.15</v>
       </c>
       <c r="AU66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV66" t="n">
         <v>4</v>
       </c>
       <c r="AW66" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX66" t="n">
         <v>5</v>
       </c>
       <c r="AY66" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ66" t="n">
         <v>9</v>
@@ -15535,13 +15535,13 @@
         <v>3</v>
       </c>
       <c r="AV69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW69" t="n">
         <v>7</v>
       </c>
       <c r="AX69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY69" t="n">
         <v>10</v>
@@ -15756,13 +15756,13 @@
         <v>3</v>
       </c>
       <c r="AW70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX70" t="n">
         <v>0</v>
       </c>
       <c r="AY70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ70" t="n">
         <v>3</v>
@@ -15974,13 +15974,13 @@
         <v>2</v>
       </c>
       <c r="AW71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX71" t="n">
         <v>4</v>
       </c>
       <c r="AY71" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ71" t="n">
         <v>6</v>
@@ -16195,13 +16195,13 @@
         <v>10</v>
       </c>
       <c r="AX72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY72" t="n">
         <v>12</v>
       </c>
       <c r="AZ72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA72" t="n">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -15002,7 +15002,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="Q67" t="n">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -14012,13 +14012,13 @@
         <v>9</v>
       </c>
       <c r="AW62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX62" t="n">
         <v>10</v>
       </c>
       <c r="AY62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ62" t="n">
         <v>19</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -14881,7 +14881,7 @@
         <v>5</v>
       </c>
       <c r="AV66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW66" t="n">
         <v>12</v>
@@ -14893,7 +14893,7 @@
         <v>17</v>
       </c>
       <c r="AZ66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA66" t="n">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP72"/>
+  <dimension ref="A1:BP84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.33</v>
@@ -1568,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.33</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ14" t="n">
         <v>2</v>
@@ -3748,7 +3748,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ17" t="n">
         <v>2.33</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5053,10 +5053,10 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -5710,7 +5710,7 @@
         <v>2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ25" t="n">
         <v>2</v>
@@ -6146,7 +6146,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR26" t="n">
         <v>1.04</v>
@@ -6364,7 +6364,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR27" t="n">
         <v>2.21</v>
@@ -6582,7 +6582,7 @@
         <v>2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR28" t="n">
         <v>1.67</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.33</v>
@@ -7451,10 +7451,10 @@
         <v>3</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR32" t="n">
         <v>1.09</v>
@@ -7669,7 +7669,7 @@
         <v>3</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.33</v>
@@ -7890,7 +7890,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR34" t="n">
         <v>1.41</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ35" t="n">
         <v>2</v>
@@ -8323,7 +8323,7 @@
         <v>1</v>
       </c>
       <c r="AP36" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.33</v>
@@ -8541,10 +8541,10 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR37" t="n">
         <v>1.35</v>
@@ -8759,7 +8759,7 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ38" t="n">
         <v>2</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.67</v>
@@ -9634,7 +9634,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR42" t="n">
         <v>1.66</v>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AQ43" t="n">
         <v>1</v>
@@ -10070,7 +10070,7 @@
         <v>3</v>
       </c>
       <c r="AQ44" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AR44" t="n">
         <v>0.96</v>
@@ -10288,7 +10288,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ45" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR45" t="n">
         <v>0.89</v>
@@ -10503,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ46" t="n">
         <v>1</v>
@@ -10721,10 +10721,10 @@
         <v>1</v>
       </c>
       <c r="AP47" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR47" t="n">
         <v>0.87</v>
@@ -10939,10 +10939,10 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR48" t="n">
         <v>1.01</v>
@@ -11157,7 +11157,7 @@
         <v>2</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ49" t="n">
         <v>2.33</v>
@@ -11375,7 +11375,7 @@
         <v>3</v>
       </c>
       <c r="AP50" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ50" t="n">
         <v>2</v>
@@ -11596,7 +11596,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ51" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR51" t="n">
         <v>1.68</v>
@@ -11814,7 +11814,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR52" t="n">
         <v>1.05</v>
@@ -12029,7 +12029,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AQ53" t="n">
         <v>2</v>
@@ -12465,7 +12465,7 @@
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AQ55" t="n">
         <v>1</v>
@@ -12686,7 +12686,7 @@
         <v>2</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR56" t="n">
         <v>1.03</v>
@@ -12901,10 +12901,10 @@
         <v>1.5</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ57" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AR57" t="n">
         <v>1.53</v>
@@ -13122,7 +13122,7 @@
         <v>3</v>
       </c>
       <c r="AQ58" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR58" t="n">
         <v>1.22</v>
@@ -13340,7 +13340,7 @@
         <v>1</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR59" t="n">
         <v>1.14</v>
@@ -13555,7 +13555,7 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.67</v>
@@ -13773,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.33</v>
@@ -13994,7 +13994,7 @@
         <v>2</v>
       </c>
       <c r="AQ62" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR62" t="n">
         <v>1.49</v>
@@ -14209,10 +14209,10 @@
         <v>2</v>
       </c>
       <c r="AP63" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ63" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR63" t="n">
         <v>1.18</v>
@@ -14430,7 +14430,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR64" t="n">
         <v>1.92</v>
@@ -14866,7 +14866,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR66" t="n">
         <v>0.93</v>
@@ -15081,7 +15081,7 @@
         <v>2</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.67</v>
@@ -15299,7 +15299,7 @@
         <v>2</v>
       </c>
       <c r="AP68" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.33</v>
@@ -15517,7 +15517,7 @@
         <v>1.5</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ69" t="n">
         <v>1</v>
@@ -15738,7 +15738,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR70" t="n">
         <v>1.68</v>
@@ -15953,7 +15953,7 @@
         <v>1.5</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ71" t="n">
         <v>2</v>
@@ -16174,7 +16174,7 @@
         <v>2</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR72" t="n">
         <v>2.16</v>
@@ -16250,6 +16250,2622 @@
       </c>
       <c r="BP72" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
+        <v>8217363</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>45906.35416666666</v>
+      </c>
+      <c r="F73" t="n">
+        <v>7</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>2</v>
+      </c>
+      <c r="M73" t="n">
+        <v>3</v>
+      </c>
+      <c r="N73" t="n">
+        <v>5</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>['78', '89']</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>['52', '59', '72']</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="R73" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S73" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U73" t="n">
+        <v>3</v>
+      </c>
+      <c r="V73" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="W73" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF73" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BG73" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH73" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BI73" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ73" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BK73" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL73" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM73" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BN73" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO73" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BP73" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>8217376</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>45906.45833333334</v>
+      </c>
+      <c r="F74" t="n">
+        <v>7</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>3</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V74" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X74" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BG74" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH74" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ74" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK74" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL74" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM74" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN74" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO74" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP74" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>8217377</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>45906.45833333334</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>['42']</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R75" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S75" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V75" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X75" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ75" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8217372</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>45906.45833333334</v>
+      </c>
+      <c r="F76" t="n">
+        <v>7</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R76" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S76" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V76" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X76" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG76" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH76" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BI76" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BJ76" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK76" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BL76" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8217418</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>45906.45833333334</v>
+      </c>
+      <c r="F77" t="n">
+        <v>7</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>3</v>
+      </c>
+      <c r="K77" t="n">
+        <v>3</v>
+      </c>
+      <c r="L77" t="n">
+        <v>2</v>
+      </c>
+      <c r="M77" t="n">
+        <v>3</v>
+      </c>
+      <c r="N77" t="n">
+        <v>5</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>['47', '90+1']</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>['9', '23', '29']</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U77" t="n">
+        <v>3</v>
+      </c>
+      <c r="V77" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="W77" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X77" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI77" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ77" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK77" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL77" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8217370</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>45906.45833333334</v>
+      </c>
+      <c r="F78" t="n">
+        <v>7</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>3</v>
+      </c>
+      <c r="K78" t="n">
+        <v>4</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>3</v>
+      </c>
+      <c r="N78" t="n">
+        <v>4</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>['15', '25', '42']</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R78" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V78" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="W78" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X78" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8217329</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>45906.45833333334</v>
+      </c>
+      <c r="F79" t="n">
+        <v>7</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" t="n">
+        <v>2</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S79" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V79" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X79" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ79" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8217885</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>45906.45833333334</v>
+      </c>
+      <c r="F80" t="n">
+        <v>7</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R80" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S80" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U80" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V80" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W80" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X80" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ80" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8217371</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>45906.45833333334</v>
+      </c>
+      <c r="F81" t="n">
+        <v>7</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" t="n">
+        <v>3</v>
+      </c>
+      <c r="N81" t="n">
+        <v>4</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>['2', '36', '77']</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R81" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S81" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U81" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V81" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W81" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X81" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ81" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BK81" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="n">
+        <v>8217887</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>45906.45833333334</v>
+      </c>
+      <c r="F82" t="n">
+        <v>7</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R82" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U82" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V82" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W82" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X82" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI82" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ82" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BK82" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL82" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8217888</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>45906.45833333334</v>
+      </c>
+      <c r="F83" t="n">
+        <v>7</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>3</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" t="n">
+        <v>4</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>['56', '81', '86']</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R83" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S83" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U83" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V83" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W83" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X83" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI83" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ83" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL83" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM83" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN83" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="n">
+        <v>8217886</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>45906.5625</v>
+      </c>
+      <c r="F84" t="n">
+        <v>7</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>2</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2</v>
+      </c>
+      <c r="L84" t="n">
+        <v>2</v>
+      </c>
+      <c r="M84" t="n">
+        <v>2</v>
+      </c>
+      <c r="N84" t="n">
+        <v>4</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>['7', '12']</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>['56', '90+8']</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R84" t="n">
+        <v>2</v>
+      </c>
+      <c r="S84" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U84" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V84" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W84" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X84" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI84" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ84" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK84" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BL84" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BM84" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -16410,13 +16410,13 @@
         <v>4</v>
       </c>
       <c r="AW73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX73" t="n">
         <v>8</v>
       </c>
       <c r="AY73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ73" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -16849,13 +16849,13 @@
         <v>15</v>
       </c>
       <c r="AX75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY75" t="n">
         <v>21</v>
       </c>
       <c r="AZ75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA75" t="n">
         <v>5</v>
@@ -17058,13 +17058,13 @@
         <v>2.83</v>
       </c>
       <c r="AU76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV76" t="n">
         <v>4</v>
       </c>
       <c r="AW76" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX76" t="n">
         <v>2</v>
@@ -17076,13 +17076,13 @@
         <v>6</v>
       </c>
       <c r="BA76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB76" t="n">
         <v>2</v>
       </c>
       <c r="BC76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD76" t="n">
         <v>1.4</v>
@@ -17500,16 +17500,16 @@
         <v>4</v>
       </c>
       <c r="AW78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX78" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY78" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ78" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA78" t="n">
         <v>6</v>
@@ -17721,13 +17721,13 @@
         <v>7</v>
       </c>
       <c r="AX79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY79" t="n">
         <v>14</v>
       </c>
       <c r="AZ79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA79" t="n">
         <v>3</v>
@@ -17939,13 +17939,13 @@
         <v>5</v>
       </c>
       <c r="AX80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY80" t="n">
         <v>7</v>
       </c>
       <c r="AZ80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA80" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -16846,13 +16846,13 @@
         <v>3</v>
       </c>
       <c r="AW75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX75" t="n">
         <v>10</v>
       </c>
       <c r="AY75" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ75" t="n">
         <v>13</v>
@@ -17500,13 +17500,13 @@
         <v>4</v>
       </c>
       <c r="AW78" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX78" t="n">
         <v>7</v>
       </c>
       <c r="AY78" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ78" t="n">
         <v>11</v>
@@ -18372,13 +18372,13 @@
         <v>6</v>
       </c>
       <c r="AW82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX82" t="n">
         <v>7</v>
       </c>
       <c r="AY82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ82" t="n">
         <v>13</v>
@@ -18802,7 +18802,7 @@
         <v>2.5</v>
       </c>
       <c r="AU84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV84" t="n">
         <v>5</v>
@@ -18811,13 +18811,13 @@
         <v>10</v>
       </c>
       <c r="AX84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY84" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ84" t="n">
         <v>16</v>
-      </c>
-      <c r="AZ84" t="n">
-        <v>15</v>
       </c>
       <c r="BA84" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP84"/>
+  <dimension ref="A1:BP86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.5</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ20" t="n">
         <v>1</v>
@@ -5274,7 +5274,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
         <v>1</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR28" t="n">
         <v>0.73</v>
@@ -6800,7 +6800,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR29" t="n">
         <v>0.89</v>
@@ -8977,7 +8977,7 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ39" t="n">
         <v>2.33</v>
@@ -12901,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.33</v>
@@ -13119,7 +13119,7 @@
         <v>2</v>
       </c>
       <c r="AP58" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ58" t="n">
         <v>2</v>
@@ -13776,7 +13776,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR61" t="n">
         <v>1.28</v>
@@ -15738,7 +15738,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR70" t="n">
         <v>1.75</v>
@@ -18866,6 +18866,442 @@
       </c>
       <c r="BP84" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8217299</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>45913.35416666666</v>
+      </c>
+      <c r="F85" t="n">
+        <v>8</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R85" t="n">
+        <v>2</v>
+      </c>
+      <c r="S85" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U85" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V85" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X85" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8217328</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>45913.35416666666</v>
+      </c>
+      <c r="F86" t="n">
+        <v>8</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>2</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>2</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>['68', '84']</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="R86" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S86" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U86" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="V86" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="W86" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X86" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI86" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ86" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BK86" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL86" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM86" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN86" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO86" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BP86" t="n">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP86"/>
+  <dimension ref="A1:BP96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
@@ -2222,7 +2222,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.75</v>
@@ -3748,7 +3748,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ18" t="n">
         <v>1</v>
@@ -4620,7 +4620,7 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.25</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.5</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.25</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ26" t="n">
         <v>2.25</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.5</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.25</v>
@@ -7015,7 +7015,7 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ30" t="n">
         <v>1</v>
@@ -7233,7 +7233,7 @@
         <v>1</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.5</v>
@@ -7454,7 +7454,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR32" t="n">
         <v>1.53</v>
@@ -7890,7 +7890,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ34" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR34" t="n">
         <v>2.2</v>
@@ -8108,7 +8108,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR35" t="n">
         <v>0.89</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36" t="n">
         <v>1</v>
@@ -8762,7 +8762,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR38" t="n">
         <v>0.62</v>
@@ -8980,7 +8980,7 @@
         <v>1</v>
       </c>
       <c r="AQ39" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR39" t="n">
         <v>1.87</v>
@@ -9198,7 +9198,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR40" t="n">
         <v>0.82</v>
@@ -9849,10 +9849,10 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR43" t="n">
         <v>1.16</v>
@@ -10067,7 +10067,7 @@
         <v>3</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.75</v>
@@ -10285,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.5</v>
@@ -10506,7 +10506,7 @@
         <v>1</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR46" t="n">
         <v>1.06</v>
@@ -11160,7 +11160,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR49" t="n">
         <v>1.11</v>
@@ -11378,7 +11378,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ50" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR50" t="n">
         <v>0.84</v>
@@ -11814,7 +11814,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR52" t="n">
         <v>1.1</v>
@@ -12029,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.75</v>
@@ -12247,7 +12247,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ54" t="n">
         <v>1</v>
@@ -12468,7 +12468,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ55" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR55" t="n">
         <v>1.18</v>
@@ -12683,7 +12683,7 @@
         <v>1</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.5</v>
@@ -13558,7 +13558,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR60" t="n">
         <v>1.24</v>
@@ -13991,7 +13991,7 @@
         <v>1.5</v>
       </c>
       <c r="AP62" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ62" t="n">
         <v>2.25</v>
@@ -14427,10 +14427,10 @@
         <v>0.5</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR64" t="n">
         <v>1.37</v>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.25</v>
@@ -14863,7 +14863,7 @@
         <v>0</v>
       </c>
       <c r="AP66" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.5</v>
@@ -15084,7 +15084,7 @@
         <v>1</v>
       </c>
       <c r="AQ67" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR67" t="n">
         <v>1.28</v>
@@ -15299,7 +15299,7 @@
         <v>1</v>
       </c>
       <c r="AP68" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.5</v>
@@ -15517,7 +15517,7 @@
         <v>0</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ69" t="n">
         <v>1</v>
@@ -15956,7 +15956,7 @@
         <v>2</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR71" t="n">
         <v>1.52</v>
@@ -19302,6 +19302,2186 @@
       </c>
       <c r="BP86" t="n">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8217401</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>45913.45833333334</v>
+      </c>
+      <c r="F87" t="n">
+        <v>8</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R87" t="n">
+        <v>2</v>
+      </c>
+      <c r="S87" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T87" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U87" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V87" t="n">
+        <v>3</v>
+      </c>
+      <c r="W87" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X87" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BH87" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BI87" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ87" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BK87" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BL87" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BM87" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8217330</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>45913.45833333334</v>
+      </c>
+      <c r="F88" t="n">
+        <v>8</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1</v>
+      </c>
+      <c r="N88" t="n">
+        <v>2</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R88" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S88" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="T88" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U88" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V88" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="W88" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X88" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BH88" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI88" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ88" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BK88" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL88" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BM88" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BN88" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BO88" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP88" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8217400</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>45913.45833333334</v>
+      </c>
+      <c r="F89" t="n">
+        <v>8</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2</v>
+      </c>
+      <c r="N89" t="n">
+        <v>3</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>['57', '80']</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R89" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S89" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T89" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U89" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V89" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W89" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X89" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF89" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG89" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH89" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI89" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ89" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BK89" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL89" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM89" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN89" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO89" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP89" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8217399</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>45913.45833333334</v>
+      </c>
+      <c r="F90" t="n">
+        <v>8</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>2</v>
+      </c>
+      <c r="L90" t="n">
+        <v>2</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>3</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>['16', '28']</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R90" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S90" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="T90" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U90" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V90" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W90" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X90" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="BF90" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BG90" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH90" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI90" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ90" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK90" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL90" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM90" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN90" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO90" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP90" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>8217367</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>45913.45833333334</v>
+      </c>
+      <c r="F91" t="n">
+        <v>8</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>['90+7']</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R91" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S91" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T91" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U91" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V91" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W91" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X91" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF91" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BG91" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH91" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI91" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ91" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK91" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL91" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BM91" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN91" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO91" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP91" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="n">
+        <v>8217422</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>45913.45833333334</v>
+      </c>
+      <c r="F92" t="n">
+        <v>8</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1</v>
+      </c>
+      <c r="N92" t="n">
+        <v>2</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="R92" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T92" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U92" t="n">
+        <v>3</v>
+      </c>
+      <c r="V92" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W92" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X92" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AT92" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC92" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BE92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="BF92" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="BG92" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH92" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BI92" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ92" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BK92" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL92" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BM92" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN92" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO92" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BP92" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="n">
+        <v>8217419</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>45913.45833333334</v>
+      </c>
+      <c r="F93" t="n">
+        <v>8</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>3</v>
+      </c>
+      <c r="R93" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S93" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T93" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U93" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V93" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W93" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X93" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF93" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG93" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH93" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BI93" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ93" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BK93" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM93" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN93" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO93" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BP93" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="n">
+        <v>8217420</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>45913.45833333334</v>
+      </c>
+      <c r="F94" t="n">
+        <v>8</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" t="n">
+        <v>3</v>
+      </c>
+      <c r="N94" t="n">
+        <v>4</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>['28', '82', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="R94" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S94" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T94" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U94" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V94" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W94" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X94" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH94" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BI94" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BJ94" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BK94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL94" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM94" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP94" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="n">
+        <v>8217426</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>45913.45833333334</v>
+      </c>
+      <c r="F95" t="n">
+        <v>8</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>2</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1</v>
+      </c>
+      <c r="N95" t="n">
+        <v>2</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S95" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="T95" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U95" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V95" t="n">
+        <v>3</v>
+      </c>
+      <c r="W95" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X95" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF95" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG95" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH95" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI95" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ95" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK95" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL95" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM95" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BN95" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO95" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP95" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="n">
+        <v>8217421</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>45913.45833333334</v>
+      </c>
+      <c r="F96" t="n">
+        <v>8</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="n">
+        <v>2</v>
+      </c>
+      <c r="L96" t="n">
+        <v>3</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1</v>
+      </c>
+      <c r="N96" t="n">
+        <v>4</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>['44', '71', '90+1']</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R96" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S96" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T96" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U96" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V96" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W96" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X96" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF96" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG96" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH96" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI96" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ96" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK96" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BM96" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BN96" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -19456,7 +19456,7 @@
         <v>2.61</v>
       </c>
       <c r="AU87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV87" t="n">
         <v>1</v>
@@ -19465,13 +19465,13 @@
         <v>4</v>
       </c>
       <c r="AX87" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY87" t="n">
         <v>7</v>
       </c>
-      <c r="AY87" t="n">
-        <v>6</v>
-      </c>
       <c r="AZ87" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA87" t="n">
         <v>2</v>
@@ -19674,7 +19674,7 @@
         <v>3.28</v>
       </c>
       <c r="AU88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV88" t="n">
         <v>1</v>
@@ -19686,7 +19686,7 @@
         <v>3</v>
       </c>
       <c r="AY88" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ88" t="n">
         <v>4</v>
@@ -19892,16 +19892,16 @@
         <v>2.75</v>
       </c>
       <c r="AU89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY89" t="n">
         <v>11</v>
@@ -19910,13 +19910,13 @@
         <v>11</v>
       </c>
       <c r="BA89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB89" t="n">
         <v>6</v>
       </c>
       <c r="BC89" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD89" t="n">
         <v>2.39</v>
@@ -20110,19 +20110,19 @@
         <v>2.67</v>
       </c>
       <c r="AU90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV90" t="n">
         <v>2</v>
       </c>
       <c r="AW90" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX90" t="n">
         <v>13</v>
       </c>
       <c r="AY90" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ90" t="n">
         <v>15</v>
@@ -20328,7 +20328,7 @@
         <v>3.17</v>
       </c>
       <c r="AU91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV91" t="n">
         <v>4</v>
@@ -20340,7 +20340,7 @@
         <v>7</v>
       </c>
       <c r="AY91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ91" t="n">
         <v>11</v>
@@ -20549,19 +20549,19 @@
         <v>4</v>
       </c>
       <c r="AV92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW92" t="n">
         <v>10</v>
       </c>
       <c r="AX92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY92" t="n">
         <v>14</v>
       </c>
       <c r="AZ92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA92" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -19247,13 +19247,13 @@
         <v>11</v>
       </c>
       <c r="AX86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY86" t="n">
         <v>17</v>
       </c>
       <c r="AZ86" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA86" t="n">
         <v>7</v>
@@ -19456,19 +19456,19 @@
         <v>2.61</v>
       </c>
       <c r="AU87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV87" t="n">
         <v>1</v>
       </c>
       <c r="AW87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX87" t="n">
         <v>8</v>
       </c>
       <c r="AY87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ87" t="n">
         <v>9</v>
@@ -19898,16 +19898,16 @@
         <v>4</v>
       </c>
       <c r="AW89" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY89" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ89" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA89" t="n">
         <v>5</v>
@@ -20546,19 +20546,19 @@
         <v>2.31</v>
       </c>
       <c r="AU92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV92" t="n">
         <v>4</v>
       </c>
       <c r="AW92" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX92" t="n">
         <v>7</v>
       </c>
       <c r="AY92" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AZ92" t="n">
         <v>11</v>
@@ -20988,13 +20988,13 @@
         <v>3</v>
       </c>
       <c r="AW94" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX94" t="n">
         <v>8</v>
       </c>
       <c r="AY94" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ94" t="n">
         <v>11</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP96"/>
+  <dimension ref="A1:BP107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.25</v>
@@ -1568,7 +1568,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.5</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
         <v>2.25</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ16" t="n">
         <v>2.25</v>
@@ -4181,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ21" t="n">
         <v>2</v>
@@ -5492,7 +5492,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -5710,7 +5710,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR26" t="n">
         <v>2.21</v>
@@ -6364,7 +6364,7 @@
         <v>2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR27" t="n">
         <v>1.04</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.25</v>
@@ -7236,7 +7236,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR31" t="n">
         <v>1.41</v>
@@ -7451,7 +7451,7 @@
         <v>3</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ32" t="n">
         <v>1</v>
@@ -7669,10 +7669,10 @@
         <v>3</v>
       </c>
       <c r="AP33" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR33" t="n">
         <v>1.09</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.75</v>
@@ -8105,7 +8105,7 @@
         <v>1</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ35" t="n">
         <v>1</v>
@@ -8326,7 +8326,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR36" t="n">
         <v>1.67</v>
@@ -8541,10 +8541,10 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR37" t="n">
         <v>1.35</v>
@@ -8759,7 +8759,7 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AQ38" t="n">
         <v>2.25</v>
@@ -9416,7 +9416,7 @@
         <v>3</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR41" t="n">
         <v>0.96</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AQ42" t="n">
         <v>1</v>
@@ -10070,7 +10070,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR44" t="n">
         <v>0.89</v>
@@ -10503,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.75</v>
@@ -10721,10 +10721,10 @@
         <v>1</v>
       </c>
       <c r="AP47" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ47" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR47" t="n">
         <v>0.87</v>
@@ -10939,10 +10939,10 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR48" t="n">
         <v>1.01</v>
@@ -11157,7 +11157,7 @@
         <v>3</v>
       </c>
       <c r="AP49" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ49" t="n">
         <v>2.25</v>
@@ -11375,7 +11375,7 @@
         <v>2</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AQ50" t="n">
         <v>2</v>
@@ -11593,10 +11593,10 @@
         <v>1.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR51" t="n">
         <v>1.53</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.75</v>
@@ -12032,7 +12032,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR53" t="n">
         <v>1.03</v>
@@ -12904,7 +12904,7 @@
         <v>1</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR57" t="n">
         <v>1.68</v>
@@ -13122,7 +13122,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ58" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR58" t="n">
         <v>1.14</v>
@@ -13340,7 +13340,7 @@
         <v>3</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR59" t="n">
         <v>1.22</v>
@@ -13555,7 +13555,7 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.25</v>
@@ -13773,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.25</v>
@@ -13994,7 +13994,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ62" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR62" t="n">
         <v>1.49</v>
@@ -14209,10 +14209,10 @@
         <v>2</v>
       </c>
       <c r="AP63" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR63" t="n">
         <v>1.18</v>
@@ -14648,7 +14648,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR65" t="n">
         <v>0.93</v>
@@ -14866,7 +14866,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR66" t="n">
         <v>2.16</v>
@@ -15081,7 +15081,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.75</v>
@@ -15302,7 +15302,7 @@
         <v>1</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR68" t="n">
         <v>1.92</v>
@@ -15520,7 +15520,7 @@
         <v>2</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR69" t="n">
         <v>1.68</v>
@@ -15735,7 +15735,7 @@
         <v>2</v>
       </c>
       <c r="AP70" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.25</v>
@@ -15953,7 +15953,7 @@
         <v>2</v>
       </c>
       <c r="AP71" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ71" t="n">
         <v>1</v>
@@ -16171,7 +16171,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ72" t="n">
         <v>1</v>
@@ -16389,10 +16389,10 @@
         <v>1</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR73" t="n">
         <v>0.97</v>
@@ -16607,10 +16607,10 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR74" t="n">
         <v>1.55</v>
@@ -16825,10 +16825,10 @@
         <v>1.67</v>
       </c>
       <c r="AP75" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ75" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR75" t="n">
         <v>1.5</v>
@@ -17043,10 +17043,10 @@
         <v>2</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR76" t="n">
         <v>1.77</v>
@@ -17261,10 +17261,10 @@
         <v>0.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR77" t="n">
         <v>1.4</v>
@@ -17482,7 +17482,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR78" t="n">
         <v>1.16</v>
@@ -17697,10 +17697,10 @@
         <v>2.33</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR79" t="n">
         <v>1.18</v>
@@ -17915,10 +17915,10 @@
         <v>2</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR80" t="n">
         <v>1.37</v>
@@ -18133,7 +18133,7 @@
         <v>1</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.5</v>
@@ -18351,10 +18351,10 @@
         <v>2</v>
       </c>
       <c r="AP82" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ82" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR82" t="n">
         <v>1.07</v>
@@ -18569,10 +18569,10 @@
         <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR83" t="n">
         <v>1.81</v>
@@ -18787,10 +18787,10 @@
         <v>1.67</v>
       </c>
       <c r="AP84" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR84" t="n">
         <v>1.65</v>
@@ -21482,6 +21482,2404 @@
       </c>
       <c r="BP96" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="n">
+        <v>8217431</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>45920.35416666666</v>
+      </c>
+      <c r="F97" t="n">
+        <v>9</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>2</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>2</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>['65', '87']</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R97" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S97" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T97" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U97" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V97" t="n">
+        <v>3</v>
+      </c>
+      <c r="W97" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X97" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ97" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR97" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS97" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT97" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU97" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="BF97" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BG97" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH97" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI97" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ97" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK97" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM97" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BN97" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="n">
+        <v>8217302</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>45920.35416666666</v>
+      </c>
+      <c r="F98" t="n">
+        <v>9</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>2</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1</v>
+      </c>
+      <c r="N98" t="n">
+        <v>3</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>['67', '69']</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R98" t="n">
+        <v>2</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U98" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V98" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="W98" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X98" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD98" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BE98" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF98" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG98" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH98" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI98" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ98" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BK98" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL98" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM98" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN98" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO98" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP98" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="n">
+        <v>8217424</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>45920.45833333334</v>
+      </c>
+      <c r="F99" t="n">
+        <v>9</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>1</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R99" t="n">
+        <v>2</v>
+      </c>
+      <c r="S99" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T99" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U99" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V99" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W99" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X99" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU99" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF99" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BG99" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH99" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI99" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ99" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK99" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="n">
+        <v>8217425</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>45920.45833333334</v>
+      </c>
+      <c r="F100" t="n">
+        <v>9</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1</v>
+      </c>
+      <c r="K100" t="n">
+        <v>2</v>
+      </c>
+      <c r="L100" t="n">
+        <v>2</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2</v>
+      </c>
+      <c r="N100" t="n">
+        <v>4</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>['16', '79']</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>['39', '67']</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R100" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S100" t="n">
+        <v>3</v>
+      </c>
+      <c r="T100" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U100" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V100" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W100" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X100" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU100" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY100" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD100" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE100" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF100" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BG100" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH100" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BI100" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK100" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL100" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="n">
+        <v>8217395</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>45920.45833333334</v>
+      </c>
+      <c r="F101" t="n">
+        <v>9</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" t="n">
+        <v>2</v>
+      </c>
+      <c r="N101" t="n">
+        <v>3</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>['19', '73']</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R101" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U101" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="V101" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W101" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X101" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BG101" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH101" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BI101" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BJ101" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK101" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BL101" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="BP101" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="n">
+        <v>8217396</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>45920.45833333334</v>
+      </c>
+      <c r="F102" t="n">
+        <v>9</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>3</v>
+      </c>
+      <c r="K102" t="n">
+        <v>4</v>
+      </c>
+      <c r="L102" t="n">
+        <v>1</v>
+      </c>
+      <c r="M102" t="n">
+        <v>3</v>
+      </c>
+      <c r="N102" t="n">
+        <v>4</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>['23', '36', '45']</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R102" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S102" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T102" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U102" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V102" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W102" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X102" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BE102" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF102" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BG102" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH102" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI102" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ102" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK102" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BL102" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BM102" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BN102" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO102" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP102" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="n">
+        <v>8217427</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>45920.45833333334</v>
+      </c>
+      <c r="F103" t="n">
+        <v>9</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" t="n">
+        <v>4</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>4</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>['45', '71', '75', '90+2']</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R103" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S103" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T103" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U103" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="V103" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W103" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X103" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE103" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF103" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG103" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH103" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI103" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ103" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK103" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL103" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BM103" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN103" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="n">
+        <v>8217394</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>45920.45833333334</v>
+      </c>
+      <c r="F104" t="n">
+        <v>9</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1</v>
+      </c>
+      <c r="N104" t="n">
+        <v>2</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R104" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S104" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T104" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U104" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V104" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W104" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X104" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE104" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="BF104" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BG104" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH104" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI104" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ104" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BK104" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL104" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM104" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN104" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP104" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="n">
+        <v>8217436</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>45920.45833333334</v>
+      </c>
+      <c r="F105" t="n">
+        <v>9</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>2</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>2</v>
+      </c>
+      <c r="L105" t="n">
+        <v>3</v>
+      </c>
+      <c r="M105" t="n">
+        <v>2</v>
+      </c>
+      <c r="N105" t="n">
+        <v>5</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>['4', '15', '90+1']</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>['54', '83']</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R105" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S105" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T105" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U105" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V105" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="W105" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X105" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD105" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BE105" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF105" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BG105" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH105" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI105" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ105" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK105" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL105" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM105" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BN105" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="n">
+        <v>8217443</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>45920.45833333334</v>
+      </c>
+      <c r="F106" t="n">
+        <v>9</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>2</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" t="n">
+        <v>3</v>
+      </c>
+      <c r="L106" t="n">
+        <v>4</v>
+      </c>
+      <c r="M106" t="n">
+        <v>2</v>
+      </c>
+      <c r="N106" t="n">
+        <v>6</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>['9', '45+5', '61', '90+1']</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>['38', '89']</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R106" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S106" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T106" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U106" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V106" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="W106" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X106" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB106" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC106" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD106" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE106" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF106" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BG106" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH106" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BI106" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ106" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK106" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL106" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM106" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BN106" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO106" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BP106" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="n">
+        <v>8217423</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>45920.45833333334</v>
+      </c>
+      <c r="F107" t="n">
+        <v>9</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" t="n">
+        <v>3</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>3</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>['42', '64', '68']</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R107" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S107" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="T107" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U107" t="n">
+        <v>3</v>
+      </c>
+      <c r="V107" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W107" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X107" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB107" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF107" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BG107" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH107" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BI107" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ107" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK107" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL107" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM107" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BN107" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO107" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BP107" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP107"/>
+  <dimension ref="A1:BP108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,7 +2440,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.4</v>
@@ -9195,7 +9195,7 @@
         <v>1</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.25</v>
@@ -10288,7 +10288,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR45" t="n">
         <v>1.66</v>
@@ -12465,7 +12465,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ55" t="n">
         <v>2.25</v>
@@ -12686,7 +12686,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR56" t="n">
         <v>1.05</v>
@@ -17479,7 +17479,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ78" t="n">
         <v>0.8</v>
@@ -18136,7 +18136,7 @@
         <v>2</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR81" t="n">
         <v>1.56</v>
@@ -22579,7 +22579,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>8217396</v>
+        <v>8217368</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -22599,197 +22599,197 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
         <v>3</v>
       </c>
       <c r="N102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>['23', '36', '45']</t>
+          <t>['38', '75', '90']</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="R102" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S102" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="T102" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U102" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="V102" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="W102" t="n">
         <v>1.36</v>
       </c>
       <c r="X102" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z102" t="n">
-        <v>4.17</v>
+        <v>3.1</v>
       </c>
       <c r="AA102" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AB102" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD102" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AF102" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AG102" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AH102" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AI102" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AJ102" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AK102" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AL102" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AM102" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AN102" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="AO102" t="n">
         <v>1.5</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.8</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AT102" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD102" t="n">
         <v>2.16</v>
       </c>
-      <c r="AU102" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV102" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW102" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX102" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY102" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ102" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA102" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB102" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC102" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD102" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BE102" t="n">
-        <v>8.5</v>
+        <v>6.45</v>
       </c>
       <c r="BF102" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="BG102" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="BH102" t="n">
-        <v>2.76</v>
+        <v>3.46</v>
       </c>
       <c r="BI102" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="BJ102" t="n">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="BK102" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="BL102" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="BM102" t="n">
-        <v>2.78</v>
+        <v>2.27</v>
       </c>
       <c r="BN102" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="BO102" t="n">
-        <v>3.85</v>
+        <v>3.03</v>
       </c>
       <c r="BP102" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="103">
@@ -22797,7 +22797,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>8217427</v>
+        <v>8217396</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -22817,197 +22817,197 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="I103" t="n">
         <v>1</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N103" t="n">
         <v>4</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>['45', '71', '75', '90+2']</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '36', '45']</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="R103" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="S103" t="n">
-        <v>3.7</v>
+        <v>2.58</v>
       </c>
       <c r="T103" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="U103" t="n">
-        <v>3.31</v>
+        <v>2.74</v>
       </c>
       <c r="V103" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="W103" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="X103" t="n">
-        <v>5.75</v>
+        <v>8.5</v>
       </c>
       <c r="Y103" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR103" t="n">
         <v>1.08</v>
       </c>
-      <c r="Z103" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA103" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB103" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC103" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD103" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE103" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF103" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG103" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AH103" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI103" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AJ103" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AK103" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL103" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM103" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AN103" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO103" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP103" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ103" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AR103" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AS103" t="n">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="AT103" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="AU103" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV103" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW103" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX103" t="n">
         <v>6</v>
       </c>
       <c r="AY103" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ103" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB103" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BC103" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BD103" t="n">
-        <v>1.58</v>
+        <v>3.05</v>
       </c>
       <c r="BE103" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="BF103" t="n">
-        <v>2.67</v>
+        <v>1.53</v>
       </c>
       <c r="BG103" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="BH103" t="n">
-        <v>3.75</v>
+        <v>2.76</v>
       </c>
       <c r="BI103" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="BJ103" t="n">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="BK103" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="BL103" t="n">
-        <v>2.29</v>
+        <v>1.66</v>
       </c>
       <c r="BM103" t="n">
-        <v>1.95</v>
+        <v>2.78</v>
       </c>
       <c r="BN103" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="BO103" t="n">
-        <v>2.45</v>
+        <v>3.85</v>
       </c>
       <c r="BP103" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="104">
@@ -23015,7 +23015,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>8217394</v>
+        <v>8217427</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -23035,197 +23035,197 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
         <v>1</v>
       </c>
       <c r="L104" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['45', '71', '75', '90+2']</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="R104" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S104" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T104" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U104" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="V104" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W104" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X104" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH104" t="n">
         <v>2.1</v>
       </c>
-      <c r="S104" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T104" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="U104" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V104" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="W104" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X104" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA104" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AC104" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD104" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AE104" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF104" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AG104" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH104" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AI104" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AJ104" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AK104" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AL104" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR104" t="n">
         <v>1.28</v>
       </c>
-      <c r="AM104" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN104" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AO104" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP104" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AQ104" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR104" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AS104" t="n">
-        <v>1.18</v>
+        <v>0.98</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.79</v>
+        <v>2.26</v>
       </c>
       <c r="AU104" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW104" t="n">
         <v>4</v>
       </c>
-      <c r="AV104" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW104" t="n">
+      <c r="AX104" t="n">
         <v>6</v>
       </c>
-      <c r="AX104" t="n">
-        <v>9</v>
-      </c>
       <c r="AY104" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ104" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC104" t="n">
         <v>7</v>
       </c>
       <c r="BD104" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="BE104" t="n">
-        <v>7.35</v>
+        <v>8.9</v>
       </c>
       <c r="BF104" t="n">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="BG104" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BH104" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="BI104" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="BJ104" t="n">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="BK104" t="n">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="BL104" t="n">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="BM104" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="BN104" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="BO104" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="BP104" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="105">
@@ -23233,7 +23233,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>8217436</v>
+        <v>8217394</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -23253,197 +23253,197 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N105" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>['4', '15', '90+1']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>['54', '83']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="R105" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="S105" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="T105" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="U105" t="n">
-        <v>3.28</v>
+        <v>2.65</v>
       </c>
       <c r="V105" t="n">
-        <v>2.47</v>
+        <v>3.15</v>
       </c>
       <c r="W105" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="X105" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.18</v>
+        <v>2.72</v>
       </c>
       <c r="AA105" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AB105" t="n">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="AC105" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD105" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AF105" t="n">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="AG105" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH105" t="n">
         <v>1.7</v>
       </c>
-      <c r="AH105" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AI105" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AJ105" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AK105" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL105" t="n">
         <v>1.28</v>
       </c>
       <c r="AM105" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AN105" t="n">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AO105" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AP105" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AR105" t="n">
-        <v>2.03</v>
+        <v>1.61</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AT105" t="n">
-        <v>3.66</v>
+        <v>2.79</v>
       </c>
       <c r="AU105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC105" t="n">
         <v>7</v>
       </c>
-      <c r="AV105" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW105" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX105" t="n">
+      <c r="BD105" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE105" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="BF105" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BG105" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH105" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI105" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ105" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BK105" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL105" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM105" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN105" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO105" t="n">
         <v>3</v>
       </c>
-      <c r="AY105" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ105" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA105" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB105" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC105" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD105" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BE105" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BF105" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BG105" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BH105" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI105" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BJ105" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BK105" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BL105" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BM105" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BN105" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BO105" t="n">
-        <v>2.65</v>
-      </c>
       <c r="BP105" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="106">
@@ -23451,7 +23451,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>8217443</v>
+        <v>8217436</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -23471,197 +23471,197 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="I106" t="n">
         <v>2</v>
       </c>
       <c r="J106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
+        <v>2</v>
+      </c>
+      <c r="L106" t="n">
         <v>3</v>
       </c>
-      <c r="L106" t="n">
+      <c r="M106" t="n">
+        <v>2</v>
+      </c>
+      <c r="N106" t="n">
+        <v>5</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>['4', '15', '90+1']</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>['54', '83']</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R106" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S106" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T106" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U106" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V106" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="W106" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X106" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF106" t="n">
         <v>4</v>
       </c>
-      <c r="M106" t="n">
-        <v>2</v>
-      </c>
-      <c r="N106" t="n">
-        <v>6</v>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>['9', '45+5', '61', '90+1']</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>['38', '89']</t>
-        </is>
-      </c>
-      <c r="Q106" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="R106" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="S106" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T106" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U106" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V106" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="W106" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X106" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y106" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AA106" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB106" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AC106" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD106" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AE106" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF106" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AG106" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AH106" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI106" t="n">
         <v>1.57</v>
       </c>
-      <c r="AI106" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AJ106" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AK106" t="n">
         <v>1.25</v>
       </c>
       <c r="AL106" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AM106" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN106" t="n">
         <v>1.75</v>
       </c>
-      <c r="AN106" t="n">
+      <c r="AO106" t="n">
         <v>2.25</v>
       </c>
-      <c r="AO106" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AP106" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.23</v>
+        <v>2.03</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="AT106" t="n">
-        <v>2.36</v>
+        <v>3.66</v>
       </c>
       <c r="AU106" t="n">
         <v>7</v>
       </c>
       <c r="AV106" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW106" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AX106" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AY106" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ106" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB106" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC106" t="n">
         <v>16</v>
       </c>
-      <c r="BA106" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB106" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC106" t="n">
-        <v>15</v>
-      </c>
       <c r="BD106" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="BE106" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BF106" t="n">
-        <v>2.75</v>
+        <v>3.22</v>
       </c>
       <c r="BG106" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BH106" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="BI106" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="BJ106" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="BK106" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="BL106" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="BM106" t="n">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="BN106" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="BO106" t="n">
-        <v>3.16</v>
+        <v>2.65</v>
       </c>
       <c r="BP106" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="107">
@@ -23669,7 +23669,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>8217423</v>
+        <v>8217443</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -23689,196 +23689,414 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L107" t="n">
+        <v>4</v>
+      </c>
+      <c r="M107" t="n">
+        <v>2</v>
+      </c>
+      <c r="N107" t="n">
+        <v>6</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>['9', '45+5', '61', '90+1']</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>['38', '89']</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R107" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S107" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T107" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U107" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V107" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="W107" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X107" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA107" t="n">
         <v>3</v>
       </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>3</v>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>['42', '64', '68']</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q107" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="R107" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="S107" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="T107" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U107" t="n">
-        <v>3</v>
-      </c>
-      <c r="V107" t="n">
+      <c r="AB107" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF107" t="n">
         <v>2.6</v>
       </c>
-      <c r="W107" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X107" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Y107" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA107" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB107" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AC107" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD107" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE107" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF107" t="n">
-        <v>3.84</v>
-      </c>
       <c r="AG107" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AH107" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AI107" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AJ107" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AK107" t="n">
         <v>1.25</v>
       </c>
       <c r="AL107" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AM107" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AN107" t="n">
-        <v>0.25</v>
+        <v>2.25</v>
       </c>
       <c r="AO107" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AP107" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.82</v>
+        <v>1.23</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.57</v>
+        <v>1.13</v>
       </c>
       <c r="AT107" t="n">
-        <v>3.39</v>
+        <v>2.36</v>
       </c>
       <c r="AU107" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW107" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX107" t="n">
         <v>14</v>
       </c>
-      <c r="AX107" t="n">
-        <v>6</v>
-      </c>
       <c r="AY107" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ107" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="BA107" t="n">
         <v>8</v>
       </c>
       <c r="BB107" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF107" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BG107" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH107" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BI107" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ107" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK107" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL107" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM107" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BN107" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO107" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BP107" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="n">
+        <v>8217423</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>45920.45833333334</v>
+      </c>
+      <c r="F108" t="n">
+        <v>9</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" t="n">
+        <v>3</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>3</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>['42', '64', '68']</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R108" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S108" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="T108" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U108" t="n">
+        <v>3</v>
+      </c>
+      <c r="V108" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W108" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X108" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AU108" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY108" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB108" t="n">
         <v>4</v>
       </c>
-      <c r="BC107" t="n">
+      <c r="BC108" t="n">
         <v>12</v>
       </c>
-      <c r="BD107" t="n">
+      <c r="BD108" t="n">
         <v>1.62</v>
       </c>
-      <c r="BE107" t="n">
+      <c r="BE108" t="n">
         <v>7.7</v>
       </c>
-      <c r="BF107" t="n">
+      <c r="BF108" t="n">
         <v>3.04</v>
       </c>
-      <c r="BG107" t="n">
+      <c r="BG108" t="n">
         <v>1.18</v>
       </c>
-      <c r="BH107" t="n">
+      <c r="BH108" t="n">
         <v>3.83</v>
       </c>
-      <c r="BI107" t="n">
+      <c r="BI108" t="n">
         <v>1.39</v>
       </c>
-      <c r="BJ107" t="n">
+      <c r="BJ108" t="n">
         <v>2.65</v>
       </c>
-      <c r="BK107" t="n">
+      <c r="BK108" t="n">
         <v>1.71</v>
       </c>
-      <c r="BL107" t="n">
+      <c r="BL108" t="n">
         <v>2.04</v>
       </c>
-      <c r="BM107" t="n">
+      <c r="BM108" t="n">
         <v>2.14</v>
       </c>
-      <c r="BN107" t="n">
+      <c r="BN108" t="n">
         <v>1.64</v>
       </c>
-      <c r="BO107" t="n">
+      <c r="BO108" t="n">
         <v>2.76</v>
       </c>
-      <c r="BP107" t="n">
+      <c r="BP108" t="n">
         <v>1.36</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -21636,10 +21636,10 @@
         <v>2.73</v>
       </c>
       <c r="AU97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW97" t="n">
         <v>4</v>
@@ -21648,10 +21648,10 @@
         <v>14</v>
       </c>
       <c r="AY97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ97" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA97" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -22735,13 +22735,13 @@
         <v>7</v>
       </c>
       <c r="AX102" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY102" t="n">
         <v>9</v>
       </c>
       <c r="AZ102" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA102" t="n">
         <v>6</v>
@@ -23162,7 +23162,7 @@
         <v>2.26</v>
       </c>
       <c r="AU104" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV104" t="n">
         <v>2</v>
@@ -23171,13 +23171,13 @@
         <v>4</v>
       </c>
       <c r="AX104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY104" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ104" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA104" t="n">
         <v>6</v>
@@ -23398,13 +23398,13 @@
         <v>10</v>
       </c>
       <c r="BA105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB105" t="n">
         <v>2</v>
       </c>
       <c r="BC105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD105" t="n">
         <v>1.7</v>
@@ -23607,13 +23607,13 @@
         <v>4</v>
       </c>
       <c r="AX106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY106" t="n">
         <v>11</v>
       </c>
       <c r="AZ106" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA106" t="n">
         <v>6</v>
@@ -23837,10 +23837,10 @@
         <v>8</v>
       </c>
       <c r="BB107" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC107" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD107" t="n">
         <v>1.55</v>
@@ -23935,7 +23935,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>['42', '64', '68']</t>
+          <t>['42', '64', '67']</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -24052,13 +24052,13 @@
         <v>7</v>
       </c>
       <c r="BA108" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB108" t="n">
         <v>4</v>
       </c>
       <c r="BC108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD108" t="n">
         <v>1.62</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -21645,13 +21645,13 @@
         <v>4</v>
       </c>
       <c r="AX97" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY97" t="n">
         <v>13</v>
       </c>
       <c r="AZ97" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA97" t="n">
         <v>4</v>
@@ -22075,7 +22075,7 @@
         <v>3</v>
       </c>
       <c r="AV99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW99" t="n">
         <v>5</v>
@@ -22087,7 +22087,7 @@
         <v>8</v>
       </c>
       <c r="AZ99" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA99" t="n">
         <v>2</v>
@@ -22517,13 +22517,13 @@
         <v>4</v>
       </c>
       <c r="AX101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY101" t="n">
         <v>7</v>
       </c>
       <c r="AZ101" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA101" t="n">
         <v>3</v>
@@ -22944,13 +22944,13 @@
         <v>2.16</v>
       </c>
       <c r="AU103" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV103" t="n">
         <v>6</v>
       </c>
       <c r="AW103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX103" t="n">
         <v>6</v>
@@ -23171,13 +23171,13 @@
         <v>4</v>
       </c>
       <c r="AX104" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY104" t="n">
         <v>12</v>
       </c>
       <c r="AZ104" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA104" t="n">
         <v>6</v>
@@ -23386,16 +23386,16 @@
         <v>1</v>
       </c>
       <c r="AW105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX105" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ105" t="n">
         <v>9</v>
-      </c>
-      <c r="AY105" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ105" t="n">
-        <v>10</v>
       </c>
       <c r="BA105" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP108"/>
+  <dimension ref="A1:BP120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         <v>2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.8</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.8</v>
@@ -2222,7 +2222,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.6</v>
@@ -3748,7 +3748,7 @@
         <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ18" t="n">
         <v>1</v>
@@ -4617,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.4</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.8</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.4</v>
@@ -6582,7 +6582,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR28" t="n">
         <v>0.73</v>
@@ -6797,10 +6797,10 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR29" t="n">
         <v>0.89</v>
@@ -7015,10 +7015,10 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR30" t="n">
         <v>2.14</v>
@@ -7233,7 +7233,7 @@
         <v>1</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.8</v>
@@ -7454,7 +7454,7 @@
         <v>2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR32" t="n">
         <v>1.53</v>
@@ -7890,7 +7890,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR34" t="n">
         <v>2.2</v>
@@ -8108,7 +8108,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR35" t="n">
         <v>0.89</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.8</v>
@@ -8762,7 +8762,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR38" t="n">
         <v>0.62</v>
@@ -8977,10 +8977,10 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ39" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR39" t="n">
         <v>1.87</v>
@@ -9198,7 +9198,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR40" t="n">
         <v>0.82</v>
@@ -9413,7 +9413,7 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.4</v>
@@ -9849,10 +9849,10 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR43" t="n">
         <v>1.16</v>
@@ -10067,7 +10067,7 @@
         <v>3</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.4</v>
@@ -10285,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.8</v>
@@ -10506,7 +10506,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AR46" t="n">
         <v>1.06</v>
@@ -11160,7 +11160,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR49" t="n">
         <v>1.11</v>
@@ -11378,7 +11378,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ50" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR50" t="n">
         <v>0.84</v>
@@ -11814,7 +11814,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AR52" t="n">
         <v>1.1</v>
@@ -12029,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.6</v>
@@ -12247,7 +12247,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ54" t="n">
         <v>1</v>
@@ -12468,7 +12468,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ55" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR55" t="n">
         <v>1.18</v>
@@ -12683,7 +12683,7 @@
         <v>1</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.8</v>
@@ -12901,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="AP57" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ57" t="n">
         <v>1</v>
@@ -13119,7 +13119,7 @@
         <v>2</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.6</v>
@@ -13337,7 +13337,7 @@
         <v>3</v>
       </c>
       <c r="AP59" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.4</v>
@@ -13558,7 +13558,7 @@
         <v>2</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR60" t="n">
         <v>1.24</v>
@@ -13776,7 +13776,7 @@
         <v>2</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR61" t="n">
         <v>1.28</v>
@@ -13991,7 +13991,7 @@
         <v>1.5</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.8</v>
@@ -14427,10 +14427,10 @@
         <v>0.5</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR64" t="n">
         <v>1.37</v>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.8</v>
@@ -14863,7 +14863,7 @@
         <v>0</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.4</v>
@@ -15084,7 +15084,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR67" t="n">
         <v>1.28</v>
@@ -15517,7 +15517,7 @@
         <v>0</v>
       </c>
       <c r="AP69" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.8</v>
@@ -15738,7 +15738,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR70" t="n">
         <v>1.75</v>
@@ -15956,7 +15956,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR71" t="n">
         <v>1.52</v>
@@ -16174,7 +16174,7 @@
         <v>2</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR72" t="n">
         <v>1.75</v>
@@ -19005,10 +19005,10 @@
         <v>1.67</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR85" t="n">
         <v>1.21</v>
@@ -19223,10 +19223,10 @@
         <v>0.33</v>
       </c>
       <c r="AP86" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR86" t="n">
         <v>1.77</v>
@@ -19441,10 +19441,10 @@
         <v>1.33</v>
       </c>
       <c r="AP87" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR87" t="n">
         <v>1.43</v>
@@ -19659,10 +19659,10 @@
         <v>2.33</v>
       </c>
       <c r="AP88" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ88" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR88" t="n">
         <v>1.58</v>
@@ -19877,10 +19877,10 @@
         <v>2</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ89" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR89" t="n">
         <v>1.36</v>
@@ -20095,10 +20095,10 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AR90" t="n">
         <v>1.5</v>
@@ -20313,7 +20313,7 @@
         <v>1</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ91" t="n">
         <v>1</v>
@@ -20531,10 +20531,10 @@
         <v>1</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR92" t="n">
         <v>1.39</v>
@@ -20752,7 +20752,7 @@
         <v>1</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR93" t="n">
         <v>1.72</v>
@@ -20967,10 +20967,10 @@
         <v>2</v>
       </c>
       <c r="AP94" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ94" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR94" t="n">
         <v>1.23</v>
@@ -21185,10 +21185,10 @@
         <v>2</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR95" t="n">
         <v>1.13</v>
@@ -21403,10 +21403,10 @@
         <v>1.33</v>
       </c>
       <c r="AP96" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR96" t="n">
         <v>1.27</v>
@@ -24098,6 +24098,2622 @@
       </c>
       <c r="BP108" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="n">
+        <v>8217434</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>45927.35416666666</v>
+      </c>
+      <c r="F109" t="n">
+        <v>10</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1</v>
+      </c>
+      <c r="N109" t="n">
+        <v>2</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R109" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S109" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T109" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U109" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V109" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W109" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X109" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BI109" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ109" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BK109" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="n">
+        <v>8217303</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>45927.35416666666</v>
+      </c>
+      <c r="F110" t="n">
+        <v>10</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" t="n">
+        <v>2</v>
+      </c>
+      <c r="L110" t="n">
+        <v>2</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" t="n">
+        <v>3</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>['8', '90+5']</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R110" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S110" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="T110" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U110" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V110" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W110" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X110" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="BI110" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ110" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BK110" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO110" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP110" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="n">
+        <v>8217438</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>45927.45833333334</v>
+      </c>
+      <c r="F111" t="n">
+        <v>10</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" t="n">
+        <v>2</v>
+      </c>
+      <c r="L111" t="n">
+        <v>2</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" t="n">
+        <v>3</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>['45+2', '63']</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R111" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S111" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T111" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U111" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V111" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W111" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X111" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX111" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY111" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ111" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB111" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="BF111" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH111" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI111" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ111" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BK111" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL111" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM111" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN111" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO111" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BP111" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="n">
+        <v>8217437</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>45927.45833333334</v>
+      </c>
+      <c r="F112" t="n">
+        <v>10</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" t="n">
+        <v>3</v>
+      </c>
+      <c r="N112" t="n">
+        <v>4</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>['62', '75', '90+3']</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R112" t="n">
+        <v>2</v>
+      </c>
+      <c r="S112" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T112" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U112" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V112" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="W112" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X112" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH112" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI112" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ112" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK112" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BL112" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM112" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BN112" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO112" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP112" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="n">
+        <v>8217428</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>45927.45833333334</v>
+      </c>
+      <c r="F113" t="n">
+        <v>10</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>2</v>
+      </c>
+      <c r="K113" t="n">
+        <v>2</v>
+      </c>
+      <c r="L113" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" t="n">
+        <v>2</v>
+      </c>
+      <c r="N113" t="n">
+        <v>3</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>['36', '45+6']</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R113" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S113" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T113" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U113" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V113" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W113" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X113" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY113" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH113" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="BI113" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ113" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK113" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL113" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM113" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN113" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO113" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BP113" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="n">
+        <v>8217369</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>45927.45833333334</v>
+      </c>
+      <c r="F114" t="n">
+        <v>10</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" t="n">
+        <v>2</v>
+      </c>
+      <c r="K114" t="n">
+        <v>3</v>
+      </c>
+      <c r="L114" t="n">
+        <v>4</v>
+      </c>
+      <c r="M114" t="n">
+        <v>2</v>
+      </c>
+      <c r="N114" t="n">
+        <v>6</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>['30', '55', '87', '90+2']</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>['3', '39']</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R114" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S114" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T114" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U114" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V114" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="W114" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X114" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH114" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BI114" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN114" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO114" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BP114" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="n">
+        <v>8217445</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>45927.45833333334</v>
+      </c>
+      <c r="F115" t="n">
+        <v>10</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>2</v>
+      </c>
+      <c r="K115" t="n">
+        <v>2</v>
+      </c>
+      <c r="L115" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" t="n">
+        <v>2</v>
+      </c>
+      <c r="N115" t="n">
+        <v>3</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>['3', '39']</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="R115" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S115" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T115" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U115" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V115" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W115" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X115" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ115" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BK115" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO115" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BP115" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="n">
+        <v>8217463</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>45927.45833333334</v>
+      </c>
+      <c r="F116" t="n">
+        <v>10</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R116" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S116" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="T116" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U116" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V116" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="W116" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X116" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="n">
+        <v>8217430</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>45927.45833333334</v>
+      </c>
+      <c r="F117" t="n">
+        <v>10</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>2</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" t="n">
+        <v>3</v>
+      </c>
+      <c r="L117" t="n">
+        <v>7</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1</v>
+      </c>
+      <c r="N117" t="n">
+        <v>8</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>['39', '41', '54', '59', '62', '80', '83']</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R117" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S117" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="T117" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U117" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V117" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="W117" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X117" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="n">
+        <v>8217429</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>45927.45833333334</v>
+      </c>
+      <c r="F118" t="n">
+        <v>10</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1</v>
+      </c>
+      <c r="N118" t="n">
+        <v>1</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R118" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="T118" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U118" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V118" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W118" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X118" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="n">
+        <v>8217439</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>45927.45833333334</v>
+      </c>
+      <c r="F119" t="n">
+        <v>10</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>2</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>2</v>
+      </c>
+      <c r="L119" t="n">
+        <v>2</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>2</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>['7', '31']</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R119" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S119" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="T119" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U119" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V119" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="W119" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X119" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="n">
+        <v>8217444</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>45927.45833333334</v>
+      </c>
+      <c r="F120" t="n">
+        <v>10</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2</v>
+      </c>
+      <c r="L120" t="n">
+        <v>4</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1</v>
+      </c>
+      <c r="N120" t="n">
+        <v>5</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>['34', '43', '84', '88']</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R120" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="S120" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T120" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U120" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V120" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W120" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X120" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -24479,13 +24479,13 @@
         <v>6</v>
       </c>
       <c r="AX110" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY110" t="n">
         <v>9</v>
       </c>
       <c r="AZ110" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA110" t="n">
         <v>8</v>
@@ -26002,13 +26002,13 @@
         <v>1</v>
       </c>
       <c r="AW117" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX117" t="n">
         <v>2</v>
       </c>
       <c r="AY117" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ117" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -25787,13 +25787,13 @@
         <v>3</v>
       </c>
       <c r="AX116" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY116" t="n">
         <v>4</v>
       </c>
       <c r="AZ116" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA116" t="n">
         <v>1</v>
@@ -25996,13 +25996,13 @@
         <v>2.73</v>
       </c>
       <c r="AU117" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV117" t="n">
         <v>1</v>
       </c>
       <c r="AW117" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX117" t="n">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -24906,7 +24906,7 @@
         <v>2.42</v>
       </c>
       <c r="AU112" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV112" t="n">
         <v>5</v>
@@ -24915,13 +24915,13 @@
         <v>14</v>
       </c>
       <c r="AX112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY112" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ112" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA112" t="n">
         <v>8</v>
@@ -26214,7 +26214,7 @@
         <v>2.16</v>
       </c>
       <c r="AU118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV118" t="n">
         <v>2</v>
@@ -26226,7 +26226,7 @@
         <v>5</v>
       </c>
       <c r="AY118" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ118" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP120"/>
+  <dimension ref="A1:BP122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.8</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.8</v>
@@ -2876,7 +2876,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR26" t="n">
         <v>2.21</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.2</v>
@@ -7236,7 +7236,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR31" t="n">
         <v>1.41</v>
@@ -8759,7 +8759,7 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.8</v>
@@ -11375,7 +11375,7 @@
         <v>2</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AQ50" t="n">
         <v>2.2</v>
@@ -13994,7 +13994,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR62" t="n">
         <v>1.49</v>
@@ -15081,7 +15081,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ67" t="n">
         <v>2</v>
@@ -15302,7 +15302,7 @@
         <v>1</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR68" t="n">
         <v>1.92</v>
@@ -16389,7 +16389,7 @@
         <v>1</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.4</v>
@@ -16825,7 +16825,7 @@
         <v>1.67</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.6</v>
@@ -18354,7 +18354,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR82" t="n">
         <v>1.07</v>
@@ -18790,7 +18790,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR84" t="n">
         <v>1.65</v>
@@ -22493,7 +22493,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ101" t="n">
         <v>0.8</v>
@@ -22929,10 +22929,10 @@
         <v>1.5</v>
       </c>
       <c r="AP103" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR103" t="n">
         <v>1.08</v>
@@ -23586,7 +23586,7 @@
         <v>2</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR106" t="n">
         <v>2.03</v>
@@ -26714,6 +26714,442 @@
       </c>
       <c r="BP120" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="n">
+        <v>8217304</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>45934.35416666666</v>
+      </c>
+      <c r="F121" t="n">
+        <v>11</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1</v>
+      </c>
+      <c r="N121" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R121" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S121" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T121" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U121" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="V121" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W121" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X121" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="n">
+        <v>8217435</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>45934.35416666666</v>
+      </c>
+      <c r="F122" t="n">
+        <v>11</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" t="n">
+        <v>3</v>
+      </c>
+      <c r="M122" t="n">
+        <v>2</v>
+      </c>
+      <c r="N122" t="n">
+        <v>5</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>['6', '57', '69']</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>['76', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R122" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S122" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T122" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U122" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V122" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W122" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X122" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP132"/>
+  <dimension ref="A1:BP143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.5</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.67</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.67</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.67</v>
@@ -4402,7 +4402,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4617,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.17</v>
@@ -5274,7 +5274,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -5710,7 +5710,7 @@
         <v>1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -5925,10 +5925,10 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ25" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.17</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.67</v>
@@ -7018,7 +7018,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR30" t="n">
         <v>1.53</v>
@@ -7451,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.5</v>
@@ -7672,7 +7672,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ33" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR33" t="n">
         <v>2.2</v>
@@ -7887,10 +7887,10 @@
         <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR34" t="n">
         <v>0.89</v>
@@ -8105,10 +8105,10 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR35" t="n">
         <v>2.14</v>
@@ -8326,7 +8326,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR36" t="n">
         <v>0.73</v>
@@ -8762,7 +8762,7 @@
         <v>0.17</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR38" t="n">
         <v>0.62</v>
@@ -8977,10 +8977,10 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ39" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR39" t="n">
         <v>1.87</v>
@@ -9198,7 +9198,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR40" t="n">
         <v>1.06</v>
@@ -9413,7 +9413,7 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.17</v>
@@ -9634,7 +9634,7 @@
         <v>1</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR42" t="n">
         <v>1.11</v>
@@ -9852,7 +9852,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR43" t="n">
         <v>1.16</v>
@@ -10067,7 +10067,7 @@
         <v>3</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.67</v>
@@ -10285,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.5</v>
@@ -10506,7 +10506,7 @@
         <v>1</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR46" t="n">
         <v>0.82</v>
@@ -11160,7 +11160,7 @@
         <v>0.17</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR49" t="n">
         <v>0.84</v>
@@ -11378,7 +11378,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR50" t="n">
         <v>1.11</v>
@@ -11593,7 +11593,7 @@
         <v>1</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ51" t="n">
         <v>1</v>
@@ -11814,7 +11814,7 @@
         <v>1</v>
       </c>
       <c r="AQ52" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR52" t="n">
         <v>1.18</v>
@@ -12029,7 +12029,7 @@
         <v>2</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.83</v>
@@ -12247,10 +12247,10 @@
         <v>1.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR54" t="n">
         <v>1.64</v>
@@ -12901,7 +12901,7 @@
         <v>3</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.67</v>
@@ -13122,7 +13122,7 @@
         <v>1</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR58" t="n">
         <v>1.1</v>
@@ -13337,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.5</v>
@@ -13558,7 +13558,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR60" t="n">
         <v>1.24</v>
@@ -13776,7 +13776,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR61" t="n">
         <v>1.28</v>
@@ -13991,7 +13991,7 @@
         <v>1.5</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ62" t="n">
         <v>2</v>
@@ -14427,7 +14427,7 @@
         <v>0</v>
       </c>
       <c r="AP64" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.17</v>
@@ -14442,22 +14442,22 @@
         <v>3.38</v>
       </c>
       <c r="AU64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV64" t="n">
         <v>3</v>
       </c>
       <c r="AW64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY64" t="n">
         <v>12</v>
       </c>
       <c r="AZ64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA64" t="n">
         <v>9</v>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.67</v>
@@ -14863,7 +14863,7 @@
         <v>0.5</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.8</v>
@@ -15302,7 +15302,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR68" t="n">
         <v>1.75</v>
@@ -15317,16 +15317,16 @@
         <v>6</v>
       </c>
       <c r="AV68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY68" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ68" t="n">
         <v>7</v>
@@ -15517,7 +15517,7 @@
         <v>0</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.67</v>
@@ -15738,7 +15738,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR70" t="n">
         <v>1.52</v>
@@ -15956,7 +15956,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR71" t="n">
         <v>1.75</v>
@@ -16174,7 +16174,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ72" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR72" t="n">
         <v>1.28</v>
@@ -16398,10 +16398,10 @@
         <v>0.97</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AT73" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AU73" t="n">
         <v>5</v>
@@ -17703,13 +17703,13 @@
         <v>0.67</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AS79" t="n">
         <v>1.09</v>
       </c>
       <c r="AT79" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AU79" t="n">
         <v>6</v>
@@ -19005,10 +19005,10 @@
         <v>0.33</v>
       </c>
       <c r="AP85" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR85" t="n">
         <v>1.77</v>
@@ -19223,19 +19223,19 @@
         <v>1.67</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR86" t="n">
         <v>1.21</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AU86" t="n">
         <v>8</v>
@@ -19444,7 +19444,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR87" t="n">
         <v>1.27</v>
@@ -19659,10 +19659,10 @@
         <v>1</v>
       </c>
       <c r="AP88" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR88" t="n">
         <v>1.5</v>
@@ -19880,7 +19880,7 @@
         <v>1</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR89" t="n">
         <v>1.72</v>
@@ -19898,13 +19898,13 @@
         <v>3</v>
       </c>
       <c r="AW89" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX89" t="n">
         <v>11</v>
       </c>
       <c r="AY89" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ89" t="n">
         <v>14</v>
@@ -20095,10 +20095,10 @@
         <v>2</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ90" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR90" t="n">
         <v>1.36</v>
@@ -20313,7 +20313,7 @@
         <v>1.33</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.8</v>
@@ -20531,10 +20531,10 @@
         <v>2</v>
       </c>
       <c r="AP92" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR92" t="n">
         <v>1.23</v>
@@ -20749,10 +20749,10 @@
         <v>1</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR93" t="n">
         <v>1.39</v>
@@ -20967,10 +20967,10 @@
         <v>2</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ94" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR94" t="n">
         <v>1.13</v>
@@ -20991,13 +20991,13 @@
         <v>7</v>
       </c>
       <c r="AX94" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY94" t="n">
         <v>9</v>
       </c>
       <c r="AZ94" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA94" t="n">
         <v>6</v>
@@ -21185,10 +21185,10 @@
         <v>2.33</v>
       </c>
       <c r="AP95" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ95" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR95" t="n">
         <v>1.58</v>
@@ -21403,19 +21403,19 @@
         <v>1</v>
       </c>
       <c r="AP96" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AS96" t="n">
         <v>1.27</v>
       </c>
       <c r="AT96" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="AU96" t="n">
         <v>5</v>
@@ -22063,13 +22063,13 @@
         <v>1.83</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AS99" t="n">
         <v>1.57</v>
       </c>
       <c r="AT99" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="AU99" t="n">
         <v>5</v>
@@ -23156,10 +23156,10 @@
         <v>1.61</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="AU104" t="n">
         <v>4</v>
@@ -24240,16 +24240,16 @@
         <v>1</v>
       </c>
       <c r="AQ109" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AS109" t="n">
         <v>1.41</v>
       </c>
       <c r="AT109" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="AU109" t="n">
         <v>4</v>
@@ -24455,7 +24455,7 @@
         <v>1</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.8</v>
@@ -24673,10 +24673,10 @@
         <v>1</v>
       </c>
       <c r="AP111" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR111" t="n">
         <v>1.52</v>
@@ -24688,22 +24688,22 @@
         <v>2.51</v>
       </c>
       <c r="AU111" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV111" t="n">
         <v>4</v>
       </c>
-      <c r="AV111" t="n">
-        <v>3</v>
-      </c>
       <c r="AW111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX111" t="n">
         <v>7</v>
       </c>
       <c r="AY111" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ111" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA111" t="n">
         <v>4</v>
@@ -24891,10 +24891,10 @@
         <v>2</v>
       </c>
       <c r="AP112" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR112" t="n">
         <v>1.35</v>
@@ -25109,10 +25109,10 @@
         <v>1</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR113" t="n">
         <v>1.51</v>
@@ -25327,10 +25327,10 @@
         <v>2.25</v>
       </c>
       <c r="AP114" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR114" t="n">
         <v>1.43</v>
@@ -25545,19 +25545,19 @@
         <v>1.75</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ115" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR115" t="n">
         <v>1.5</v>
       </c>
       <c r="AS115" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AU115" t="n">
         <v>6</v>
@@ -25763,19 +25763,19 @@
         <v>1.25</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR116" t="n">
         <v>1.08</v>
       </c>
       <c r="AS116" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="AT116" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AU116" t="n">
         <v>7</v>
@@ -25981,19 +25981,19 @@
         <v>0.25</v>
       </c>
       <c r="AP117" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AS117" t="n">
         <v>0.97</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AU117" t="n">
         <v>12</v>
@@ -26199,10 +26199,10 @@
         <v>1</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR118" t="n">
         <v>1.38</v>
@@ -26417,10 +26417,10 @@
         <v>0.75</v>
       </c>
       <c r="AP119" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AR119" t="n">
         <v>1.77</v>
@@ -26438,13 +26438,13 @@
         <v>8</v>
       </c>
       <c r="AW119" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX119" t="n">
         <v>10</v>
       </c>
       <c r="AY119" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ119" t="n">
         <v>18</v>
@@ -26638,7 +26638,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR120" t="n">
         <v>1.49</v>
@@ -27295,13 +27295,13 @@
         <v>0.67</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AS123" t="n">
         <v>1.27</v>
       </c>
       <c r="AT123" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="AU123" t="n">
         <v>5</v>
@@ -28170,10 +28170,10 @@
         <v>1.34</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AT127" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AU127" t="n">
         <v>2</v>
@@ -29330,6 +29330,2404 @@
       </c>
       <c r="BP132" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="n">
+        <v>8217507</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>45941.45833333334</v>
+      </c>
+      <c r="F133" t="n">
+        <v>12</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" t="n">
+        <v>2</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" t="n">
+        <v>2</v>
+      </c>
+      <c r="N133" t="n">
+        <v>3</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>['38', '60']</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R133" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S133" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T133" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U133" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X133" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="n">
+        <v>8217506</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>45941.45833333334</v>
+      </c>
+      <c r="F134" t="n">
+        <v>12</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" t="n">
+        <v>1</v>
+      </c>
+      <c r="N134" t="n">
+        <v>2</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R134" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S134" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="T134" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U134" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V134" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W134" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X134" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="n">
+        <v>8217505</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>45941.45833333334</v>
+      </c>
+      <c r="F135" t="n">
+        <v>12</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>1</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" t="n">
+        <v>2</v>
+      </c>
+      <c r="L135" t="n">
+        <v>3</v>
+      </c>
+      <c r="M135" t="n">
+        <v>2</v>
+      </c>
+      <c r="N135" t="n">
+        <v>5</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>['31', '72', '78']</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>['16', '56']</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R135" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S135" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T135" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U135" t="n">
+        <v>3</v>
+      </c>
+      <c r="V135" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W135" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X135" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="n">
+        <v>8217467</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>45941.45833333334</v>
+      </c>
+      <c r="F136" t="n">
+        <v>12</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>2</v>
+      </c>
+      <c r="K136" t="n">
+        <v>2</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>2</v>
+      </c>
+      <c r="N136" t="n">
+        <v>2</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>['26', '40']</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R136" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T136" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U136" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V136" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W136" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X136" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="n">
+        <v>8217466</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>45941.45833333334</v>
+      </c>
+      <c r="F137" t="n">
+        <v>12</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>2</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>2</v>
+      </c>
+      <c r="L137" t="n">
+        <v>2</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>2</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>['12', '36']</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="R137" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S137" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T137" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U137" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V137" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W137" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X137" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>8217465</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>45941.45833333334</v>
+      </c>
+      <c r="F138" t="n">
+        <v>12</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1</v>
+      </c>
+      <c r="N138" t="n">
+        <v>1</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="R138" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S138" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T138" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U138" t="n">
+        <v>3</v>
+      </c>
+      <c r="V138" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W138" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X138" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>8217447</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>45941.45833333334</v>
+      </c>
+      <c r="F139" t="n">
+        <v>12</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1</v>
+      </c>
+      <c r="L139" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1</v>
+      </c>
+      <c r="N139" t="n">
+        <v>2</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="R139" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S139" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T139" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U139" t="n">
+        <v>3</v>
+      </c>
+      <c r="V139" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W139" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X139" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>8217441</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>45941.45833333334</v>
+      </c>
+      <c r="F140" t="n">
+        <v>12</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" t="n">
+        <v>1</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="R140" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S140" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="T140" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U140" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V140" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W140" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X140" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>8217504</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>45941.45833333334</v>
+      </c>
+      <c r="F141" t="n">
+        <v>12</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>2</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>2</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>['62', '83']</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R141" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S141" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T141" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U141" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V141" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W141" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X141" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>8217442</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>45941.45833333334</v>
+      </c>
+      <c r="F142" t="n">
+        <v>12</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>4</v>
+      </c>
+      <c r="N142" t="n">
+        <v>4</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>['8', '83', '90', '90+3']</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R142" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S142" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T142" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U142" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V142" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W142" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X142" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>8217265</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>45941.5625</v>
+      </c>
+      <c r="F143" t="n">
+        <v>12</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R143" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S143" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T143" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U143" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V143" t="n">
+        <v>3</v>
+      </c>
+      <c r="W143" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X143" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -28526,19 +28526,19 @@
         <v>2</v>
       </c>
       <c r="AV133">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW133">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX133">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY133">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ133">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA133">
         <v>6</v>
@@ -29144,7 +29144,7 @@
         <v>0</v>
       </c>
       <c r="AV136">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW136">
         <v>13</v>
@@ -29156,7 +29156,7 @@
         <v>13</v>
       </c>
       <c r="AZ136">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA136">
         <v>2</v>
@@ -29559,13 +29559,13 @@
         <v>5</v>
       </c>
       <c r="AW138">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX138">
         <v>7</v>
       </c>
       <c r="AY138">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ138">
         <v>12</v>
@@ -29759,7 +29759,7 @@
         <v>2.87</v>
       </c>
       <c r="AU139">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV139">
         <v>4</v>
@@ -29771,7 +29771,7 @@
         <v>5</v>
       </c>
       <c r="AY139">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ139">
         <v>9</v>
@@ -30174,19 +30174,19 @@
         <v>3</v>
       </c>
       <c r="AV141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW141">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX141">
         <v>9</v>
       </c>
       <c r="AY141">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ141">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA141">
         <v>4</v>
@@ -30383,13 +30383,13 @@
         <v>7</v>
       </c>
       <c r="AW142">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX142">
         <v>6</v>
       </c>
       <c r="AY142">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ142">
         <v>13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP143"/>
+  <dimension ref="A1:BP145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.33</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.67</v>
@@ -2876,7 +2876,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.67</v>
@@ -7015,7 +7015,7 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.17</v>
@@ -10288,7 +10288,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR45" t="n">
         <v>1.66</v>
@@ -10506,7 +10506,7 @@
         <v>1</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR46" t="n">
         <v>0.82</v>
@@ -13340,7 +13340,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR59" t="n">
         <v>1.05</v>
@@ -13558,7 +13558,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR60" t="n">
         <v>1.24</v>
@@ -13773,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.33</v>
@@ -15953,7 +15953,7 @@
         <v>1.5</v>
       </c>
       <c r="AP71" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.17</v>
@@ -17043,10 +17043,10 @@
         <v>1</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR76" t="n">
         <v>1.56</v>
@@ -17479,7 +17479,7 @@
         <v>2</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ78" t="n">
         <v>1</v>
@@ -19880,7 +19880,7 @@
         <v>1</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR89" t="n">
         <v>1.72</v>
@@ -21839,7 +21839,7 @@
         <v>1.75</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.17</v>
@@ -22496,7 +22496,7 @@
         <v>1</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR101" t="n">
         <v>1.22</v>
@@ -23365,7 +23365,7 @@
         <v>2.25</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ105" t="n">
         <v>2</v>
@@ -26638,7 +26638,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR120" t="n">
         <v>1.49</v>
@@ -27728,7 +27728,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR125" t="n">
         <v>1.35</v>
@@ -27943,7 +27943,7 @@
         <v>0.8</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ126" t="n">
         <v>0.67</v>
@@ -28379,7 +28379,7 @@
         <v>1.6</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.83</v>
@@ -30562,7 +30562,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR138" t="n">
         <v>1.34</v>
@@ -31728,6 +31728,442 @@
       </c>
       <c r="BP143" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
+        <v>8217269</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>45948.35416666666</v>
+      </c>
+      <c r="F144" t="n">
+        <v>13</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1</v>
+      </c>
+      <c r="L144" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>1</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R144" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S144" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="T144" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U144" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V144" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W144" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X144" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="BI144" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ144" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK144" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL144" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM144" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN144" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO144" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BP144" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>8217274</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>45948.35416666666</v>
+      </c>
+      <c r="F145" t="n">
+        <v>13</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>2</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>2</v>
+      </c>
+      <c r="L145" t="n">
+        <v>2</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1</v>
+      </c>
+      <c r="N145" t="n">
+        <v>3</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>['2', '41']</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="R145" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S145" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="T145" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U145" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V145" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W145" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X145" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO145" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP145" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP145"/>
+  <dimension ref="A1:BP155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.14</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.29</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.17</v>
@@ -6364,7 +6364,7 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AR27" t="n">
         <v>2.21</v>
@@ -6800,7 +6800,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR29" t="n">
         <v>1.67</v>
@@ -7018,7 +7018,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR30" t="n">
         <v>1.53</v>
@@ -7236,7 +7236,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR31" t="n">
         <v>0.89</v>
@@ -7454,7 +7454,7 @@
         <v>1</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR32" t="n">
         <v>1.41</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.83</v>
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.33</v>
@@ -8105,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.17</v>
@@ -8323,10 +8323,10 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR36" t="n">
         <v>0.73</v>
@@ -8544,7 +8544,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR37" t="n">
         <v>1.09</v>
@@ -8759,7 +8759,7 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.5</v>
@@ -9198,7 +9198,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR40" t="n">
         <v>1.06</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.83</v>
@@ -10070,7 +10070,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR44" t="n">
         <v>0.89</v>
@@ -10285,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.29</v>
@@ -10721,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="AP47" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.83</v>
@@ -11157,7 +11157,7 @@
         <v>2</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AQ49" t="n">
         <v>2.33</v>
@@ -11375,7 +11375,7 @@
         <v>3</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.5</v>
@@ -11596,7 +11596,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR51" t="n">
         <v>1.68</v>
@@ -12029,7 +12029,7 @@
         <v>2</v>
       </c>
       <c r="AP53" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.83</v>
@@ -12247,7 +12247,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.83</v>
@@ -12904,7 +12904,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR57" t="n">
         <v>1.22</v>
@@ -13119,10 +13119,10 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR58" t="n">
         <v>1.1</v>
@@ -13776,7 +13776,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR61" t="n">
         <v>1.28</v>
@@ -13994,7 +13994,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ62" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AR62" t="n">
         <v>1.49</v>
@@ -14212,7 +14212,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR63" t="n">
         <v>1.18</v>
@@ -14427,7 +14427,7 @@
         <v>0</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.17</v>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.67</v>
@@ -14866,7 +14866,7 @@
         <v>1</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR66" t="n">
         <v>1.37</v>
@@ -15084,7 +15084,7 @@
         <v>1</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR67" t="n">
         <v>1.92</v>
@@ -15299,7 +15299,7 @@
         <v>2</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.33</v>
@@ -15517,10 +15517,10 @@
         <v>0</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR69" t="n">
         <v>1.68</v>
@@ -15738,7 +15738,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR70" t="n">
         <v>1.52</v>
@@ -16171,7 +16171,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.83</v>
@@ -16389,7 +16389,7 @@
         <v>1</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.17</v>
@@ -16610,7 +16610,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ74" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AR74" t="n">
         <v>1.07</v>
@@ -16825,10 +16825,10 @@
         <v>2</v>
       </c>
       <c r="AP75" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR75" t="n">
         <v>1.55</v>
@@ -17264,7 +17264,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR77" t="n">
         <v>1.18</v>
@@ -17482,7 +17482,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR78" t="n">
         <v>1.77</v>
@@ -17697,7 +17697,7 @@
         <v>0</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.67</v>
@@ -18133,7 +18133,7 @@
         <v>1.67</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.83</v>
@@ -18351,7 +18351,7 @@
         <v>2</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.17</v>
@@ -18572,7 +18572,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR83" t="n">
         <v>1.4</v>
@@ -18790,7 +18790,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR84" t="n">
         <v>1.65</v>
@@ -19008,7 +19008,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR85" t="n">
         <v>1.77</v>
@@ -19223,7 +19223,7 @@
         <v>1.67</v>
       </c>
       <c r="AP86" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.33</v>
@@ -19444,7 +19444,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR87" t="n">
         <v>1.27</v>
@@ -19659,10 +19659,10 @@
         <v>1</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR88" t="n">
         <v>1.5</v>
@@ -20316,7 +20316,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR91" t="n">
         <v>1.43</v>
@@ -20531,7 +20531,7 @@
         <v>2</v>
       </c>
       <c r="AP92" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.5</v>
@@ -21185,7 +21185,7 @@
         <v>2.33</v>
       </c>
       <c r="AP95" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ95" t="n">
         <v>2.33</v>
@@ -21403,7 +21403,7 @@
         <v>1</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.83</v>
@@ -21842,7 +21842,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR98" t="n">
         <v>1.57</v>
@@ -22057,7 +22057,7 @@
         <v>2</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.83</v>
@@ -22278,7 +22278,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR100" t="n">
         <v>1.28</v>
@@ -22711,10 +22711,10 @@
         <v>1.5</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR102" t="n">
         <v>1.08</v>
@@ -22932,7 +22932,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR103" t="n">
         <v>1.16</v>
@@ -23147,7 +23147,7 @@
         <v>1.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.17</v>
@@ -23368,7 +23368,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ105" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AR105" t="n">
         <v>2.03</v>
@@ -23801,7 +23801,7 @@
         <v>0.25</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.67</v>
@@ -24019,10 +24019,10 @@
         <v>1.33</v>
       </c>
       <c r="AP108" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR108" t="n">
         <v>1.23</v>
@@ -24458,7 +24458,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR110" t="n">
         <v>1.39</v>
@@ -24673,7 +24673,7 @@
         <v>1</v>
       </c>
       <c r="AP111" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.17</v>
@@ -24891,7 +24891,7 @@
         <v>2</v>
       </c>
       <c r="AP112" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ112" t="n">
         <v>2.33</v>
@@ -25327,7 +25327,7 @@
         <v>2.25</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.5</v>
@@ -25545,7 +25545,7 @@
         <v>1.75</v>
       </c>
       <c r="AP115" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.83</v>
@@ -25981,10 +25981,10 @@
         <v>0.25</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR117" t="n">
         <v>1.78</v>
@@ -26202,7 +26202,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR118" t="n">
         <v>1.38</v>
@@ -26420,7 +26420,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR119" t="n">
         <v>1.77</v>
@@ -26853,10 +26853,10 @@
         <v>1.8</v>
       </c>
       <c r="AP121" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AQ121" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AR121" t="n">
         <v>1.19</v>
@@ -27071,10 +27071,10 @@
         <v>1.8</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR122" t="n">
         <v>1.25</v>
@@ -27289,7 +27289,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.67</v>
@@ -27507,7 +27507,7 @@
         <v>1.4</v>
       </c>
       <c r="AP124" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.17</v>
@@ -27946,7 +27946,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR126" t="n">
         <v>1.7</v>
@@ -28161,7 +28161,7 @@
         <v>1.4</v>
       </c>
       <c r="AP127" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.17</v>
@@ -28818,7 +28818,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR130" t="n">
         <v>1.73</v>
@@ -29036,7 +29036,7 @@
         <v>1</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR131" t="n">
         <v>1.17</v>
@@ -29254,7 +29254,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR132" t="n">
         <v>1.65</v>
@@ -29469,7 +29469,7 @@
         <v>1</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.33</v>
@@ -29690,7 +29690,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR134" t="n">
         <v>1.51</v>
@@ -29908,7 +29908,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR135" t="n">
         <v>1.25</v>
@@ -30341,7 +30341,7 @@
         <v>1</v>
       </c>
       <c r="AP137" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ137" t="n">
         <v>0.83</v>
@@ -30995,7 +30995,7 @@
         <v>0.8</v>
       </c>
       <c r="AP140" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.17</v>
@@ -31213,7 +31213,7 @@
         <v>1.8</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.5</v>
@@ -31431,7 +31431,7 @@
         <v>2.2</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ142" t="n">
         <v>2.33</v>
@@ -31652,7 +31652,7 @@
         <v>1</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR143" t="n">
         <v>1.7</v>
@@ -32164,6 +32164,2186 @@
       </c>
       <c r="BP145" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>8217448</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>45948.45833333334</v>
+      </c>
+      <c r="F146" t="n">
+        <v>13</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>3</v>
+      </c>
+      <c r="J146" t="n">
+        <v>1</v>
+      </c>
+      <c r="K146" t="n">
+        <v>4</v>
+      </c>
+      <c r="L146" t="n">
+        <v>3</v>
+      </c>
+      <c r="M146" t="n">
+        <v>1</v>
+      </c>
+      <c r="N146" t="n">
+        <v>4</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>['14', '21', '45+2']</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R146" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S146" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="T146" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U146" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V146" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W146" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X146" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF146" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="BG146" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH146" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI146" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ146" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BK146" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL146" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM146" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN146" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO146" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BP146" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>8217486</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>45948.45833333334</v>
+      </c>
+      <c r="F147" t="n">
+        <v>13</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" t="n">
+        <v>1</v>
+      </c>
+      <c r="K147" t="n">
+        <v>2</v>
+      </c>
+      <c r="L147" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1</v>
+      </c>
+      <c r="N147" t="n">
+        <v>2</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="R147" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S147" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U147" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V147" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X147" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI147" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ147" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK147" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL147" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM147" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN147" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO147" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BP147" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>8217488</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>45948.45833333334</v>
+      </c>
+      <c r="F148" t="n">
+        <v>13</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="n">
+        <v>1</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R148" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S148" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T148" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U148" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V148" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W148" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X148" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BL148" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM148" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO148" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP148" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>8217489</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>45948.45833333334</v>
+      </c>
+      <c r="F149" t="n">
+        <v>13</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>2</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>2</v>
+      </c>
+      <c r="L149" t="n">
+        <v>3</v>
+      </c>
+      <c r="M149" t="n">
+        <v>1</v>
+      </c>
+      <c r="N149" t="n">
+        <v>4</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>['23', '41', '57']</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>['90+10']</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R149" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S149" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T149" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U149" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V149" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W149" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X149" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO149" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP149" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>8217490</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>45948.45833333334</v>
+      </c>
+      <c r="F150" t="n">
+        <v>13</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="R150" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S150" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T150" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U150" t="n">
+        <v>3</v>
+      </c>
+      <c r="V150" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W150" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X150" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF150" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG150" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH150" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BI150" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ150" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK150" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL150" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM150" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN150" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO150" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BP150" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>8217406</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>45948.45833333334</v>
+      </c>
+      <c r="F151" t="n">
+        <v>13</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>1</v>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R151" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S151" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T151" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U151" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V151" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W151" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X151" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH151" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="BI151" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ151" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BK151" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL151" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM151" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN151" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO151" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BP151" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="n">
+        <v>8217449</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>45948.45833333334</v>
+      </c>
+      <c r="F152" t="n">
+        <v>13</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>1</v>
+      </c>
+      <c r="K152" t="n">
+        <v>1</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>2</v>
+      </c>
+      <c r="N152" t="n">
+        <v>2</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>['20', '61']</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R152" t="n">
+        <v>2</v>
+      </c>
+      <c r="S152" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T152" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U152" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V152" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W152" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X152" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI152" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ152" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK152" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL152" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM152" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BN152" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO152" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BP152" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>8217468</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>45948.45833333334</v>
+      </c>
+      <c r="F153" t="n">
+        <v>13</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1</v>
+      </c>
+      <c r="L153" t="n">
+        <v>4</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
+        <v>4</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>['8', '72', '79', '90+3']</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R153" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S153" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T153" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U153" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V153" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W153" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X153" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG153" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH153" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="BI153" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ153" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK153" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BL153" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM153" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN153" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO153" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="BP153" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="n">
+        <v>8217521</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>45948.45833333334</v>
+      </c>
+      <c r="F154" t="n">
+        <v>13</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K154" t="n">
+        <v>1</v>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="n">
+        <v>2</v>
+      </c>
+      <c r="N154" t="n">
+        <v>3</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>['31', '68']</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R154" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S154" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T154" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U154" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V154" t="n">
+        <v>3</v>
+      </c>
+      <c r="W154" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X154" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BI154" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ154" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK154" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO154" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BP154" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="n">
+        <v>8217485</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>45948.45833333334</v>
+      </c>
+      <c r="F155" t="n">
+        <v>13</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>1</v>
+      </c>
+      <c r="K155" t="n">
+        <v>1</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="n">
+        <v>4</v>
+      </c>
+      <c r="N155" t="n">
+        <v>5</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>['33', '51', '73', '79']</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R155" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S155" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="T155" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U155" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V155" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W155" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X155" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BI155" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BK155" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO155" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP155" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -32536,22 +32536,22 @@
         <v>3.08</v>
       </c>
       <c r="AU147" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX147" t="n">
         <v>4</v>
       </c>
-      <c r="AV147" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW147" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX147" t="n">
-        <v>3</v>
-      </c>
       <c r="AY147" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ147" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA147" t="n">
         <v>9</v>
@@ -32754,19 +32754,19 @@
         <v>3.08</v>
       </c>
       <c r="AU148" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV148" t="n">
         <v>2</v>
       </c>
       <c r="AW148" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX148" t="n">
         <v>1</v>
       </c>
       <c r="AY148" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ148" t="n">
         <v>3</v>
@@ -33626,7 +33626,7 @@
         <v>2.01</v>
       </c>
       <c r="AU152" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV152" t="n">
         <v>4</v>
@@ -33638,7 +33638,7 @@
         <v>6</v>
       </c>
       <c r="AY152" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ152" t="n">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -32389,7 +32389,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>8217486</v>
+        <v>8217468</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -32409,197 +32409,197 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="I147" t="n">
         <v>1</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L147" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>['8', '72', '79', '90+3']</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q147" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R147" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S147" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U147" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V147" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X147" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD147" t="n">
         <v>2.27</v>
       </c>
-      <c r="R147" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S147" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T147" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="U147" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V147" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W147" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X147" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA147" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB147" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AC147" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD147" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE147" t="n">
+      <c r="BE147" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG147" t="n">
         <v>1.24</v>
       </c>
-      <c r="AF147" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AG147" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH147" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AI147" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AJ147" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK147" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AL147" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM147" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AN147" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AO147" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AP147" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AQ147" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AR147" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS147" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AT147" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AU147" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV147" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW147" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX147" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY147" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ147" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA147" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB147" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC147" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD147" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BE147" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF147" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG147" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BH147" t="n">
-        <v>3.52</v>
+        <v>3.37</v>
       </c>
       <c r="BI147" t="n">
         <v>1.46</v>
       </c>
       <c r="BJ147" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BK147" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="BL147" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="BM147" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="BN147" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="BO147" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="BP147" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="148">
@@ -32607,7 +32607,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>8217488</v>
+        <v>8217490</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -32627,12 +32627,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -32664,160 +32664,160 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="R148" t="n">
         <v>2.1</v>
       </c>
       <c r="S148" t="n">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="T148" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="U148" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="V148" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="W148" t="n">
         <v>1.4</v>
       </c>
       <c r="X148" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="Y148" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z148" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AA148" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AB148" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC148" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AD148" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="AE148" t="n">
         <v>1.25</v>
       </c>
       <c r="AF148" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="AG148" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AH148" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AI148" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AJ148" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AK148" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AL148" t="n">
         <v>1.28</v>
       </c>
       <c r="AM148" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AN148" t="n">
-        <v>1.67</v>
+        <v>0.83</v>
       </c>
       <c r="AO148" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.86</v>
+        <v>1.14</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.29</v>
+        <v>0.57</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AT148" t="n">
-        <v>3.08</v>
+        <v>2.28</v>
       </c>
       <c r="AU148" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW148" t="n">
         <v>9</v>
       </c>
-      <c r="AV148" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW148" t="n">
+      <c r="AX148" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ148" t="n">
         <v>15</v>
-      </c>
-      <c r="AX148" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY148" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ148" t="n">
-        <v>3</v>
       </c>
       <c r="BA148" t="n">
         <v>6</v>
       </c>
       <c r="BB148" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BC148" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD148" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BE148" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="BF148" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="BG148" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BH148" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="BI148" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="BJ148" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="BK148" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="BL148" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="BM148" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="BN148" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BO148" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="BP148" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="149">
@@ -33043,7 +33043,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>8217490</v>
+        <v>8217488</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -33063,12 +33063,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -33091,7 +33091,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -33100,160 +33100,160 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="R150" t="n">
         <v>2.1</v>
       </c>
       <c r="S150" t="n">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="T150" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="U150" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="V150" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="W150" t="n">
         <v>1.4</v>
       </c>
       <c r="X150" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="Y150" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z150" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AA150" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB150" t="n">
         <v>3.4</v>
       </c>
-      <c r="AB150" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AC150" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AD150" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="AE150" t="n">
         <v>1.25</v>
       </c>
       <c r="AF150" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="AG150" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AI150" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AJ150" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AK150" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AL150" t="n">
         <v>1.28</v>
       </c>
       <c r="AM150" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AN150" t="n">
-        <v>0.83</v>
+        <v>1.67</v>
       </c>
       <c r="AO150" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.57</v>
+        <v>1.29</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.23</v>
+        <v>1.87</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.28</v>
+        <v>3.08</v>
       </c>
       <c r="AU150" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AV150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ150" t="n">
         <v>3</v>
-      </c>
-      <c r="AW150" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX150" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY150" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ150" t="n">
-        <v>15</v>
       </c>
       <c r="BA150" t="n">
         <v>6</v>
       </c>
       <c r="BB150" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC150" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BD150" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BE150" t="n">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
       <c r="BF150" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="BG150" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BH150" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="BI150" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="BJ150" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="BK150" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="BL150" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="BM150" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="BN150" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BO150" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="BP150" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="151">
@@ -33261,7 +33261,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>8217406</v>
+        <v>8217486</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -33281,197 +33281,197 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
         <v>1</v>
       </c>
       <c r="N151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="R151" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="S151" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T151" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U151" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V151" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W151" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X151" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF151" t="n">
         <v>3.85</v>
       </c>
-      <c r="T151" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U151" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V151" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="W151" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X151" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Y151" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z151" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA151" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB151" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AC151" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AE151" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF151" t="n">
-        <v>3.76</v>
-      </c>
       <c r="AG151" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH151" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AI151" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AJ151" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AK151" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AL151" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AM151" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AN151" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO151" t="n">
         <v>1.17</v>
       </c>
-      <c r="AO151" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AP151" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="AT151" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="AU151" t="n">
         <v>5</v>
       </c>
       <c r="AV151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW151" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY151" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC151" t="n">
         <v>18</v>
       </c>
-      <c r="AZ151" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA151" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB151" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC151" t="n">
-        <v>14</v>
-      </c>
       <c r="BD151" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="BE151" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF151" t="n">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="BG151" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BH151" t="n">
-        <v>3.89</v>
+        <v>3.52</v>
       </c>
       <c r="BI151" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="BJ151" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BK151" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="BL151" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="BM151" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="BN151" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BO151" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="BP151" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="152">
@@ -33479,7 +33479,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>8217449</v>
+        <v>8217485</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -33499,12 +33499,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -33517,179 +33517,179 @@
         <v>1</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N152" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>['20', '61']</t>
+          <t>['33', '51', '73', '79']</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="R152" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S152" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="T152" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U152" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="V152" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="W152" t="n">
         <v>1.36</v>
       </c>
       <c r="X152" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="Y152" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z152" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AA152" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB152" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AC152" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AD152" t="n">
-        <v>7.9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF152" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AG152" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH152" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AI152" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AJ152" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AK152" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AL152" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AM152" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AN152" t="n">
-        <v>0.17</v>
+        <v>1.67</v>
       </c>
       <c r="AO152" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP152" t="n">
-        <v>0.14</v>
+        <v>1.43</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.71</v>
+        <v>1.33</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AS152" t="n">
-        <v>0.86</v>
+        <v>1.23</v>
       </c>
       <c r="AT152" t="n">
-        <v>2.01</v>
+        <v>2.47</v>
       </c>
       <c r="AU152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV152" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW152" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA152" t="n">
         <v>6</v>
       </c>
-      <c r="AX152" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY152" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ152" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA152" t="n">
-        <v>3</v>
-      </c>
       <c r="BB152" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC152" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BD152" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="BE152" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF152" t="n">
-        <v>2.07</v>
+        <v>2.64</v>
       </c>
       <c r="BG152" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BH152" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="BI152" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BJ152" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="BK152" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="BL152" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BM152" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="BN152" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BO152" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="BP152" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="153">
@@ -33697,7 +33697,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>8217468</v>
+        <v>8217406</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -33717,197 +33717,197 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N153" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>['8', '72', '79', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>3.95</v>
+        <v>2.55</v>
       </c>
       <c r="R153" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S153" t="n">
-        <v>2.62</v>
+        <v>3.85</v>
       </c>
       <c r="T153" t="n">
         <v>1.36</v>
       </c>
       <c r="U153" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V153" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="W153" t="n">
         <v>1.42</v>
       </c>
       <c r="X153" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="Y153" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z153" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA153" t="n">
         <v>3.5</v>
       </c>
-      <c r="AA153" t="n">
-        <v>3.69</v>
-      </c>
       <c r="AB153" t="n">
-        <v>1.95</v>
+        <v>3.35</v>
       </c>
       <c r="AC153" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AD153" t="n">
-        <v>9</v>
+        <v>10.4</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF153" t="n">
-        <v>3.34</v>
+        <v>3.76</v>
       </c>
       <c r="AG153" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AH153" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AI153" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AJ153" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AK153" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AL153" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AM153" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AN153" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AO153" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.71</v>
+        <v>1.17</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.59</v>
+        <v>1.87</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AT153" t="n">
-        <v>3.09</v>
+        <v>3.18</v>
       </c>
       <c r="AU153" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW153" t="n">
         <v>13</v>
       </c>
       <c r="AX153" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY153" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ153" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA153" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="BB153" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC153" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD153" t="n">
-        <v>2.27</v>
+        <v>1.49</v>
       </c>
       <c r="BE153" t="n">
-        <v>6.35</v>
+        <v>7</v>
       </c>
       <c r="BF153" t="n">
-        <v>2</v>
+        <v>3.14</v>
       </c>
       <c r="BG153" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="BH153" t="n">
-        <v>3.37</v>
+        <v>3.89</v>
       </c>
       <c r="BI153" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BJ153" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="BK153" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="BL153" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BM153" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="BN153" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="BO153" t="n">
-        <v>3.11</v>
+        <v>2.72</v>
       </c>
       <c r="BP153" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="154">
@@ -34133,7 +34133,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>8217485</v>
+        <v>8217449</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -34153,12 +34153,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="I155" t="n">
@@ -34171,179 +34171,179 @@
         <v>1</v>
       </c>
       <c r="L155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N155" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>['33', '51', '73', '79']</t>
+          <t>['20', '61']</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="R155" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S155" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="T155" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U155" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V155" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="W155" t="n">
         <v>1.36</v>
       </c>
       <c r="X155" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z155" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA155" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB155" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AD155" t="n">
-        <v>8.949999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF155" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="AG155" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AI155" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD155" t="n">
         <v>1.82</v>
       </c>
-      <c r="AJ155" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK155" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL155" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM155" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN155" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO155" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP155" t="n">
+      <c r="BE155" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI155" t="n">
         <v>1.43</v>
       </c>
-      <c r="AQ155" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR155" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AS155" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AT155" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AU155" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV155" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW155" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX155" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY155" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ155" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA155" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB155" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC155" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD155" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BE155" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF155" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BG155" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BH155" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="BI155" t="n">
-        <v>1.47</v>
-      </c>
       <c r="BJ155" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="BK155" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="BL155" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BM155" t="n">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="BN155" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="BO155" t="n">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="BP155" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -32103,16 +32103,16 @@
         <v>4</v>
       </c>
       <c r="AV145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW145" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX145" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY145" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ145" t="n">
         <v>11</v>
@@ -32775,10 +32775,10 @@
         <v>6</v>
       </c>
       <c r="BB148" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC148" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD148" t="n">
         <v>1.63</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -32389,7 +32389,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>8217468</v>
+        <v>8217486</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -32409,197 +32409,197 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="I147" t="n">
         <v>1</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L147" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1</v>
+      </c>
+      <c r="N147" t="n">
+        <v>2</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="R147" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S147" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U147" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V147" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X147" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU147" t="n">
         <v>4</v>
       </c>
-      <c r="M147" t="n">
-        <v>0</v>
-      </c>
-      <c r="N147" t="n">
+      <c r="AV147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX147" t="n">
         <v>4</v>
       </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>['8', '72', '79', '90+3']</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q147" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R147" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S147" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T147" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U147" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V147" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="W147" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X147" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA147" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="AB147" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC147" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD147" t="n">
+      <c r="AY147" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA147" t="n">
         <v>9</v>
       </c>
-      <c r="AE147" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF147" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AG147" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH147" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI147" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AJ147" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AK147" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AL147" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM147" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN147" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO147" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP147" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ147" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR147" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AS147" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AT147" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AU147" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV147" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW147" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX147" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY147" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ147" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA147" t="n">
-        <v>3</v>
-      </c>
       <c r="BB147" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BC147" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="BD147" t="n">
-        <v>2.27</v>
+        <v>1.35</v>
       </c>
       <c r="BE147" t="n">
-        <v>6.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF147" t="n">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="BG147" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BH147" t="n">
-        <v>3.37</v>
+        <v>3.52</v>
       </c>
       <c r="BI147" t="n">
         <v>1.46</v>
       </c>
       <c r="BJ147" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="BK147" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="BL147" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="BM147" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="BN147" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="BO147" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="BP147" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="148">
@@ -32607,7 +32607,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>8217490</v>
+        <v>8217488</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -32627,12 +32627,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -32664,160 +32664,160 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="R148" t="n">
         <v>2.1</v>
       </c>
       <c r="S148" t="n">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="T148" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="U148" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="V148" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="W148" t="n">
         <v>1.4</v>
       </c>
       <c r="X148" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="Y148" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z148" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AA148" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB148" t="n">
         <v>3.4</v>
       </c>
-      <c r="AB148" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AC148" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AD148" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="AE148" t="n">
         <v>1.25</v>
       </c>
       <c r="AF148" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="AG148" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AH148" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AI148" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AJ148" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AK148" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AL148" t="n">
         <v>1.28</v>
       </c>
       <c r="AM148" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AN148" t="n">
-        <v>0.83</v>
+        <v>1.67</v>
       </c>
       <c r="AO148" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="AQ148" t="n">
-        <v>0.57</v>
+        <v>1.29</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.23</v>
+        <v>1.87</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.28</v>
+        <v>3.08</v>
       </c>
       <c r="AU148" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AV148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ148" t="n">
         <v>3</v>
-      </c>
-      <c r="AW148" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX148" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY148" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ148" t="n">
-        <v>15</v>
       </c>
       <c r="BA148" t="n">
         <v>6</v>
       </c>
       <c r="BB148" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC148" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BD148" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BE148" t="n">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
       <c r="BF148" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="BG148" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BH148" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="BI148" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="BJ148" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="BK148" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="BL148" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="BM148" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="BN148" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BO148" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="BP148" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="149">
@@ -32978,13 +32978,13 @@
         <v>2</v>
       </c>
       <c r="AW149" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX149" t="n">
         <v>8</v>
       </c>
       <c r="AY149" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ149" t="n">
         <v>10</v>
@@ -33043,7 +33043,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>8217488</v>
+        <v>8217490</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -33063,12 +33063,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -33091,7 +33091,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -33100,160 +33100,160 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="R150" t="n">
         <v>2.1</v>
       </c>
       <c r="S150" t="n">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="T150" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="U150" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="V150" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="W150" t="n">
         <v>1.4</v>
       </c>
       <c r="X150" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="Y150" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z150" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AA150" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AB150" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC150" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AD150" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="AE150" t="n">
         <v>1.25</v>
       </c>
       <c r="AF150" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="AG150" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AI150" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AJ150" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AK150" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AL150" t="n">
         <v>1.28</v>
       </c>
       <c r="AM150" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AN150" t="n">
-        <v>1.67</v>
+        <v>0.83</v>
       </c>
       <c r="AO150" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.86</v>
+        <v>1.14</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.29</v>
+        <v>0.57</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AT150" t="n">
-        <v>3.08</v>
+        <v>2.28</v>
       </c>
       <c r="AU150" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW150" t="n">
         <v>9</v>
       </c>
-      <c r="AV150" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW150" t="n">
+      <c r="AX150" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ150" t="n">
         <v>15</v>
-      </c>
-      <c r="AX150" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY150" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ150" t="n">
-        <v>3</v>
       </c>
       <c r="BA150" t="n">
         <v>6</v>
       </c>
       <c r="BB150" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BC150" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BD150" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BE150" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="BF150" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="BG150" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BH150" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="BI150" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="BJ150" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="BK150" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="BL150" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="BM150" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="BN150" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BO150" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="BP150" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="151">
@@ -33261,7 +33261,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>8217486</v>
+        <v>8217406</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -33281,197 +33281,197 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
         <v>1</v>
       </c>
       <c r="N151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="R151" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S151" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T151" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U151" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V151" t="n">
         <v>2.38</v>
       </c>
-      <c r="S151" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T151" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="U151" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V151" t="n">
-        <v>2.5</v>
-      </c>
       <c r="W151" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X151" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="Y151" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z151" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AA151" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AB151" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="AC151" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AD151" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF151" t="n">
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
       <c r="AG151" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH151" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AI151" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AJ151" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AK151" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL151" t="n">
         <v>1.2</v>
       </c>
-      <c r="AL151" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AM151" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AN151" t="n">
-        <v>2.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO151" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ151" t="n">
         <v>1.17</v>
       </c>
-      <c r="AP151" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AQ151" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AR151" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="AT151" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="AU151" t="n">
         <v>5</v>
       </c>
       <c r="AV151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW151" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ151" t="n">
         <v>4</v>
       </c>
-      <c r="AY151" t="n">
+      <c r="BA151" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC151" t="n">
         <v>14</v>
       </c>
-      <c r="AZ151" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA151" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB151" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC151" t="n">
-        <v>18</v>
-      </c>
       <c r="BD151" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="BE151" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BF151" t="n">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="BG151" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BH151" t="n">
-        <v>3.52</v>
+        <v>3.89</v>
       </c>
       <c r="BI151" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BJ151" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BK151" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="BL151" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="BM151" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="BN151" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BO151" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="BP151" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="152">
@@ -33479,7 +33479,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>8217485</v>
+        <v>8217449</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -33499,12 +33499,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -33517,179 +33517,179 @@
         <v>1</v>
       </c>
       <c r="L152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N152" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>['33', '51', '73', '79']</t>
+          <t>['20', '61']</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="R152" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S152" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="T152" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U152" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V152" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="W152" t="n">
         <v>1.36</v>
       </c>
       <c r="X152" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="Y152" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z152" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA152" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB152" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AC152" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AD152" t="n">
-        <v>8.949999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF152" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="AG152" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH152" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AI152" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD152" t="n">
         <v>1.82</v>
       </c>
-      <c r="AJ152" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK152" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL152" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM152" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN152" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO152" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP152" t="n">
+      <c r="BE152" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI152" t="n">
         <v>1.43</v>
       </c>
-      <c r="AQ152" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR152" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AS152" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AT152" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AU152" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV152" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW152" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX152" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY152" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ152" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA152" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB152" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC152" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD152" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BE152" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF152" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BG152" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BH152" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="BI152" t="n">
-        <v>1.47</v>
-      </c>
       <c r="BJ152" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="BK152" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="BL152" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BM152" t="n">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="BN152" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="BO152" t="n">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="BP152" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="153">
@@ -33697,7 +33697,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>8217406</v>
+        <v>8217468</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -33717,197 +33717,197 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
+          <t>['8', '72', '79', '90+3']</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
       <c r="Q153" t="n">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="R153" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S153" t="n">
-        <v>3.85</v>
+        <v>2.62</v>
       </c>
       <c r="T153" t="n">
         <v>1.36</v>
       </c>
       <c r="U153" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V153" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="W153" t="n">
         <v>1.42</v>
       </c>
       <c r="X153" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="Y153" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z153" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA153" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="AB153" t="n">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC153" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AD153" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF153" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="AG153" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AH153" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AI153" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AJ153" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AK153" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AL153" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AM153" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ153" t="n">
         <v>1.71</v>
       </c>
-      <c r="AN153" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO153" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP153" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ153" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AR153" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AT153" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="AU153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW153" t="n">
         <v>13</v>
       </c>
       <c r="AX153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA153" t="n">
         <v>3</v>
       </c>
-      <c r="AY153" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ153" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA153" t="n">
-        <v>12</v>
-      </c>
       <c r="BB153" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BC153" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BD153" t="n">
-        <v>1.49</v>
+        <v>2.27</v>
       </c>
       <c r="BE153" t="n">
-        <v>7</v>
+        <v>6.35</v>
       </c>
       <c r="BF153" t="n">
-        <v>3.14</v>
+        <v>2</v>
       </c>
       <c r="BG153" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BH153" t="n">
-        <v>3.89</v>
+        <v>3.37</v>
       </c>
       <c r="BI153" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="BJ153" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="BK153" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="BL153" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BM153" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="BN153" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="BO153" t="n">
-        <v>2.72</v>
+        <v>3.11</v>
       </c>
       <c r="BP153" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="154">
@@ -34133,7 +34133,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>8217449</v>
+        <v>8217485</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -34153,12 +34153,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="I155" t="n">
@@ -34171,179 +34171,179 @@
         <v>1</v>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N155" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>['20', '61']</t>
+          <t>['33', '51', '73', '79']</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="R155" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S155" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="T155" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U155" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="V155" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="W155" t="n">
         <v>1.36</v>
       </c>
       <c r="X155" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z155" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AA155" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB155" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AD155" t="n">
-        <v>7.9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF155" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AG155" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AI155" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AJ155" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AK155" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AL155" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AM155" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AN155" t="n">
-        <v>0.17</v>
+        <v>1.67</v>
       </c>
       <c r="AO155" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP155" t="n">
-        <v>0.14</v>
+        <v>1.43</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.71</v>
+        <v>1.33</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AS155" t="n">
-        <v>0.86</v>
+        <v>1.23</v>
       </c>
       <c r="AT155" t="n">
-        <v>2.01</v>
+        <v>2.47</v>
       </c>
       <c r="AU155" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV155" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW155" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA155" t="n">
         <v>6</v>
       </c>
-      <c r="AX155" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY155" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ155" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA155" t="n">
-        <v>3</v>
-      </c>
       <c r="BB155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC155" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BD155" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="BE155" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF155" t="n">
-        <v>2.07</v>
+        <v>2.64</v>
       </c>
       <c r="BG155" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BH155" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="BI155" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BJ155" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="BK155" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="BL155" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BM155" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="BN155" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BO155" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="BP155" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -32760,13 +32760,13 @@
         <v>2</v>
       </c>
       <c r="AW148" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX148" t="n">
         <v>1</v>
       </c>
       <c r="AY148" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ148" t="n">
         <v>3</v>
@@ -34071,13 +34071,13 @@
         <v>13</v>
       </c>
       <c r="AX154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY154" t="n">
         <v>24</v>
       </c>
       <c r="AZ154" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA154" t="n">
         <v>14</v>
@@ -34289,13 +34289,13 @@
         <v>10</v>
       </c>
       <c r="AX155" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY155" t="n">
         <v>12</v>
       </c>
       <c r="AZ155" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA155" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP155"/>
+  <dimension ref="A1:BP156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2222,7 +2222,7 @@
         <v>0.14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.83</v>
@@ -7236,7 +7236,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR31" t="n">
         <v>0.89</v>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ43" t="n">
         <v>2.17</v>
@@ -12465,7 +12465,7 @@
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.67</v>
@@ -14866,7 +14866,7 @@
         <v>1</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR66" t="n">
         <v>1.37</v>
@@ -19441,7 +19441,7 @@
         <v>1.33</v>
       </c>
       <c r="AP87" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ87" t="n">
         <v>1</v>
@@ -20316,7 +20316,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR91" t="n">
         <v>1.43</v>
@@ -24458,7 +24458,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR110" t="n">
         <v>1.39</v>
@@ -26635,7 +26635,7 @@
         <v>1.25</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.14</v>
@@ -33396,7 +33396,7 @@
         <v>1</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR151" t="n">
         <v>1.87</v>
@@ -34344,6 +34344,224 @@
       </c>
       <c r="BP155" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>8217484</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>45951.65625</v>
+      </c>
+      <c r="F156" t="n">
+        <v>12</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" t="n">
+        <v>1</v>
+      </c>
+      <c r="K156" t="n">
+        <v>2</v>
+      </c>
+      <c r="L156" t="n">
+        <v>2</v>
+      </c>
+      <c r="M156" t="n">
+        <v>2</v>
+      </c>
+      <c r="N156" t="n">
+        <v>4</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>['19', '78']</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>['3', '62']</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R156" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S156" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="T156" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U156" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V156" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="W156" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X156" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="BI156" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ156" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK156" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO156" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BP156" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -34399,7 +34399,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>['19', '78']</t>
+          <t>['19', '77']</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP156"/>
+  <dimension ref="A1:BP168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3963,10 +3963,10 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4181,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4617,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5053,10 +5053,10 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5271,10 +5271,10 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -5489,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -5710,7 +5710,7 @@
         <v>1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -5925,10 +5925,10 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -6146,7 +6146,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR26" t="n">
         <v>1.04</v>
@@ -6582,7 +6582,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR28" t="n">
         <v>1.35</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.57</v>
@@ -7233,7 +7233,7 @@
         <v>1</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.14</v>
@@ -7672,7 +7672,7 @@
         <v>1</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR33" t="n">
         <v>2.2</v>
@@ -7890,7 +7890,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR34" t="n">
         <v>0.89</v>
@@ -8108,7 +8108,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR35" t="n">
         <v>2.14</v>
@@ -8541,7 +8541,7 @@
         <v>3</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.14</v>
@@ -8762,7 +8762,7 @@
         <v>0.14</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR38" t="n">
         <v>0.62</v>
@@ -8977,10 +8977,10 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ39" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR39" t="n">
         <v>1.87</v>
@@ -9195,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.43</v>
@@ -9413,10 +9413,10 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR41" t="n">
         <v>0.96</v>
@@ -9634,7 +9634,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR42" t="n">
         <v>1.11</v>
@@ -9849,10 +9849,10 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR43" t="n">
         <v>1.16</v>
@@ -10067,7 +10067,7 @@
         <v>3</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.43</v>
@@ -10503,7 +10503,7 @@
         <v>1</v>
       </c>
       <c r="AP46" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.14</v>
@@ -10724,7 +10724,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR47" t="n">
         <v>0.87</v>
@@ -10939,10 +10939,10 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AR48" t="n">
         <v>1.01</v>
@@ -11160,7 +11160,7 @@
         <v>0.14</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR49" t="n">
         <v>0.84</v>
@@ -11378,7 +11378,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR50" t="n">
         <v>1.11</v>
@@ -11593,7 +11593,7 @@
         <v>1</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.33</v>
@@ -11811,10 +11811,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ52" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR52" t="n">
         <v>1.18</v>
@@ -12032,7 +12032,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR53" t="n">
         <v>1.14</v>
@@ -12250,7 +12250,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR54" t="n">
         <v>1.64</v>
@@ -12465,10 +12465,10 @@
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AR55" t="n">
         <v>1.03</v>
@@ -12683,10 +12683,10 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR56" t="n">
         <v>1.53</v>
@@ -12901,7 +12901,7 @@
         <v>3</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.43</v>
@@ -13337,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.29</v>
@@ -13555,7 +13555,7 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.14</v>
@@ -13991,7 +13991,7 @@
         <v>1.5</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.71</v>
@@ -14209,7 +14209,7 @@
         <v>2</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.14</v>
@@ -14430,7 +14430,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR64" t="n">
         <v>2.16</v>
@@ -14648,7 +14648,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR65" t="n">
         <v>0.93</v>
@@ -15302,7 +15302,7 @@
         <v>1</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR68" t="n">
         <v>1.75</v>
@@ -15735,7 +15735,7 @@
         <v>2</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ70" t="n">
         <v>1</v>
@@ -15956,7 +15956,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR71" t="n">
         <v>1.75</v>
@@ -16174,7 +16174,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR72" t="n">
         <v>1.28</v>
@@ -16392,7 +16392,7 @@
         <v>0.14</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR73" t="n">
         <v>0.97</v>
@@ -16607,7 +16607,7 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.71</v>
@@ -17261,7 +17261,7 @@
         <v>2.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.14</v>
@@ -17700,7 +17700,7 @@
         <v>1</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AR79" t="n">
         <v>1.83</v>
@@ -17915,10 +17915,10 @@
         <v>0.33</v>
       </c>
       <c r="AP80" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR80" t="n">
         <v>1.16</v>
@@ -18136,7 +18136,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR81" t="n">
         <v>1.5</v>
@@ -18354,7 +18354,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR82" t="n">
         <v>1.37</v>
@@ -18569,7 +18569,7 @@
         <v>0.33</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.57</v>
@@ -18787,7 +18787,7 @@
         <v>1.67</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.29</v>
@@ -19005,7 +19005,7 @@
         <v>0.33</v>
       </c>
       <c r="AP85" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.71</v>
@@ -19226,7 +19226,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR86" t="n">
         <v>1.21</v>
@@ -19441,7 +19441,7 @@
         <v>1.33</v>
       </c>
       <c r="AP87" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ87" t="n">
         <v>1</v>
@@ -20095,10 +20095,10 @@
         <v>2</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ90" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR90" t="n">
         <v>1.36</v>
@@ -20313,7 +20313,7 @@
         <v>1.33</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.14</v>
@@ -20534,7 +20534,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR92" t="n">
         <v>1.23</v>
@@ -20752,7 +20752,7 @@
         <v>1</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR93" t="n">
         <v>1.39</v>
@@ -20967,10 +20967,10 @@
         <v>2</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR94" t="n">
         <v>1.13</v>
@@ -21188,7 +21188,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ95" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR95" t="n">
         <v>1.58</v>
@@ -21406,7 +21406,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR96" t="n">
         <v>1.92</v>
@@ -21621,10 +21621,10 @@
         <v>0.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AR97" t="n">
         <v>1.6</v>
@@ -22060,7 +22060,7 @@
         <v>1</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR99" t="n">
         <v>1.84</v>
@@ -22275,7 +22275,7 @@
         <v>1</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.57</v>
@@ -22493,7 +22493,7 @@
         <v>1.5</v>
       </c>
       <c r="AP101" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.29</v>
@@ -22929,7 +22929,7 @@
         <v>1.75</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.43</v>
@@ -23150,7 +23150,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR104" t="n">
         <v>1.61</v>
@@ -23583,10 +23583,10 @@
         <v>1.5</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR106" t="n">
         <v>1.73</v>
@@ -23804,7 +23804,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR107" t="n">
         <v>1.35</v>
@@ -24240,7 +24240,7 @@
         <v>1</v>
       </c>
       <c r="AQ109" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR109" t="n">
         <v>1.78</v>
@@ -24455,7 +24455,7 @@
         <v>1</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.14</v>
@@ -24676,7 +24676,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR111" t="n">
         <v>1.52</v>
@@ -24894,7 +24894,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR112" t="n">
         <v>1.35</v>
@@ -25112,7 +25112,7 @@
         <v>1</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR113" t="n">
         <v>1.51</v>
@@ -25330,7 +25330,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR114" t="n">
         <v>1.43</v>
@@ -25548,7 +25548,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR115" t="n">
         <v>1.5</v>
@@ -25763,10 +25763,10 @@
         <v>1.25</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR116" t="n">
         <v>1.08</v>
@@ -26199,7 +26199,7 @@
         <v>1</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ118" t="n">
         <v>1</v>
@@ -26417,7 +26417,7 @@
         <v>0.75</v>
       </c>
       <c r="AP119" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.43</v>
@@ -26635,7 +26635,7 @@
         <v>1.25</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.14</v>
@@ -27292,7 +27292,7 @@
         <v>1</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR123" t="n">
         <v>1.91</v>
@@ -27510,7 +27510,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR124" t="n">
         <v>1.56</v>
@@ -27725,7 +27725,7 @@
         <v>1.8</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.29</v>
@@ -28164,7 +28164,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR127" t="n">
         <v>1.34</v>
@@ -28382,7 +28382,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR128" t="n">
         <v>1.94</v>
@@ -28597,10 +28597,10 @@
         <v>0.6</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AR129" t="n">
         <v>1.13</v>
@@ -28815,7 +28815,7 @@
         <v>1</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.33</v>
@@ -29033,7 +29033,7 @@
         <v>1.4</v>
       </c>
       <c r="AP131" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.14</v>
@@ -29251,7 +29251,7 @@
         <v>1.4</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.43</v>
@@ -29472,7 +29472,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR133" t="n">
         <v>2.04</v>
@@ -29687,7 +29687,7 @@
         <v>0.2</v>
       </c>
       <c r="AP134" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.71</v>
@@ -29905,7 +29905,7 @@
         <v>1.4</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ135" t="n">
         <v>1</v>
@@ -30126,7 +30126,7 @@
         <v>1</v>
       </c>
       <c r="AQ136" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR136" t="n">
         <v>1.32</v>
@@ -30344,7 +30344,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR137" t="n">
         <v>1.34</v>
@@ -30559,7 +30559,7 @@
         <v>1</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.14</v>
@@ -30777,10 +30777,10 @@
         <v>2</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR139" t="n">
         <v>1.9</v>
@@ -30998,7 +30998,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR140" t="n">
         <v>1.65</v>
@@ -31216,7 +31216,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR141" t="n">
         <v>1.53</v>
@@ -31434,7 +31434,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ142" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR142" t="n">
         <v>1.33</v>
@@ -32389,7 +32389,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>8217486</v>
+        <v>8217521</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -32409,113 +32409,113 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
         <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L147" t="n">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['31', '68']</t>
         </is>
       </c>
       <c r="Q147" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R147" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S147" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U147" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V147" t="n">
+        <v>3</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X147" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG147" t="n">
         <v>2.27</v>
       </c>
-      <c r="R147" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S147" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T147" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="U147" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V147" t="n">
+      <c r="AH147" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN147" t="n">
         <v>2.5</v>
-      </c>
-      <c r="W147" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X147" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA147" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB147" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AC147" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD147" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE147" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF147" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AG147" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH147" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AI147" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AJ147" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK147" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AL147" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM147" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AN147" t="n">
-        <v>2.33</v>
       </c>
       <c r="AO147" t="n">
         <v>1.17</v>
@@ -32524,82 +32524,82 @@
         <v>2.14</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="AT147" t="n">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="AU147" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AV147" t="n">
         <v>2</v>
       </c>
       <c r="AW147" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX147" t="n">
         <v>4</v>
       </c>
       <c r="AY147" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AZ147" t="n">
         <v>6</v>
       </c>
       <c r="BA147" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BB147" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BC147" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BD147" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="BE147" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="BF147" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BG147" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BH147" t="n">
-        <v>3.52</v>
+        <v>3.92</v>
       </c>
       <c r="BI147" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BJ147" t="n">
         <v>2.7</v>
       </c>
       <c r="BK147" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BL147" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="BM147" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="BN147" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="BO147" t="n">
-        <v>2.98</v>
+        <v>2.71</v>
       </c>
       <c r="BP147" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="148">
@@ -32607,7 +32607,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>8217488</v>
+        <v>8217490</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -32627,12 +32627,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -32664,160 +32664,160 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="R148" t="n">
         <v>2.1</v>
       </c>
       <c r="S148" t="n">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="T148" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="U148" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="V148" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="W148" t="n">
         <v>1.4</v>
       </c>
       <c r="X148" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="Y148" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z148" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AA148" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AB148" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC148" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AD148" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="AE148" t="n">
         <v>1.25</v>
       </c>
       <c r="AF148" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="AG148" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AH148" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AI148" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AJ148" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AK148" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AL148" t="n">
         <v>1.28</v>
       </c>
       <c r="AM148" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AN148" t="n">
-        <v>1.67</v>
+        <v>0.83</v>
       </c>
       <c r="AO148" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.86</v>
+        <v>1.14</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.29</v>
+        <v>0.57</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AT148" t="n">
-        <v>3.08</v>
+        <v>2.28</v>
       </c>
       <c r="AU148" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW148" t="n">
         <v>9</v>
       </c>
-      <c r="AV148" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW148" t="n">
-        <v>16</v>
-      </c>
       <c r="AX148" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AY148" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AZ148" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="BA148" t="n">
         <v>6</v>
       </c>
       <c r="BB148" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BC148" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BD148" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BE148" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="BF148" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="BG148" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BH148" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="BI148" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="BJ148" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="BK148" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="BL148" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="BM148" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="BN148" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BO148" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="BP148" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="149">
@@ -33043,7 +33043,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>8217490</v>
+        <v>8217488</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -33063,12 +33063,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -33091,7 +33091,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -33100,160 +33100,160 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="R150" t="n">
         <v>2.1</v>
       </c>
       <c r="S150" t="n">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="T150" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="U150" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="V150" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="W150" t="n">
         <v>1.4</v>
       </c>
       <c r="X150" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="Y150" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z150" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AA150" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB150" t="n">
         <v>3.4</v>
       </c>
-      <c r="AB150" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AC150" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AD150" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="AE150" t="n">
         <v>1.25</v>
       </c>
       <c r="AF150" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="AG150" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AI150" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AJ150" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AK150" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AL150" t="n">
         <v>1.28</v>
       </c>
       <c r="AM150" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AN150" t="n">
-        <v>0.83</v>
+        <v>1.67</v>
       </c>
       <c r="AO150" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.57</v>
+        <v>1.29</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.23</v>
+        <v>1.87</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.28</v>
+        <v>3.08</v>
       </c>
       <c r="AU150" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AV150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ150" t="n">
         <v>3</v>
-      </c>
-      <c r="AW150" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX150" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY150" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ150" t="n">
-        <v>15</v>
       </c>
       <c r="BA150" t="n">
         <v>6</v>
       </c>
       <c r="BB150" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC150" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BD150" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BE150" t="n">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
       <c r="BF150" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="BG150" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BH150" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="BI150" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="BJ150" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="BK150" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="BL150" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="BM150" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="BN150" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BO150" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="BP150" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="151">
@@ -33261,7 +33261,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>8217406</v>
+        <v>8217468</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -33281,197 +33281,197 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
+          <t>['8', '72', '79', '90+3']</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
       <c r="Q151" t="n">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="R151" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S151" t="n">
-        <v>3.85</v>
+        <v>2.62</v>
       </c>
       <c r="T151" t="n">
         <v>1.36</v>
       </c>
       <c r="U151" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V151" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="W151" t="n">
         <v>1.42</v>
       </c>
       <c r="X151" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="Y151" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z151" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA151" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="AB151" t="n">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC151" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AD151" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF151" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="AG151" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AH151" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AI151" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AJ151" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AK151" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AL151" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AM151" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ151" t="n">
         <v>1.71</v>
       </c>
-      <c r="AN151" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO151" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP151" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ151" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AR151" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AT151" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="AU151" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW151" t="n">
         <v>13</v>
       </c>
       <c r="AX151" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA151" t="n">
         <v>3</v>
       </c>
-      <c r="AY151" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ151" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA151" t="n">
-        <v>12</v>
-      </c>
       <c r="BB151" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BC151" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BD151" t="n">
-        <v>1.49</v>
+        <v>2.27</v>
       </c>
       <c r="BE151" t="n">
-        <v>7</v>
+        <v>6.35</v>
       </c>
       <c r="BF151" t="n">
-        <v>3.14</v>
+        <v>2</v>
       </c>
       <c r="BG151" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BH151" t="n">
-        <v>3.89</v>
+        <v>3.37</v>
       </c>
       <c r="BI151" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="BJ151" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="BK151" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="BL151" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BM151" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="BN151" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="BO151" t="n">
-        <v>2.72</v>
+        <v>3.11</v>
       </c>
       <c r="BP151" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="152">
@@ -33479,7 +33479,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>8217449</v>
+        <v>8217486</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -33499,197 +33499,197 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>1</v>
       </c>
       <c r="K152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N152" t="n">
         <v>2</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>['20', '61']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="R152" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="S152" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="T152" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="U152" t="n">
-        <v>2.83</v>
+        <v>3.22</v>
       </c>
       <c r="V152" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="W152" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X152" t="n">
-        <v>6.9</v>
+        <v>5.5</v>
       </c>
       <c r="Y152" t="n">
         <v>1.07</v>
       </c>
       <c r="Z152" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AA152" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AB152" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AC152" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AD152" t="n">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AF152" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="AG152" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AH152" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI152" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ152" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK152" t="n">
         <v>1.74</v>
-      </c>
-      <c r="AI152" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AJ152" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AK152" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL152" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM152" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AN152" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AO152" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AP152" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AQ152" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AR152" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AS152" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AT152" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AU152" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV152" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW152" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX152" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY152" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ152" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA152" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB152" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC152" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD152" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BE152" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF152" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BG152" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BH152" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI152" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BJ152" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BK152" t="n">
-        <v>1.8</v>
       </c>
       <c r="BL152" t="n">
         <v>1.95</v>
       </c>
       <c r="BM152" t="n">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="BN152" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="BO152" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="BP152" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="153">
@@ -33697,7 +33697,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>8217468</v>
+        <v>8217406</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -33717,197 +33717,197 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N153" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>['8', '72', '79', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>3.95</v>
+        <v>2.55</v>
       </c>
       <c r="R153" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S153" t="n">
-        <v>2.62</v>
+        <v>3.85</v>
       </c>
       <c r="T153" t="n">
         <v>1.36</v>
       </c>
       <c r="U153" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V153" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="W153" t="n">
         <v>1.42</v>
       </c>
       <c r="X153" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="Y153" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z153" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA153" t="n">
         <v>3.5</v>
       </c>
-      <c r="AA153" t="n">
-        <v>3.69</v>
-      </c>
       <c r="AB153" t="n">
-        <v>1.95</v>
+        <v>3.35</v>
       </c>
       <c r="AC153" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AD153" t="n">
-        <v>9</v>
+        <v>10.4</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF153" t="n">
-        <v>3.34</v>
+        <v>3.76</v>
       </c>
       <c r="AG153" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AH153" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AI153" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AJ153" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AK153" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AL153" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AM153" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AN153" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AO153" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.71</v>
+        <v>1.14</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.59</v>
+        <v>1.87</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AT153" t="n">
-        <v>3.09</v>
+        <v>3.18</v>
       </c>
       <c r="AU153" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW153" t="n">
         <v>13</v>
       </c>
       <c r="AX153" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY153" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ153" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA153" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="BB153" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC153" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD153" t="n">
-        <v>2.27</v>
+        <v>1.49</v>
       </c>
       <c r="BE153" t="n">
-        <v>6.35</v>
+        <v>7</v>
       </c>
       <c r="BF153" t="n">
-        <v>2</v>
+        <v>3.14</v>
       </c>
       <c r="BG153" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="BH153" t="n">
-        <v>3.37</v>
+        <v>3.89</v>
       </c>
       <c r="BI153" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BJ153" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="BK153" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="BL153" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BM153" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="BN153" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="BO153" t="n">
-        <v>3.11</v>
+        <v>2.72</v>
       </c>
       <c r="BP153" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="154">
@@ -33915,7 +33915,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>8217521</v>
+        <v>8217485</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -33935,12 +33935,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="I154" t="n">
@@ -33956,176 +33956,176 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N154" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>['31', '68']</t>
+          <t>['33', '51', '73', '79']</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="R154" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="S154" t="n">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="T154" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="U154" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="V154" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="W154" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="X154" t="n">
-        <v>6.75</v>
+        <v>7.3</v>
       </c>
       <c r="Y154" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Z154" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AA154" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AB154" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AC154" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AD154" t="n">
-        <v>8</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AE154" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AF154" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="AG154" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="AH154" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AI154" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AJ154" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AK154" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AL154" t="n">
         <v>1.25</v>
       </c>
       <c r="AM154" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AN154" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO154" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.14</v>
+        <v>1.43</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AT154" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="AU154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC154" t="n">
         <v>11</v>
       </c>
-      <c r="AV154" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW154" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX154" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY154" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ154" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA154" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB154" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC154" t="n">
-        <v>14</v>
-      </c>
       <c r="BD154" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="BE154" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="BF154" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="BG154" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BH154" t="n">
-        <v>3.92</v>
+        <v>3.56</v>
       </c>
       <c r="BI154" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BJ154" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="BK154" t="n">
-        <v>1.73</v>
+        <v>1.99</v>
       </c>
       <c r="BL154" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="BM154" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="BN154" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BO154" t="n">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="BP154" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="155">
@@ -34133,7 +34133,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>8217485</v>
+        <v>8217449</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -34153,12 +34153,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="I155" t="n">
@@ -34171,179 +34171,179 @@
         <v>1</v>
       </c>
       <c r="L155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N155" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>['33', '51', '73', '79']</t>
+          <t>['20', '61']</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="R155" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S155" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="T155" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U155" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V155" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="W155" t="n">
         <v>1.36</v>
       </c>
       <c r="X155" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z155" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA155" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB155" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AD155" t="n">
-        <v>8.949999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF155" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="AG155" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AI155" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD155" t="n">
         <v>1.82</v>
       </c>
-      <c r="AJ155" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK155" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL155" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM155" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN155" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO155" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP155" t="n">
+      <c r="BE155" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI155" t="n">
         <v>1.43</v>
       </c>
-      <c r="AQ155" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR155" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AS155" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AT155" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AU155" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV155" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW155" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX155" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY155" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ155" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA155" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB155" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC155" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD155" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BE155" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF155" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BG155" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BH155" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="BI155" t="n">
-        <v>1.47</v>
-      </c>
       <c r="BJ155" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="BK155" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="BL155" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BM155" t="n">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="BN155" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="BO155" t="n">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="BP155" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="156">
@@ -34483,7 +34483,7 @@
         <v>1.17</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.14</v>
@@ -34562,6 +34562,2622 @@
       </c>
       <c r="BP156" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>8217266</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>45955.35416666666</v>
+      </c>
+      <c r="F157" t="n">
+        <v>14</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>1</v>
+      </c>
+      <c r="K157" t="n">
+        <v>1</v>
+      </c>
+      <c r="L157" t="n">
+        <v>2</v>
+      </c>
+      <c r="M157" t="n">
+        <v>1</v>
+      </c>
+      <c r="N157" t="n">
+        <v>3</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>['65', '71']</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R157" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S157" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="T157" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U157" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V157" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W157" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X157" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO157" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP157" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>8217551</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>45955.35416666666</v>
+      </c>
+      <c r="F158" t="n">
+        <v>14</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>1</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="R158" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S158" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T158" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U158" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V158" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W158" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X158" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BG158" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH158" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI158" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK158" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL158" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM158" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BN158" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO158" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP158" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>8217491</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>45955.45833333334</v>
+      </c>
+      <c r="F159" t="n">
+        <v>14</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>1</v>
+      </c>
+      <c r="K159" t="n">
+        <v>1</v>
+      </c>
+      <c r="L159" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" t="n">
+        <v>1</v>
+      </c>
+      <c r="N159" t="n">
+        <v>2</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R159" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S159" t="n">
+        <v>3</v>
+      </c>
+      <c r="T159" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U159" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V159" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W159" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X159" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO159" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP159" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>8217469</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>45955.45833333334</v>
+      </c>
+      <c r="F160" t="n">
+        <v>14</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>1</v>
+      </c>
+      <c r="L160" t="n">
+        <v>4</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>4</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>['45+9', '52', '69', '86']</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R160" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S160" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U160" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V160" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W160" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X160" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>8217522</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>45955.45833333334</v>
+      </c>
+      <c r="F161" t="n">
+        <v>14</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L161" t="n">
+        <v>2</v>
+      </c>
+      <c r="M161" t="n">
+        <v>2</v>
+      </c>
+      <c r="N161" t="n">
+        <v>4</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>['10', '68']</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>['51', '60']</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="R161" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S161" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T161" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W161" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X161" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO161" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP161" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>8217535</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>45955.45833333334</v>
+      </c>
+      <c r="F162" t="n">
+        <v>14</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1</v>
+      </c>
+      <c r="L162" t="n">
+        <v>2</v>
+      </c>
+      <c r="M162" t="n">
+        <v>1</v>
+      </c>
+      <c r="N162" t="n">
+        <v>3</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>['73', '81']</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R162" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S162" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="T162" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U162" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V162" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="W162" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X162" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO162" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BP162" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>8217536</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>45955.45833333334</v>
+      </c>
+      <c r="F163" t="n">
+        <v>14</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>2</v>
+      </c>
+      <c r="J163" t="n">
+        <v>2</v>
+      </c>
+      <c r="K163" t="n">
+        <v>4</v>
+      </c>
+      <c r="L163" t="n">
+        <v>3</v>
+      </c>
+      <c r="M163" t="n">
+        <v>2</v>
+      </c>
+      <c r="N163" t="n">
+        <v>5</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>['27', '37', '87']</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>['6', '45+1']</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R163" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S163" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T163" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U163" t="n">
+        <v>3</v>
+      </c>
+      <c r="V163" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="W163" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X163" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN163" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO163" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BP163" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>8217537</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>45955.45833333334</v>
+      </c>
+      <c r="F164" t="n">
+        <v>14</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>1</v>
+      </c>
+      <c r="K164" t="n">
+        <v>1</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>3</v>
+      </c>
+      <c r="N164" t="n">
+        <v>3</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>['12', '49', '51']</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S164" t="n">
+        <v>4</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U164" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V164" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W164" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X164" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO164" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BP164" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>8217538</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>45955.45833333334</v>
+      </c>
+      <c r="F165" t="n">
+        <v>14</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>2</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>2</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>['72', '90']</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>3</v>
+      </c>
+      <c r="R165" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S165" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U165" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V165" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W165" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X165" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI165" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM165" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN165" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO165" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP165" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>8217539</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>45955.45833333334</v>
+      </c>
+      <c r="F166" t="n">
+        <v>14</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R166" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S166" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T166" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U166" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V166" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="W166" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X166" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP166" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>8217470</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>45955.45833333334</v>
+      </c>
+      <c r="F167" t="n">
+        <v>14</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" t="n">
+        <v>2</v>
+      </c>
+      <c r="K167" t="n">
+        <v>3</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="n">
+        <v>2</v>
+      </c>
+      <c r="N167" t="n">
+        <v>3</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>['7', '27']</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R167" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S167" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T167" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U167" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V167" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W167" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X167" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI167" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ167" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BK167" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BM167" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BN167" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BO167" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP167" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>8217471</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>45955.45833333334</v>
+      </c>
+      <c r="F168" t="n">
+        <v>14</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>2</v>
+      </c>
+      <c r="M168" t="n">
+        <v>2</v>
+      </c>
+      <c r="N168" t="n">
+        <v>4</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>['51', '90+5']</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>['46', '90+1']</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="R168" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S168" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="T168" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U168" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V168" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="W168" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X168" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO168" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BP168" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -32389,7 +32389,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>8217521</v>
+        <v>8217486</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -32409,113 +32409,113 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L147" t="n">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>['31', '68']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="R147" t="n">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="S147" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T147" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U147" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V147" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W147" t="n">
         <v>1.44</v>
       </c>
-      <c r="U147" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V147" t="n">
-        <v>3</v>
-      </c>
-      <c r="W147" t="n">
-        <v>1.32</v>
-      </c>
       <c r="X147" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="Y147" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Z147" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA147" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="AB147" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AC147" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AD147" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AE147" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AF147" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="AG147" t="n">
-        <v>2.27</v>
+        <v>1.77</v>
       </c>
       <c r="AH147" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AI147" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AJ147" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AK147" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AL147" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM147" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AN147" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AO147" t="n">
         <v>1.17</v>
@@ -32524,82 +32524,82 @@
         <v>2.14</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="AT147" t="n">
-        <v>2.56</v>
+        <v>3.08</v>
       </c>
       <c r="AU147" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AV147" t="n">
         <v>2</v>
       </c>
       <c r="AW147" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX147" t="n">
         <v>4</v>
       </c>
       <c r="AY147" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AZ147" t="n">
         <v>6</v>
       </c>
       <c r="BA147" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BB147" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BC147" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BD147" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="BE147" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF147" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BG147" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BH147" t="n">
-        <v>3.92</v>
+        <v>3.52</v>
       </c>
       <c r="BI147" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BJ147" t="n">
         <v>2.7</v>
       </c>
       <c r="BK147" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BL147" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="BM147" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="BN147" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="BO147" t="n">
-        <v>2.71</v>
+        <v>2.98</v>
       </c>
       <c r="BP147" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="148">
@@ -32607,7 +32607,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>8217490</v>
+        <v>8217488</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -32627,12 +32627,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -32664,160 +32664,160 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="R148" t="n">
         <v>2.1</v>
       </c>
       <c r="S148" t="n">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="T148" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="U148" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="V148" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="W148" t="n">
         <v>1.4</v>
       </c>
       <c r="X148" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="Y148" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z148" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AA148" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB148" t="n">
         <v>3.4</v>
       </c>
-      <c r="AB148" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AC148" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AD148" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="AE148" t="n">
         <v>1.25</v>
       </c>
       <c r="AF148" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="AG148" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AH148" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AI148" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AJ148" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AK148" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AL148" t="n">
         <v>1.28</v>
       </c>
       <c r="AM148" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AN148" t="n">
-        <v>0.83</v>
+        <v>1.67</v>
       </c>
       <c r="AO148" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="AQ148" t="n">
-        <v>0.57</v>
+        <v>1.29</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.23</v>
+        <v>1.87</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.28</v>
+        <v>3.08</v>
       </c>
       <c r="AU148" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AV148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ148" t="n">
         <v>3</v>
-      </c>
-      <c r="AW148" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX148" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY148" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ148" t="n">
-        <v>15</v>
       </c>
       <c r="BA148" t="n">
         <v>6</v>
       </c>
       <c r="BB148" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC148" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BD148" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BE148" t="n">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
       <c r="BF148" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="BG148" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BH148" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="BI148" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="BJ148" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="BK148" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="BL148" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="BM148" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="BN148" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BO148" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="BP148" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="149">
@@ -33043,7 +33043,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>8217488</v>
+        <v>8217490</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -33063,12 +33063,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -33091,7 +33091,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -33100,160 +33100,160 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="R150" t="n">
         <v>2.1</v>
       </c>
       <c r="S150" t="n">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="T150" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="U150" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="V150" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="W150" t="n">
         <v>1.4</v>
       </c>
       <c r="X150" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="Y150" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z150" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AA150" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AB150" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC150" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AD150" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="AE150" t="n">
         <v>1.25</v>
       </c>
       <c r="AF150" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="AG150" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AI150" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AJ150" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AK150" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AL150" t="n">
         <v>1.28</v>
       </c>
       <c r="AM150" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AN150" t="n">
-        <v>1.67</v>
+        <v>0.83</v>
       </c>
       <c r="AO150" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.86</v>
+        <v>1.14</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.29</v>
+        <v>0.57</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AT150" t="n">
-        <v>3.08</v>
+        <v>2.28</v>
       </c>
       <c r="AU150" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW150" t="n">
         <v>9</v>
       </c>
-      <c r="AV150" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW150" t="n">
-        <v>16</v>
-      </c>
       <c r="AX150" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AY150" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AZ150" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="BA150" t="n">
         <v>6</v>
       </c>
       <c r="BB150" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BC150" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BD150" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BE150" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="BF150" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="BG150" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BH150" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="BI150" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="BJ150" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="BK150" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="BL150" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="BM150" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="BN150" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BO150" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="BP150" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="151">
@@ -33261,7 +33261,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>8217468</v>
+        <v>8217406</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -33281,197 +33281,197 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N151" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>['8', '72', '79', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>3.95</v>
+        <v>2.55</v>
       </c>
       <c r="R151" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S151" t="n">
-        <v>2.62</v>
+        <v>3.85</v>
       </c>
       <c r="T151" t="n">
         <v>1.36</v>
       </c>
       <c r="U151" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V151" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="W151" t="n">
         <v>1.42</v>
       </c>
       <c r="X151" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="Y151" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z151" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA151" t="n">
         <v>3.5</v>
       </c>
-      <c r="AA151" t="n">
-        <v>3.69</v>
-      </c>
       <c r="AB151" t="n">
-        <v>1.95</v>
+        <v>3.35</v>
       </c>
       <c r="AC151" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AD151" t="n">
-        <v>9</v>
+        <v>10.4</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF151" t="n">
-        <v>3.34</v>
+        <v>3.76</v>
       </c>
       <c r="AG151" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AH151" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AI151" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AJ151" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AK151" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AL151" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AM151" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AN151" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AO151" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.71</v>
+        <v>1.14</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.59</v>
+        <v>1.87</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AT151" t="n">
-        <v>3.09</v>
+        <v>3.18</v>
       </c>
       <c r="AU151" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW151" t="n">
         <v>13</v>
       </c>
       <c r="AX151" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY151" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ151" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA151" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="BB151" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC151" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD151" t="n">
-        <v>2.27</v>
+        <v>1.49</v>
       </c>
       <c r="BE151" t="n">
-        <v>6.35</v>
+        <v>7</v>
       </c>
       <c r="BF151" t="n">
-        <v>2</v>
+        <v>3.14</v>
       </c>
       <c r="BG151" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="BH151" t="n">
-        <v>3.37</v>
+        <v>3.89</v>
       </c>
       <c r="BI151" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BJ151" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="BK151" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="BL151" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BM151" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="BN151" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="BO151" t="n">
-        <v>3.11</v>
+        <v>2.72</v>
       </c>
       <c r="BP151" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="152">
@@ -33479,7 +33479,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>8217486</v>
+        <v>8217449</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -33499,197 +33499,197 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J152" t="n">
         <v>1</v>
       </c>
       <c r="K152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N152" t="n">
         <v>2</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['20', '61']</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="R152" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="S152" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="T152" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="U152" t="n">
-        <v>3.22</v>
+        <v>2.83</v>
       </c>
       <c r="V152" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="W152" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="X152" t="n">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="Y152" t="n">
         <v>1.07</v>
       </c>
       <c r="Z152" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AA152" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="AB152" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AC152" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AD152" t="n">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AF152" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="AG152" t="n">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AH152" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="AI152" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="AJ152" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AK152" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG152" t="n">
         <v>1.2</v>
       </c>
-      <c r="AL152" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM152" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AN152" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AO152" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AP152" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AQ152" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AR152" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS152" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AT152" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AU152" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV152" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW152" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX152" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY152" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ152" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA152" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB152" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC152" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD152" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BE152" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF152" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG152" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BH152" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="BI152" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BJ152" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="BK152" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="BL152" t="n">
         <v>1.95</v>
       </c>
       <c r="BM152" t="n">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="BN152" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="BO152" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="BP152" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="153">
@@ -33697,7 +33697,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>8217406</v>
+        <v>8217468</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -33717,197 +33717,197 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
+          <t>['8', '72', '79', '90+3']</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
       <c r="Q153" t="n">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="R153" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S153" t="n">
-        <v>3.85</v>
+        <v>2.62</v>
       </c>
       <c r="T153" t="n">
         <v>1.36</v>
       </c>
       <c r="U153" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V153" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="W153" t="n">
         <v>1.42</v>
       </c>
       <c r="X153" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="Y153" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z153" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA153" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="AB153" t="n">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC153" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AD153" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF153" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="AG153" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AH153" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AI153" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AJ153" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AK153" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AL153" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AM153" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ153" t="n">
         <v>1.71</v>
       </c>
-      <c r="AN153" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO153" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP153" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ153" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AR153" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AT153" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="AU153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW153" t="n">
         <v>13</v>
       </c>
       <c r="AX153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA153" t="n">
         <v>3</v>
       </c>
-      <c r="AY153" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ153" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA153" t="n">
-        <v>12</v>
-      </c>
       <c r="BB153" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BC153" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BD153" t="n">
-        <v>1.49</v>
+        <v>2.27</v>
       </c>
       <c r="BE153" t="n">
-        <v>7</v>
+        <v>6.35</v>
       </c>
       <c r="BF153" t="n">
-        <v>3.14</v>
+        <v>2</v>
       </c>
       <c r="BG153" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BH153" t="n">
-        <v>3.89</v>
+        <v>3.37</v>
       </c>
       <c r="BI153" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="BJ153" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="BK153" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="BL153" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BM153" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="BN153" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="BO153" t="n">
-        <v>2.72</v>
+        <v>3.11</v>
       </c>
       <c r="BP153" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="154">
@@ -33915,7 +33915,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>8217485</v>
+        <v>8217521</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -33935,12 +33935,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="I154" t="n">
@@ -33956,176 +33956,176 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N154" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>['33', '51', '73', '79']</t>
+          <t>['31', '68']</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="R154" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="S154" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="T154" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U154" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V154" t="n">
+        <v>3</v>
+      </c>
+      <c r="W154" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X154" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE154" t="n">
         <v>1.4</v>
       </c>
-      <c r="U154" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V154" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W154" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X154" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Y154" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z154" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA154" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB154" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC154" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD154" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="AE154" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AF154" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="AG154" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="AH154" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AI154" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AJ154" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AK154" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL154" t="n">
         <v>1.25</v>
       </c>
       <c r="AM154" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AN154" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AO154" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AP154" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ154" t="n">
         <v>1.43</v>
       </c>
-      <c r="AQ154" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AR154" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AT154" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="AU154" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AV154" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AW154" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX154" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AY154" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AZ154" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BA154" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BB154" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BC154" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BD154" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BE154" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="BF154" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="BG154" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BH154" t="n">
-        <v>3.56</v>
+        <v>3.92</v>
       </c>
       <c r="BI154" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BJ154" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="BK154" t="n">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="BL154" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="BM154" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="BN154" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="BO154" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="BP154" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="155">
@@ -34133,7 +34133,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>8217449</v>
+        <v>8217485</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -34153,12 +34153,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="I155" t="n">
@@ -34171,179 +34171,179 @@
         <v>1</v>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N155" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>['20', '61']</t>
+          <t>['33', '51', '73', '79']</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="R155" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S155" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="T155" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U155" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="V155" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="W155" t="n">
         <v>1.36</v>
       </c>
       <c r="X155" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z155" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AA155" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB155" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AD155" t="n">
-        <v>7.9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF155" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AG155" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AI155" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AJ155" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AK155" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AL155" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AM155" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AN155" t="n">
-        <v>0.17</v>
+        <v>1.67</v>
       </c>
       <c r="AO155" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP155" t="n">
-        <v>0.14</v>
+        <v>1.43</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.71</v>
+        <v>1.33</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AS155" t="n">
-        <v>0.86</v>
+        <v>1.23</v>
       </c>
       <c r="AT155" t="n">
-        <v>2.01</v>
+        <v>2.47</v>
       </c>
       <c r="AU155" t="n">
         <v>2</v>
       </c>
       <c r="AV155" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW155" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA155" t="n">
         <v>6</v>
       </c>
-      <c r="AX155" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY155" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ155" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA155" t="n">
-        <v>3</v>
-      </c>
       <c r="BB155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC155" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BD155" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="BE155" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF155" t="n">
-        <v>2.07</v>
+        <v>2.64</v>
       </c>
       <c r="BG155" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BH155" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="BI155" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BJ155" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="BK155" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="BL155" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BM155" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="BN155" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BO155" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="BP155" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="156">
@@ -34569,7 +34569,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>8217266</v>
+        <v>8217551</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -34589,197 +34589,197 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>['65', '71']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>2.6</v>
+        <v>4.89</v>
       </c>
       <c r="R157" t="n">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="S157" t="n">
-        <v>3.96</v>
+        <v>2.38</v>
       </c>
       <c r="T157" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="U157" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V157" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="W157" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X157" t="n">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="Y157" t="n">
         <v>1.07</v>
       </c>
       <c r="Z157" t="n">
-        <v>2.1</v>
+        <v>4.18</v>
       </c>
       <c r="AA157" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AB157" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH157" t="n">
         <v>3.4</v>
       </c>
-      <c r="AC157" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD157" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE157" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF157" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG157" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AH157" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AI157" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AJ157" t="n">
+      <c r="BI157" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL157" t="n">
         <v>1.95</v>
       </c>
-      <c r="AK157" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL157" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM157" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AN157" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO157" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP157" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ157" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AR157" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AS157" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AT157" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU157" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV157" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW157" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX157" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY157" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ157" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA157" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB157" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC157" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD157" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BE157" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF157" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BG157" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BH157" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI157" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BJ157" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BK157" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BL157" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BM157" t="n">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="BN157" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="BO157" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="BP157" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="158">
@@ -34787,7 +34787,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>8217551</v>
+        <v>8217266</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -34807,197 +34807,197 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['65', '71']</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>4.89</v>
+        <v>2.6</v>
       </c>
       <c r="R158" t="n">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="S158" t="n">
-        <v>2.38</v>
+        <v>3.96</v>
       </c>
       <c r="T158" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="U158" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V158" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="W158" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X158" t="n">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="Y158" t="n">
         <v>1.07</v>
       </c>
       <c r="Z158" t="n">
-        <v>4.18</v>
+        <v>2.1</v>
       </c>
       <c r="AA158" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AB158" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BG158" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH158" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI158" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BK158" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC158" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD158" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE158" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF158" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AG158" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH158" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AI158" t="n">
+      <c r="BL158" t="n">
         <v>1.85</v>
       </c>
-      <c r="AJ158" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AK158" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL158" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM158" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN158" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO158" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AP158" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ158" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR158" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AS158" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT158" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU158" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV158" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW158" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX158" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY158" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ158" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA158" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB158" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC158" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD158" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BE158" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BF158" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BG158" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH158" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI158" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BJ158" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BK158" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BL158" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BM158" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="BN158" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="BO158" t="n">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="BP158" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="159">
@@ -35005,7 +35005,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>8217491</v>
+        <v>8217536</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -35025,197 +35025,197 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K159" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N159" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['27', '37', '87']</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['6', '45+1']</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R159" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="S159" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T159" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U159" t="n">
         <v>3</v>
       </c>
-      <c r="T159" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U159" t="n">
-        <v>2.9</v>
-      </c>
       <c r="V159" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="W159" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X159" t="n">
-        <v>5.8</v>
+        <v>6.15</v>
       </c>
       <c r="Y159" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z159" t="n">
         <v>2.65</v>
       </c>
       <c r="AA159" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB159" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AC159" t="n">
         <v>1.01</v>
       </c>
       <c r="AD159" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="AE159" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF159" t="n">
         <v>3.6</v>
       </c>
       <c r="AG159" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH159" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AI159" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AJ159" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AK159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL159" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL159" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AM159" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AN159" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO159" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AP159" t="n">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="AU159" t="n">
         <v>5</v>
       </c>
       <c r="AV159" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW159" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX159" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AY159" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ159" t="n">
         <v>12</v>
       </c>
-      <c r="AZ159" t="n">
-        <v>9</v>
-      </c>
       <c r="BA159" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB159" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC159" t="n">
         <v>6</v>
       </c>
-      <c r="BC159" t="n">
-        <v>10</v>
-      </c>
       <c r="BD159" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL159" t="n">
         <v>2.1</v>
       </c>
-      <c r="BE159" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="BF159" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BG159" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BH159" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI159" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BJ159" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BK159" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BL159" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BM159" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="BN159" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="BO159" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="BP159" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="160">
@@ -35223,7 +35223,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>8217469</v>
+        <v>8217522</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -35243,12 +35243,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="I160" t="n">
@@ -35261,179 +35261,179 @@
         <v>1</v>
       </c>
       <c r="L160" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N160" t="n">
         <v>4</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>['45+9', '52', '69', '86']</t>
+          <t>['10', '68']</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51', '60']</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>2.96</v>
+        <v>4.39</v>
       </c>
       <c r="R160" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="S160" t="n">
-        <v>3.13</v>
+        <v>2.49</v>
       </c>
       <c r="T160" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="U160" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V160" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="W160" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="X160" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="Y160" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Z160" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="AA160" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AB160" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="AC160" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AD160" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF160" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AG160" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AH160" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AI160" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AJ160" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AK160" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AL160" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AM160" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AN160" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="AO160" t="n">
-        <v>1.17</v>
+        <v>2.17</v>
       </c>
       <c r="AP160" t="n">
         <v>1.14</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR160" t="n">
-        <v>1.87</v>
+        <v>1.08</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="AT160" t="n">
-        <v>2.99</v>
+        <v>2.56</v>
       </c>
       <c r="AU160" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY160" t="n">
         <v>6</v>
       </c>
-      <c r="AV160" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW160" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX160" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY160" t="n">
-        <v>14</v>
-      </c>
       <c r="AZ160" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA160" t="n">
         <v>4</v>
       </c>
-      <c r="BA160" t="n">
-        <v>5</v>
-      </c>
       <c r="BB160" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BC160" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD160" t="n">
-        <v>1.89</v>
+        <v>2.88</v>
       </c>
       <c r="BE160" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF160" t="n">
-        <v>2.46</v>
+        <v>1.53</v>
       </c>
       <c r="BG160" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BH160" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BI160" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BJ160" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BK160" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="BL160" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="BM160" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="BN160" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="BO160" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="BP160" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="161">
@@ -35441,7 +35441,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>8217522</v>
+        <v>8217538</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -35461,197 +35461,197 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L161" t="n">
         <v>2</v>
       </c>
       <c r="M161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>['10', '68']</t>
+          <t>['72', '90']</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>['51', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>4.39</v>
+        <v>3</v>
       </c>
       <c r="R161" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="S161" t="n">
-        <v>2.49</v>
+        <v>3.54</v>
       </c>
       <c r="T161" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U161" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V161" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W161" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X161" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE161" t="n">
         <v>1.38</v>
       </c>
-      <c r="U161" t="n">
+      <c r="AF161" t="n">
         <v>2.8</v>
       </c>
-      <c r="V161" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W161" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X161" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y161" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z161" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA161" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB161" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC161" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD161" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE161" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF161" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AG161" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AI161" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AJ161" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AK161" t="n">
-        <v>1.79</v>
+        <v>1.28</v>
       </c>
       <c r="AL161" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AM161" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AN161" t="n">
-        <v>1.17</v>
+        <v>2.17</v>
       </c>
       <c r="AO161" t="n">
-        <v>2.17</v>
+        <v>0.83</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.14</v>
+        <v>2.29</v>
       </c>
       <c r="AQ161" t="n">
-        <v>2</v>
+        <v>0.71</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.08</v>
+        <v>1.49</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AT161" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="AU161" t="n">
         <v>3</v>
       </c>
       <c r="AV161" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AW161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO161" t="n">
         <v>3</v>
       </c>
-      <c r="AX161" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY161" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ161" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA161" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB161" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC161" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD161" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BE161" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF161" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BG161" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BH161" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI161" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BJ161" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BK161" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BL161" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM161" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BN161" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BO161" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BP161" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="162">
@@ -35659,7 +35659,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>8217535</v>
+        <v>8217539</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -35679,197 +35679,197 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="I162" t="n">
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>['73', '81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="R162" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="S162" t="n">
-        <v>3.06</v>
+        <v>3.55</v>
       </c>
       <c r="T162" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="U162" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="V162" t="n">
-        <v>2.92</v>
+        <v>2.41</v>
       </c>
       <c r="W162" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="X162" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="Y162" t="n">
         <v>1.08</v>
       </c>
       <c r="Z162" t="n">
-        <v>2.71</v>
+        <v>2.15</v>
       </c>
       <c r="AA162" t="n">
-        <v>3.21</v>
+        <v>3.6</v>
       </c>
       <c r="AB162" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="AC162" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD162" t="n">
-        <v>9</v>
+        <v>12.8</v>
       </c>
       <c r="AE162" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ162" t="n">
         <v>1.29</v>
       </c>
-      <c r="AF162" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG162" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH162" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI162" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AJ162" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AK162" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL162" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM162" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AN162" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO162" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AP162" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ162" t="n">
-        <v>2</v>
-      </c>
       <c r="AR162" t="n">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="AS162" t="n">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="AT162" t="n">
-        <v>3.17</v>
+        <v>2.59</v>
       </c>
       <c r="AU162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW162" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX162" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY162" t="n">
         <v>9</v>
       </c>
       <c r="AZ162" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC162" t="n">
         <v>6</v>
       </c>
-      <c r="BA162" t="n">
+      <c r="BD162" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BE162" t="n">
         <v>7</v>
       </c>
-      <c r="BB162" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC162" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD162" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BE162" t="n">
-        <v>8.5</v>
-      </c>
       <c r="BF162" t="n">
-        <v>2.84</v>
+        <v>2.35</v>
       </c>
       <c r="BG162" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="BH162" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BI162" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="BJ162" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO162" t="n">
         <v>2.7</v>
       </c>
-      <c r="BK162" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BL162" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BM162" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BN162" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BO162" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BP162" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="163">
@@ -35877,7 +35877,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>8217536</v>
+        <v>8217469</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -35897,197 +35897,197 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K163" t="n">
+        <v>1</v>
+      </c>
+      <c r="L163" t="n">
         <v>4</v>
       </c>
-      <c r="L163" t="n">
-        <v>3</v>
-      </c>
       <c r="M163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>['27', '37', '87']</t>
+          <t>['45+9', '52', '69', '86']</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>['6', '45+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="R163" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S163" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="T163" t="n">
         <v>1.33</v>
       </c>
       <c r="U163" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V163" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="W163" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X163" t="n">
-        <v>6.15</v>
+        <v>5.6</v>
       </c>
       <c r="Y163" t="n">
         <v>1.09</v>
       </c>
       <c r="Z163" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="AA163" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AB163" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AC163" t="n">
         <v>1.01</v>
       </c>
       <c r="AD163" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE163" t="n">
         <v>1.24</v>
       </c>
       <c r="AF163" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AG163" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH163" t="n">
         <v>1.93</v>
       </c>
-      <c r="AH163" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AI163" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AJ163" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AK163" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AL163" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AM163" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AN163" t="n">
-        <v>1.5</v>
+        <v>0.83</v>
       </c>
       <c r="AO163" t="n">
-        <v>1.83</v>
+        <v>1.17</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.71</v>
+        <v>1.14</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.57</v>
+        <v>1</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="AT163" t="n">
-        <v>2.66</v>
+        <v>2.99</v>
       </c>
       <c r="AU163" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA163" t="n">
         <v>5</v>
-      </c>
-      <c r="AV163" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW163" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX163" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY163" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ163" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA163" t="n">
-        <v>3</v>
       </c>
       <c r="BB163" t="n">
         <v>3</v>
       </c>
       <c r="BC163" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD163" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="BE163" t="n">
-        <v>7.42</v>
+        <v>8.6</v>
       </c>
       <c r="BF163" t="n">
-        <v>1.96</v>
+        <v>2.46</v>
       </c>
       <c r="BG163" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="BH163" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="BI163" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BJ163" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BK163" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BL163" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BM163" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BN163" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="BO163" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BP163" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="164">
@@ -36095,7 +36095,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>8217537</v>
+        <v>8217491</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -36115,12 +36115,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="I164" t="n">
@@ -36133,95 +36133,95 @@
         <v>1</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M164" t="n">
+        <v>1</v>
+      </c>
+      <c r="N164" t="n">
+        <v>2</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S164" t="n">
         <v>3</v>
       </c>
-      <c r="N164" t="n">
-        <v>3</v>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P164" t="inlineStr">
-        <is>
-          <t>['12', '49', '51']</t>
-        </is>
-      </c>
-      <c r="Q164" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R164" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S164" t="n">
-        <v>4</v>
-      </c>
       <c r="T164" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U164" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="V164" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="W164" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X164" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="Y164" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z164" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="AA164" t="n">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="AB164" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF164" t="n">
         <v>3.6</v>
       </c>
-      <c r="AC164" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD164" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE164" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF164" t="n">
-        <v>3.32</v>
-      </c>
       <c r="AG164" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AH164" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AI164" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AJ164" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AK164" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AL164" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AM164" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="AN164" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AO164" t="n">
         <v>1.17</v>
@@ -36230,82 +36230,82 @@
         <v>1</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR164" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="AS164" t="n">
-        <v>0.99</v>
+        <v>1.23</v>
       </c>
       <c r="AT164" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="AU164" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV164" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AW164" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ164" t="n">
         <v>9</v>
-      </c>
-      <c r="AX164" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY164" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ164" t="n">
-        <v>16</v>
       </c>
       <c r="BA164" t="n">
         <v>4</v>
       </c>
       <c r="BB164" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BC164" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BD164" t="n">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="BE164" t="n">
-        <v>8.699999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="BF164" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO164" t="n">
         <v>2.88</v>
       </c>
-      <c r="BG164" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH164" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BI164" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BJ164" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BK164" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BL164" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BM164" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BN164" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BO164" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BP164" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="165">
@@ -36313,7 +36313,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>8217538</v>
+        <v>8217470</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -36333,197 +36333,197 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>['72', '90']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '27']</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="R165" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="S165" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="T165" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="U165" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="V165" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="W165" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X165" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AL165" t="n">
         <v>1.3</v>
       </c>
-      <c r="X165" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Y165" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z165" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA165" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB165" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC165" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD165" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE165" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF165" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG165" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AH165" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI165" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ165" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK165" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL165" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AM165" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AN165" t="n">
         <v>2.17</v>
       </c>
       <c r="AO165" t="n">
-        <v>0.83</v>
+        <v>1.5</v>
       </c>
       <c r="AP165" t="n">
-        <v>2.29</v>
+        <v>1.86</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.49</v>
+        <v>1.81</v>
       </c>
       <c r="AS165" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="AT165" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="AU165" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW165" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AX165" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AY165" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="AZ165" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA165" t="n">
         <v>5</v>
-      </c>
-      <c r="BA165" t="n">
-        <v>0</v>
       </c>
       <c r="BB165" t="n">
         <v>5</v>
       </c>
       <c r="BC165" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BD165" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="BE165" t="n">
-        <v>6.3</v>
+        <v>6.15</v>
       </c>
       <c r="BF165" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="BG165" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI165" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BM165" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BN165" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BO165" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP165" t="n">
         <v>1.3</v>
-      </c>
-      <c r="BH165" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BI165" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BJ165" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BK165" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BL165" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BM165" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BN165" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BO165" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP165" t="n">
-        <v>1.28</v>
       </c>
     </row>
     <row r="166">
@@ -36531,7 +36531,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>8217539</v>
+        <v>8217471</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -36551,12 +36551,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="I166" t="n">
@@ -36569,179 +36569,179 @@
         <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51', '90+5']</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['46', '90+1']</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="R166" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S166" t="n">
-        <v>3.55</v>
+        <v>4.61</v>
       </c>
       <c r="T166" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="U166" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="V166" t="n">
-        <v>2.41</v>
+        <v>3.16</v>
       </c>
       <c r="W166" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="X166" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="Y166" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z166" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AA166" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AB166" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="AC166" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AD166" t="n">
-        <v>12.8</v>
+        <v>8</v>
       </c>
       <c r="AE166" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AF166" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="AG166" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH166" t="n">
         <v>1.7</v>
       </c>
-      <c r="AH166" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AI166" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AJ166" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AK166" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AL166" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AM166" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AN166" t="n">
-        <v>2.17</v>
+        <v>1</v>
       </c>
       <c r="AO166" t="n">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="AP166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.29</v>
+        <v>0.71</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="AS166" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AT166" t="n">
-        <v>2.59</v>
+        <v>2.93</v>
       </c>
       <c r="AU166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW166" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX166" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY166" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ166" t="n">
         <v>9</v>
       </c>
       <c r="BA166" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BB166" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC166" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD166" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="BE166" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF166" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="BG166" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BH166" t="n">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="BI166" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="BJ166" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="BK166" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL166" t="n">
         <v>2.05</v>
       </c>
-      <c r="BL166" t="n">
-        <v>2</v>
-      </c>
       <c r="BM166" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="BN166" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="BO166" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="BP166" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="167">
@@ -36749,7 +36749,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>8217470</v>
+        <v>8217537</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -36769,197 +36769,197 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K167" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
         <v>3</v>
-      </c>
-      <c r="L167" t="n">
-        <v>1</v>
-      </c>
-      <c r="M167" t="n">
-        <v>2</v>
       </c>
       <c r="N167" t="n">
         <v>3</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>['7', '27']</t>
+          <t>['12', '49', '51']</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="R167" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S167" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="T167" t="n">
         <v>1.4</v>
       </c>
       <c r="U167" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V167" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="W167" t="n">
         <v>1.41</v>
       </c>
       <c r="X167" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Y167" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z167" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AA167" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="AB167" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AC167" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD167" t="n">
         <v>9</v>
       </c>
       <c r="AE167" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF167" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="AG167" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AH167" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AI167" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AJ167" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AK167" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="AL167" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AM167" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="AN167" t="n">
-        <v>2.17</v>
+        <v>1.17</v>
       </c>
       <c r="AO167" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.86</v>
+        <v>1</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AR167" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="AS167" t="n">
-        <v>1.39</v>
+        <v>0.99</v>
       </c>
       <c r="AT167" t="n">
-        <v>3.2</v>
+        <v>2.53</v>
       </c>
       <c r="AU167" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AV167" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AW167" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX167" t="n">
         <v>8</v>
       </c>
-      <c r="AX167" t="n">
+      <c r="AY167" t="n">
         <v>11</v>
       </c>
-      <c r="AY167" t="n">
-        <v>15</v>
-      </c>
       <c r="AZ167" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA167" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC167" t="n">
         <v>5</v>
       </c>
-      <c r="BB167" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC167" t="n">
-        <v>10</v>
-      </c>
       <c r="BD167" t="n">
-        <v>2.08</v>
+        <v>1.54</v>
       </c>
       <c r="BE167" t="n">
-        <v>6.15</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BF167" t="n">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="BG167" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="BH167" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="BI167" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="BJ167" t="n">
-        <v>2.14</v>
+        <v>2.63</v>
       </c>
       <c r="BK167" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="BL167" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="BM167" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="BN167" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="BO167" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="BP167" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="168">
@@ -36967,7 +36967,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>8217471</v>
+        <v>8217535</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -36987,149 +36987,149 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="I168" t="n">
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L168" t="n">
         <v>2</v>
       </c>
       <c r="M168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N168" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>['51', '90+5']</t>
+          <t>['73', '81']</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>['46', '90+1']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="R168" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S168" t="n">
-        <v>4.61</v>
+        <v>3.06</v>
       </c>
       <c r="T168" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="U168" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V168" t="n">
-        <v>3.16</v>
+        <v>2.92</v>
       </c>
       <c r="W168" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="X168" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Y168" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z168" t="n">
-        <v>1.9</v>
+        <v>2.71</v>
       </c>
       <c r="AA168" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="AB168" t="n">
-        <v>3.9</v>
+        <v>2.64</v>
       </c>
       <c r="AC168" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AD168" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE168" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AF168" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="AG168" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AH168" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AI168" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AJ168" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AK168" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL168" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AM168" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="AN168" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AO168" t="n">
-        <v>0.67</v>
+        <v>2.33</v>
       </c>
       <c r="AP168" t="n">
-        <v>1</v>
+        <v>1.86</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.71</v>
+        <v>2</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AS168" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="AT168" t="n">
-        <v>2.93</v>
+        <v>3.17</v>
       </c>
       <c r="AU168" t="n">
         <v>3</v>
       </c>
       <c r="AV168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY168" t="n">
         <v>9</v>
       </c>
-      <c r="AX168" t="n">
+      <c r="AZ168" t="n">
         <v>6</v>
-      </c>
-      <c r="AY168" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ168" t="n">
-        <v>9</v>
       </c>
       <c r="BA168" t="n">
         <v>7</v>
@@ -37141,43 +37141,43 @@
         <v>9</v>
       </c>
       <c r="BD168" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BN168" t="n">
         <v>1.65</v>
       </c>
-      <c r="BE168" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF168" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG168" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BH168" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="BI168" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BJ168" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BK168" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BL168" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BM168" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BN168" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BO168" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BP168" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -36242,7 +36242,7 @@
         <v>2.51</v>
       </c>
       <c r="AU164" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV164" t="n">
         <v>4</v>
@@ -36254,7 +36254,7 @@
         <v>5</v>
       </c>
       <c r="AY164" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ164" t="n">
         <v>9</v>
@@ -36466,13 +36466,13 @@
         <v>2</v>
       </c>
       <c r="AW165" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX165" t="n">
         <v>11</v>
       </c>
       <c r="AY165" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ165" t="n">
         <v>13</v>
@@ -36678,13 +36678,13 @@
         <v>2.93</v>
       </c>
       <c r="AU166" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV166" t="n">
         <v>3</v>
       </c>
       <c r="AW166" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX166" t="n">
         <v>6</v>
@@ -36896,19 +36896,19 @@
         <v>2.53</v>
       </c>
       <c r="AU167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV167" t="n">
         <v>8</v>
       </c>
       <c r="AW167" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX167" t="n">
         <v>8</v>
       </c>
       <c r="AY167" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ167" t="n">
         <v>16</v>
@@ -37114,10 +37114,10 @@
         <v>3.17</v>
       </c>
       <c r="AU168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV168" t="n">
         <v>3</v>
-      </c>
-      <c r="AV168" t="n">
-        <v>2</v>
       </c>
       <c r="AW168" t="n">
         <v>6</v>
@@ -37126,10 +37126,10 @@
         <v>4</v>
       </c>
       <c r="AY168" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ168" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA168" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP168"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.29</v>
@@ -3312,7 +3312,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -11596,7 +11596,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR51" t="n">
         <v>1.68</v>
@@ -12029,7 +12029,7 @@
         <v>2</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.57</v>
@@ -17482,7 +17482,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR78" t="n">
         <v>1.77</v>
@@ -19223,7 +19223,7 @@
         <v>1.67</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.29</v>
@@ -24022,7 +24022,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR108" t="n">
         <v>1.23</v>
@@ -25545,7 +25545,7 @@
         <v>1.75</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.57</v>
@@ -28818,7 +28818,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR130" t="n">
         <v>1.73</v>
@@ -30995,7 +30995,7 @@
         <v>0.8</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.43</v>
@@ -33829,7 +33829,7 @@
         <v>2</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.71</v>
@@ -34268,7 +34268,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR155" t="n">
         <v>1.24</v>
@@ -34943,13 +34943,13 @@
         <v>8</v>
       </c>
       <c r="AX158" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY158" t="n">
         <v>15</v>
       </c>
       <c r="AZ158" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA158" t="n">
         <v>7</v>
@@ -35379,13 +35379,13 @@
         <v>3</v>
       </c>
       <c r="AX160" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY160" t="n">
         <v>6</v>
       </c>
       <c r="AZ160" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA160" t="n">
         <v>4</v>
@@ -35806,13 +35806,13 @@
         <v>2.59</v>
       </c>
       <c r="AU162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV162" t="n">
         <v>1</v>
       </c>
       <c r="AW162" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX162" t="n">
         <v>8</v>
@@ -36024,13 +36024,13 @@
         <v>2.99</v>
       </c>
       <c r="AU163" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV163" t="n">
         <v>3</v>
       </c>
       <c r="AW163" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX163" t="n">
         <v>1</v>
@@ -36242,7 +36242,7 @@
         <v>2.51</v>
       </c>
       <c r="AU164" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV164" t="n">
         <v>4</v>
@@ -36254,7 +36254,7 @@
         <v>5</v>
       </c>
       <c r="AY164" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ164" t="n">
         <v>9</v>
@@ -36466,13 +36466,13 @@
         <v>2</v>
       </c>
       <c r="AW165" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX165" t="n">
         <v>11</v>
       </c>
       <c r="AY165" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ165" t="n">
         <v>13</v>
@@ -36905,13 +36905,13 @@
         <v>10</v>
       </c>
       <c r="AX167" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY167" t="n">
         <v>13</v>
       </c>
       <c r="AZ167" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA167" t="n">
         <v>4</v>
@@ -37178,6 +37178,224 @@
       </c>
       <c r="BP168" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>8217324</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>45958.69791666666</v>
+      </c>
+      <c r="F169" t="n">
+        <v>4</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>1</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>1</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>1</v>
+      </c>
+      <c r="N169" t="n">
+        <v>2</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="R169" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S169" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T169" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U169" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V169" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="W169" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X169" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BP169" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -32389,7 +32389,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>8217486</v>
+        <v>8217488</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -32409,197 +32409,197 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="R147" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S147" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="T147" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="U147" t="n">
-        <v>3.22</v>
+        <v>2.84</v>
       </c>
       <c r="V147" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="W147" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X147" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="Y147" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z147" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AA147" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="AB147" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AC147" t="n">
         <v>1.05</v>
       </c>
       <c r="AD147" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AE147" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF147" t="n">
-        <v>3.85</v>
+        <v>3.52</v>
       </c>
       <c r="AG147" t="n">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AH147" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AI147" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AJ147" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AK147" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AL147" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AM147" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP147" t="n">
         <v>1.86</v>
       </c>
-      <c r="AN147" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AO147" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AP147" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AQ147" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AT147" t="n">
         <v>3.08</v>
       </c>
       <c r="AU147" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AV147" t="n">
         <v>2</v>
       </c>
       <c r="AW147" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AX147" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY147" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AZ147" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA147" t="n">
         <v>6</v>
       </c>
-      <c r="BA147" t="n">
-        <v>9</v>
-      </c>
       <c r="BB147" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="BC147" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="BD147" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="BE147" t="n">
-        <v>9.199999999999999</v>
+        <v>6.65</v>
       </c>
       <c r="BF147" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH147" t="n">
         <v>3.35</v>
       </c>
-      <c r="BG147" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BH147" t="n">
-        <v>3.52</v>
-      </c>
       <c r="BI147" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BJ147" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="BK147" t="n">
-        <v>1.74</v>
+        <v>2.13</v>
       </c>
       <c r="BL147" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BM147" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="BN147" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="BO147" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BP147" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="148">
@@ -32607,7 +32607,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>8217488</v>
+        <v>8217489</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -32627,197 +32627,197 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N148" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['23', '41', '57']</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+10']</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="R148" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S148" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="T148" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U148" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="V148" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="W148" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X148" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="Y148" t="n">
         <v>1.05</v>
       </c>
       <c r="Z148" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA148" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AB148" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AC148" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AD148" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AE148" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF148" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="AG148" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AH148" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ148" t="n">
         <v>1.8</v>
       </c>
-      <c r="AI148" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AJ148" t="n">
+      <c r="AK148" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL148" t="n">
         <v>1.87</v>
       </c>
-      <c r="AK148" t="n">
+      <c r="BM148" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO148" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP148" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AL148" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AM148" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AN148" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO148" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP148" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ148" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR148" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS148" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AT148" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AU148" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV148" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW148" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX148" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY148" t="n">
-        <v>25</v>
-      </c>
-      <c r="AZ148" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA148" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB148" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC148" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD148" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BE148" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="BF148" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BG148" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BH148" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI148" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BJ148" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BK148" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BL148" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BM148" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BN148" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BO148" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP148" t="n">
-        <v>1.29</v>
       </c>
     </row>
     <row r="149">
@@ -32825,7 +32825,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>8217489</v>
+        <v>8217490</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -32845,197 +32845,197 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>1</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="R149" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S149" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T149" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U149" t="n">
         <v>3</v>
       </c>
-      <c r="M149" t="n">
-        <v>1</v>
-      </c>
-      <c r="N149" t="n">
-        <v>4</v>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>['23', '41', '57']</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>['90+10']</t>
-        </is>
-      </c>
-      <c r="Q149" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="R149" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S149" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T149" t="n">
+      <c r="V149" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W149" t="n">
         <v>1.4</v>
-      </c>
-      <c r="U149" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V149" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="W149" t="n">
-        <v>1.38</v>
       </c>
       <c r="X149" t="n">
         <v>7</v>
       </c>
       <c r="Y149" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z149" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AA149" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB149" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC149" t="n">
         <v>1.01</v>
       </c>
       <c r="AD149" t="n">
-        <v>8.5</v>
+        <v>10.3</v>
       </c>
       <c r="AE149" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL149" t="n">
         <v>1.28</v>
       </c>
-      <c r="AF149" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG149" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AH149" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AI149" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AJ149" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK149" t="n">
+      <c r="AM149" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG149" t="n">
         <v>1.19</v>
       </c>
-      <c r="AL149" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AM149" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AN149" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO149" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AP149" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ149" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR149" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AS149" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AT149" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU149" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV149" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW149" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX149" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY149" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ149" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA149" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB149" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC149" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD149" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BE149" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF149" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG149" t="n">
-        <v>1.24</v>
-      </c>
       <c r="BH149" t="n">
-        <v>2.8</v>
+        <v>3.68</v>
       </c>
       <c r="BI149" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="BJ149" t="n">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="BK149" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM149" t="n">
         <v>2.05</v>
       </c>
-      <c r="BL149" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BM149" t="n">
-        <v>2.32</v>
-      </c>
       <c r="BN149" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="BO149" t="n">
-        <v>3.45</v>
+        <v>2.83</v>
       </c>
       <c r="BP149" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="150">
@@ -33043,7 +33043,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>8217490</v>
+        <v>8217449</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -33063,197 +33063,197 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="I150" t="n">
         <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '61']</t>
         </is>
       </c>
       <c r="Q150" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R150" t="n">
+        <v>2</v>
+      </c>
+      <c r="S150" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T150" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U150" t="n">
         <v>2.83</v>
       </c>
-      <c r="R150" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S150" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="T150" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U150" t="n">
-        <v>3</v>
-      </c>
       <c r="V150" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="W150" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X150" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="Y150" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z150" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AA150" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AB150" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AC150" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AD150" t="n">
-        <v>10.3</v>
+        <v>7.9</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF150" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="AG150" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AI150" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AJ150" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="AK150" t="n">
         <v>1.35</v>
       </c>
       <c r="AL150" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AM150" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AN150" t="n">
-        <v>0.83</v>
+        <v>0.17</v>
       </c>
       <c r="AO150" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.14</v>
+        <v>0.14</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.05</v>
+        <v>0.86</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.28</v>
+        <v>2.01</v>
       </c>
       <c r="AU150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV150" t="n">
         <v>4</v>
       </c>
-      <c r="AV150" t="n">
+      <c r="AW150" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA150" t="n">
         <v>3</v>
       </c>
-      <c r="AW150" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX150" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY150" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ150" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA150" t="n">
+      <c r="BB150" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC150" t="n">
         <v>6</v>
       </c>
-      <c r="BB150" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC150" t="n">
-        <v>12</v>
-      </c>
       <c r="BD150" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="BE150" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BF150" t="n">
-        <v>2.88</v>
+        <v>2.07</v>
       </c>
       <c r="BG150" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BH150" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="BI150" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BJ150" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="BK150" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="BL150" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="BM150" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="BN150" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="BO150" t="n">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="BP150" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="151">
@@ -33261,7 +33261,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>8217406</v>
+        <v>8217521</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -33281,197 +33281,197 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="I151" t="n">
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['31', '68']</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="R151" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="S151" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="T151" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="U151" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V151" t="n">
+        <v>3</v>
+      </c>
+      <c r="W151" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X151" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF151" t="n">
         <v>2.9</v>
       </c>
-      <c r="V151" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="W151" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X151" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Y151" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z151" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA151" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB151" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AC151" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AE151" t="n">
+      <c r="AG151" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK151" t="n">
         <v>1.28</v>
       </c>
-      <c r="AF151" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AG151" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH151" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AI151" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ151" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AK151" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AL151" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AM151" t="n">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="AN151" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO151" t="n">
         <v>1.17</v>
       </c>
-      <c r="AO151" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AP151" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="AS151" t="n">
         <v>1.31</v>
       </c>
       <c r="AT151" t="n">
-        <v>3.18</v>
+        <v>2.56</v>
       </c>
       <c r="AU151" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AV151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW151" t="n">
         <v>13</v>
       </c>
       <c r="AX151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY151" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AZ151" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA151" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BC151" t="n">
         <v>14</v>
       </c>
       <c r="BD151" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="BE151" t="n">
-        <v>7</v>
+        <v>8.9</v>
       </c>
       <c r="BF151" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="BG151" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BH151" t="n">
-        <v>3.89</v>
+        <v>3.92</v>
       </c>
       <c r="BI151" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BJ151" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BK151" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="BL151" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="BM151" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="BN151" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="BO151" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="BP151" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="152">
@@ -33479,7 +33479,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>8217449</v>
+        <v>8217486</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -33499,197 +33499,197 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>1</v>
       </c>
       <c r="K152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N152" t="n">
         <v>2</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>['20', '61']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="R152" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="S152" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="T152" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="U152" t="n">
-        <v>2.83</v>
+        <v>3.22</v>
       </c>
       <c r="V152" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="W152" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X152" t="n">
-        <v>6.9</v>
+        <v>5.5</v>
       </c>
       <c r="Y152" t="n">
         <v>1.07</v>
       </c>
       <c r="Z152" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AA152" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AB152" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AC152" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AD152" t="n">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AF152" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="AG152" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AH152" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI152" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ152" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK152" t="n">
         <v>1.74</v>
-      </c>
-      <c r="AI152" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AJ152" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AK152" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL152" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM152" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AN152" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AO152" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AP152" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AQ152" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AR152" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AS152" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AT152" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AU152" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV152" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW152" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX152" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY152" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ152" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA152" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB152" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC152" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD152" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BE152" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF152" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BG152" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BH152" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI152" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BJ152" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BK152" t="n">
-        <v>1.8</v>
       </c>
       <c r="BL152" t="n">
         <v>1.95</v>
       </c>
       <c r="BM152" t="n">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="BN152" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="BO152" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="BP152" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="153">
@@ -33697,7 +33697,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>8217468</v>
+        <v>8217485</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -33717,197 +33717,197 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K153" t="n">
         <v>1</v>
       </c>
       <c r="L153" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" t="n">
         <v>4</v>
       </c>
-      <c r="M153" t="n">
-        <v>0</v>
-      </c>
       <c r="N153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>['8', '72', '79', '90+3']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '51', '73', '79']</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>3.95</v>
+        <v>2.45</v>
       </c>
       <c r="R153" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S153" t="n">
-        <v>2.62</v>
+        <v>4.15</v>
       </c>
       <c r="T153" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U153" t="n">
         <v>2.88</v>
       </c>
       <c r="V153" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="W153" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="X153" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="Y153" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z153" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="AA153" t="n">
-        <v>3.69</v>
+        <v>3.2</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="AC153" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AD153" t="n">
-        <v>9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AF153" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="AG153" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH153" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AI153" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AJ153" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AK153" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL153" t="n">
         <v>1.25</v>
       </c>
       <c r="AM153" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AN153" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AO153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP153" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ153" t="n">
         <v>1.29</v>
       </c>
-      <c r="AQ153" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AR153" t="n">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AT153" t="n">
-        <v>3.09</v>
+        <v>2.47</v>
       </c>
       <c r="AU153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA153" t="n">
         <v>6</v>
-      </c>
-      <c r="AV153" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW153" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX153" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY153" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ153" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA153" t="n">
-        <v>3</v>
       </c>
       <c r="BB153" t="n">
         <v>5</v>
       </c>
       <c r="BC153" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD153" t="n">
-        <v>2.27</v>
+        <v>1.53</v>
       </c>
       <c r="BE153" t="n">
-        <v>6.35</v>
+        <v>8.4</v>
       </c>
       <c r="BF153" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="BG153" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BH153" t="n">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="BI153" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BJ153" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="BK153" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="BL153" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="BM153" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="BN153" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BO153" t="n">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="BP153" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="154">
@@ -33915,7 +33915,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>8217521</v>
+        <v>8217468</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -33935,197 +33935,197 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
         <v>1</v>
       </c>
       <c r="L154" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['8', '72', '79', '90+3']</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>['31', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>2.48</v>
+        <v>3.95</v>
       </c>
       <c r="R154" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S154" t="n">
-        <v>4.4</v>
+        <v>2.62</v>
       </c>
       <c r="T154" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="U154" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="V154" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="W154" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="X154" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="Y154" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Z154" t="n">
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="AA154" t="n">
-        <v>3.25</v>
+        <v>3.69</v>
       </c>
       <c r="AB154" t="n">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="AC154" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AD154" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE154" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AF154" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="AG154" t="n">
-        <v>2.27</v>
+        <v>1.98</v>
       </c>
       <c r="AH154" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AI154" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AJ154" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AK154" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AL154" t="n">
         <v>1.25</v>
       </c>
       <c r="AM154" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="AN154" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="AO154" t="n">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.14</v>
+        <v>1.29</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AT154" t="n">
-        <v>2.56</v>
+        <v>3.09</v>
       </c>
       <c r="AU154" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AV154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW154" t="n">
         <v>13</v>
       </c>
       <c r="AX154" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY154" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AZ154" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA154" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="BB154" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC154" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BD154" t="n">
-        <v>1.45</v>
+        <v>2.27</v>
       </c>
       <c r="BE154" t="n">
-        <v>8.9</v>
+        <v>6.35</v>
       </c>
       <c r="BF154" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="BG154" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="BH154" t="n">
-        <v>3.92</v>
+        <v>3.37</v>
       </c>
       <c r="BI154" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BJ154" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BK154" t="n">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="BL154" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="BM154" t="n">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="BN154" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="BO154" t="n">
-        <v>2.71</v>
+        <v>3.11</v>
       </c>
       <c r="BP154" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="155">
@@ -34133,7 +34133,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>8217485</v>
+        <v>8217406</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -34153,197 +34153,197 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="I155" t="n">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N155" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>['33', '51', '73', '79']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R155" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="S155" t="n">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="T155" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U155" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V155" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="W155" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X155" t="n">
-        <v>7.3</v>
+        <v>6.25</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z155" t="n">
         <v>2.05</v>
       </c>
       <c r="AA155" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AB155" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AD155" t="n">
-        <v>8.949999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="AE155" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK155" t="n">
         <v>1.31</v>
       </c>
-      <c r="AF155" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AG155" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH155" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AI155" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AJ155" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK155" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AL155" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AM155" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AN155" t="n">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AO155" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AT155" t="n">
-        <v>2.47</v>
+        <v>3.18</v>
       </c>
       <c r="AU155" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV155" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AW155" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA155" t="n">
         <v>12</v>
       </c>
-      <c r="AY155" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ155" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA155" t="n">
-        <v>6</v>
-      </c>
       <c r="BB155" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC155" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BD155" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="BE155" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BF155" t="n">
-        <v>2.64</v>
+        <v>3.14</v>
       </c>
       <c r="BG155" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BH155" t="n">
-        <v>3.56</v>
+        <v>3.89</v>
       </c>
       <c r="BI155" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="BJ155" t="n">
-        <v>2.47</v>
+        <v>2.68</v>
       </c>
       <c r="BK155" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="BL155" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="BM155" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="BN155" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="BO155" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="BP155" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="156">
@@ -34569,7 +34569,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>8217551</v>
+        <v>8217266</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -34589,197 +34589,197 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['65', '71']</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>4.89</v>
+        <v>2.6</v>
       </c>
       <c r="R157" t="n">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="S157" t="n">
-        <v>2.38</v>
+        <v>3.96</v>
       </c>
       <c r="T157" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="U157" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V157" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="W157" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X157" t="n">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="Y157" t="n">
         <v>1.07</v>
       </c>
       <c r="Z157" t="n">
-        <v>4.18</v>
+        <v>2.1</v>
       </c>
       <c r="AA157" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AD157" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AE157" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS157" t="n">
         <v>1.29</v>
       </c>
-      <c r="AF157" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AG157" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH157" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AI157" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ157" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AK157" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL157" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM157" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN157" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO157" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AP157" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ157" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR157" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AS157" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AT157" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AU157" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AV157" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AW157" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX157" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AY157" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AZ157" t="n">
         <v>14</v>
       </c>
       <c r="BA157" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BB157" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BC157" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BD157" t="n">
-        <v>3.22</v>
+        <v>1.78</v>
       </c>
       <c r="BE157" t="n">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="BF157" t="n">
-        <v>1.54</v>
+        <v>2.54</v>
       </c>
       <c r="BG157" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="BH157" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BI157" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="BJ157" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="BK157" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="BL157" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BM157" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="BN157" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="BO157" t="n">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="BP157" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="158">
@@ -34787,7 +34787,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>8217266</v>
+        <v>8217551</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -34807,197 +34807,197 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>['65', '71']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>2.6</v>
+        <v>4.89</v>
       </c>
       <c r="R158" t="n">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="S158" t="n">
-        <v>3.96</v>
+        <v>2.38</v>
       </c>
       <c r="T158" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="U158" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V158" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="W158" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X158" t="n">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="Y158" t="n">
         <v>1.07</v>
       </c>
       <c r="Z158" t="n">
-        <v>2.1</v>
+        <v>4.18</v>
       </c>
       <c r="AA158" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AB158" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="AC158" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AD158" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF158" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AG158" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AI158" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AJ158" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AK158" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="AL158" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AM158" t="n">
-        <v>1.71</v>
+        <v>1.18</v>
       </c>
       <c r="AN158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO158" t="n">
         <v>1.83</v>
       </c>
-      <c r="AO158" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AP158" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.57</v>
+        <v>1.57</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="AT158" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AU158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW158" t="n">
         <v>7</v>
       </c>
-      <c r="AV158" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW158" t="n">
+      <c r="AX158" t="n">
         <v>8</v>
       </c>
-      <c r="AX158" t="n">
-        <v>12</v>
-      </c>
       <c r="AY158" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AZ158" t="n">
         <v>14</v>
       </c>
       <c r="BA158" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BB158" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BC158" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="BD158" t="n">
-        <v>1.78</v>
+        <v>3.22</v>
       </c>
       <c r="BE158" t="n">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BF158" t="n">
-        <v>2.54</v>
+        <v>1.54</v>
       </c>
       <c r="BG158" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="BH158" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BI158" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="BJ158" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="BK158" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="BL158" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BM158" t="n">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="BN158" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="BO158" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="BP158" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="159">
@@ -35005,7 +35005,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>8217536</v>
+        <v>8217538</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -35025,197 +35025,197 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>2</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>['72', '90']</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>3</v>
+      </c>
+      <c r="R159" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S159" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T159" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U159" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V159" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W159" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X159" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX159" t="n">
         <v>4</v>
       </c>
-      <c r="L159" t="n">
+      <c r="AY159" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO159" t="n">
         <v>3</v>
       </c>
-      <c r="M159" t="n">
-        <v>2</v>
-      </c>
-      <c r="N159" t="n">
-        <v>5</v>
-      </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>['27', '37', '87']</t>
-        </is>
-      </c>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>['6', '45+1']</t>
-        </is>
-      </c>
-      <c r="Q159" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R159" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S159" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T159" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U159" t="n">
-        <v>3</v>
-      </c>
-      <c r="V159" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="W159" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X159" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="Y159" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z159" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA159" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB159" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC159" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD159" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE159" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF159" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG159" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH159" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI159" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AJ159" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AK159" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL159" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM159" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AN159" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO159" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AP159" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AQ159" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR159" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AS159" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AT159" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AU159" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV159" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW159" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX159" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY159" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ159" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA159" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB159" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC159" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD159" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BE159" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="BF159" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BG159" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BH159" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="BI159" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BJ159" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BK159" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BL159" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BM159" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BN159" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BO159" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BP159" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="160">
@@ -35223,7 +35223,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>8217522</v>
+        <v>8217491</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -35243,149 +35243,149 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K160" t="n">
         <v>1</v>
       </c>
       <c r="L160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N160" t="n">
+        <v>2</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R160" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S160" t="n">
+        <v>3</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U160" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V160" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W160" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X160" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV160" t="n">
         <v>4</v>
       </c>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>['10', '68']</t>
-        </is>
-      </c>
-      <c r="P160" t="inlineStr">
-        <is>
-          <t>['51', '60']</t>
-        </is>
-      </c>
-      <c r="Q160" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="R160" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S160" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T160" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U160" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V160" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W160" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X160" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y160" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z160" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA160" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB160" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC160" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD160" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE160" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF160" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG160" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH160" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI160" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AJ160" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AK160" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL160" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AM160" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN160" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO160" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AP160" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ160" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR160" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AS160" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AT160" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU160" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV160" t="n">
+      <c r="AW160" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ160" t="n">
         <v>9</v>
-      </c>
-      <c r="AW160" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX160" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY160" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ160" t="n">
-        <v>19</v>
       </c>
       <c r="BA160" t="n">
         <v>4</v>
@@ -35397,43 +35397,43 @@
         <v>11</v>
       </c>
       <c r="BD160" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO160" t="n">
         <v>2.88</v>
       </c>
-      <c r="BE160" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF160" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BG160" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BH160" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI160" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BJ160" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BK160" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BL160" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM160" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BN160" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BO160" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BP160" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="161">
@@ -35441,7 +35441,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>8217538</v>
+        <v>8217471</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -35461,12 +35461,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="I161" t="n">
@@ -35482,176 +35482,176 @@
         <v>2</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N161" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>['72', '90']</t>
+          <t>['51', '90+5']</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['46', '90+1']</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="R161" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="S161" t="n">
-        <v>3.54</v>
+        <v>4.61</v>
       </c>
       <c r="T161" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="U161" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="V161" t="n">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="W161" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X161" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL161" t="n">
         <v>1.3</v>
       </c>
-      <c r="X161" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Y161" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z161" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA161" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB161" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC161" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD161" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE161" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF161" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG161" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AH161" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI161" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ161" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK161" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL161" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AM161" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AN161" t="n">
-        <v>2.17</v>
+        <v>1</v>
       </c>
       <c r="AO161" t="n">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.29</v>
+        <v>1</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.71</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AT161" t="n">
-        <v>2.69</v>
+        <v>2.93</v>
       </c>
       <c r="AU161" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV161" t="n">
         <v>3</v>
       </c>
-      <c r="AV161" t="n">
-        <v>1</v>
-      </c>
       <c r="AW161" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AX161" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY161" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AZ161" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BA161" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB161" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC161" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BD161" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="BE161" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
       <c r="BF161" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="BG161" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BH161" t="n">
-        <v>3.42</v>
+        <v>3.83</v>
       </c>
       <c r="BI161" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="BJ161" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="BK161" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="BL161" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BM161" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="BN161" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="BO161" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="BP161" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="162">
@@ -35659,7 +35659,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>8217539</v>
+        <v>8217536</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -35679,197 +35679,197 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K162" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '37', '87']</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '45+1']</t>
         </is>
       </c>
       <c r="Q162" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R162" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S162" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T162" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U162" t="n">
+        <v>3</v>
+      </c>
+      <c r="V162" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="W162" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X162" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z162" t="n">
         <v>2.65</v>
       </c>
-      <c r="R162" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="S162" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T162" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="U162" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V162" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="W162" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X162" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Y162" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z162" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AA162" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF162" t="n">
         <v>3.6</v>
       </c>
-      <c r="AB162" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AC162" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD162" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="AE162" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF162" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AG162" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI162" t="n">
         <v>1.7</v>
       </c>
-      <c r="AH162" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AI162" t="n">
+      <c r="AJ162" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ162" t="n">
         <v>1.57</v>
       </c>
-      <c r="AJ162" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AK162" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL162" t="n">
+      <c r="AR162" t="n">
         <v>1.27</v>
       </c>
-      <c r="AM162" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AN162" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO162" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AP162" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ162" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR162" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AS162" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AT162" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="AU162" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW162" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX162" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY162" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ162" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB162" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC162" t="n">
         <v>6</v>
       </c>
       <c r="BD162" t="n">
-        <v>1.61</v>
+        <v>2.02</v>
       </c>
       <c r="BE162" t="n">
-        <v>7</v>
+        <v>7.42</v>
       </c>
       <c r="BF162" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="BG162" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BH162" t="n">
-        <v>3.5</v>
+        <v>4.08</v>
       </c>
       <c r="BI162" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="BJ162" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="BK162" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="BL162" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BM162" t="n">
-        <v>2.29</v>
+        <v>2.04</v>
       </c>
       <c r="BN162" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="BO162" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BP162" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="163">
@@ -35877,7 +35877,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>8217469</v>
+        <v>8217470</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -35897,77 +35897,77 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="I163" t="n">
         <v>1</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L163" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N163" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>['45+9', '52', '69', '86']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '27']</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="R163" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="S163" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="T163" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U163" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="V163" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W163" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X163" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z163" t="n">
         <v>2.62</v>
       </c>
-      <c r="W163" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X163" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y163" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z163" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AA163" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AB163" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AC163" t="n">
         <v>1.01</v>
@@ -35976,25 +35976,25 @@
         <v>9</v>
       </c>
       <c r="AE163" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF163" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AG163" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AH163" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AI163" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AJ163" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AK163" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AL163" t="n">
         <v>1.3</v>
@@ -36003,91 +36003,91 @@
         <v>1.47</v>
       </c>
       <c r="AN163" t="n">
-        <v>0.83</v>
+        <v>2.17</v>
       </c>
       <c r="AO163" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="AT163" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AU163" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW163" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX163" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AY163" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ163" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="BA163" t="n">
         <v>5</v>
       </c>
       <c r="BB163" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH163" t="n">
         <v>3</v>
       </c>
-      <c r="BC163" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD163" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BE163" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF163" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BG163" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BH163" t="n">
-        <v>4</v>
-      </c>
       <c r="BI163" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="BJ163" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="BK163" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="BL163" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="BM163" t="n">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="BN163" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="BO163" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="BP163" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="164">
@@ -36095,7 +36095,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>8217491</v>
+        <v>8217522</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -36115,149 +36115,149 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K164" t="n">
         <v>1</v>
       </c>
       <c r="L164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N164" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['10', '68']</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['51', '60']</t>
         </is>
       </c>
       <c r="Q164" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S164" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U164" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V164" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W164" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X164" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF164" t="n">
         <v>3.2</v>
       </c>
-      <c r="R164" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="S164" t="n">
+      <c r="AG164" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU164" t="n">
         <v>3</v>
       </c>
-      <c r="T164" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U164" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V164" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W164" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X164" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Y164" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z164" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA164" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB164" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC164" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD164" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AE164" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF164" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG164" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH164" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AI164" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AJ164" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AK164" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AL164" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM164" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN164" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO164" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AP164" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ164" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AR164" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AS164" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AT164" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AU164" t="n">
-        <v>5</v>
-      </c>
       <c r="AV164" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW164" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX164" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AY164" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AZ164" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="BA164" t="n">
         <v>4</v>
@@ -36269,43 +36269,43 @@
         <v>11</v>
       </c>
       <c r="BD164" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="BE164" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="BF164" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="BG164" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BH164" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI164" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="BJ164" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="BK164" t="n">
-        <v>1.96</v>
+        <v>1.59</v>
       </c>
       <c r="BL164" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="BM164" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="BN164" t="n">
-        <v>1.49</v>
+        <v>1.74</v>
       </c>
       <c r="BO164" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="BP164" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="165">
@@ -36313,7 +36313,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>8217470</v>
+        <v>8217535</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -36333,77 +36333,77 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K165" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N165" t="n">
         <v>3</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['73', '81']</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>['7', '27']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="R165" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S165" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="T165" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="U165" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="V165" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="W165" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X165" t="n">
         <v>7</v>
       </c>
       <c r="Y165" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z165" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="AA165" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="AB165" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AC165" t="n">
         <v>1.01</v>
@@ -36412,118 +36412,118 @@
         <v>9</v>
       </c>
       <c r="AE165" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF165" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AG165" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH165" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AI165" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AJ165" t="n">
         <v>2.1</v>
       </c>
       <c r="AK165" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AL165" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AM165" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AN165" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AO165" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="AP165" t="n">
         <v>1.86</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AS165" t="n">
         <v>1.39</v>
       </c>
       <c r="AT165" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="AU165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ165" t="n">
         <v>7</v>
       </c>
-      <c r="AV165" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW165" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX165" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY165" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ165" t="n">
-        <v>13</v>
-      </c>
       <c r="BA165" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB165" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC165" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD165" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="BE165" t="n">
-        <v>6.15</v>
+        <v>8.5</v>
       </c>
       <c r="BF165" t="n">
-        <v>2.19</v>
+        <v>2.84</v>
       </c>
       <c r="BG165" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BH165" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="BI165" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="BJ165" t="n">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="BK165" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="BL165" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="BM165" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="BN165" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="BO165" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="BP165" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="166">
@@ -36531,7 +36531,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>8217471</v>
+        <v>8217537</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -36551,176 +36551,176 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="I166" t="n">
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N166" t="n">
+        <v>3</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>['12', '49', '51']</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R166" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S166" t="n">
         <v>4</v>
-      </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>['51', '90+5']</t>
-        </is>
-      </c>
-      <c r="P166" t="inlineStr">
-        <is>
-          <t>['46', '90+1']</t>
-        </is>
-      </c>
-      <c r="Q166" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="R166" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="S166" t="n">
-        <v>4.61</v>
       </c>
       <c r="T166" t="n">
         <v>1.4</v>
       </c>
       <c r="U166" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V166" t="n">
-        <v>3.16</v>
+        <v>2.77</v>
       </c>
       <c r="W166" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="X166" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y166" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z166" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AA166" t="n">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="AB166" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AC166" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AD166" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE166" t="n">
         <v>1.32</v>
       </c>
       <c r="AF166" t="n">
-        <v>2.85</v>
+        <v>3.32</v>
       </c>
       <c r="AG166" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AH166" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AI166" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AJ166" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AK166" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AL166" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AM166" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AN166" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AO166" t="n">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AP166" t="n">
         <v>1</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.71</v>
+        <v>1.43</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AS166" t="n">
-        <v>1.17</v>
+        <v>0.99</v>
       </c>
       <c r="AT166" t="n">
-        <v>2.93</v>
+        <v>2.53</v>
       </c>
       <c r="AU166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA166" t="n">
         <v>4</v>
       </c>
-      <c r="AV166" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW166" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX166" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY166" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ166" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA166" t="n">
-        <v>7</v>
-      </c>
       <c r="BB166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC166" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BD166" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="BE166" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BF166" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="BG166" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BH166" t="n">
-        <v>3.83</v>
+        <v>3.75</v>
       </c>
       <c r="BI166" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="BJ166" t="n">
         <v>2.63</v>
@@ -36729,19 +36729,19 @@
         <v>1.73</v>
       </c>
       <c r="BL166" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="BM166" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="BN166" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BO166" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="BP166" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="167">
@@ -36749,7 +36749,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>8217537</v>
+        <v>8217469</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -36769,197 +36769,197 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K167" t="n">
         <v>1</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M167" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
+          <t>['45+9', '52', '69', '86']</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>['12', '49', '51']</t>
-        </is>
-      </c>
       <c r="Q167" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="R167" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S167" t="n">
-        <v>4</v>
+        <v>3.13</v>
       </c>
       <c r="T167" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U167" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="V167" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="W167" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X167" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y167" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z167" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AA167" t="n">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="AB167" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="AC167" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AD167" t="n">
         <v>9</v>
       </c>
       <c r="AE167" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AF167" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="AG167" t="n">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AH167" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AI167" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AJ167" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="AK167" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AL167" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AM167" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AN167" t="n">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="AO167" t="n">
         <v>1.17</v>
       </c>
       <c r="AP167" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AR167" t="n">
-        <v>1.54</v>
+        <v>1.87</v>
       </c>
       <c r="AS167" t="n">
-        <v>0.99</v>
+        <v>1.12</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.53</v>
+        <v>2.99</v>
       </c>
       <c r="AU167" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV167" t="n">
         <v>3</v>
       </c>
-      <c r="AV167" t="n">
+      <c r="AW167" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC167" t="n">
         <v>8</v>
       </c>
-      <c r="AW167" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX167" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY167" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ167" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA167" t="n">
+      <c r="BD167" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH167" t="n">
         <v>4</v>
       </c>
-      <c r="BB167" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC167" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD167" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BE167" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BF167" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BG167" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH167" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BI167" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="BJ167" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="BK167" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BL167" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="BM167" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="BN167" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO167" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BP167" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="168">
@@ -36967,7 +36967,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>8217535</v>
+        <v>8217539</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -36987,197 +36987,197 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="I168" t="n">
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>['73', '81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="R168" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="S168" t="n">
-        <v>3.06</v>
+        <v>3.55</v>
       </c>
       <c r="T168" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="U168" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="V168" t="n">
-        <v>2.92</v>
+        <v>2.41</v>
       </c>
       <c r="W168" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="X168" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="Y168" t="n">
         <v>1.08</v>
       </c>
       <c r="Z168" t="n">
-        <v>2.71</v>
+        <v>2.15</v>
       </c>
       <c r="AA168" t="n">
-        <v>3.21</v>
+        <v>3.6</v>
       </c>
       <c r="AB168" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="AC168" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD168" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY168" t="n">
         <v>9</v>
       </c>
-      <c r="AE168" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF168" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG168" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH168" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI168" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AJ168" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AK168" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL168" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM168" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AN168" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO168" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AP168" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ168" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR168" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS168" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AT168" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AU168" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV168" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW168" t="n">
+      <c r="AZ168" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC168" t="n">
         <v>6</v>
       </c>
-      <c r="AX168" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY168" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ168" t="n">
+      <c r="BD168" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BE168" t="n">
         <v>7</v>
       </c>
-      <c r="BA168" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB168" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC168" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD168" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BE168" t="n">
-        <v>8.5</v>
-      </c>
       <c r="BF168" t="n">
-        <v>2.84</v>
+        <v>2.35</v>
       </c>
       <c r="BG168" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="BH168" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BI168" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="BJ168" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO168" t="n">
         <v>2.7</v>
       </c>
-      <c r="BK168" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BL168" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BM168" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BN168" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BO168" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BP168" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="169">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -32389,7 +32389,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>8217488</v>
+        <v>8217486</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -32409,197 +32409,197 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L147" t="n">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="Q147" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="R147" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S147" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U147" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V147" t="n">
         <v>2.5</v>
       </c>
-      <c r="R147" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S147" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T147" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U147" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="V147" t="n">
-        <v>2.73</v>
-      </c>
       <c r="W147" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X147" t="n">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="Y147" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z147" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AA147" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="AB147" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AC147" t="n">
         <v>1.05</v>
       </c>
       <c r="AD147" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AE147" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF147" t="n">
-        <v>3.52</v>
+        <v>3.85</v>
       </c>
       <c r="AG147" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AH147" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AI147" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AJ147" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AK147" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AL147" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AM147" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AN147" t="n">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="AO147" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR147" t="n">
         <v>1.5</v>
       </c>
-      <c r="AP147" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ147" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR147" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AS147" t="n">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AT147" t="n">
         <v>3.08</v>
       </c>
       <c r="AU147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW147" t="n">
         <v>9</v>
       </c>
-      <c r="AV147" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW147" t="n">
-        <v>16</v>
-      </c>
       <c r="AX147" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY147" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AZ147" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BA147" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BB147" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BC147" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="BD147" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="BE147" t="n">
-        <v>6.65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF147" t="n">
-        <v>2.43</v>
+        <v>3.35</v>
       </c>
       <c r="BG147" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BH147" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="BI147" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BJ147" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="BK147" t="n">
-        <v>2.13</v>
+        <v>1.74</v>
       </c>
       <c r="BL147" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BM147" t="n">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="BN147" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="BO147" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BP147" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="148">
@@ -32607,7 +32607,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>8217489</v>
+        <v>8217488</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -32627,197 +32627,197 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>['23', '41', '57']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>['90+10']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="R148" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S148" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="T148" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U148" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V148" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W148" t="n">
         <v>1.4</v>
       </c>
-      <c r="U148" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V148" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="W148" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X148" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="Y148" t="n">
         <v>1.05</v>
       </c>
       <c r="Z148" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BL148" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA148" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB148" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AC148" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD148" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE148" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF148" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG148" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AH148" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AI148" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AJ148" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK148" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AL148" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AM148" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AN148" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO148" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AP148" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ148" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR148" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AS148" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AT148" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU148" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV148" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW148" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX148" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY148" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ148" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA148" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB148" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC148" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD148" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BE148" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF148" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG148" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BH148" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI148" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BJ148" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BK148" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BL148" t="n">
-        <v>1.87</v>
-      </c>
       <c r="BM148" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BN148" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="BO148" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BP148" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="149">
@@ -32825,7 +32825,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>8217490</v>
+        <v>8217489</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -32845,197 +32845,197 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N149" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['23', '41', '57']</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+10']</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="R149" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S149" t="n">
-        <v>3.72</v>
+        <v>4.4</v>
       </c>
       <c r="T149" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="U149" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="V149" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="W149" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X149" t="n">
         <v>7</v>
       </c>
       <c r="Y149" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z149" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AA149" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB149" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="AC149" t="n">
         <v>1.01</v>
       </c>
       <c r="AD149" t="n">
-        <v>10.3</v>
+        <v>8.5</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF149" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO149" t="n">
         <v>3.45</v>
       </c>
-      <c r="AG149" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH149" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AI149" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AJ149" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AK149" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL149" t="n">
+      <c r="BP149" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AM149" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AN149" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AO149" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP149" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ149" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AR149" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AS149" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AT149" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU149" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV149" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW149" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX149" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY149" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ149" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA149" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB149" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC149" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD149" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BE149" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BF149" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BG149" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH149" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="BI149" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BJ149" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BK149" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BL149" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BM149" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BN149" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BO149" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BP149" t="n">
-        <v>1.34</v>
       </c>
     </row>
     <row r="150">
@@ -33043,7 +33043,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>8217449</v>
+        <v>8217490</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -33063,197 +33063,197 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="I150" t="n">
         <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>['20', '61']</t>
-        </is>
-      </c>
       <c r="Q150" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="R150" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S150" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="T150" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="U150" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="V150" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W150" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X150" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB150" t="n">
         <v>2.9</v>
       </c>
-      <c r="W150" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X150" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Y150" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA150" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB150" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AC150" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD150" t="n">
-        <v>7.9</v>
+        <v>10.3</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF150" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AG150" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AI150" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AJ150" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="AK150" t="n">
         <v>1.35</v>
       </c>
       <c r="AL150" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AM150" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AN150" t="n">
-        <v>0.17</v>
+        <v>0.83</v>
       </c>
       <c r="AO150" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.14</v>
+        <v>1.14</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AS150" t="n">
-        <v>0.86</v>
+        <v>1.05</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="AU150" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV150" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW150" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA150" t="n">
         <v>6</v>
       </c>
-      <c r="AX150" t="n">
+      <c r="BB150" t="n">
         <v>6</v>
       </c>
-      <c r="AY150" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ150" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA150" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB150" t="n">
-        <v>3</v>
-      </c>
       <c r="BC150" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BD150" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="BE150" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BF150" t="n">
-        <v>2.07</v>
+        <v>2.88</v>
       </c>
       <c r="BG150" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BH150" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="BI150" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BJ150" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="BK150" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="BL150" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="BM150" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="BN150" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="BO150" t="n">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="BP150" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="151">
@@ -33261,7 +33261,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>8217521</v>
+        <v>8217406</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -33281,197 +33281,197 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="I151" t="n">
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>['31', '68']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="R151" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="S151" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="T151" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="U151" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="V151" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="W151" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="X151" t="n">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="Y151" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z151" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AA151" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AB151" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="AC151" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AD151" t="n">
-        <v>8</v>
+        <v>10.4</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AF151" t="n">
-        <v>2.9</v>
+        <v>3.76</v>
       </c>
       <c r="AG151" t="n">
-        <v>2.27</v>
+        <v>1.83</v>
       </c>
       <c r="AH151" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="AI151" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AJ151" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AK151" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AL151" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AM151" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AN151" t="n">
-        <v>2.5</v>
+        <v>1.17</v>
       </c>
       <c r="AO151" t="n">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AP151" t="n">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="AS151" t="n">
         <v>1.31</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.56</v>
+        <v>3.18</v>
       </c>
       <c r="AU151" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AV151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW151" t="n">
         <v>13</v>
       </c>
       <c r="AX151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ151" t="n">
         <v>4</v>
       </c>
-      <c r="AY151" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ151" t="n">
-        <v>6</v>
-      </c>
       <c r="BA151" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BB151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BC151" t="n">
         <v>14</v>
       </c>
       <c r="BD151" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="BE151" t="n">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="BF151" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="BG151" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BH151" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="BI151" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BJ151" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BK151" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="BL151" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="BM151" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="BN151" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="BO151" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BP151" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="152">
@@ -33479,7 +33479,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>8217486</v>
+        <v>8217449</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -33499,197 +33499,197 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J152" t="n">
         <v>1</v>
       </c>
       <c r="K152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N152" t="n">
         <v>2</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['20', '61']</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="R152" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="S152" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="T152" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="U152" t="n">
-        <v>3.22</v>
+        <v>2.83</v>
       </c>
       <c r="V152" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="W152" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="X152" t="n">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="Y152" t="n">
         <v>1.07</v>
       </c>
       <c r="Z152" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AA152" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="AB152" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AC152" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AD152" t="n">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AF152" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="AG152" t="n">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AH152" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="AI152" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="AJ152" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AK152" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG152" t="n">
         <v>1.2</v>
       </c>
-      <c r="AL152" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM152" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AN152" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AO152" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AP152" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AQ152" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AR152" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS152" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AT152" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AU152" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV152" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW152" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX152" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY152" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ152" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA152" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB152" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC152" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD152" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BE152" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF152" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG152" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BH152" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="BI152" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BJ152" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="BK152" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="BL152" t="n">
         <v>1.95</v>
       </c>
       <c r="BM152" t="n">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="BN152" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="BO152" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="BP152" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="153">
@@ -33697,7 +33697,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>8217485</v>
+        <v>8217468</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -33717,197 +33717,197 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
         <v>1</v>
       </c>
       <c r="L153" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
         <v>4</v>
       </c>
-      <c r="N153" t="n">
-        <v>5</v>
-      </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['8', '72', '79', '90+3']</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>['33', '51', '73', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>2.45</v>
+        <v>3.95</v>
       </c>
       <c r="R153" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S153" t="n">
-        <v>4.15</v>
+        <v>2.62</v>
       </c>
       <c r="T153" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U153" t="n">
         <v>2.88</v>
       </c>
       <c r="V153" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="W153" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X153" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="Y153" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z153" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA153" t="n">
-        <v>3.2</v>
+        <v>3.69</v>
       </c>
       <c r="AB153" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="AC153" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AD153" t="n">
-        <v>8.949999999999999</v>
+        <v>9</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AF153" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="AG153" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH153" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AI153" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AJ153" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AK153" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AL153" t="n">
         <v>1.25</v>
       </c>
       <c r="AM153" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AN153" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AO153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.29</v>
+        <v>1.71</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AT153" t="n">
-        <v>2.47</v>
+        <v>3.09</v>
       </c>
       <c r="AU153" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV153" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AW153" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX153" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AY153" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AZ153" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BA153" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BB153" t="n">
         <v>5</v>
       </c>
       <c r="BC153" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BD153" t="n">
-        <v>1.53</v>
+        <v>2.27</v>
       </c>
       <c r="BE153" t="n">
-        <v>8.4</v>
+        <v>6.35</v>
       </c>
       <c r="BF153" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="BG153" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BH153" t="n">
-        <v>3.56</v>
+        <v>3.37</v>
       </c>
       <c r="BI153" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BJ153" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="BK153" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="BL153" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BM153" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="BN153" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="BO153" t="n">
-        <v>2.85</v>
+        <v>3.11</v>
       </c>
       <c r="BP153" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="154">
@@ -33915,7 +33915,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>8217468</v>
+        <v>8217521</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -33935,197 +33935,197 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K154" t="n">
         <v>1</v>
       </c>
       <c r="L154" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>['8', '72', '79', '90+3']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31', '68']</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>3.95</v>
+        <v>2.48</v>
       </c>
       <c r="R154" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="S154" t="n">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="T154" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="U154" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="V154" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="W154" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="X154" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="Y154" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Z154" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="AA154" t="n">
-        <v>3.69</v>
+        <v>3.25</v>
       </c>
       <c r="AB154" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI154" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC154" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD154" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE154" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF154" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AG154" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH154" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI154" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AJ154" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AK154" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AL154" t="n">
         <v>1.25</v>
       </c>
       <c r="AM154" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR154" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN154" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO154" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP154" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ154" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR154" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AS154" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AT154" t="n">
-        <v>3.09</v>
+        <v>2.56</v>
       </c>
       <c r="AU154" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AV154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW154" t="n">
         <v>13</v>
       </c>
       <c r="AX154" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY154" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AZ154" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA154" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="BB154" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BC154" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD154" t="n">
-        <v>2.27</v>
+        <v>1.45</v>
       </c>
       <c r="BE154" t="n">
-        <v>6.35</v>
+        <v>8.9</v>
       </c>
       <c r="BF154" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="BG154" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BH154" t="n">
-        <v>3.37</v>
+        <v>3.92</v>
       </c>
       <c r="BI154" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BJ154" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="BK154" t="n">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="BL154" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="BM154" t="n">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="BN154" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="BO154" t="n">
-        <v>3.11</v>
+        <v>2.71</v>
       </c>
       <c r="BP154" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="155">
@@ -34133,7 +34133,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>8217406</v>
+        <v>8217485</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -34153,197 +34153,197 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="I155" t="n">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N155" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['33', '51', '73', '79']</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R155" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="S155" t="n">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="T155" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U155" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V155" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W155" t="n">
         <v>1.36</v>
       </c>
-      <c r="U155" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V155" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="W155" t="n">
-        <v>1.42</v>
-      </c>
       <c r="X155" t="n">
-        <v>6.25</v>
+        <v>7.3</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z155" t="n">
         <v>2.05</v>
       </c>
       <c r="AA155" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AB155" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AD155" t="n">
-        <v>10.4</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF155" t="n">
-        <v>3.76</v>
+        <v>3.22</v>
       </c>
       <c r="AG155" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH155" t="n">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="AI155" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN155" t="n">
         <v>1.67</v>
       </c>
-      <c r="AJ155" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AK155" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AL155" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AM155" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AN155" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AO155" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP155" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.87</v>
+        <v>1.24</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AT155" t="n">
-        <v>3.18</v>
+        <v>2.47</v>
       </c>
       <c r="AU155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB155" t="n">
         <v>5</v>
       </c>
-      <c r="AV155" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW155" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX155" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY155" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ155" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA155" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB155" t="n">
-        <v>2</v>
-      </c>
       <c r="BC155" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BD155" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="BE155" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF155" t="n">
-        <v>3.14</v>
+        <v>2.64</v>
       </c>
       <c r="BG155" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BH155" t="n">
-        <v>3.89</v>
+        <v>3.56</v>
       </c>
       <c r="BI155" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="BJ155" t="n">
-        <v>2.68</v>
+        <v>2.47</v>
       </c>
       <c r="BK155" t="n">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="BL155" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="BM155" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="BN155" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="BO155" t="n">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="BP155" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="156">
@@ -34569,7 +34569,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>8217266</v>
+        <v>8217551</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -34589,197 +34589,197 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>['65', '71']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>2.6</v>
+        <v>4.89</v>
       </c>
       <c r="R157" t="n">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="S157" t="n">
-        <v>3.96</v>
+        <v>2.38</v>
       </c>
       <c r="T157" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="U157" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V157" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="W157" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X157" t="n">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="Y157" t="n">
         <v>1.07</v>
       </c>
       <c r="Z157" t="n">
-        <v>2.1</v>
+        <v>4.18</v>
       </c>
       <c r="AA157" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AB157" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AD157" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF157" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AG157" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AI157" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AJ157" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AK157" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="AL157" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AM157" t="n">
-        <v>1.71</v>
+        <v>1.18</v>
       </c>
       <c r="AN157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO157" t="n">
         <v>1.83</v>
       </c>
-      <c r="AO157" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AP157" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.57</v>
+        <v>1.57</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AS157" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AU157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW157" t="n">
         <v>7</v>
       </c>
-      <c r="AV157" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW157" t="n">
+      <c r="AX157" t="n">
         <v>8</v>
       </c>
-      <c r="AX157" t="n">
-        <v>12</v>
-      </c>
       <c r="AY157" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AZ157" t="n">
         <v>14</v>
       </c>
       <c r="BA157" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BB157" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BC157" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="BD157" t="n">
-        <v>1.78</v>
+        <v>3.22</v>
       </c>
       <c r="BE157" t="n">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BF157" t="n">
-        <v>2.54</v>
+        <v>1.54</v>
       </c>
       <c r="BG157" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="BH157" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BI157" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="BJ157" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="BK157" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="BL157" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BM157" t="n">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="BN157" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="BO157" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="BP157" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="158">
@@ -34787,7 +34787,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>8217551</v>
+        <v>8217266</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -34807,197 +34807,197 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['65', '71']</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>4.89</v>
+        <v>2.6</v>
       </c>
       <c r="R158" t="n">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="S158" t="n">
-        <v>2.38</v>
+        <v>3.96</v>
       </c>
       <c r="T158" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="U158" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V158" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="W158" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X158" t="n">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="Y158" t="n">
         <v>1.07</v>
       </c>
       <c r="Z158" t="n">
-        <v>4.18</v>
+        <v>2.1</v>
       </c>
       <c r="AA158" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="AC158" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AD158" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AE158" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS158" t="n">
         <v>1.29</v>
       </c>
-      <c r="AF158" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AG158" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH158" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AI158" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ158" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AK158" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL158" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM158" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN158" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO158" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AP158" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ158" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR158" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AS158" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AT158" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AU158" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AV158" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AW158" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX158" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AY158" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AZ158" t="n">
         <v>14</v>
       </c>
       <c r="BA158" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BB158" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BC158" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BD158" t="n">
-        <v>3.22</v>
+        <v>1.78</v>
       </c>
       <c r="BE158" t="n">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="BF158" t="n">
-        <v>1.54</v>
+        <v>2.54</v>
       </c>
       <c r="BG158" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="BH158" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BI158" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="BJ158" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="BK158" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="BL158" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BM158" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="BN158" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="BO158" t="n">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="BP158" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="159">
@@ -35005,7 +35005,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>8217538</v>
+        <v>8217536</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -35025,197 +35025,197 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K159" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N159" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>['72', '90']</t>
+          <t>['27', '37', '87']</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '45+1']</t>
         </is>
       </c>
       <c r="Q159" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R159" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S159" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T159" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U159" t="n">
         <v>3</v>
       </c>
-      <c r="R159" t="n">
+      <c r="V159" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="W159" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X159" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH159" t="n">
         <v>1.91</v>
       </c>
-      <c r="S159" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="T159" t="n">
+      <c r="AI159" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM159" t="n">
         <v>1.48</v>
       </c>
-      <c r="U159" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V159" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="W159" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X159" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Y159" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z159" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA159" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB159" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC159" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD159" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE159" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF159" t="n">
+      <c r="AN159" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ159" t="n">
         <v>2.8</v>
       </c>
-      <c r="AG159" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AH159" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI159" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ159" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK159" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL159" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM159" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN159" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO159" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP159" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AQ159" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AR159" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AS159" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AT159" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AU159" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV159" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW159" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX159" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY159" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ159" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA159" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB159" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC159" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD159" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BE159" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="BF159" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BG159" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BH159" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BI159" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BJ159" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BK159" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="BL159" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="BM159" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="BN159" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="BO159" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="BP159" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="160">
@@ -35223,7 +35223,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>8217491</v>
+        <v>8217522</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -35243,149 +35243,149 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K160" t="n">
         <v>1</v>
       </c>
       <c r="L160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N160" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['10', '68']</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['51', '60']</t>
         </is>
       </c>
       <c r="Q160" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="R160" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S160" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U160" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V160" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W160" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X160" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF160" t="n">
         <v>3.2</v>
       </c>
-      <c r="R160" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="S160" t="n">
+      <c r="AG160" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU160" t="n">
         <v>3</v>
       </c>
-      <c r="T160" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U160" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V160" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W160" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X160" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Y160" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z160" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA160" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB160" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC160" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD160" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AE160" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF160" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG160" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH160" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AI160" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AJ160" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AK160" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AL160" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM160" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN160" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO160" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AP160" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ160" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AR160" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AS160" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AT160" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AU160" t="n">
-        <v>5</v>
-      </c>
       <c r="AV160" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW160" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX160" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AY160" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AZ160" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="BA160" t="n">
         <v>4</v>
@@ -35397,43 +35397,43 @@
         <v>11</v>
       </c>
       <c r="BD160" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="BE160" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="BF160" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="BG160" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BH160" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI160" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="BJ160" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="BK160" t="n">
-        <v>1.96</v>
+        <v>1.59</v>
       </c>
       <c r="BL160" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="BM160" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="BN160" t="n">
-        <v>1.49</v>
+        <v>1.74</v>
       </c>
       <c r="BO160" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="BP160" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="161">
@@ -35441,7 +35441,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>8217471</v>
+        <v>8217538</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -35461,12 +35461,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="I161" t="n">
@@ -35482,176 +35482,176 @@
         <v>2</v>
       </c>
       <c r="M161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>['51', '90+5']</t>
+          <t>['72', '90']</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>['46', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="R161" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="S161" t="n">
-        <v>4.61</v>
+        <v>3.54</v>
       </c>
       <c r="T161" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="U161" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="V161" t="n">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="W161" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X161" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD161" t="n">
         <v>7.5</v>
       </c>
-      <c r="Y161" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z161" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA161" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB161" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AC161" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD161" t="n">
-        <v>8</v>
-      </c>
       <c r="AE161" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AF161" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AG161" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AI161" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AJ161" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AK161" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL161" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL161" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AM161" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AN161" t="n">
-        <v>1</v>
+        <v>2.17</v>
       </c>
       <c r="AO161" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AP161" t="n">
-        <v>1</v>
+        <v>2.29</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.71</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AT161" t="n">
-        <v>2.93</v>
+        <v>2.69</v>
       </c>
       <c r="AU161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX161" t="n">
         <v>4</v>
       </c>
-      <c r="AV161" t="n">
+      <c r="AY161" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO161" t="n">
         <v>3</v>
       </c>
-      <c r="AW161" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX161" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY161" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ161" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA161" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB161" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC161" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD161" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BE161" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF161" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG161" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BH161" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="BI161" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BJ161" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BK161" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BL161" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BM161" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BN161" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BO161" t="n">
-        <v>2.76</v>
-      </c>
       <c r="BP161" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="162">
@@ -35659,7 +35659,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>8217536</v>
+        <v>8217539</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -35679,197 +35679,197 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R162" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S162" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T162" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U162" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V162" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="W162" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X162" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB162" t="n">
         <v>5</v>
-      </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>['27', '37', '87']</t>
-        </is>
-      </c>
-      <c r="P162" t="inlineStr">
-        <is>
-          <t>['6', '45+1']</t>
-        </is>
-      </c>
-      <c r="Q162" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R162" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S162" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T162" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U162" t="n">
-        <v>3</v>
-      </c>
-      <c r="V162" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="W162" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X162" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="Y162" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z162" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA162" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB162" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC162" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD162" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE162" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF162" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG162" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH162" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI162" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AJ162" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AK162" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL162" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM162" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AN162" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO162" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AP162" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AQ162" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR162" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AS162" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AT162" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AU162" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV162" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW162" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX162" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY162" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ162" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA162" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB162" t="n">
-        <v>3</v>
       </c>
       <c r="BC162" t="n">
         <v>6</v>
       </c>
       <c r="BD162" t="n">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="BE162" t="n">
-        <v>7.42</v>
+        <v>7</v>
       </c>
       <c r="BF162" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="BG162" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BH162" t="n">
-        <v>4.08</v>
+        <v>3.5</v>
       </c>
       <c r="BI162" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="BJ162" t="n">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="BK162" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="BL162" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BM162" t="n">
-        <v>2.04</v>
+        <v>2.29</v>
       </c>
       <c r="BN162" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BO162" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BP162" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="163">
@@ -35877,7 +35877,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>8217470</v>
+        <v>8217469</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -35897,77 +35897,77 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="I163" t="n">
         <v>1</v>
       </c>
       <c r="J163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L163" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['45+9', '52', '69', '86']</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>['7', '27']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="R163" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="S163" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="T163" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U163" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="V163" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="W163" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X163" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="Y163" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z163" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="AA163" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AB163" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AC163" t="n">
         <v>1.01</v>
@@ -35976,25 +35976,25 @@
         <v>9</v>
       </c>
       <c r="AE163" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF163" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AG163" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AH163" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AI163" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AJ163" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AK163" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AL163" t="n">
         <v>1.3</v>
@@ -36003,91 +36003,91 @@
         <v>1.47</v>
       </c>
       <c r="AN163" t="n">
-        <v>2.17</v>
+        <v>0.83</v>
       </c>
       <c r="AO163" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.86</v>
+        <v>1.14</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.71</v>
+        <v>1</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="AT163" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="AU163" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW163" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX163" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AY163" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ163" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="BA163" t="n">
         <v>5</v>
       </c>
       <c r="BB163" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC163" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD163" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL163" t="n">
         <v>2.08</v>
       </c>
-      <c r="BE163" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="BF163" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BG163" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BH163" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI163" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BJ163" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BK163" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BL163" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BM163" t="n">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="BN163" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="BO163" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="BP163" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="164">
@@ -36095,7 +36095,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>8217522</v>
+        <v>8217491</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -36115,149 +36115,149 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K164" t="n">
         <v>1</v>
       </c>
       <c r="L164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N164" t="n">
+        <v>2</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S164" t="n">
+        <v>3</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U164" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V164" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W164" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X164" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV164" t="n">
         <v>4</v>
       </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>['10', '68']</t>
-        </is>
-      </c>
-      <c r="P164" t="inlineStr">
-        <is>
-          <t>['51', '60']</t>
-        </is>
-      </c>
-      <c r="Q164" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="R164" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S164" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T164" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U164" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V164" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W164" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X164" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y164" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z164" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA164" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB164" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC164" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD164" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE164" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF164" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG164" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH164" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI164" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AJ164" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AK164" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL164" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AM164" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN164" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO164" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AP164" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ164" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR164" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AS164" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AT164" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU164" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV164" t="n">
+      <c r="AW164" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ164" t="n">
         <v>9</v>
-      </c>
-      <c r="AW164" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX164" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY164" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ164" t="n">
-        <v>19</v>
       </c>
       <c r="BA164" t="n">
         <v>4</v>
@@ -36269,43 +36269,43 @@
         <v>11</v>
       </c>
       <c r="BD164" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO164" t="n">
         <v>2.88</v>
       </c>
-      <c r="BE164" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF164" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BG164" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BH164" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI164" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BJ164" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BK164" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BL164" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM164" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BN164" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BO164" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BP164" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="165">
@@ -36313,7 +36313,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>8217535</v>
+        <v>8217470</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -36333,77 +36333,77 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N165" t="n">
         <v>3</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>['73', '81']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['7', '27']</t>
         </is>
       </c>
       <c r="Q165" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R165" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S165" t="n">
         <v>3.2</v>
       </c>
-      <c r="R165" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S165" t="n">
-        <v>3.06</v>
-      </c>
       <c r="T165" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="U165" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V165" t="n">
         <v>2.8</v>
       </c>
-      <c r="V165" t="n">
-        <v>2.92</v>
-      </c>
       <c r="W165" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X165" t="n">
         <v>7</v>
       </c>
       <c r="Y165" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z165" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AA165" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="AB165" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AC165" t="n">
         <v>1.01</v>
@@ -36412,118 +36412,118 @@
         <v>9</v>
       </c>
       <c r="AE165" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF165" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AG165" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH165" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AI165" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AJ165" t="n">
         <v>2.1</v>
       </c>
       <c r="AK165" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AL165" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AM165" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AN165" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AO165" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP165" t="n">
         <v>1.86</v>
       </c>
       <c r="AQ165" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AS165" t="n">
         <v>1.39</v>
       </c>
       <c r="AT165" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="AU165" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH165" t="n">
         <v>3</v>
       </c>
-      <c r="AW165" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX165" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY165" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ165" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA165" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB165" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC165" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD165" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BE165" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BF165" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BG165" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BH165" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BI165" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="BJ165" t="n">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="BK165" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL165" t="n">
         <v>1.7</v>
       </c>
-      <c r="BL165" t="n">
-        <v>1.9</v>
-      </c>
       <c r="BM165" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="BN165" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="BO165" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="BP165" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="166">
@@ -36531,7 +36531,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>8217537</v>
+        <v>8217471</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -36551,176 +36551,176 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="I166" t="n">
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M166" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N166" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51', '90+5']</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>['12', '49', '51']</t>
+          <t>['46', '90+1']</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="R166" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S166" t="n">
-        <v>4</v>
+        <v>4.61</v>
       </c>
       <c r="T166" t="n">
         <v>1.4</v>
       </c>
       <c r="U166" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V166" t="n">
-        <v>2.77</v>
+        <v>3.16</v>
       </c>
       <c r="W166" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="X166" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="Y166" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z166" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AA166" t="n">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="AB166" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AC166" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AD166" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE166" t="n">
         <v>1.32</v>
       </c>
       <c r="AF166" t="n">
-        <v>3.32</v>
+        <v>2.85</v>
       </c>
       <c r="AG166" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AH166" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AI166" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AJ166" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AK166" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG166" t="n">
         <v>1.18</v>
       </c>
-      <c r="AL166" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AM166" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AN166" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO166" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AP166" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ166" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR166" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AS166" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="AT166" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AU166" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV166" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW166" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX166" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY166" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ166" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA166" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB166" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC166" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD166" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BE166" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BF166" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BG166" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BH166" t="n">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
       <c r="BI166" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BJ166" t="n">
         <v>2.63</v>
@@ -36729,19 +36729,19 @@
         <v>1.73</v>
       </c>
       <c r="BL166" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="BM166" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="BN166" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BO166" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="BP166" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="167">
@@ -36749,7 +36749,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>8217469</v>
+        <v>8217537</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -36769,197 +36769,197 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K167" t="n">
         <v>1</v>
       </c>
       <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>3</v>
+      </c>
+      <c r="N167" t="n">
+        <v>3</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>['12', '49', '51']</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R167" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S167" t="n">
         <v>4</v>
       </c>
-      <c r="M167" t="n">
-        <v>0</v>
-      </c>
-      <c r="N167" t="n">
-        <v>4</v>
-      </c>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>['45+9', '52', '69', '86']</t>
-        </is>
-      </c>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q167" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R167" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="S167" t="n">
-        <v>3.13</v>
-      </c>
       <c r="T167" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U167" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="V167" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="W167" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X167" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="Y167" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z167" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AA167" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="AB167" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AC167" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD167" t="n">
         <v>9</v>
       </c>
       <c r="AE167" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL167" t="n">
         <v>1.24</v>
       </c>
-      <c r="AF167" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG167" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AH167" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI167" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AJ167" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AK167" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL167" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AM167" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="AN167" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="AO167" t="n">
         <v>1.17</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR167" t="n">
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
       <c r="AS167" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.99</v>
+        <v>2.53</v>
       </c>
       <c r="AU167" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC167" t="n">
         <v>5</v>
       </c>
-      <c r="AV167" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW167" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX167" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY167" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ167" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA167" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB167" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC167" t="n">
-        <v>8</v>
-      </c>
       <c r="BD167" t="n">
-        <v>1.89</v>
+        <v>1.54</v>
       </c>
       <c r="BE167" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BF167" t="n">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="BG167" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BH167" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BI167" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="BJ167" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="BK167" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BL167" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="BM167" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="BN167" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="BO167" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BP167" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="168">
@@ -36967,7 +36967,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>8217539</v>
+        <v>8217535</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -36987,197 +36987,197 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="I168" t="n">
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73', '81']</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="R168" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="S168" t="n">
-        <v>3.55</v>
+        <v>3.06</v>
       </c>
       <c r="T168" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="U168" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="V168" t="n">
-        <v>2.41</v>
+        <v>2.92</v>
       </c>
       <c r="W168" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="X168" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="Y168" t="n">
         <v>1.08</v>
       </c>
       <c r="Z168" t="n">
-        <v>2.15</v>
+        <v>2.71</v>
       </c>
       <c r="AA168" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH168" t="n">
         <v>3.6</v>
       </c>
-      <c r="AB168" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AC168" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD168" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="AE168" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF168" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AG168" t="n">
+      <c r="BI168" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK168" t="n">
         <v>1.7</v>
       </c>
-      <c r="AH168" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AI168" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ168" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AK168" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL168" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AM168" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AN168" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO168" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AP168" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ168" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR168" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AS168" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AT168" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AU168" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV168" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW168" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX168" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY168" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ168" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA168" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB168" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC168" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD168" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BE168" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF168" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BG168" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BH168" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI168" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BJ168" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="BK168" t="n">
-        <v>2.05</v>
-      </c>
       <c r="BL168" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BM168" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="BN168" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BO168" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="BP168" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="169">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -37341,13 +37341,13 @@
         <v>11</v>
       </c>
       <c r="AX169" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY169" t="n">
         <v>15</v>
       </c>
       <c r="AZ169" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA169" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -32389,7 +32389,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>8217486</v>
+        <v>8217468</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -32409,197 +32409,197 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="I147" t="n">
         <v>1</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L147" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>['8', '72', '79', '90+3']</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q147" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R147" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S147" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U147" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V147" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X147" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD147" t="n">
         <v>2.27</v>
       </c>
-      <c r="R147" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S147" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T147" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="U147" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V147" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W147" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X147" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA147" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB147" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AC147" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD147" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE147" t="n">
+      <c r="BE147" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG147" t="n">
         <v>1.24</v>
       </c>
-      <c r="AF147" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AG147" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH147" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AI147" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AJ147" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK147" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AL147" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM147" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AN147" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AO147" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AP147" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AQ147" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AR147" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS147" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AT147" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AU147" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV147" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW147" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX147" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY147" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ147" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA147" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB147" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC147" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD147" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BE147" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF147" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG147" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BH147" t="n">
-        <v>3.52</v>
+        <v>3.37</v>
       </c>
       <c r="BI147" t="n">
         <v>1.46</v>
       </c>
       <c r="BJ147" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BK147" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="BL147" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="BM147" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="BN147" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="BO147" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="BP147" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="148">
@@ -32607,7 +32607,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>8217488</v>
+        <v>8217490</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -32627,12 +32627,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -32664,160 +32664,160 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="R148" t="n">
         <v>2.1</v>
       </c>
       <c r="S148" t="n">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="T148" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="U148" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="V148" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="W148" t="n">
         <v>1.4</v>
       </c>
       <c r="X148" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="Y148" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z148" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AA148" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AB148" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC148" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AD148" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="AE148" t="n">
         <v>1.25</v>
       </c>
       <c r="AF148" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="AG148" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AH148" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AI148" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AJ148" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AK148" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AL148" t="n">
         <v>1.28</v>
       </c>
       <c r="AM148" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AN148" t="n">
-        <v>1.67</v>
+        <v>0.83</v>
       </c>
       <c r="AO148" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.86</v>
+        <v>1.14</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.29</v>
+        <v>0.57</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AT148" t="n">
-        <v>3.08</v>
+        <v>2.28</v>
       </c>
       <c r="AU148" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW148" t="n">
         <v>9</v>
       </c>
-      <c r="AV148" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW148" t="n">
-        <v>16</v>
-      </c>
       <c r="AX148" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AY148" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AZ148" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="BA148" t="n">
         <v>6</v>
       </c>
       <c r="BB148" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BC148" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BD148" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BE148" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="BF148" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="BG148" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BH148" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="BI148" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="BJ148" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="BK148" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="BL148" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="BM148" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="BN148" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BO148" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="BP148" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="149">
@@ -33043,7 +33043,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>8217490</v>
+        <v>8217488</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -33063,12 +33063,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -33091,7 +33091,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -33100,160 +33100,160 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="R150" t="n">
         <v>2.1</v>
       </c>
       <c r="S150" t="n">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="T150" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="U150" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="V150" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="W150" t="n">
         <v>1.4</v>
       </c>
       <c r="X150" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="Y150" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z150" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AA150" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB150" t="n">
         <v>3.4</v>
       </c>
-      <c r="AB150" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AC150" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AD150" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="AE150" t="n">
         <v>1.25</v>
       </c>
       <c r="AF150" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="AG150" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AI150" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AJ150" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AK150" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AL150" t="n">
         <v>1.28</v>
       </c>
       <c r="AM150" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AN150" t="n">
-        <v>0.83</v>
+        <v>1.67</v>
       </c>
       <c r="AO150" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.57</v>
+        <v>1.29</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.23</v>
+        <v>1.87</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.28</v>
+        <v>3.08</v>
       </c>
       <c r="AU150" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AV150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ150" t="n">
         <v>3</v>
-      </c>
-      <c r="AW150" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX150" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY150" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ150" t="n">
-        <v>15</v>
       </c>
       <c r="BA150" t="n">
         <v>6</v>
       </c>
       <c r="BB150" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC150" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BD150" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BE150" t="n">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
       <c r="BF150" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="BG150" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BH150" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="BI150" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="BJ150" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="BK150" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="BL150" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="BM150" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="BN150" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BO150" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="BP150" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="151">
@@ -33261,7 +33261,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>8217406</v>
+        <v>8217486</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -33281,197 +33281,197 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
         <v>1</v>
       </c>
       <c r="N151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="R151" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="S151" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T151" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U151" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V151" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W151" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X151" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF151" t="n">
         <v>3.85</v>
       </c>
-      <c r="T151" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U151" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V151" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="W151" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X151" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Y151" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z151" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA151" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB151" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AC151" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AE151" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF151" t="n">
-        <v>3.76</v>
-      </c>
       <c r="AG151" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH151" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AI151" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AJ151" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AK151" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AL151" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AM151" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AN151" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO151" t="n">
         <v>1.17</v>
       </c>
-      <c r="AO151" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AP151" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.14</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AS151" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH151" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI151" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ151" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK151" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL151" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM151" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN151" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO151" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BP151" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AT151" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AU151" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV151" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW151" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX151" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY151" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ151" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA151" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB151" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC151" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD151" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BE151" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF151" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BG151" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BH151" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="BI151" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BJ151" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BK151" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BL151" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BM151" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BN151" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BO151" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BP151" t="n">
-        <v>1.34</v>
       </c>
     </row>
     <row r="152">
@@ -33479,7 +33479,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>8217449</v>
+        <v>8217485</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -33499,12 +33499,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -33517,179 +33517,179 @@
         <v>1</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N152" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>['20', '61']</t>
+          <t>['33', '51', '73', '79']</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="R152" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S152" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="T152" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U152" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="V152" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="W152" t="n">
         <v>1.36</v>
       </c>
       <c r="X152" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="Y152" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z152" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AA152" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB152" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AC152" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AD152" t="n">
-        <v>7.9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF152" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AG152" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH152" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AI152" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AJ152" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AK152" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AL152" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AM152" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AN152" t="n">
-        <v>0.17</v>
+        <v>1.67</v>
       </c>
       <c r="AO152" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP152" t="n">
-        <v>0.14</v>
+        <v>1.43</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.71</v>
+        <v>1.29</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AS152" t="n">
-        <v>0.86</v>
+        <v>1.23</v>
       </c>
       <c r="AT152" t="n">
-        <v>2.01</v>
+        <v>2.47</v>
       </c>
       <c r="AU152" t="n">
         <v>2</v>
       </c>
       <c r="AV152" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW152" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA152" t="n">
         <v>6</v>
       </c>
-      <c r="AX152" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY152" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ152" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA152" t="n">
-        <v>3</v>
-      </c>
       <c r="BB152" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC152" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BD152" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="BE152" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF152" t="n">
-        <v>2.07</v>
+        <v>2.64</v>
       </c>
       <c r="BG152" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BH152" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="BI152" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BJ152" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="BK152" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="BL152" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BM152" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="BN152" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BO152" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="BP152" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="153">
@@ -33697,7 +33697,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>8217468</v>
+        <v>8217406</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -33717,197 +33717,197 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N153" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>['8', '72', '79', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>3.95</v>
+        <v>2.55</v>
       </c>
       <c r="R153" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S153" t="n">
-        <v>2.62</v>
+        <v>3.85</v>
       </c>
       <c r="T153" t="n">
         <v>1.36</v>
       </c>
       <c r="U153" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V153" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="W153" t="n">
         <v>1.42</v>
       </c>
       <c r="X153" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="Y153" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z153" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA153" t="n">
         <v>3.5</v>
       </c>
-      <c r="AA153" t="n">
-        <v>3.69</v>
-      </c>
       <c r="AB153" t="n">
-        <v>1.95</v>
+        <v>3.35</v>
       </c>
       <c r="AC153" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AD153" t="n">
-        <v>9</v>
+        <v>10.4</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF153" t="n">
-        <v>3.34</v>
+        <v>3.76</v>
       </c>
       <c r="AG153" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AH153" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AI153" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AJ153" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AK153" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AL153" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AM153" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AN153" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AO153" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.71</v>
+        <v>1.14</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.59</v>
+        <v>1.87</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AT153" t="n">
-        <v>3.09</v>
+        <v>3.18</v>
       </c>
       <c r="AU153" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW153" t="n">
         <v>13</v>
       </c>
       <c r="AX153" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY153" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ153" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA153" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="BB153" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC153" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD153" t="n">
-        <v>2.27</v>
+        <v>1.49</v>
       </c>
       <c r="BE153" t="n">
-        <v>6.35</v>
+        <v>7</v>
       </c>
       <c r="BF153" t="n">
-        <v>2</v>
+        <v>3.14</v>
       </c>
       <c r="BG153" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="BH153" t="n">
-        <v>3.37</v>
+        <v>3.89</v>
       </c>
       <c r="BI153" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BJ153" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="BK153" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="BL153" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BM153" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="BN153" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="BO153" t="n">
-        <v>3.11</v>
+        <v>2.72</v>
       </c>
       <c r="BP153" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="154">
@@ -34133,7 +34133,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>8217485</v>
+        <v>8217449</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -34153,12 +34153,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="I155" t="n">
@@ -34171,179 +34171,179 @@
         <v>1</v>
       </c>
       <c r="L155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N155" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>['33', '51', '73', '79']</t>
+          <t>['20', '61']</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="R155" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S155" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="T155" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U155" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V155" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="W155" t="n">
         <v>1.36</v>
       </c>
       <c r="X155" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z155" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA155" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB155" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AD155" t="n">
-        <v>8.949999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF155" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="AG155" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AI155" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD155" t="n">
         <v>1.82</v>
       </c>
-      <c r="AJ155" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK155" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL155" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM155" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN155" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO155" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP155" t="n">
+      <c r="BE155" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI155" t="n">
         <v>1.43</v>
       </c>
-      <c r="AQ155" t="n">
+      <c r="BJ155" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK155" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO155" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BP155" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AR155" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AS155" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AT155" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AU155" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV155" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW155" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX155" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY155" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ155" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA155" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB155" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC155" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD155" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BE155" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF155" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BG155" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BH155" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="BI155" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BJ155" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BK155" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BL155" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BM155" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BN155" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BO155" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BP155" t="n">
-        <v>1.36</v>
       </c>
     </row>
     <row r="156">
@@ -35005,7 +35005,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>8217536</v>
+        <v>8217469</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -35025,197 +35025,197 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K159" t="n">
+        <v>1</v>
+      </c>
+      <c r="L159" t="n">
         <v>4</v>
       </c>
-      <c r="L159" t="n">
-        <v>3</v>
-      </c>
       <c r="M159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>['27', '37', '87']</t>
+          <t>['45+9', '52', '69', '86']</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>['6', '45+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="R159" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S159" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="T159" t="n">
         <v>1.33</v>
       </c>
       <c r="U159" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V159" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="W159" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X159" t="n">
-        <v>6.15</v>
+        <v>5.6</v>
       </c>
       <c r="Y159" t="n">
         <v>1.09</v>
       </c>
       <c r="Z159" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="AA159" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AB159" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AC159" t="n">
         <v>1.01</v>
       </c>
       <c r="AD159" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE159" t="n">
         <v>1.24</v>
       </c>
       <c r="AF159" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AG159" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH159" t="n">
         <v>1.93</v>
       </c>
-      <c r="AH159" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AI159" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AJ159" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AK159" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AL159" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AM159" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AN159" t="n">
-        <v>1.5</v>
+        <v>0.83</v>
       </c>
       <c r="AO159" t="n">
-        <v>1.83</v>
+        <v>1.17</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.71</v>
+        <v>1.14</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.57</v>
+        <v>1</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.66</v>
+        <v>2.99</v>
       </c>
       <c r="AU159" t="n">
         <v>5</v>
       </c>
       <c r="AV159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW159" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX159" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AY159" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AZ159" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BA159" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB159" t="n">
         <v>3</v>
       </c>
       <c r="BC159" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD159" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="BE159" t="n">
-        <v>7.42</v>
+        <v>8.6</v>
       </c>
       <c r="BF159" t="n">
-        <v>1.96</v>
+        <v>2.46</v>
       </c>
       <c r="BG159" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="BH159" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="BI159" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BJ159" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BK159" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BL159" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BM159" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BN159" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="BO159" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BP159" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="160">
@@ -35223,7 +35223,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>8217522</v>
+        <v>8217491</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -35243,149 +35243,149 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K160" t="n">
         <v>1</v>
       </c>
       <c r="L160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N160" t="n">
+        <v>2</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R160" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S160" t="n">
+        <v>3</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U160" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V160" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W160" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X160" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV160" t="n">
         <v>4</v>
       </c>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>['10', '68']</t>
-        </is>
-      </c>
-      <c r="P160" t="inlineStr">
-        <is>
-          <t>['51', '60']</t>
-        </is>
-      </c>
-      <c r="Q160" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="R160" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S160" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T160" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U160" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V160" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W160" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X160" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y160" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z160" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA160" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB160" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC160" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD160" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE160" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF160" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG160" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH160" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI160" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AJ160" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AK160" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL160" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AM160" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN160" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO160" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AP160" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ160" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR160" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AS160" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AT160" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU160" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV160" t="n">
+      <c r="AW160" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ160" t="n">
         <v>9</v>
-      </c>
-      <c r="AW160" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX160" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY160" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ160" t="n">
-        <v>19</v>
       </c>
       <c r="BA160" t="n">
         <v>4</v>
@@ -35397,43 +35397,43 @@
         <v>11</v>
       </c>
       <c r="BD160" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO160" t="n">
         <v>2.88</v>
       </c>
-      <c r="BE160" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF160" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BG160" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BH160" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI160" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BJ160" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BK160" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BL160" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM160" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BN160" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BO160" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BP160" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="161">
@@ -35441,7 +35441,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>8217538</v>
+        <v>8217522</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -35461,197 +35461,197 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L161" t="n">
         <v>2</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N161" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>['72', '90']</t>
+          <t>['10', '68']</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51', '60']</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>3</v>
+        <v>4.39</v>
       </c>
       <c r="R161" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="S161" t="n">
-        <v>3.54</v>
+        <v>2.49</v>
       </c>
       <c r="T161" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W161" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X161" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AS161" t="n">
         <v>1.48</v>
       </c>
-      <c r="U161" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V161" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="W161" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X161" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Y161" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z161" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA161" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB161" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC161" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD161" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE161" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF161" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG161" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AH161" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI161" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ161" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK161" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL161" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM161" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN161" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO161" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP161" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AQ161" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AR161" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AS161" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AT161" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="AU161" t="n">
         <v>3</v>
       </c>
       <c r="AV161" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AW161" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX161" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA161" t="n">
         <v>4</v>
       </c>
-      <c r="AY161" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ161" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA161" t="n">
-        <v>0</v>
-      </c>
       <c r="BB161" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BC161" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BD161" t="n">
-        <v>2.12</v>
+        <v>2.88</v>
       </c>
       <c r="BE161" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="BF161" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="BG161" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="BH161" t="n">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="BI161" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="BJ161" t="n">
-        <v>2.44</v>
+        <v>2.95</v>
       </c>
       <c r="BK161" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="BL161" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="BM161" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="BN161" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="BO161" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="BP161" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="162">
@@ -35659,7 +35659,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>8217539</v>
+        <v>8217471</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -35679,12 +35679,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="I162" t="n">
@@ -35697,179 +35697,179 @@
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51', '90+5']</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['46', '90+1']</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="R162" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S162" t="n">
-        <v>3.55</v>
+        <v>4.61</v>
       </c>
       <c r="T162" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="U162" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="V162" t="n">
-        <v>2.41</v>
+        <v>3.16</v>
       </c>
       <c r="W162" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="X162" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="Y162" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z162" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AA162" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AB162" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="AC162" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AD162" t="n">
-        <v>12.8</v>
+        <v>8</v>
       </c>
       <c r="AE162" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AF162" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="AG162" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH162" t="n">
         <v>1.7</v>
       </c>
-      <c r="AH162" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AI162" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AJ162" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AK162" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AL162" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AM162" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AN162" t="n">
-        <v>2.17</v>
+        <v>1</v>
       </c>
       <c r="AO162" t="n">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="AP162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.29</v>
+        <v>0.71</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="AS162" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AT162" t="n">
-        <v>2.59</v>
+        <v>2.93</v>
       </c>
       <c r="AU162" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW162" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX162" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY162" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ162" t="n">
         <v>9</v>
       </c>
       <c r="BA162" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BB162" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC162" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD162" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="BE162" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF162" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="BG162" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BH162" t="n">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="BI162" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="BJ162" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="BK162" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL162" t="n">
         <v>2.05</v>
       </c>
-      <c r="BL162" t="n">
-        <v>2</v>
-      </c>
       <c r="BM162" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="BN162" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="BO162" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="BP162" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="163">
@@ -35877,7 +35877,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>8217469</v>
+        <v>8217535</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -35897,77 +35897,77 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K163" t="n">
         <v>1</v>
       </c>
       <c r="L163" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N163" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>['45+9', '52', '69', '86']</t>
+          <t>['73', '81']</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="R163" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S163" t="n">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="T163" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="U163" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V163" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="W163" t="n">
         <v>1.44</v>
       </c>
       <c r="X163" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="Y163" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z163" t="n">
-        <v>2.37</v>
+        <v>2.71</v>
       </c>
       <c r="AA163" t="n">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="AB163" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AC163" t="n">
         <v>1.01</v>
@@ -35976,115 +35976,115 @@
         <v>9</v>
       </c>
       <c r="AE163" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF163" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AG163" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AH163" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AI163" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AJ163" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AK163" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL163" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AM163" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AN163" t="n">
-        <v>0.83</v>
+        <v>1.67</v>
       </c>
       <c r="AO163" t="n">
-        <v>1.17</v>
+        <v>2.33</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="AT163" t="n">
-        <v>2.99</v>
+        <v>3.17</v>
       </c>
       <c r="AU163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV163" t="n">
         <v>3</v>
       </c>
       <c r="AW163" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC163" t="n">
         <v>9</v>
       </c>
-      <c r="AX163" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY163" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ163" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA163" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB163" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC163" t="n">
-        <v>8</v>
-      </c>
       <c r="BD163" t="n">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="BE163" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="BF163" t="n">
-        <v>2.46</v>
+        <v>2.84</v>
       </c>
       <c r="BG163" t="n">
         <v>1.25</v>
       </c>
       <c r="BH163" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BI163" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="BJ163" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="BK163" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BL163" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="BM163" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="BN163" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="BO163" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="BP163" t="n">
         <v>1.34</v>
@@ -36095,7 +36095,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>8217491</v>
+        <v>8217536</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -36115,197 +36115,197 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N164" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['27', '37', '87']</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['6', '45+1']</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R164" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="S164" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U164" t="n">
         <v>3</v>
       </c>
-      <c r="T164" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U164" t="n">
-        <v>2.9</v>
-      </c>
       <c r="V164" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="W164" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X164" t="n">
-        <v>5.8</v>
+        <v>6.15</v>
       </c>
       <c r="Y164" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z164" t="n">
         <v>2.65</v>
       </c>
       <c r="AA164" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB164" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AC164" t="n">
         <v>1.01</v>
       </c>
       <c r="AD164" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="AE164" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF164" t="n">
         <v>3.6</v>
       </c>
       <c r="AG164" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH164" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AI164" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AJ164" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AK164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL164" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL164" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AM164" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AN164" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO164" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AP164" t="n">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AR164" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AS164" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AT164" t="n">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="AU164" t="n">
         <v>5</v>
       </c>
       <c r="AV164" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW164" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX164" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AY164" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ164" t="n">
         <v>12</v>
       </c>
-      <c r="AZ164" t="n">
-        <v>9</v>
-      </c>
       <c r="BA164" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB164" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BC164" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BD164" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL164" t="n">
         <v>2.1</v>
       </c>
-      <c r="BE164" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="BF164" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BG164" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BH164" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI164" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BJ164" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BK164" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BL164" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BM164" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="BN164" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="BO164" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="BP164" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="165">
@@ -36313,7 +36313,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>8217470</v>
+        <v>8217537</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -36333,197 +36333,197 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K165" t="n">
+        <v>1</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
         <v>3</v>
-      </c>
-      <c r="L165" t="n">
-        <v>1</v>
-      </c>
-      <c r="M165" t="n">
-        <v>2</v>
       </c>
       <c r="N165" t="n">
         <v>3</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>['7', '27']</t>
+          <t>['12', '49', '51']</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="R165" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S165" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="T165" t="n">
         <v>1.4</v>
       </c>
       <c r="U165" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V165" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="W165" t="n">
         <v>1.41</v>
       </c>
       <c r="X165" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Y165" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z165" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AA165" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="AB165" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AC165" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD165" t="n">
         <v>9</v>
       </c>
       <c r="AE165" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF165" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="AG165" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AH165" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AI165" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AJ165" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AK165" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="AL165" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AM165" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="AN165" t="n">
-        <v>2.17</v>
+        <v>1.17</v>
       </c>
       <c r="AO165" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.86</v>
+        <v>1</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="AS165" t="n">
-        <v>1.39</v>
+        <v>0.99</v>
       </c>
       <c r="AT165" t="n">
-        <v>3.2</v>
+        <v>2.53</v>
       </c>
       <c r="AU165" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV165" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AW165" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX165" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY165" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ165" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BA165" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC165" t="n">
         <v>5</v>
       </c>
-      <c r="BB165" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC165" t="n">
-        <v>10</v>
-      </c>
       <c r="BD165" t="n">
-        <v>2.08</v>
+        <v>1.54</v>
       </c>
       <c r="BE165" t="n">
-        <v>6.15</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BF165" t="n">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="BG165" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="BH165" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="BI165" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="BJ165" t="n">
-        <v>2.14</v>
+        <v>2.63</v>
       </c>
       <c r="BK165" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="BL165" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="BM165" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="BN165" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="BO165" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="BP165" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="166">
@@ -36531,7 +36531,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>8217471</v>
+        <v>8217538</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -36551,12 +36551,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="I166" t="n">
@@ -36572,176 +36572,176 @@
         <v>2</v>
       </c>
       <c r="M166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>['51', '90+5']</t>
+          <t>['72', '90']</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>['46', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="R166" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="S166" t="n">
-        <v>4.61</v>
+        <v>3.54</v>
       </c>
       <c r="T166" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="U166" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="V166" t="n">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="W166" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X166" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD166" t="n">
         <v>7.5</v>
       </c>
-      <c r="Y166" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z166" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA166" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB166" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AC166" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD166" t="n">
-        <v>8</v>
-      </c>
       <c r="AE166" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AF166" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AG166" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AH166" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AI166" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AJ166" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AK166" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL166" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL166" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AM166" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AN166" t="n">
-        <v>1</v>
+        <v>2.17</v>
       </c>
       <c r="AO166" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AP166" t="n">
-        <v>1</v>
+        <v>2.29</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.71</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AS166" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AT166" t="n">
-        <v>2.93</v>
+        <v>2.69</v>
       </c>
       <c r="AU166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX166" t="n">
         <v>4</v>
       </c>
-      <c r="AV166" t="n">
+      <c r="AY166" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO166" t="n">
         <v>3</v>
       </c>
-      <c r="AW166" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX166" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY166" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ166" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA166" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB166" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC166" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD166" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BE166" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF166" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG166" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BH166" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="BI166" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BJ166" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BK166" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BL166" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BM166" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BN166" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BO166" t="n">
-        <v>2.76</v>
-      </c>
       <c r="BP166" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="167">
@@ -36749,7 +36749,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>8217537</v>
+        <v>8217539</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -36769,31 +36769,31 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="I167" t="n">
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -36802,164 +36802,164 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>['12', '49', '51']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="R167" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="S167" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="T167" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="U167" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="V167" t="n">
-        <v>2.77</v>
+        <v>2.41</v>
       </c>
       <c r="W167" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="X167" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="Y167" t="n">
         <v>1.08</v>
       </c>
       <c r="Z167" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AA167" t="n">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="AB167" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AC167" t="n">
         <v>1.03</v>
       </c>
       <c r="AD167" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY167" t="n">
         <v>9</v>
       </c>
-      <c r="AE167" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF167" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AG167" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AH167" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AI167" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ167" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AK167" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AL167" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AM167" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AN167" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO167" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AP167" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ167" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR167" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AS167" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="AT167" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AU167" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV167" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW167" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX167" t="n">
+      <c r="AZ167" t="n">
         <v>9</v>
       </c>
-      <c r="AY167" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ167" t="n">
-        <v>17</v>
-      </c>
       <c r="BA167" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BB167" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BC167" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD167" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="BE167" t="n">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="BF167" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="BG167" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BH167" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="BI167" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="BJ167" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="BK167" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="BL167" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="BM167" t="n">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="BN167" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BO167" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BP167" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="168">
@@ -36967,7 +36967,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>8217535</v>
+        <v>8217470</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -36987,77 +36987,77 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N168" t="n">
         <v>3</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>['73', '81']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['7', '27']</t>
         </is>
       </c>
       <c r="Q168" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R168" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S168" t="n">
         <v>3.2</v>
       </c>
-      <c r="R168" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S168" t="n">
-        <v>3.06</v>
-      </c>
       <c r="T168" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="U168" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V168" t="n">
         <v>2.8</v>
       </c>
-      <c r="V168" t="n">
-        <v>2.92</v>
-      </c>
       <c r="W168" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X168" t="n">
         <v>7</v>
       </c>
       <c r="Y168" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z168" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AA168" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="AB168" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AC168" t="n">
         <v>1.01</v>
@@ -37066,118 +37066,118 @@
         <v>9</v>
       </c>
       <c r="AE168" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF168" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AG168" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH168" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AI168" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AJ168" t="n">
         <v>2.1</v>
       </c>
       <c r="AK168" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AL168" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AM168" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AN168" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AO168" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP168" t="n">
         <v>1.86</v>
       </c>
       <c r="AQ168" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AS168" t="n">
         <v>1.39</v>
       </c>
       <c r="AT168" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="AU168" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH168" t="n">
         <v>3</v>
       </c>
-      <c r="AW168" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX168" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY168" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ168" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA168" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB168" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC168" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD168" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BE168" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BF168" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BG168" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BH168" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BI168" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="BJ168" t="n">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="BK168" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL168" t="n">
         <v>1.7</v>
       </c>
-      <c r="BL168" t="n">
-        <v>1.9</v>
-      </c>
       <c r="BM168" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="BN168" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="BO168" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="BP168" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="169">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -32389,7 +32389,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>8217468</v>
+        <v>8217486</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -32409,197 +32409,197 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="I147" t="n">
         <v>1</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L147" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1</v>
+      </c>
+      <c r="N147" t="n">
+        <v>2</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="R147" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S147" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U147" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V147" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X147" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU147" t="n">
         <v>4</v>
       </c>
-      <c r="M147" t="n">
-        <v>0</v>
-      </c>
-      <c r="N147" t="n">
+      <c r="AV147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX147" t="n">
         <v>4</v>
       </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>['8', '72', '79', '90+3']</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q147" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R147" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S147" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T147" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U147" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V147" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="W147" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X147" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA147" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="AB147" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC147" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD147" t="n">
+      <c r="AY147" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA147" t="n">
         <v>9</v>
       </c>
-      <c r="AE147" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF147" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AG147" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH147" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI147" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AJ147" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AK147" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AL147" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM147" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN147" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO147" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP147" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ147" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR147" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AS147" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AT147" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AU147" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV147" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW147" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX147" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY147" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ147" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA147" t="n">
-        <v>3</v>
-      </c>
       <c r="BB147" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BC147" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="BD147" t="n">
-        <v>2.27</v>
+        <v>1.35</v>
       </c>
       <c r="BE147" t="n">
-        <v>6.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF147" t="n">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="BG147" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BH147" t="n">
-        <v>3.37</v>
+        <v>3.52</v>
       </c>
       <c r="BI147" t="n">
         <v>1.46</v>
       </c>
       <c r="BJ147" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="BK147" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="BL147" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="BM147" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="BN147" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="BO147" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="BP147" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="148">
@@ -32607,7 +32607,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>8217490</v>
+        <v>8217488</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -32627,12 +32627,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -32664,160 +32664,160 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="R148" t="n">
         <v>2.1</v>
       </c>
       <c r="S148" t="n">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="T148" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="U148" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="V148" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="W148" t="n">
         <v>1.4</v>
       </c>
       <c r="X148" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="Y148" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z148" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AA148" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB148" t="n">
         <v>3.4</v>
       </c>
-      <c r="AB148" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AC148" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AD148" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="AE148" t="n">
         <v>1.25</v>
       </c>
       <c r="AF148" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="AG148" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AH148" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AI148" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AJ148" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AK148" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AL148" t="n">
         <v>1.28</v>
       </c>
       <c r="AM148" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AN148" t="n">
-        <v>0.83</v>
+        <v>1.67</v>
       </c>
       <c r="AO148" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="AQ148" t="n">
-        <v>0.57</v>
+        <v>1.29</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.23</v>
+        <v>1.87</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.28</v>
+        <v>3.08</v>
       </c>
       <c r="AU148" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AV148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ148" t="n">
         <v>3</v>
-      </c>
-      <c r="AW148" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX148" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY148" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ148" t="n">
-        <v>15</v>
       </c>
       <c r="BA148" t="n">
         <v>6</v>
       </c>
       <c r="BB148" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC148" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BD148" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BE148" t="n">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
       <c r="BF148" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="BG148" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BH148" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="BI148" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="BJ148" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="BK148" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="BL148" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="BM148" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="BN148" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BO148" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="BP148" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="149">
@@ -33043,7 +33043,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>8217488</v>
+        <v>8217490</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -33063,12 +33063,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -33091,7 +33091,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -33100,160 +33100,160 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="R150" t="n">
         <v>2.1</v>
       </c>
       <c r="S150" t="n">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="T150" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="U150" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="V150" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="W150" t="n">
         <v>1.4</v>
       </c>
       <c r="X150" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="Y150" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z150" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AA150" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AB150" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC150" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AD150" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="AE150" t="n">
         <v>1.25</v>
       </c>
       <c r="AF150" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="AG150" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AI150" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AJ150" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AK150" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AL150" t="n">
         <v>1.28</v>
       </c>
       <c r="AM150" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AN150" t="n">
-        <v>1.67</v>
+        <v>0.83</v>
       </c>
       <c r="AO150" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.86</v>
+        <v>1.14</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.29</v>
+        <v>0.57</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AT150" t="n">
-        <v>3.08</v>
+        <v>2.28</v>
       </c>
       <c r="AU150" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW150" t="n">
         <v>9</v>
       </c>
-      <c r="AV150" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW150" t="n">
-        <v>16</v>
-      </c>
       <c r="AX150" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AY150" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AZ150" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="BA150" t="n">
         <v>6</v>
       </c>
       <c r="BB150" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BC150" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BD150" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BE150" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="BF150" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="BG150" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BH150" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="BI150" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="BJ150" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="BK150" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="BL150" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="BM150" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="BN150" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BO150" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="BP150" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="151">
@@ -33261,7 +33261,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>8217486</v>
+        <v>8217406</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -33281,197 +33281,197 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
         <v>1</v>
       </c>
       <c r="N151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="R151" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S151" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T151" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U151" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V151" t="n">
         <v>2.38</v>
       </c>
-      <c r="S151" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T151" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="U151" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V151" t="n">
-        <v>2.5</v>
-      </c>
       <c r="W151" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X151" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="Y151" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z151" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AA151" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AB151" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="AC151" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AD151" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF151" t="n">
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
       <c r="AG151" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH151" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AI151" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AJ151" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AK151" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL151" t="n">
         <v>1.2</v>
       </c>
-      <c r="AL151" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AM151" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AN151" t="n">
-        <v>2.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO151" t="n">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AP151" t="n">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.14</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="AT151" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="AU151" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ151" t="n">
         <v>4</v>
       </c>
-      <c r="AV151" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW151" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX151" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY151" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ151" t="n">
-        <v>6</v>
-      </c>
       <c r="BA151" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BB151" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="BC151" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BD151" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="BE151" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BF151" t="n">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="BG151" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BH151" t="n">
-        <v>3.52</v>
+        <v>3.89</v>
       </c>
       <c r="BI151" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BJ151" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BK151" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="BL151" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="BM151" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="BN151" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BO151" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="BP151" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="152">
@@ -33479,7 +33479,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>8217485</v>
+        <v>8217449</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -33499,12 +33499,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -33517,179 +33517,179 @@
         <v>1</v>
       </c>
       <c r="L152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N152" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>['33', '51', '73', '79']</t>
+          <t>['20', '61']</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="R152" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S152" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="T152" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U152" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V152" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="W152" t="n">
         <v>1.36</v>
       </c>
       <c r="X152" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="Y152" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z152" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA152" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB152" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AC152" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AD152" t="n">
-        <v>8.949999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF152" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="AG152" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH152" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AI152" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD152" t="n">
         <v>1.82</v>
       </c>
-      <c r="AJ152" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK152" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL152" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM152" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN152" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO152" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP152" t="n">
+      <c r="BE152" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI152" t="n">
         <v>1.43</v>
       </c>
-      <c r="AQ152" t="n">
+      <c r="BJ152" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK152" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL152" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM152" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BN152" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO152" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BP152" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AR152" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AS152" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AT152" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AU152" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV152" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW152" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX152" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY152" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ152" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA152" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB152" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC152" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD152" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BE152" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF152" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BG152" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BH152" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="BI152" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BJ152" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BK152" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BL152" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BM152" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BN152" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BO152" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BP152" t="n">
-        <v>1.36</v>
       </c>
     </row>
     <row r="153">
@@ -33697,7 +33697,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>8217406</v>
+        <v>8217468</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -33717,197 +33717,197 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
+          <t>['8', '72', '79', '90+3']</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
       <c r="Q153" t="n">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="R153" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S153" t="n">
-        <v>3.85</v>
+        <v>2.62</v>
       </c>
       <c r="T153" t="n">
         <v>1.36</v>
       </c>
       <c r="U153" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V153" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="W153" t="n">
         <v>1.42</v>
       </c>
       <c r="X153" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="Y153" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z153" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA153" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="AB153" t="n">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC153" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AD153" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF153" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="AG153" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AH153" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AI153" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AJ153" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AK153" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AL153" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AM153" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ153" t="n">
         <v>1.71</v>
       </c>
-      <c r="AN153" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO153" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP153" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ153" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AR153" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AT153" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="AU153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW153" t="n">
         <v>13</v>
       </c>
       <c r="AX153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA153" t="n">
         <v>3</v>
       </c>
-      <c r="AY153" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ153" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA153" t="n">
-        <v>12</v>
-      </c>
       <c r="BB153" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BC153" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BD153" t="n">
-        <v>1.49</v>
+        <v>2.27</v>
       </c>
       <c r="BE153" t="n">
-        <v>7</v>
+        <v>6.35</v>
       </c>
       <c r="BF153" t="n">
-        <v>3.14</v>
+        <v>2</v>
       </c>
       <c r="BG153" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BH153" t="n">
-        <v>3.89</v>
+        <v>3.37</v>
       </c>
       <c r="BI153" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="BJ153" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="BK153" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="BL153" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BM153" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="BN153" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="BO153" t="n">
-        <v>2.72</v>
+        <v>3.11</v>
       </c>
       <c r="BP153" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="154">
@@ -34133,7 +34133,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>8217449</v>
+        <v>8217485</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -34153,12 +34153,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="I155" t="n">
@@ -34171,179 +34171,179 @@
         <v>1</v>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N155" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>['20', '61']</t>
+          <t>['33', '51', '73', '79']</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="R155" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S155" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="T155" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U155" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="V155" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="W155" t="n">
         <v>1.36</v>
       </c>
       <c r="X155" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z155" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AA155" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB155" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AD155" t="n">
-        <v>7.9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF155" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AG155" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AI155" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AJ155" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AK155" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AL155" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AM155" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AN155" t="n">
-        <v>0.17</v>
+        <v>1.67</v>
       </c>
       <c r="AO155" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP155" t="n">
-        <v>0.14</v>
+        <v>1.43</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.71</v>
+        <v>1.29</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AS155" t="n">
-        <v>0.86</v>
+        <v>1.23</v>
       </c>
       <c r="AT155" t="n">
-        <v>2.01</v>
+        <v>2.47</v>
       </c>
       <c r="AU155" t="n">
         <v>2</v>
       </c>
       <c r="AV155" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW155" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA155" t="n">
         <v>6</v>
       </c>
-      <c r="AX155" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY155" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ155" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA155" t="n">
-        <v>3</v>
-      </c>
       <c r="BB155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC155" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BD155" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="BE155" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF155" t="n">
-        <v>2.07</v>
+        <v>2.64</v>
       </c>
       <c r="BG155" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BH155" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="BI155" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BJ155" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="BK155" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="BL155" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BM155" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="BN155" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BO155" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="BP155" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="156">
@@ -35005,7 +35005,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>8217469</v>
+        <v>8217536</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -35025,197 +35025,197 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K159" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L159" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N159" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>['45+9', '52', '69', '86']</t>
+          <t>['27', '37', '87']</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '45+1']</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="R159" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S159" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="T159" t="n">
         <v>1.33</v>
       </c>
       <c r="U159" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V159" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="W159" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X159" t="n">
-        <v>5.6</v>
+        <v>6.15</v>
       </c>
       <c r="Y159" t="n">
         <v>1.09</v>
       </c>
       <c r="Z159" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="AA159" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AB159" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC159" t="n">
         <v>1.01</v>
       </c>
       <c r="AD159" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE159" t="n">
         <v>1.24</v>
       </c>
       <c r="AF159" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG159" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AH159" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AI159" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AJ159" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AK159" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL159" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AM159" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AN159" t="n">
-        <v>0.83</v>
+        <v>1.5</v>
       </c>
       <c r="AO159" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.14</v>
+        <v>1.71</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1</v>
+        <v>1.57</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.87</v>
+        <v>1.27</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.99</v>
+        <v>2.66</v>
       </c>
       <c r="AU159" t="n">
         <v>5</v>
       </c>
       <c r="AV159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA159" t="n">
         <v>3</v>
-      </c>
-      <c r="AW159" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX159" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY159" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ159" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA159" t="n">
-        <v>5</v>
       </c>
       <c r="BB159" t="n">
         <v>3</v>
       </c>
       <c r="BC159" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD159" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="BE159" t="n">
-        <v>8.6</v>
+        <v>7.42</v>
       </c>
       <c r="BF159" t="n">
-        <v>2.46</v>
+        <v>1.96</v>
       </c>
       <c r="BG159" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BH159" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="BI159" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="BJ159" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BK159" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BL159" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BM159" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="BN159" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BO159" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BP159" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="160">
@@ -35223,7 +35223,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>8217491</v>
+        <v>8217522</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -35243,149 +35243,149 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K160" t="n">
         <v>1</v>
       </c>
       <c r="L160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N160" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['10', '68']</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['51', '60']</t>
         </is>
       </c>
       <c r="Q160" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="R160" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S160" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U160" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V160" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W160" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X160" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF160" t="n">
         <v>3.2</v>
       </c>
-      <c r="R160" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="S160" t="n">
+      <c r="AG160" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU160" t="n">
         <v>3</v>
       </c>
-      <c r="T160" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U160" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V160" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W160" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X160" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Y160" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z160" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA160" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB160" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC160" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD160" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AE160" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF160" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG160" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH160" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AI160" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AJ160" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AK160" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AL160" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM160" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN160" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO160" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AP160" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ160" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AR160" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AS160" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AT160" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AU160" t="n">
-        <v>5</v>
-      </c>
       <c r="AV160" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW160" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX160" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AY160" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AZ160" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="BA160" t="n">
         <v>4</v>
@@ -35397,43 +35397,43 @@
         <v>11</v>
       </c>
       <c r="BD160" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="BE160" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="BF160" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="BG160" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BH160" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI160" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="BJ160" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="BK160" t="n">
-        <v>1.96</v>
+        <v>1.59</v>
       </c>
       <c r="BL160" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="BM160" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="BN160" t="n">
-        <v>1.49</v>
+        <v>1.74</v>
       </c>
       <c r="BO160" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="BP160" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="161">
@@ -35441,7 +35441,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>8217522</v>
+        <v>8217538</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -35461,197 +35461,197 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L161" t="n">
         <v>2</v>
       </c>
       <c r="M161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>['10', '68']</t>
+          <t>['72', '90']</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>['51', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>4.39</v>
+        <v>3</v>
       </c>
       <c r="R161" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="S161" t="n">
-        <v>2.49</v>
+        <v>3.54</v>
       </c>
       <c r="T161" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U161" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V161" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W161" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X161" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE161" t="n">
         <v>1.38</v>
       </c>
-      <c r="U161" t="n">
+      <c r="AF161" t="n">
         <v>2.8</v>
       </c>
-      <c r="V161" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W161" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X161" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y161" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z161" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA161" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB161" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC161" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD161" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE161" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF161" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AG161" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AI161" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AJ161" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AK161" t="n">
-        <v>1.79</v>
+        <v>1.28</v>
       </c>
       <c r="AL161" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AM161" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AN161" t="n">
-        <v>1.17</v>
+        <v>2.17</v>
       </c>
       <c r="AO161" t="n">
-        <v>2.17</v>
+        <v>0.83</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.14</v>
+        <v>2.29</v>
       </c>
       <c r="AQ161" t="n">
-        <v>2</v>
+        <v>0.71</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.08</v>
+        <v>1.49</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AT161" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="AU161" t="n">
         <v>3</v>
       </c>
       <c r="AV161" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AW161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO161" t="n">
         <v>3</v>
       </c>
-      <c r="AX161" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY161" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ161" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA161" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB161" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC161" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD161" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BE161" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF161" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BG161" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BH161" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI161" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BJ161" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BK161" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BL161" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM161" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BN161" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BO161" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BP161" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="162">
@@ -35659,7 +35659,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>8217471</v>
+        <v>8217539</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -35679,12 +35679,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="I162" t="n">
@@ -35697,179 +35697,179 @@
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>['51', '90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>['46', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="R162" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S162" t="n">
-        <v>4.61</v>
+        <v>3.55</v>
       </c>
       <c r="T162" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="U162" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="V162" t="n">
-        <v>3.16</v>
+        <v>2.41</v>
       </c>
       <c r="W162" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="X162" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="Y162" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z162" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AA162" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AB162" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="AC162" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AD162" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX162" t="n">
         <v>8</v>
       </c>
-      <c r="AE162" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF162" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AG162" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH162" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI162" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ162" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AK162" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL162" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM162" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AN162" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO162" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP162" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ162" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AR162" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AS162" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AT162" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AU162" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV162" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW162" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX162" t="n">
-        <v>6</v>
-      </c>
       <c r="AY162" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ162" t="n">
         <v>9</v>
       </c>
       <c r="BA162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BE162" t="n">
         <v>7</v>
       </c>
-      <c r="BB162" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC162" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD162" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BE162" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF162" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="BG162" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BH162" t="n">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="BI162" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="BJ162" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="BK162" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="BL162" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BM162" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BN162" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="BO162" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="BP162" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="163">
@@ -35877,7 +35877,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>8217535</v>
+        <v>8217469</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -35897,77 +35897,77 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K163" t="n">
         <v>1</v>
       </c>
       <c r="L163" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>['73', '81']</t>
+          <t>['45+9', '52', '69', '86']</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="R163" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S163" t="n">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="T163" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="U163" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V163" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="W163" t="n">
         <v>1.44</v>
       </c>
       <c r="X163" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="Y163" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z163" t="n">
-        <v>2.71</v>
+        <v>2.37</v>
       </c>
       <c r="AA163" t="n">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="AB163" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="AC163" t="n">
         <v>1.01</v>
@@ -35976,115 +35976,115 @@
         <v>9</v>
       </c>
       <c r="AE163" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AF163" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AG163" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AH163" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AI163" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AJ163" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AK163" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AL163" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AM163" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AN163" t="n">
-        <v>1.67</v>
+        <v>0.83</v>
       </c>
       <c r="AO163" t="n">
-        <v>2.33</v>
+        <v>1.17</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.86</v>
+        <v>1.14</v>
       </c>
       <c r="AQ163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="AT163" t="n">
-        <v>3.17</v>
+        <v>2.99</v>
       </c>
       <c r="AU163" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV163" t="n">
         <v>3</v>
       </c>
       <c r="AW163" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ163" t="n">
         <v>4</v>
       </c>
-      <c r="AY163" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ163" t="n">
-        <v>7</v>
-      </c>
       <c r="BA163" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BB163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC163" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD163" t="n">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="BE163" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="BF163" t="n">
-        <v>2.84</v>
+        <v>2.46</v>
       </c>
       <c r="BG163" t="n">
         <v>1.25</v>
       </c>
       <c r="BH163" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BI163" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="BJ163" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="BK163" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BL163" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="BM163" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="BN163" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO163" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="BP163" t="n">
         <v>1.34</v>
@@ -36095,7 +36095,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>8217536</v>
+        <v>8217491</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -36115,197 +36115,197 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K164" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>1</v>
+      </c>
+      <c r="N164" t="n">
+        <v>2</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S164" t="n">
         <v>3</v>
       </c>
-      <c r="M164" t="n">
-        <v>2</v>
-      </c>
-      <c r="N164" t="n">
-        <v>5</v>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>['27', '37', '87']</t>
-        </is>
-      </c>
-      <c r="P164" t="inlineStr">
-        <is>
-          <t>['6', '45+1']</t>
-        </is>
-      </c>
-      <c r="Q164" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R164" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S164" t="n">
-        <v>3.15</v>
-      </c>
       <c r="T164" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="U164" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V164" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="W164" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X164" t="n">
-        <v>6.15</v>
+        <v>5.8</v>
       </c>
       <c r="Y164" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z164" t="n">
         <v>2.65</v>
       </c>
       <c r="AA164" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB164" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AC164" t="n">
         <v>1.01</v>
       </c>
       <c r="AD164" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AE164" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF164" t="n">
         <v>3.6</v>
       </c>
       <c r="AG164" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH164" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AI164" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AJ164" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AK164" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL164" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AM164" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AN164" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO164" t="n">
-        <v>1.83</v>
+        <v>1.17</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.71</v>
+        <v>1</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AR164" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AS164" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AT164" t="n">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="AU164" t="n">
         <v>5</v>
       </c>
       <c r="AV164" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW164" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX164" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AY164" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC164" t="n">
         <v>11</v>
       </c>
-      <c r="AZ164" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA164" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB164" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC164" t="n">
-        <v>6</v>
-      </c>
       <c r="BD164" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="BE164" t="n">
-        <v>7.42</v>
+        <v>6.3</v>
       </c>
       <c r="BF164" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK164" t="n">
         <v>1.96</v>
       </c>
-      <c r="BG164" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BH164" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="BI164" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BJ164" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BK164" t="n">
-        <v>1.66</v>
-      </c>
       <c r="BL164" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="BM164" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="BN164" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="BO164" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="BP164" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="165">
@@ -36313,7 +36313,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>8217537</v>
+        <v>8217470</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -36333,197 +36333,197 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N165" t="n">
         <v>3</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>['12', '49', '51']</t>
+          <t>['7', '27']</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="R165" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S165" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="T165" t="n">
         <v>1.4</v>
       </c>
       <c r="U165" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V165" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="W165" t="n">
         <v>1.41</v>
       </c>
       <c r="X165" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Y165" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z165" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AA165" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="AB165" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="AC165" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AD165" t="n">
         <v>9</v>
       </c>
       <c r="AE165" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AF165" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="AG165" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AH165" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AI165" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AJ165" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AK165" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="AL165" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AM165" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AN165" t="n">
-        <v>1.17</v>
+        <v>2.17</v>
       </c>
       <c r="AO165" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AP165" t="n">
-        <v>1</v>
+        <v>1.86</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="AS165" t="n">
-        <v>0.99</v>
+        <v>1.39</v>
       </c>
       <c r="AT165" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="AU165" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH165" t="n">
         <v>3</v>
       </c>
-      <c r="AV165" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW165" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX165" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY165" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ165" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA165" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB165" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC165" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD165" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BE165" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BF165" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BG165" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH165" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BI165" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="BJ165" t="n">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="BK165" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="BL165" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="BM165" t="n">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="BN165" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="BO165" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="BP165" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="166">
@@ -36531,7 +36531,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>8217538</v>
+        <v>8217471</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -36551,12 +36551,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="I166" t="n">
@@ -36572,176 +36572,176 @@
         <v>2</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N166" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>['72', '90']</t>
+          <t>['51', '90+5']</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['46', '90+1']</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="R166" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="S166" t="n">
-        <v>3.54</v>
+        <v>4.61</v>
       </c>
       <c r="T166" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="U166" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="V166" t="n">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="W166" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X166" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL166" t="n">
         <v>1.3</v>
       </c>
-      <c r="X166" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Y166" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z166" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA166" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB166" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC166" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD166" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE166" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF166" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG166" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AH166" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI166" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ166" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK166" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL166" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AM166" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AN166" t="n">
-        <v>2.17</v>
+        <v>1</v>
       </c>
       <c r="AO166" t="n">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="AP166" t="n">
-        <v>2.29</v>
+        <v>1</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.71</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AS166" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AT166" t="n">
-        <v>2.69</v>
+        <v>2.93</v>
       </c>
       <c r="AU166" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV166" t="n">
         <v>3</v>
       </c>
-      <c r="AV166" t="n">
-        <v>1</v>
-      </c>
       <c r="AW166" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AX166" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY166" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AZ166" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BA166" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB166" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC166" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BD166" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="BE166" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
       <c r="BF166" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="BG166" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BH166" t="n">
-        <v>3.42</v>
+        <v>3.83</v>
       </c>
       <c r="BI166" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="BJ166" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="BK166" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="BL166" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BM166" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="BN166" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="BO166" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="BP166" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="167">
@@ -36749,7 +36749,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>8217539</v>
+        <v>8217537</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -36769,31 +36769,31 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="I167" t="n">
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -36802,164 +36802,164 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '49', '51']</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="R167" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="S167" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="T167" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="U167" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="V167" t="n">
-        <v>2.41</v>
+        <v>2.77</v>
       </c>
       <c r="W167" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="X167" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="Y167" t="n">
         <v>1.08</v>
       </c>
       <c r="Z167" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA167" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AB167" t="n">
         <v>3.6</v>
-      </c>
-      <c r="AB167" t="n">
-        <v>3.05</v>
       </c>
       <c r="AC167" t="n">
         <v>1.03</v>
       </c>
       <c r="AD167" t="n">
-        <v>12.8</v>
+        <v>9</v>
       </c>
       <c r="AE167" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AF167" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH167" t="n">
         <v>3.75</v>
       </c>
-      <c r="AG167" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH167" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AI167" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ167" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AK167" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL167" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AM167" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AN167" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO167" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AP167" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ167" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR167" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AS167" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AT167" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AU167" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV167" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW167" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX167" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY167" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ167" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA167" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB167" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC167" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD167" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BE167" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF167" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BG167" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BH167" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BI167" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BJ167" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="BK167" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="BL167" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="BM167" t="n">
-        <v>2.29</v>
+        <v>2.02</v>
       </c>
       <c r="BN167" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BO167" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BP167" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="168">
@@ -36967,7 +36967,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>8217470</v>
+        <v>8217535</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -36987,77 +36987,77 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N168" t="n">
         <v>3</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['73', '81']</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>['7', '27']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="R168" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S168" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="T168" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="U168" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="V168" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="W168" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X168" t="n">
         <v>7</v>
       </c>
       <c r="Y168" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z168" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="AA168" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="AB168" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AC168" t="n">
         <v>1.01</v>
@@ -37066,118 +37066,118 @@
         <v>9</v>
       </c>
       <c r="AE168" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF168" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AG168" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH168" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AI168" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AJ168" t="n">
         <v>2.1</v>
       </c>
       <c r="AK168" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AL168" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AM168" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AN168" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AO168" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="AP168" t="n">
         <v>1.86</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AS168" t="n">
         <v>1.39</v>
       </c>
       <c r="AT168" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="AU168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ168" t="n">
         <v>7</v>
       </c>
-      <c r="AV168" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW168" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX168" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY168" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ168" t="n">
-        <v>13</v>
-      </c>
       <c r="BA168" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB168" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC168" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD168" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="BE168" t="n">
-        <v>6.15</v>
+        <v>8.5</v>
       </c>
       <c r="BF168" t="n">
-        <v>2.19</v>
+        <v>2.84</v>
       </c>
       <c r="BG168" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BH168" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="BI168" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="BJ168" t="n">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="BK168" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="BL168" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="BM168" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="BN168" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="BO168" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="BP168" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="169">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2876,7 +2876,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.29</v>
@@ -3748,7 +3748,7 @@
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.57</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.57</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.71</v>
@@ -10506,7 +10506,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR46" t="n">
         <v>0.82</v>
@@ -10942,7 +10942,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR48" t="n">
         <v>1.01</v>
@@ -12468,7 +12468,7 @@
         <v>2</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR55" t="n">
         <v>1.03</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.43</v>
@@ -13558,7 +13558,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR60" t="n">
         <v>1.24</v>
@@ -13991,7 +13991,7 @@
         <v>1.5</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.71</v>
@@ -16825,7 +16825,7 @@
         <v>2</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.43</v>
@@ -17700,7 +17700,7 @@
         <v>1</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR79" t="n">
         <v>1.83</v>
@@ -19880,7 +19880,7 @@
         <v>1</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR89" t="n">
         <v>1.72</v>
@@ -20095,7 +20095,7 @@
         <v>2</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ90" t="n">
         <v>2</v>
@@ -21624,7 +21624,7 @@
         <v>1</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR97" t="n">
         <v>1.6</v>
@@ -23147,7 +23147,7 @@
         <v>1.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ104" t="n">
         <v>1</v>
@@ -24455,7 +24455,7 @@
         <v>1</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.14</v>
@@ -26638,7 +26638,7 @@
         <v>2</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR120" t="n">
         <v>1.49</v>
@@ -27507,7 +27507,7 @@
         <v>1.4</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.14</v>
@@ -28600,7 +28600,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR129" t="n">
         <v>1.13</v>
@@ -30559,10 +30559,10 @@
         <v>1</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR138" t="n">
         <v>1.34</v>
@@ -32088,7 +32088,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR145" t="n">
         <v>1.58</v>
@@ -32303,7 +32303,7 @@
         <v>1.17</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ146" t="n">
         <v>1</v>
@@ -35137,7 +35137,7 @@
         <v>1.83</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ159" t="n">
         <v>1.57</v>
@@ -36666,7 +36666,7 @@
         <v>1</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR166" t="n">
         <v>1.76</v>
@@ -37396,6 +37396,442 @@
       </c>
       <c r="BP169" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="n">
+        <v>8217397</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>45969.39583333334</v>
+      </c>
+      <c r="F170" t="n">
+        <v>15</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" t="n">
+        <v>1</v>
+      </c>
+      <c r="K170" t="n">
+        <v>2</v>
+      </c>
+      <c r="L170" t="n">
+        <v>3</v>
+      </c>
+      <c r="M170" t="n">
+        <v>1</v>
+      </c>
+      <c r="N170" t="n">
+        <v>4</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>['21', '56', '90+3']</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R170" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S170" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T170" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U170" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V170" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="W170" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X170" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BN170" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO170" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BP170" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="n">
+        <v>8217276</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>45969.39583333334</v>
+      </c>
+      <c r="F171" t="n">
+        <v>15</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>2</v>
+      </c>
+      <c r="N171" t="n">
+        <v>2</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>['74', '78']</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="R171" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S171" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="T171" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U171" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V171" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W171" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X171" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI171" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM171" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BN171" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO171" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BP171" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP171"/>
+  <dimension ref="A1:BP180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.43</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ3" t="n">
         <v>1</v>
@@ -1568,7 +1568,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.14</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.43</v>
@@ -3094,7 +3094,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4181,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.43</v>
@@ -5271,10 +5271,10 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -5489,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -6579,10 +6579,10 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR28" t="n">
         <v>1.35</v>
@@ -7233,7 +7233,7 @@
         <v>1</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.14</v>
@@ -7454,7 +7454,7 @@
         <v>1</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR32" t="n">
         <v>1.41</v>
@@ -7672,7 +7672,7 @@
         <v>1</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR33" t="n">
         <v>2.2</v>
@@ -8544,7 +8544,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR37" t="n">
         <v>1.09</v>
@@ -8759,7 +8759,7 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.71</v>
@@ -8977,10 +8977,10 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ39" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR39" t="n">
         <v>1.87</v>
@@ -9195,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.43</v>
@@ -9634,7 +9634,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR42" t="n">
         <v>1.11</v>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ43" t="n">
         <v>2</v>
@@ -10285,10 +10285,10 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR45" t="n">
         <v>1.66</v>
@@ -10724,7 +10724,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR47" t="n">
         <v>0.87</v>
@@ -11157,10 +11157,10 @@
         <v>2</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR49" t="n">
         <v>0.84</v>
@@ -11593,10 +11593,10 @@
         <v>1</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR51" t="n">
         <v>1.68</v>
@@ -12032,7 +12032,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR53" t="n">
         <v>1.14</v>
@@ -12247,10 +12247,10 @@
         <v>1.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR54" t="n">
         <v>1.64</v>
@@ -12465,7 +12465,7 @@
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.63</v>
@@ -12683,7 +12683,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.14</v>
@@ -13340,7 +13340,7 @@
         <v>2</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR59" t="n">
         <v>1.05</v>
@@ -13773,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.71</v>
@@ -14209,10 +14209,10 @@
         <v>2</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR63" t="n">
         <v>1.18</v>
@@ -14648,7 +14648,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR65" t="n">
         <v>0.93</v>
@@ -15084,7 +15084,7 @@
         <v>1</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR67" t="n">
         <v>1.92</v>
@@ -15517,7 +15517,7 @@
         <v>0</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.57</v>
@@ -16174,7 +16174,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR72" t="n">
         <v>1.28</v>
@@ -16389,7 +16389,7 @@
         <v>1</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AQ73" t="n">
         <v>1</v>
@@ -16607,7 +16607,7 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.71</v>
@@ -17046,7 +17046,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR76" t="n">
         <v>1.56</v>
@@ -17264,7 +17264,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR77" t="n">
         <v>1.18</v>
@@ -17479,10 +17479,10 @@
         <v>2</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR78" t="n">
         <v>1.77</v>
@@ -17918,7 +17918,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR80" t="n">
         <v>1.16</v>
@@ -18136,7 +18136,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR81" t="n">
         <v>1.5</v>
@@ -18569,7 +18569,7 @@
         <v>0.33</v>
       </c>
       <c r="AP83" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.57</v>
@@ -18790,7 +18790,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR84" t="n">
         <v>1.65</v>
@@ -19005,7 +19005,7 @@
         <v>0.33</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.71</v>
@@ -19441,7 +19441,7 @@
         <v>1.33</v>
       </c>
       <c r="AP87" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ87" t="n">
         <v>1</v>
@@ -19659,7 +19659,7 @@
         <v>1</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.43</v>
@@ -20970,7 +20970,7 @@
         <v>2</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR94" t="n">
         <v>1.13</v>
@@ -21185,10 +21185,10 @@
         <v>2.33</v>
       </c>
       <c r="AP95" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ95" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR95" t="n">
         <v>1.58</v>
@@ -21406,7 +21406,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR96" t="n">
         <v>1.92</v>
@@ -21621,7 +21621,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.63</v>
@@ -21842,7 +21842,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR98" t="n">
         <v>1.57</v>
@@ -22060,7 +22060,7 @@
         <v>1</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR99" t="n">
         <v>1.84</v>
@@ -22496,7 +22496,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR101" t="n">
         <v>1.22</v>
@@ -22711,10 +22711,10 @@
         <v>1.5</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR102" t="n">
         <v>1.08</v>
@@ -22929,7 +22929,7 @@
         <v>1.75</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.43</v>
@@ -23365,7 +23365,7 @@
         <v>2.25</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.71</v>
@@ -23804,7 +23804,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR107" t="n">
         <v>1.35</v>
@@ -24022,7 +24022,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR108" t="n">
         <v>1.23</v>
@@ -24673,7 +24673,7 @@
         <v>1</v>
       </c>
       <c r="AP111" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.43</v>
@@ -24894,7 +24894,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR112" t="n">
         <v>1.35</v>
@@ -25112,7 +25112,7 @@
         <v>1</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR113" t="n">
         <v>1.51</v>
@@ -25327,7 +25327,7 @@
         <v>2.25</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.71</v>
@@ -25548,7 +25548,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR115" t="n">
         <v>1.5</v>
@@ -26417,7 +26417,7 @@
         <v>0.75</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.43</v>
@@ -26635,7 +26635,7 @@
         <v>1.25</v>
       </c>
       <c r="AP120" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.38</v>
@@ -26853,7 +26853,7 @@
         <v>1.8</v>
       </c>
       <c r="AP121" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AQ121" t="n">
         <v>1.71</v>
@@ -27074,7 +27074,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR122" t="n">
         <v>1.25</v>
@@ -27292,7 +27292,7 @@
         <v>1</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR123" t="n">
         <v>1.91</v>
@@ -27728,7 +27728,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR125" t="n">
         <v>1.35</v>
@@ -28379,10 +28379,10 @@
         <v>1.6</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR128" t="n">
         <v>1.94</v>
@@ -28597,7 +28597,7 @@
         <v>0.6</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.63</v>
@@ -28818,7 +28818,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR130" t="n">
         <v>1.73</v>
@@ -29036,7 +29036,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR131" t="n">
         <v>1.17</v>
@@ -29251,7 +29251,7 @@
         <v>1.4</v>
       </c>
       <c r="AP132" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.43</v>
@@ -30344,7 +30344,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR137" t="n">
         <v>1.34</v>
@@ -30777,10 +30777,10 @@
         <v>2</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR139" t="n">
         <v>1.9</v>
@@ -31213,7 +31213,7 @@
         <v>1.8</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.71</v>
@@ -31431,10 +31431,10 @@
         <v>2.2</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ142" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR142" t="n">
         <v>1.33</v>
@@ -31867,10 +31867,10 @@
         <v>1.5</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR144" t="n">
         <v>1.9</v>
@@ -32521,10 +32521,10 @@
         <v>1.17</v>
       </c>
       <c r="AP147" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR147" t="n">
         <v>1.5</v>
@@ -32742,7 +32742,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR148" t="n">
         <v>1.87</v>
@@ -33611,7 +33611,7 @@
         <v>0.33</v>
       </c>
       <c r="AP152" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.71</v>
@@ -34265,10 +34265,10 @@
         <v>1</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR155" t="n">
         <v>1.24</v>
@@ -34483,7 +34483,7 @@
         <v>1.17</v>
       </c>
       <c r="AP156" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.14</v>
@@ -34704,7 +34704,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR157" t="n">
         <v>1.19</v>
@@ -34922,7 +34922,7 @@
         <v>2</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR158" t="n">
         <v>1.31</v>
@@ -35140,7 +35140,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR159" t="n">
         <v>1.27</v>
@@ -35355,7 +35355,7 @@
         <v>2.17</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ160" t="n">
         <v>2</v>
@@ -35576,7 +35576,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR161" t="n">
         <v>1.49</v>
@@ -35791,7 +35791,7 @@
         <v>1.33</v>
       </c>
       <c r="AP162" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.29</v>
@@ -36009,7 +36009,7 @@
         <v>1.17</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ163" t="n">
         <v>1</v>
@@ -36881,7 +36881,7 @@
         <v>1.17</v>
       </c>
       <c r="AP167" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ167" t="n">
         <v>1.43</v>
@@ -37102,7 +37102,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ168" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR168" t="n">
         <v>1.78</v>
@@ -37320,7 +37320,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR169" t="n">
         <v>1.64</v>
@@ -37832,6 +37832,1968 @@
       </c>
       <c r="BP171" t="n">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>8217450</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>45969.5</v>
+      </c>
+      <c r="F172" t="n">
+        <v>15</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>1</v>
+      </c>
+      <c r="J172" t="n">
+        <v>2</v>
+      </c>
+      <c r="K172" t="n">
+        <v>3</v>
+      </c>
+      <c r="L172" t="n">
+        <v>3</v>
+      </c>
+      <c r="M172" t="n">
+        <v>3</v>
+      </c>
+      <c r="N172" t="n">
+        <v>6</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>['45+4', '47', '62']</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>['17', '26', '75']</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R172" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S172" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T172" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U172" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V172" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W172" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X172" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BP172" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="n">
+        <v>8217407</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>45969.5</v>
+      </c>
+      <c r="F173" t="n">
+        <v>15</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>2</v>
+      </c>
+      <c r="J173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K173" t="n">
+        <v>3</v>
+      </c>
+      <c r="L173" t="n">
+        <v>2</v>
+      </c>
+      <c r="M173" t="n">
+        <v>2</v>
+      </c>
+      <c r="N173" t="n">
+        <v>4</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>['13', '28']</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>['39', '65']</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R173" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S173" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T173" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U173" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V173" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W173" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X173" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF173" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="BG173" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH173" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="BI173" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ173" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BK173" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL173" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM173" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BN173" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO173" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BP173" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="n">
+        <v>8217379</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>45969.5</v>
+      </c>
+      <c r="F174" t="n">
+        <v>15</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" t="n">
+        <v>1</v>
+      </c>
+      <c r="N174" t="n">
+        <v>1</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R174" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S174" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="T174" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U174" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V174" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="W174" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X174" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF174" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BG174" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH174" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BI174" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ174" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BK174" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BL174" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BM174" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BN174" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO174" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BP174" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="n">
+        <v>8217380</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>45969.5</v>
+      </c>
+      <c r="F175" t="n">
+        <v>15</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>1</v>
+      </c>
+      <c r="L175" t="n">
+        <v>2</v>
+      </c>
+      <c r="M175" t="n">
+        <v>1</v>
+      </c>
+      <c r="N175" t="n">
+        <v>3</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>['38', '65']</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R175" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S175" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T175" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U175" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V175" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W175" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X175" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BI175" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ175" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK175" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BM175" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BN175" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP175" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="n">
+        <v>8217509</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>45969.5</v>
+      </c>
+      <c r="F176" t="n">
+        <v>15</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>1</v>
+      </c>
+      <c r="J176" t="n">
+        <v>2</v>
+      </c>
+      <c r="K176" t="n">
+        <v>3</v>
+      </c>
+      <c r="L176" t="n">
+        <v>2</v>
+      </c>
+      <c r="M176" t="n">
+        <v>2</v>
+      </c>
+      <c r="N176" t="n">
+        <v>4</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>['44', '74']</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>['7', '13']</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="R176" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S176" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T176" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U176" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V176" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W176" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X176" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF176" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BG176" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH176" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="BI176" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ176" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK176" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL176" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BM176" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN176" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO176" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP176" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="n">
+        <v>8217511</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>45969.5</v>
+      </c>
+      <c r="F177" t="n">
+        <v>15</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>2</v>
+      </c>
+      <c r="M177" t="n">
+        <v>1</v>
+      </c>
+      <c r="N177" t="n">
+        <v>3</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>['74', '90+3']</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R177" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S177" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T177" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U177" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="V177" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="W177" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X177" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF177" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG177" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH177" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="BI177" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ177" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BK177" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL177" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM177" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BN177" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO177" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BP177" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="n">
+        <v>8217409</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>45969.5</v>
+      </c>
+      <c r="F178" t="n">
+        <v>15</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>1</v>
+      </c>
+      <c r="K178" t="n">
+        <v>1</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>1</v>
+      </c>
+      <c r="N178" t="n">
+        <v>1</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R178" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S178" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T178" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U178" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V178" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W178" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X178" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY178" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BE178" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="BF178" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BG178" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH178" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="BI178" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ178" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK178" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL178" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM178" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN178" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO178" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BP178" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="n">
+        <v>8217472</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>45969.5</v>
+      </c>
+      <c r="F179" t="n">
+        <v>15</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>2</v>
+      </c>
+      <c r="J179" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" t="n">
+        <v>5</v>
+      </c>
+      <c r="L179" t="n">
+        <v>2</v>
+      </c>
+      <c r="M179" t="n">
+        <v>4</v>
+      </c>
+      <c r="N179" t="n">
+        <v>6</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>['16', '44']</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>['17', '19', '37', '52']</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R179" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S179" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T179" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U179" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V179" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W179" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X179" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF179" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BG179" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH179" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="BI179" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ179" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BK179" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL179" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM179" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN179" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO179" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BP179" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="n">
+        <v>8217510</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>45969.5</v>
+      </c>
+      <c r="F180" t="n">
+        <v>15</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R180" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S180" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="T180" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U180" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V180" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W180" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X180" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY180" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA180" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB180" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="BF180" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG180" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH180" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI180" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ180" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK180" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL180" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM180" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN180" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO180" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BP180" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -38640,7 +38640,7 @@
         <v>3.31</v>
       </c>
       <c r="AU175" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV175" t="n">
         <v>1</v>
@@ -38652,7 +38652,7 @@
         <v>6</v>
       </c>
       <c r="AY175" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ175" t="n">
         <v>7</v>
@@ -38864,13 +38864,13 @@
         <v>6</v>
       </c>
       <c r="AW176" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX176" t="n">
         <v>11</v>
       </c>
       <c r="AY176" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ176" t="n">
         <v>17</v>
@@ -39294,13 +39294,13 @@
         <v>2.97</v>
       </c>
       <c r="AU178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV178" t="n">
         <v>1</v>
       </c>
       <c r="AW178" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX178" t="n">
         <v>13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -37771,16 +37771,16 @@
         <v>2</v>
       </c>
       <c r="AV171" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX171" t="n">
         <v>3</v>
       </c>
-      <c r="AW171" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX171" t="n">
-        <v>4</v>
-      </c>
       <c r="AY171" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ171" t="n">
         <v>7</v>
@@ -37986,7 +37986,7 @@
         <v>2.79</v>
       </c>
       <c r="AU172" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV172" t="n">
         <v>8</v>
@@ -37998,7 +37998,7 @@
         <v>8</v>
       </c>
       <c r="AY172" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ172" t="n">
         <v>16</v>
@@ -38428,13 +38428,13 @@
         <v>2</v>
       </c>
       <c r="AW174" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX174" t="n">
         <v>5</v>
       </c>
       <c r="AY174" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ174" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP180"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2222,7 +2222,7 @@
         <v>0.13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.14</v>
@@ -7236,7 +7236,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR31" t="n">
         <v>0.89</v>
@@ -10503,7 +10503,7 @@
         <v>1</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.38</v>
@@ -11811,7 +11811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ52" t="n">
         <v>2</v>
@@ -14866,7 +14866,7 @@
         <v>1</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR66" t="n">
         <v>1.37</v>
@@ -17915,7 +17915,7 @@
         <v>0.33</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.63</v>
@@ -20316,7 +20316,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR91" t="n">
         <v>1.43</v>
@@ -22493,7 +22493,7 @@
         <v>1.5</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.5</v>
@@ -24458,7 +24458,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR110" t="n">
         <v>1.39</v>
@@ -29033,7 +29033,7 @@
         <v>1.4</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ131" t="n">
         <v>1</v>
@@ -33396,7 +33396,7 @@
         <v>1</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR151" t="n">
         <v>1.87</v>
@@ -34486,7 +34486,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR156" t="n">
         <v>1.47</v>
@@ -34701,7 +34701,7 @@
         <v>1.83</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.75</v>
@@ -39794,6 +39794,224 @@
       </c>
       <c r="BP180" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="n">
+        <v>8217540</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>45971.70833333334</v>
+      </c>
+      <c r="F181" t="n">
+        <v>15</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>2</v>
+      </c>
+      <c r="K181" t="n">
+        <v>2</v>
+      </c>
+      <c r="L181" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" t="n">
+        <v>2</v>
+      </c>
+      <c r="N181" t="n">
+        <v>3</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>['23', '27']</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R181" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S181" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T181" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U181" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V181" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W181" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X181" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY181" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB181" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF181" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BG181" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH181" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BI181" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ181" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK181" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL181" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM181" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN181" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO181" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BP181" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -38204,13 +38204,13 @@
         <v>3.19</v>
       </c>
       <c r="AU173" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV173" t="n">
         <v>4</v>
       </c>
       <c r="AW173" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX173" t="n">
         <v>3</v>
@@ -38428,13 +38428,13 @@
         <v>2</v>
       </c>
       <c r="AW174" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX174" t="n">
         <v>5</v>
       </c>
       <c r="AY174" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ174" t="n">
         <v>7</v>
@@ -38646,13 +38646,13 @@
         <v>1</v>
       </c>
       <c r="AW175" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX175" t="n">
         <v>6</v>
       </c>
       <c r="AY175" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ175" t="n">
         <v>7</v>
@@ -39294,19 +39294,19 @@
         <v>2.97</v>
       </c>
       <c r="AU178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV178" t="n">
         <v>1</v>
       </c>
       <c r="AW178" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX178" t="n">
         <v>13</v>
       </c>
       <c r="AY178" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ178" t="n">
         <v>14</v>
@@ -39730,13 +39730,13 @@
         <v>3.17</v>
       </c>
       <c r="AU180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV180" t="n">
         <v>1</v>
       </c>
       <c r="AW180" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX180" t="n">
         <v>8</v>
@@ -39957,13 +39957,13 @@
         <v>5</v>
       </c>
       <c r="AX181" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY181" t="n">
         <v>7</v>
       </c>
       <c r="AZ181" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA181" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -37992,13 +37992,13 @@
         <v>8</v>
       </c>
       <c r="AW172" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX172" t="n">
         <v>8</v>
       </c>
       <c r="AY172" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ172" t="n">
         <v>16</v>
@@ -39082,13 +39082,13 @@
         <v>2</v>
       </c>
       <c r="AW177" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX177" t="n">
         <v>6</v>
       </c>
       <c r="AY177" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ177" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.5</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.38</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.5</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.63</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5710,7 +5710,7 @@
         <v>1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.75</v>
@@ -6146,7 +6146,7 @@
         <v>2</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR26" t="n">
         <v>1.04</v>
@@ -6364,7 +6364,7 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR27" t="n">
         <v>2.21</v>
@@ -6800,7 +6800,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR29" t="n">
         <v>1.67</v>
@@ -7015,7 +7015,7 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ30" t="n">
         <v>1</v>
@@ -7451,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.5</v>
@@ -7887,10 +7887,10 @@
         <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR34" t="n">
         <v>0.89</v>
@@ -8105,10 +8105,10 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR35" t="n">
         <v>2.14</v>
@@ -8323,10 +8323,10 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR36" t="n">
         <v>0.73</v>
@@ -8541,7 +8541,7 @@
         <v>3</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ37" t="n">
         <v>1</v>
@@ -8762,7 +8762,7 @@
         <v>0.13</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR38" t="n">
         <v>0.62</v>
@@ -9198,7 +9198,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR40" t="n">
         <v>1.06</v>
@@ -9413,10 +9413,10 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR41" t="n">
         <v>0.96</v>
@@ -9852,7 +9852,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR43" t="n">
         <v>1.16</v>
@@ -10067,10 +10067,10 @@
         <v>3</v>
       </c>
       <c r="AP44" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR44" t="n">
         <v>0.89</v>
@@ -10721,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="AP47" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.5</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.63</v>
@@ -11375,10 +11375,10 @@
         <v>3</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR50" t="n">
         <v>1.11</v>
@@ -11814,7 +11814,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ52" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR52" t="n">
         <v>1.18</v>
@@ -12029,7 +12029,7 @@
         <v>2</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.5</v>
@@ -12686,7 +12686,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR56" t="n">
         <v>1.53</v>
@@ -12901,10 +12901,10 @@
         <v>3</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR57" t="n">
         <v>1.22</v>
@@ -13122,7 +13122,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR58" t="n">
         <v>1.1</v>
@@ -13337,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="AP59" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.5</v>
@@ -13555,7 +13555,7 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.38</v>
@@ -13776,7 +13776,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR61" t="n">
         <v>1.28</v>
@@ -13994,7 +13994,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR62" t="n">
         <v>1.49</v>
@@ -14427,10 +14427,10 @@
         <v>0</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR64" t="n">
         <v>2.16</v>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.63</v>
@@ -14863,7 +14863,7 @@
         <v>0.5</v>
       </c>
       <c r="AP66" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.38</v>
@@ -15302,7 +15302,7 @@
         <v>1</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR68" t="n">
         <v>1.75</v>
@@ -15520,7 +15520,7 @@
         <v>2</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR69" t="n">
         <v>1.68</v>
@@ -15735,7 +15735,7 @@
         <v>2</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ70" t="n">
         <v>1</v>
@@ -15953,10 +15953,10 @@
         <v>1.5</v>
       </c>
       <c r="AP71" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR71" t="n">
         <v>1.75</v>
@@ -16171,7 +16171,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.75</v>
@@ -16392,7 +16392,7 @@
         <v>0.13</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR73" t="n">
         <v>0.97</v>
@@ -16610,7 +16610,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR74" t="n">
         <v>1.07</v>
@@ -16828,7 +16828,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR75" t="n">
         <v>1.55</v>
@@ -17043,7 +17043,7 @@
         <v>1</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.5</v>
@@ -17261,7 +17261,7 @@
         <v>2.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ77" t="n">
         <v>1</v>
@@ -18133,7 +18133,7 @@
         <v>1.67</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.5</v>
@@ -18351,10 +18351,10 @@
         <v>2</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR82" t="n">
         <v>1.37</v>
@@ -18572,7 +18572,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR83" t="n">
         <v>1.4</v>
@@ -18787,7 +18787,7 @@
         <v>1.67</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.5</v>
@@ -19008,7 +19008,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR85" t="n">
         <v>1.77</v>
@@ -19223,10 +19223,10 @@
         <v>1.67</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR86" t="n">
         <v>1.21</v>
@@ -19662,7 +19662,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR88" t="n">
         <v>1.5</v>
@@ -20098,7 +20098,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ90" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR90" t="n">
         <v>1.36</v>
@@ -20313,7 +20313,7 @@
         <v>1.33</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.38</v>
@@ -20531,10 +20531,10 @@
         <v>2</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR92" t="n">
         <v>1.23</v>
@@ -20749,10 +20749,10 @@
         <v>1</v>
       </c>
       <c r="AP93" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR93" t="n">
         <v>1.39</v>
@@ -20967,7 +20967,7 @@
         <v>2</v>
       </c>
       <c r="AP94" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.75</v>
@@ -21403,7 +21403,7 @@
         <v>1</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.75</v>
@@ -21839,7 +21839,7 @@
         <v>1.75</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ98" t="n">
         <v>1</v>
@@ -22275,10 +22275,10 @@
         <v>1</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR100" t="n">
         <v>1.28</v>
@@ -22932,7 +22932,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR103" t="n">
         <v>1.16</v>
@@ -23150,7 +23150,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR104" t="n">
         <v>1.61</v>
@@ -23368,7 +23368,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR105" t="n">
         <v>2.03</v>
@@ -23583,10 +23583,10 @@
         <v>1.5</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR106" t="n">
         <v>1.73</v>
@@ -23801,7 +23801,7 @@
         <v>0.25</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.63</v>
@@ -24019,7 +24019,7 @@
         <v>1.33</v>
       </c>
       <c r="AP108" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.13</v>
@@ -24240,7 +24240,7 @@
         <v>1</v>
       </c>
       <c r="AQ109" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR109" t="n">
         <v>1.78</v>
@@ -24676,7 +24676,7 @@
         <v>2</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR111" t="n">
         <v>1.52</v>
@@ -24891,7 +24891,7 @@
         <v>2</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.88</v>
@@ -25109,7 +25109,7 @@
         <v>1</v>
       </c>
       <c r="AP113" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.75</v>
@@ -25330,7 +25330,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR114" t="n">
         <v>1.43</v>
@@ -25545,7 +25545,7 @@
         <v>1.75</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.75</v>
@@ -25763,10 +25763,10 @@
         <v>1.25</v>
       </c>
       <c r="AP116" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR116" t="n">
         <v>1.08</v>
@@ -25981,10 +25981,10 @@
         <v>0.25</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR117" t="n">
         <v>1.78</v>
@@ -26199,7 +26199,7 @@
         <v>1</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ118" t="n">
         <v>1</v>
@@ -26420,7 +26420,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR119" t="n">
         <v>1.77</v>
@@ -26856,7 +26856,7 @@
         <v>0.13</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR121" t="n">
         <v>1.19</v>
@@ -27071,7 +27071,7 @@
         <v>1.8</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.5</v>
@@ -27510,7 +27510,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR124" t="n">
         <v>1.56</v>
@@ -27725,7 +27725,7 @@
         <v>1.8</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.5</v>
@@ -27943,10 +27943,10 @@
         <v>0.8</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR126" t="n">
         <v>1.7</v>
@@ -28161,10 +28161,10 @@
         <v>1.4</v>
       </c>
       <c r="AP127" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR127" t="n">
         <v>1.34</v>
@@ -28815,7 +28815,7 @@
         <v>1</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.13</v>
@@ -29254,7 +29254,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR132" t="n">
         <v>1.65</v>
@@ -29469,10 +29469,10 @@
         <v>1</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR133" t="n">
         <v>2.04</v>
@@ -29687,10 +29687,10 @@
         <v>0.2</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR134" t="n">
         <v>1.51</v>
@@ -29905,7 +29905,7 @@
         <v>1.4</v>
       </c>
       <c r="AP135" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ135" t="n">
         <v>1</v>
@@ -30123,10 +30123,10 @@
         <v>2</v>
       </c>
       <c r="AP136" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ136" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR136" t="n">
         <v>1.32</v>
@@ -30341,7 +30341,7 @@
         <v>1</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ137" t="n">
         <v>0.75</v>
@@ -30995,10 +30995,10 @@
         <v>0.8</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR140" t="n">
         <v>1.65</v>
@@ -31216,7 +31216,7 @@
         <v>2</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR141" t="n">
         <v>1.53</v>
@@ -31652,7 +31652,7 @@
         <v>1</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR143" t="n">
         <v>1.7</v>
@@ -32085,7 +32085,7 @@
         <v>1.33</v>
       </c>
       <c r="AP145" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ145" t="n">
         <v>1.38</v>
@@ -32739,7 +32739,7 @@
         <v>1.5</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.5</v>
@@ -32957,10 +32957,10 @@
         <v>1.67</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR149" t="n">
         <v>1.26</v>
@@ -33175,10 +33175,10 @@
         <v>0.67</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="AR150" t="n">
         <v>1.23</v>
@@ -33614,7 +33614,7 @@
         <v>0.13</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR152" t="n">
         <v>1.15</v>
@@ -33829,10 +33829,10 @@
         <v>2</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR153" t="n">
         <v>1.59</v>
@@ -34047,10 +34047,10 @@
         <v>1.17</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR154" t="n">
         <v>1.25</v>
@@ -34919,7 +34919,7 @@
         <v>0.67</v>
       </c>
       <c r="AP158" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.63</v>
@@ -35358,7 +35358,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ160" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR160" t="n">
         <v>1.08</v>
@@ -35573,7 +35573,7 @@
         <v>0.83</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.75</v>
@@ -35794,7 +35794,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR162" t="n">
         <v>1.45</v>
@@ -36012,7 +36012,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR163" t="n">
         <v>1.87</v>
@@ -36227,10 +36227,10 @@
         <v>1.17</v>
       </c>
       <c r="AP164" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR164" t="n">
         <v>1.28</v>
@@ -36445,10 +36445,10 @@
         <v>1.5</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AR165" t="n">
         <v>1.81</v>
@@ -36884,7 +36884,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR167" t="n">
         <v>1.54</v>
@@ -37099,7 +37099,7 @@
         <v>2.33</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.88</v>
@@ -37317,7 +37317,7 @@
         <v>1.33</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.13</v>
@@ -40012,6 +40012,2622 @@
       </c>
       <c r="BP181" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="n">
+        <v>8217382</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>45976.5</v>
+      </c>
+      <c r="F182" t="n">
+        <v>16</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>1</v>
+      </c>
+      <c r="N182" t="n">
+        <v>1</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R182" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S182" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T182" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U182" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="V182" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W182" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X182" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK182" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL182" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM182" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN182" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP182" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ182" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS182" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT182" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AU182" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW182" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX182" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY182" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ182" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA182" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB182" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC182" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE182" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="BF182" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BG182" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH182" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="BI182" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ182" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK182" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL182" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM182" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN182" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO182" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP182" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="n">
+        <v>8217411</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>45976.5</v>
+      </c>
+      <c r="F183" t="n">
+        <v>16</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>1</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
+        <v>1</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R183" t="n">
+        <v>2</v>
+      </c>
+      <c r="S183" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="T183" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U183" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V183" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W183" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X183" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AK183" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN183" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ183" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR183" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS183" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT183" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AU183" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW183" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX183" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY183" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ183" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA183" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB183" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC183" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BE183" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF183" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG183" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH183" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI183" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ183" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK183" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL183" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM183" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN183" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO183" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP183" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="n">
+        <v>8217381</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>45976.5</v>
+      </c>
+      <c r="F184" t="n">
+        <v>16</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>0</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R184" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S184" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T184" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U184" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V184" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="W184" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X184" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA184" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK184" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN184" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP184" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ184" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AR184" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS184" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AT184" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AU184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX184" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY184" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA184" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB184" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC184" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BE184" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF184" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG184" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH184" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI184" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ184" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK184" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL184" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM184" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN184" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO184" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP184" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="n">
+        <v>8217383</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>45976.5</v>
+      </c>
+      <c r="F185" t="n">
+        <v>16</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" t="n">
+        <v>1</v>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="n">
+        <v>1</v>
+      </c>
+      <c r="N185" t="n">
+        <v>2</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R185" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S185" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T185" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U185" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="V185" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W185" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X185" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA185" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK185" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL185" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AN185" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP185" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS185" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT185" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU185" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW185" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY185" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ185" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA185" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC185" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD185" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE185" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="BF185" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG185" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH185" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BI185" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ185" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BK185" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL185" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BM185" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN185" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO185" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP185" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="n">
+        <v>8217384</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>45976.5</v>
+      </c>
+      <c r="F186" t="n">
+        <v>16</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>2</v>
+      </c>
+      <c r="K186" t="n">
+        <v>2</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>2</v>
+      </c>
+      <c r="N186" t="n">
+        <v>2</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>['21', '42']</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="R186" t="n">
+        <v>2</v>
+      </c>
+      <c r="S186" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T186" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U186" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V186" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W186" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X186" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z186" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF186" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG186" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI186" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK186" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL186" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM186" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN186" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO186" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP186" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ186" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR186" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS186" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT186" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV186" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW186" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY186" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ186" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA186" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB186" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC186" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD186" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE186" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="BF186" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BG186" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH186" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="BI186" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ186" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BK186" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BL186" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM186" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN186" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BO186" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BP186" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="n">
+        <v>8217492</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>45976.5</v>
+      </c>
+      <c r="F187" t="n">
+        <v>16</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>1</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>1</v>
+      </c>
+      <c r="L187" t="n">
+        <v>2</v>
+      </c>
+      <c r="M187" t="n">
+        <v>1</v>
+      </c>
+      <c r="N187" t="n">
+        <v>3</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>['32', '88']</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R187" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S187" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T187" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U187" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V187" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W187" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X187" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI187" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ187" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK187" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AL187" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM187" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AN187" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO187" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ187" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR187" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS187" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT187" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU187" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW187" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX187" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY187" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ187" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA187" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB187" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC187" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD187" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BE187" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF187" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BG187" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH187" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="BI187" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ187" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BK187" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL187" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM187" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN187" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO187" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BP187" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="n">
+        <v>8217473</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>45976.5</v>
+      </c>
+      <c r="F188" t="n">
+        <v>16</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>1</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>1</v>
+      </c>
+      <c r="L188" t="n">
+        <v>2</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="n">
+        <v>2</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>['45+2', '90+4']</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R188" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S188" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T188" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U188" t="n">
+        <v>3</v>
+      </c>
+      <c r="V188" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="W188" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X188" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK188" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN188" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS188" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT188" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX188" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY188" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA188" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB188" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC188" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE188" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF188" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG188" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH188" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI188" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ188" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BK188" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BL188" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM188" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN188" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO188" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP188" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="n">
+        <v>8217542</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>45976.5</v>
+      </c>
+      <c r="F189" t="n">
+        <v>16</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>1</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1</v>
+      </c>
+      <c r="K189" t="n">
+        <v>2</v>
+      </c>
+      <c r="L189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="n">
+        <v>1</v>
+      </c>
+      <c r="N189" t="n">
+        <v>2</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R189" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S189" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T189" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U189" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V189" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="W189" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X189" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AG189" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH189" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AI189" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ189" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK189" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL189" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM189" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO189" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AP189" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ189" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR189" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS189" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT189" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AU189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX189" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY189" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA189" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB189" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC189" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE189" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="BF189" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BG189" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH189" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI189" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ189" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BK189" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL189" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM189" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BN189" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO189" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BP189" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="n">
+        <v>8217410</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>45976.5</v>
+      </c>
+      <c r="F190" t="n">
+        <v>16</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R190" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S190" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="T190" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U190" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V190" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W190" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X190" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AG190" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH190" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI190" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK190" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL190" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM190" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ190" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR190" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS190" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT190" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX190" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY190" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA190" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB190" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC190" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE190" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BF190" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG190" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH190" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BI190" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ190" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BK190" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL190" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM190" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BN190" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO190" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BP190" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="n">
+        <v>8217541</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>45976.5</v>
+      </c>
+      <c r="F191" t="n">
+        <v>16</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>1</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>1</v>
+      </c>
+      <c r="L191" t="n">
+        <v>3</v>
+      </c>
+      <c r="M191" t="n">
+        <v>1</v>
+      </c>
+      <c r="N191" t="n">
+        <v>4</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>['6', '72', '77']</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R191" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S191" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T191" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U191" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V191" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W191" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X191" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK191" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL191" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN191" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ191" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY191" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA191" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB191" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC191" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE191" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF191" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BG191" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH191" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI191" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ191" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BK191" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL191" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM191" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BN191" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO191" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP191" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="n">
+        <v>8217543</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>45976.5</v>
+      </c>
+      <c r="F192" t="n">
+        <v>16</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>2</v>
+      </c>
+      <c r="J192" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" t="n">
+        <v>3</v>
+      </c>
+      <c r="L192" t="n">
+        <v>3</v>
+      </c>
+      <c r="M192" t="n">
+        <v>2</v>
+      </c>
+      <c r="N192" t="n">
+        <v>5</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>['2', '11', '86']</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>['34', '77']</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="R192" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S192" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="T192" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U192" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V192" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W192" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X192" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH192" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AK192" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL192" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AN192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AR192" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS192" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AT192" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AU192" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV192" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW192" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX192" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY192" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ192" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA192" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB192" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC192" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD192" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BE192" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF192" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BG192" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH192" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI192" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ192" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK192" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BL192" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM192" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BN192" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO192" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP192" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="n">
+        <v>8217267</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>45976.60416666666</v>
+      </c>
+      <c r="F193" t="n">
+        <v>16</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>1</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>1</v>
+      </c>
+      <c r="L193" t="n">
+        <v>2</v>
+      </c>
+      <c r="M193" t="n">
+        <v>2</v>
+      </c>
+      <c r="N193" t="n">
+        <v>4</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>['45+3', '55']</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>['52', '82']</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R193" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S193" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="T193" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U193" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V193" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W193" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X193" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH193" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AI193" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ193" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AK193" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL193" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM193" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN193" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO193" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP193" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ193" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AR193" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS193" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT193" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU193" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV193" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW193" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX193" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY193" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ193" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA193" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB193" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC193" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD193" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE193" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF193" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BG193" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH193" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI193" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ193" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BK193" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL193" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM193" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN193" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO193" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BP193" t="n">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -40384,7 +40384,7 @@
         <v>2.37</v>
       </c>
       <c r="AU183" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV183" t="n">
         <v>2</v>
@@ -40396,7 +40396,7 @@
         <v>8</v>
       </c>
       <c r="AY183" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ183" t="n">
         <v>10</v>
@@ -40611,13 +40611,13 @@
         <v>8</v>
       </c>
       <c r="AX184" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY184" t="n">
         <v>9</v>
       </c>
       <c r="AZ184" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA184" t="n">
         <v>3</v>
@@ -41044,13 +41044,13 @@
         <v>2</v>
       </c>
       <c r="AW186" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX186" t="n">
         <v>1</v>
       </c>
       <c r="AY186" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ186" t="n">
         <v>3</v>
@@ -41262,13 +41262,13 @@
         <v>2</v>
       </c>
       <c r="AW187" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX187" t="n">
         <v>5</v>
       </c>
       <c r="AY187" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ187" t="n">
         <v>7</v>
@@ -41698,13 +41698,13 @@
         <v>6</v>
       </c>
       <c r="AW189" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX189" t="n">
         <v>9</v>
       </c>
       <c r="AY189" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ189" t="n">
         <v>15</v>
@@ -41919,22 +41919,22 @@
         <v>14</v>
       </c>
       <c r="AX190" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY190" t="n">
         <v>16</v>
       </c>
       <c r="AZ190" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA190" t="n">
         <v>5</v>
       </c>
       <c r="BB190" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC190" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD190" t="n">
         <v>1.73</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -40826,13 +40826,13 @@
         <v>1</v>
       </c>
       <c r="AW185" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX185" t="n">
         <v>2</v>
       </c>
       <c r="AY185" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ185" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -41919,13 +41919,13 @@
         <v>14</v>
       </c>
       <c r="AX190" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY190" t="n">
         <v>16</v>
       </c>
       <c r="AZ190" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA190" t="n">
         <v>5</v>
@@ -42131,7 +42131,7 @@
         <v>5</v>
       </c>
       <c r="AV191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW191" t="n">
         <v>4</v>
@@ -42143,7 +42143,7 @@
         <v>9</v>
       </c>
       <c r="AZ191" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA191" t="n">
         <v>2</v>
@@ -42346,13 +42346,13 @@
         <v>2.22</v>
       </c>
       <c r="AU192" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV192" t="n">
         <v>4</v>
       </c>
       <c r="AW192" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX192" t="n">
         <v>10</v>
@@ -42567,19 +42567,19 @@
         <v>9</v>
       </c>
       <c r="AV193" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW193" t="n">
         <v>8</v>
       </c>
       <c r="AX193" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY193" t="n">
         <v>17</v>
       </c>
       <c r="AZ193" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA193" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -40172,13 +40172,13 @@
         <v>1</v>
       </c>
       <c r="AW182" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX182" t="n">
         <v>7</v>
       </c>
       <c r="AY182" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ182" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP193"/>
+  <dimension ref="A1:BP195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.5</v>
@@ -4402,7 +4402,7 @@
         <v>2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -5925,10 +5925,10 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -7672,7 +7672,7 @@
         <v>1</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR33" t="n">
         <v>2.2</v>
@@ -9195,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.25</v>
@@ -9413,7 +9413,7 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.38</v>
@@ -9852,7 +9852,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR43" t="n">
         <v>1.16</v>
@@ -11814,7 +11814,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR52" t="n">
         <v>1.18</v>
@@ -12683,7 +12683,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.38</v>
@@ -12901,7 +12901,7 @@
         <v>3</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.38</v>
@@ -16174,7 +16174,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR72" t="n">
         <v>1.28</v>
@@ -18569,7 +18569,7 @@
         <v>0.33</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.63</v>
@@ -20098,7 +20098,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR90" t="n">
         <v>1.36</v>
@@ -20313,7 +20313,7 @@
         <v>1.33</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.38</v>
@@ -20970,7 +20970,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR94" t="n">
         <v>1.13</v>
@@ -21621,7 +21621,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.63</v>
@@ -24240,7 +24240,7 @@
         <v>1</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR109" t="n">
         <v>1.78</v>
@@ -25548,7 +25548,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR115" t="n">
         <v>1.5</v>
@@ -26199,7 +26199,7 @@
         <v>1</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ118" t="n">
         <v>1</v>
@@ -29251,7 +29251,7 @@
         <v>1.4</v>
       </c>
       <c r="AP132" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.38</v>
@@ -29687,7 +29687,7 @@
         <v>0.2</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.63</v>
@@ -30126,7 +30126,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR136" t="n">
         <v>1.32</v>
@@ -30780,7 +30780,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR139" t="n">
         <v>1.9</v>
@@ -34704,7 +34704,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR157" t="n">
         <v>1.19</v>
@@ -35358,7 +35358,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR160" t="n">
         <v>1.08</v>
@@ -36445,7 +36445,7 @@
         <v>1.5</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.5</v>
@@ -36881,7 +36881,7 @@
         <v>1.17</v>
       </c>
       <c r="AP167" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ167" t="n">
         <v>1.25</v>
@@ -39279,7 +39279,7 @@
         <v>1.29</v>
       </c>
       <c r="AP178" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.5</v>
@@ -39500,7 +39500,7 @@
         <v>0.13</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR179" t="n">
         <v>1.13</v>
@@ -40590,7 +40590,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR184" t="n">
         <v>1.62</v>
@@ -42549,7 +42549,7 @@
         <v>0.57</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ193" t="n">
         <v>0.63</v>
@@ -42628,6 +42628,442 @@
       </c>
       <c r="BP193" t="n">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="n">
+        <v>8217275</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>45983.39583333334</v>
+      </c>
+      <c r="F194" t="n">
+        <v>17</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>1</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" t="n">
+        <v>2</v>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="n">
+        <v>1</v>
+      </c>
+      <c r="N194" t="n">
+        <v>2</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="R194" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S194" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T194" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U194" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V194" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X194" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK194" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ194" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AU194" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV194" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW194" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX194" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY194" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ194" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA194" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB194" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC194" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD194" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BE194" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="BF194" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG194" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH194" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI194" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BJ194" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK194" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL194" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM194" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN194" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO194" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BP194" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="n">
+        <v>8217398</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>45983.39583333334</v>
+      </c>
+      <c r="F195" t="n">
+        <v>17</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>1</v>
+      </c>
+      <c r="K195" t="n">
+        <v>1</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
+        <v>2</v>
+      </c>
+      <c r="N195" t="n">
+        <v>2</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>['43', '87']</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="R195" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S195" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T195" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U195" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V195" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X195" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS195" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT195" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV195" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW195" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX195" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY195" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ195" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA195" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB195" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC195" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD195" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BE195" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF195" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BG195" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH195" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BI195" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ195" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK195" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL195" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM195" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN195" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO195" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP195" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP195"/>
+  <dimension ref="A1:BP205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3963,10 +3963,10 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.78</v>
@@ -4617,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5053,10 +5053,10 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5271,10 +5271,10 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -5489,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -5707,10 +5707,10 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -6146,7 +6146,7 @@
         <v>2</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR26" t="n">
         <v>1.04</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.63</v>
@@ -6582,7 +6582,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR28" t="n">
         <v>1.35</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.63</v>
@@ -7233,7 +7233,7 @@
         <v>1</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.38</v>
@@ -7451,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.5</v>
@@ -7890,7 +7890,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR34" t="n">
         <v>0.89</v>
@@ -8108,7 +8108,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR35" t="n">
         <v>2.14</v>
@@ -8541,7 +8541,7 @@
         <v>3</v>
       </c>
       <c r="AP37" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ37" t="n">
         <v>1</v>
@@ -8762,7 +8762,7 @@
         <v>0.13</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR38" t="n">
         <v>0.62</v>
@@ -8977,10 +8977,10 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR39" t="n">
         <v>1.87</v>
@@ -9416,7 +9416,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR41" t="n">
         <v>0.96</v>
@@ -9634,7 +9634,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR42" t="n">
         <v>1.11</v>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.78</v>
@@ -10067,7 +10067,7 @@
         <v>3</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.38</v>
@@ -10503,7 +10503,7 @@
         <v>1</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.38</v>
@@ -10724,7 +10724,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR47" t="n">
         <v>0.87</v>
@@ -10939,10 +10939,10 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR48" t="n">
         <v>1.01</v>
@@ -11160,7 +11160,7 @@
         <v>0.13</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR49" t="n">
         <v>0.84</v>
@@ -11378,7 +11378,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR50" t="n">
         <v>1.11</v>
@@ -11593,7 +11593,7 @@
         <v>1</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.13</v>
@@ -11811,7 +11811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.78</v>
@@ -12032,7 +12032,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR53" t="n">
         <v>1.14</v>
@@ -12250,7 +12250,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR54" t="n">
         <v>1.64</v>
@@ -12465,10 +12465,10 @@
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR55" t="n">
         <v>1.03</v>
@@ -12686,7 +12686,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR56" t="n">
         <v>1.53</v>
@@ -13337,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.5</v>
@@ -13555,7 +13555,7 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.38</v>
@@ -13991,7 +13991,7 @@
         <v>1.5</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.63</v>
@@ -14209,7 +14209,7 @@
         <v>2</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ63" t="n">
         <v>1</v>
@@ -14430,7 +14430,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR64" t="n">
         <v>2.16</v>
@@ -14648,7 +14648,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR65" t="n">
         <v>0.93</v>
@@ -14863,7 +14863,7 @@
         <v>0.5</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.38</v>
@@ -15081,7 +15081,7 @@
         <v>1</v>
       </c>
       <c r="AP67" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.5</v>
@@ -15302,7 +15302,7 @@
         <v>1</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR68" t="n">
         <v>1.75</v>
@@ -15735,7 +15735,7 @@
         <v>2</v>
       </c>
       <c r="AP70" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ70" t="n">
         <v>1</v>
@@ -15956,7 +15956,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR71" t="n">
         <v>1.75</v>
@@ -16392,7 +16392,7 @@
         <v>0.13</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR73" t="n">
         <v>0.97</v>
@@ -16607,7 +16607,7 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.63</v>
@@ -17261,7 +17261,7 @@
         <v>2.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ77" t="n">
         <v>1</v>
@@ -17700,7 +17700,7 @@
         <v>1</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR79" t="n">
         <v>1.83</v>
@@ -17915,10 +17915,10 @@
         <v>0.33</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR80" t="n">
         <v>1.16</v>
@@ -18136,7 +18136,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR81" t="n">
         <v>1.5</v>
@@ -18354,7 +18354,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR82" t="n">
         <v>1.37</v>
@@ -18787,7 +18787,7 @@
         <v>1.67</v>
       </c>
       <c r="AP84" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.5</v>
@@ -19005,7 +19005,7 @@
         <v>0.33</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.63</v>
@@ -19226,7 +19226,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR86" t="n">
         <v>1.21</v>
@@ -19441,7 +19441,7 @@
         <v>1.33</v>
       </c>
       <c r="AP87" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ87" t="n">
         <v>1</v>
@@ -19877,7 +19877,7 @@
         <v>1.67</v>
       </c>
       <c r="AP89" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.38</v>
@@ -20095,7 +20095,7 @@
         <v>2</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.78</v>
@@ -20534,7 +20534,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR92" t="n">
         <v>1.23</v>
@@ -20749,10 +20749,10 @@
         <v>1</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR93" t="n">
         <v>1.39</v>
@@ -20967,7 +20967,7 @@
         <v>2</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.89</v>
@@ -21188,7 +21188,7 @@
         <v>2</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR95" t="n">
         <v>1.58</v>
@@ -21406,7 +21406,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR96" t="n">
         <v>1.92</v>
@@ -21624,7 +21624,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR97" t="n">
         <v>1.6</v>
@@ -22060,7 +22060,7 @@
         <v>1</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR99" t="n">
         <v>1.84</v>
@@ -22275,7 +22275,7 @@
         <v>1</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.63</v>
@@ -22493,7 +22493,7 @@
         <v>1.5</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.5</v>
@@ -22929,7 +22929,7 @@
         <v>1.75</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.38</v>
@@ -23150,7 +23150,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR104" t="n">
         <v>1.61</v>
@@ -23583,10 +23583,10 @@
         <v>1.5</v>
       </c>
       <c r="AP106" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR106" t="n">
         <v>1.73</v>
@@ -23804,7 +23804,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR107" t="n">
         <v>1.35</v>
@@ -24237,7 +24237,7 @@
         <v>2.25</v>
       </c>
       <c r="AP109" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.78</v>
@@ -24455,7 +24455,7 @@
         <v>1</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.38</v>
@@ -24676,7 +24676,7 @@
         <v>2</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR111" t="n">
         <v>1.52</v>
@@ -24894,7 +24894,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR112" t="n">
         <v>1.35</v>
@@ -25109,10 +25109,10 @@
         <v>1</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR113" t="n">
         <v>1.51</v>
@@ -25330,7 +25330,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR114" t="n">
         <v>1.43</v>
@@ -25763,10 +25763,10 @@
         <v>1.25</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR116" t="n">
         <v>1.08</v>
@@ -26417,7 +26417,7 @@
         <v>0.75</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.25</v>
@@ -26635,7 +26635,7 @@
         <v>1.25</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.38</v>
@@ -27292,7 +27292,7 @@
         <v>1</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR123" t="n">
         <v>1.91</v>
@@ -27510,7 +27510,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR124" t="n">
         <v>1.56</v>
@@ -27725,7 +27725,7 @@
         <v>1.8</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.5</v>
@@ -28164,7 +28164,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR127" t="n">
         <v>1.34</v>
@@ -28382,7 +28382,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR128" t="n">
         <v>1.94</v>
@@ -28597,10 +28597,10 @@
         <v>0.6</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR129" t="n">
         <v>1.13</v>
@@ -28815,7 +28815,7 @@
         <v>1</v>
       </c>
       <c r="AP130" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.13</v>
@@ -29033,7 +29033,7 @@
         <v>1.4</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ131" t="n">
         <v>1</v>
@@ -29472,7 +29472,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR133" t="n">
         <v>2.04</v>
@@ -29905,7 +29905,7 @@
         <v>1.4</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ135" t="n">
         <v>1</v>
@@ -30123,7 +30123,7 @@
         <v>2</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.78</v>
@@ -30344,7 +30344,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR137" t="n">
         <v>1.34</v>
@@ -30559,7 +30559,7 @@
         <v>1</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.38</v>
@@ -30777,7 +30777,7 @@
         <v>2</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.89</v>
@@ -30998,7 +30998,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR140" t="n">
         <v>1.65</v>
@@ -31216,7 +31216,7 @@
         <v>2</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR141" t="n">
         <v>1.53</v>
@@ -31434,7 +31434,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR142" t="n">
         <v>1.33</v>
@@ -31649,7 +31649,7 @@
         <v>1.2</v>
       </c>
       <c r="AP143" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.25</v>
@@ -34483,7 +34483,7 @@
         <v>1.17</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.38</v>
@@ -34701,7 +34701,7 @@
         <v>1.83</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.89</v>
@@ -34919,10 +34919,10 @@
         <v>0.67</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR158" t="n">
         <v>1.31</v>
@@ -35137,10 +35137,10 @@
         <v>1.83</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR159" t="n">
         <v>1.27</v>
@@ -35355,7 +35355,7 @@
         <v>2.17</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.78</v>
@@ -35573,10 +35573,10 @@
         <v>0.83</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR161" t="n">
         <v>1.49</v>
@@ -35791,10 +35791,10 @@
         <v>1.33</v>
       </c>
       <c r="AP162" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR162" t="n">
         <v>1.45</v>
@@ -36009,10 +36009,10 @@
         <v>1.17</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR163" t="n">
         <v>1.87</v>
@@ -36227,10 +36227,10 @@
         <v>1.17</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR164" t="n">
         <v>1.28</v>
@@ -36448,7 +36448,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR165" t="n">
         <v>1.81</v>
@@ -36663,10 +36663,10 @@
         <v>0.67</v>
       </c>
       <c r="AP166" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR166" t="n">
         <v>1.76</v>
@@ -36884,7 +36884,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR167" t="n">
         <v>1.54</v>
@@ -37099,10 +37099,10 @@
         <v>2.33</v>
       </c>
       <c r="AP168" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR168" t="n">
         <v>1.78</v>
@@ -37535,10 +37535,10 @@
         <v>0.71</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ170" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR170" t="n">
         <v>1.29</v>
@@ -37974,7 +37974,7 @@
         <v>2</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR172" t="n">
         <v>1.49</v>
@@ -38192,7 +38192,7 @@
         <v>1</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR173" t="n">
         <v>1.87</v>
@@ -38625,7 +38625,7 @@
         <v>1.14</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ175" t="n">
         <v>1</v>
@@ -38843,10 +38843,10 @@
         <v>1.57</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR176" t="n">
         <v>1.05</v>
@@ -39061,7 +39061,7 @@
         <v>1.29</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.13</v>
@@ -39718,7 +39718,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ180" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR180" t="n">
         <v>2.04</v>
@@ -39933,7 +39933,7 @@
         <v>1.14</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ181" t="n">
         <v>1.38</v>
@@ -40154,7 +40154,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR182" t="n">
         <v>2</v>
@@ -40372,7 +40372,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR183" t="n">
         <v>1.25</v>
@@ -40805,7 +40805,7 @@
         <v>1</v>
       </c>
       <c r="AP185" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ185" t="n">
         <v>1</v>
@@ -41026,7 +41026,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR186" t="n">
         <v>1.48</v>
@@ -41241,7 +41241,7 @@
         <v>1.43</v>
       </c>
       <c r="AP187" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.25</v>
@@ -41462,7 +41462,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR188" t="n">
         <v>1.27</v>
@@ -41677,7 +41677,7 @@
         <v>1.71</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.63</v>
@@ -41895,7 +41895,7 @@
         <v>1.43</v>
       </c>
       <c r="AP190" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ190" t="n">
         <v>1.38</v>
@@ -42116,7 +42116,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ191" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR191" t="n">
         <v>1.58</v>
@@ -42331,7 +42331,7 @@
         <v>0.71</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ192" t="n">
         <v>0.63</v>
@@ -42782,22 +42782,22 @@
         <v>3.44</v>
       </c>
       <c r="AU194" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV194" t="n">
         <v>4</v>
       </c>
       <c r="AW194" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX194" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY194" t="n">
         <v>11</v>
       </c>
       <c r="AZ194" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA194" t="n">
         <v>2</v>
@@ -43000,7 +43000,7 @@
         <v>2.73</v>
       </c>
       <c r="AU195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV195" t="n">
         <v>6</v>
@@ -43012,7 +43012,7 @@
         <v>12</v>
       </c>
       <c r="AY195" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ195" t="n">
         <v>18</v>
@@ -43064,6 +43064,2186 @@
       </c>
       <c r="BP195" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="n">
+        <v>8217512</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>45983.5</v>
+      </c>
+      <c r="F196" t="n">
+        <v>17</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>2</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>2</v>
+      </c>
+      <c r="L196" t="n">
+        <v>2</v>
+      </c>
+      <c r="M196" t="n">
+        <v>2</v>
+      </c>
+      <c r="N196" t="n">
+        <v>4</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>['9', '27']</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>['78', '82']</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R196" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S196" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T196" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U196" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V196" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W196" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X196" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR196" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS196" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT196" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU196" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW196" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX196" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY196" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ196" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA196" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB196" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC196" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD196" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE196" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF196" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG196" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH196" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BI196" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ196" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK196" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BL196" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BM196" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN196" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO196" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP196" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="n">
+        <v>8217385</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>45983.5</v>
+      </c>
+      <c r="F197" t="n">
+        <v>17</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" t="n">
+        <v>2</v>
+      </c>
+      <c r="N197" t="n">
+        <v>2</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>['49', '90+1']</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R197" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S197" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T197" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U197" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V197" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W197" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X197" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR197" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AS197" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT197" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AU197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV197" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW197" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX197" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY197" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ197" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA197" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB197" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC197" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD197" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BE197" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="BF197" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BG197" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH197" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BI197" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ197" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK197" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL197" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM197" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN197" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO197" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BP197" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="n">
+        <v>8217415</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>45983.5</v>
+      </c>
+      <c r="F198" t="n">
+        <v>17</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>1</v>
+      </c>
+      <c r="J198" t="n">
+        <v>1</v>
+      </c>
+      <c r="K198" t="n">
+        <v>2</v>
+      </c>
+      <c r="L198" t="n">
+        <v>1</v>
+      </c>
+      <c r="M198" t="n">
+        <v>3</v>
+      </c>
+      <c r="N198" t="n">
+        <v>4</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>['14', '56', '90+5']</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R198" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S198" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="T198" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U198" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V198" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W198" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X198" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ198" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB198" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC198" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD198" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE198" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF198" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG198" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH198" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="BI198" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM198" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN198" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO198" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP198" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="n">
+        <v>8217416</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>45983.5</v>
+      </c>
+      <c r="F199" t="n">
+        <v>17</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>3</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>3</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>['53', '75', '89']</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="R199" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S199" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T199" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U199" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V199" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W199" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X199" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY199" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC199" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD199" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BE199" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="BF199" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG199" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH199" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BI199" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ199" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BK199" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM199" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN199" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO199" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BP199" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="n">
+        <v>8217413</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>45983.5</v>
+      </c>
+      <c r="F200" t="n">
+        <v>17</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>1</v>
+      </c>
+      <c r="J200" t="n">
+        <v>2</v>
+      </c>
+      <c r="K200" t="n">
+        <v>3</v>
+      </c>
+      <c r="L200" t="n">
+        <v>3</v>
+      </c>
+      <c r="M200" t="n">
+        <v>3</v>
+      </c>
+      <c r="N200" t="n">
+        <v>6</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>['35', '47', '69']</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>['9', '24', '65']</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R200" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S200" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="T200" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U200" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V200" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W200" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X200" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ200" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR200" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS200" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU200" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV200" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW200" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX200" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY200" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB200" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC200" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE200" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF200" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BG200" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH200" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI200" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ200" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK200" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL200" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BM200" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BN200" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO200" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BP200" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="n">
+        <v>8217414</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>45983.5</v>
+      </c>
+      <c r="F201" t="n">
+        <v>17</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>1</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>1</v>
+      </c>
+      <c r="L201" t="n">
+        <v>3</v>
+      </c>
+      <c r="M201" t="n">
+        <v>1</v>
+      </c>
+      <c r="N201" t="n">
+        <v>4</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>['24', '56', '72']</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R201" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S201" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T201" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U201" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V201" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W201" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X201" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU201" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV201" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY201" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB201" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF201" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BG201" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI201" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ201" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK201" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL201" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BM201" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BN201" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO201" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP201" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>8217493</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>45983.5</v>
+      </c>
+      <c r="F202" t="n">
+        <v>17</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>2</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>2</v>
+      </c>
+      <c r="L202" t="n">
+        <v>2</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="n">
+        <v>2</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>['24', '32']</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R202" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S202" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T202" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U202" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V202" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W202" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X202" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AU202" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV202" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB202" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN202" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO202" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BP202" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>8217417</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>45983.5</v>
+      </c>
+      <c r="F203" t="n">
+        <v>17</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>2</v>
+      </c>
+      <c r="J203" t="n">
+        <v>2</v>
+      </c>
+      <c r="K203" t="n">
+        <v>4</v>
+      </c>
+      <c r="L203" t="n">
+        <v>2</v>
+      </c>
+      <c r="M203" t="n">
+        <v>2</v>
+      </c>
+      <c r="N203" t="n">
+        <v>4</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>['7', '13']</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>['22', '41']</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R203" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S203" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T203" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U203" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V203" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W203" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X203" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU203" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV203" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB203" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC203" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE203" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF203" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG203" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH203" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="BI203" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ203" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK203" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL203" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM203" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN203" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO203" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BP203" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>8217451</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>45983.5</v>
+      </c>
+      <c r="F204" t="n">
+        <v>17</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>1</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="n">
+        <v>1</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R204" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S204" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U204" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V204" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W204" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X204" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AR204" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AS204" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT204" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AU204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV204" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW204" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY204" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB204" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC204" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF204" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BG204" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH204" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="BI204" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ204" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BK204" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL204" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM204" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN204" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO204" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BP204" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>8217412</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>45983.5</v>
+      </c>
+      <c r="F205" t="n">
+        <v>17</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" t="n">
+        <v>1</v>
+      </c>
+      <c r="L205" t="n">
+        <v>1</v>
+      </c>
+      <c r="M205" t="n">
+        <v>1</v>
+      </c>
+      <c r="N205" t="n">
+        <v>2</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R205" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S205" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T205" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U205" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V205" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="W205" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X205" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG205" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI205" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ205" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK205" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL205" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM205" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN205" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO205" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BP205" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -45183,7 +45183,7 @@
         <v>4</v>
       </c>
       <c r="AV205" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW205" t="n">
         <v>8</v>
@@ -45195,7 +45195,7 @@
         <v>12</v>
       </c>
       <c r="AZ205" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA205" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -43445,13 +43445,13 @@
         <v>6</v>
       </c>
       <c r="AX197" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY197" t="n">
         <v>9</v>
       </c>
       <c r="AZ197" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA197" t="n">
         <v>4</v>
@@ -43660,13 +43660,13 @@
         <v>4</v>
       </c>
       <c r="AW198" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX198" t="n">
         <v>4</v>
       </c>
       <c r="AY198" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ198" t="n">
         <v>8</v>
@@ -43881,13 +43881,13 @@
         <v>12</v>
       </c>
       <c r="AX199" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY199" t="n">
         <v>19</v>
       </c>
       <c r="AZ199" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA199" t="n">
         <v>9</v>
@@ -44962,7 +44962,7 @@
         <v>2.19</v>
       </c>
       <c r="AU204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV204" t="n">
         <v>3</v>
@@ -44974,7 +44974,7 @@
         <v>14</v>
       </c>
       <c r="AY204" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ204" t="n">
         <v>17</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -44750,13 +44750,13 @@
         <v>6</v>
       </c>
       <c r="AW203" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX203" t="n">
         <v>9</v>
       </c>
       <c r="AY203" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ203" t="n">
         <v>15</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP205"/>
+  <dimension ref="A1:BP206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.63</v>
@@ -3312,7 +3312,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -8105,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.11</v>
@@ -11596,7 +11596,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR51" t="n">
         <v>1.68</v>
@@ -14427,7 +14427,7 @@
         <v>0</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.78</v>
@@ -17482,7 +17482,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR78" t="n">
         <v>1.77</v>
@@ -21403,7 +21403,7 @@
         <v>1</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ96" t="n">
         <v>1</v>
@@ -24022,7 +24022,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR108" t="n">
         <v>1.23</v>
@@ -25981,7 +25981,7 @@
         <v>0.25</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ117" t="n">
         <v>0.63</v>
@@ -28818,7 +28818,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR130" t="n">
         <v>1.73</v>
@@ -29469,7 +29469,7 @@
         <v>1</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.67</v>
@@ -32739,7 +32739,7 @@
         <v>1.5</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.5</v>
@@ -34268,7 +34268,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR155" t="n">
         <v>1.24</v>
@@ -37320,7 +37320,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR169" t="n">
         <v>1.64</v>
@@ -39064,7 +39064,7 @@
         <v>2</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR177" t="n">
         <v>1.37</v>
@@ -40151,7 +40151,7 @@
         <v>1.14</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ182" t="n">
         <v>1.33</v>
@@ -45243,6 +45243,224 @@
         <v>2.59</v>
       </c>
       <c r="BP205" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="n">
+        <v>8217508</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>45988.70833333334</v>
+      </c>
+      <c r="F206" t="n">
+        <v>18</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" t="n">
+        <v>1</v>
+      </c>
+      <c r="L206" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" t="n">
+        <v>2</v>
+      </c>
+      <c r="N206" t="n">
+        <v>3</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>['19', '90+6']</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R206" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S206" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T206" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U206" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="V206" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W206" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X206" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE206" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF206" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="BG206" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH206" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BI206" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ206" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK206" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL206" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM206" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN206" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO206" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BP206" t="n">
         <v>1.44</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP206"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ3" t="n">
         <v>1</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.33</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.78</v>
@@ -6364,7 +6364,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR27" t="n">
         <v>2.21</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.67</v>
@@ -6800,7 +6800,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR29" t="n">
         <v>1.67</v>
@@ -7015,7 +7015,7 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ30" t="n">
         <v>1</v>
@@ -7236,7 +7236,7 @@
         <v>1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR31" t="n">
         <v>0.89</v>
@@ -7454,7 +7454,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR32" t="n">
         <v>1.41</v>
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.67</v>
@@ -8323,10 +8323,10 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR36" t="n">
         <v>0.73</v>
@@ -8544,7 +8544,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR37" t="n">
         <v>1.09</v>
@@ -8759,7 +8759,7 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.33</v>
@@ -9198,7 +9198,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR40" t="n">
         <v>1.06</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ42" t="n">
         <v>1</v>
@@ -10070,7 +10070,7 @@
         <v>2</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR44" t="n">
         <v>0.89</v>
@@ -10285,10 +10285,10 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR45" t="n">
         <v>1.66</v>
@@ -10506,7 +10506,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR46" t="n">
         <v>0.82</v>
@@ -10721,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.44</v>
@@ -11157,7 +11157,7 @@
         <v>2</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.78</v>
@@ -11375,7 +11375,7 @@
         <v>3</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.33</v>
@@ -12029,7 +12029,7 @@
         <v>2</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.44</v>
@@ -12247,7 +12247,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ54" t="n">
         <v>1</v>
@@ -12904,7 +12904,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR57" t="n">
         <v>1.22</v>
@@ -13119,10 +13119,10 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR58" t="n">
         <v>1.1</v>
@@ -13340,7 +13340,7 @@
         <v>2</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR59" t="n">
         <v>1.05</v>
@@ -13558,7 +13558,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR60" t="n">
         <v>1.24</v>
@@ -13773,10 +13773,10 @@
         <v>0</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR61" t="n">
         <v>1.28</v>
@@ -13994,7 +13994,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR62" t="n">
         <v>1.49</v>
@@ -14212,7 +14212,7 @@
         <v>1</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR63" t="n">
         <v>1.18</v>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.67</v>
@@ -14866,7 +14866,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR66" t="n">
         <v>1.37</v>
@@ -15084,7 +15084,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR67" t="n">
         <v>1.92</v>
@@ -15517,10 +15517,10 @@
         <v>0</v>
       </c>
       <c r="AP69" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR69" t="n">
         <v>1.68</v>
@@ -15953,7 +15953,7 @@
         <v>1.5</v>
       </c>
       <c r="AP71" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.11</v>
@@ -16171,7 +16171,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.89</v>
@@ -16389,7 +16389,7 @@
         <v>1</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.78</v>
@@ -16610,7 +16610,7 @@
         <v>1</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR74" t="n">
         <v>1.07</v>
@@ -16825,10 +16825,10 @@
         <v>2</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR75" t="n">
         <v>1.55</v>
@@ -17043,10 +17043,10 @@
         <v>1</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR76" t="n">
         <v>1.56</v>
@@ -17264,7 +17264,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR77" t="n">
         <v>1.18</v>
@@ -17479,7 +17479,7 @@
         <v>2</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.33</v>
@@ -18133,7 +18133,7 @@
         <v>1.67</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.44</v>
@@ -18351,7 +18351,7 @@
         <v>2</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.33</v>
@@ -18572,7 +18572,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR83" t="n">
         <v>1.4</v>
@@ -18790,7 +18790,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR84" t="n">
         <v>1.65</v>
@@ -19008,7 +19008,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR85" t="n">
         <v>1.77</v>
@@ -19223,7 +19223,7 @@
         <v>1.67</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.67</v>
@@ -19659,10 +19659,10 @@
         <v>1</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR88" t="n">
         <v>1.5</v>
@@ -19880,7 +19880,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR89" t="n">
         <v>1.72</v>
@@ -20316,7 +20316,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR91" t="n">
         <v>1.43</v>
@@ -20531,7 +20531,7 @@
         <v>2</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.33</v>
@@ -21185,7 +21185,7 @@
         <v>2.33</v>
       </c>
       <c r="AP95" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.78</v>
@@ -21839,10 +21839,10 @@
         <v>1.75</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR98" t="n">
         <v>1.57</v>
@@ -22278,7 +22278,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR100" t="n">
         <v>1.28</v>
@@ -22496,7 +22496,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR101" t="n">
         <v>1.22</v>
@@ -22711,10 +22711,10 @@
         <v>1.5</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR102" t="n">
         <v>1.08</v>
@@ -22932,7 +22932,7 @@
         <v>1</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR103" t="n">
         <v>1.16</v>
@@ -23147,7 +23147,7 @@
         <v>1.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.78</v>
@@ -23365,10 +23365,10 @@
         <v>2.25</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR105" t="n">
         <v>2.03</v>
@@ -23801,7 +23801,7 @@
         <v>0.25</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.67</v>
@@ -24019,7 +24019,7 @@
         <v>1.33</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.33</v>
@@ -24458,7 +24458,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR110" t="n">
         <v>1.39</v>
@@ -24673,7 +24673,7 @@
         <v>1</v>
       </c>
       <c r="AP111" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.11</v>
@@ -24891,7 +24891,7 @@
         <v>2</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.78</v>
@@ -25327,7 +25327,7 @@
         <v>2.25</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.33</v>
@@ -25545,7 +25545,7 @@
         <v>1.75</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.89</v>
@@ -25984,7 +25984,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR117" t="n">
         <v>1.78</v>
@@ -26420,7 +26420,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR119" t="n">
         <v>1.77</v>
@@ -26638,7 +26638,7 @@
         <v>2</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR120" t="n">
         <v>1.49</v>
@@ -26853,10 +26853,10 @@
         <v>1.8</v>
       </c>
       <c r="AP121" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR121" t="n">
         <v>1.19</v>
@@ -27071,10 +27071,10 @@
         <v>1.8</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR122" t="n">
         <v>1.25</v>
@@ -27507,7 +27507,7 @@
         <v>1.4</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.33</v>
@@ -27728,7 +27728,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR125" t="n">
         <v>1.35</v>
@@ -27943,10 +27943,10 @@
         <v>0.8</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR126" t="n">
         <v>1.7</v>
@@ -28161,7 +28161,7 @@
         <v>1.4</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.78</v>
@@ -28379,7 +28379,7 @@
         <v>1.6</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.44</v>
@@ -29036,7 +29036,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR131" t="n">
         <v>1.17</v>
@@ -29254,7 +29254,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR132" t="n">
         <v>1.65</v>
@@ -29690,7 +29690,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR134" t="n">
         <v>1.51</v>
@@ -30341,7 +30341,7 @@
         <v>1</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ137" t="n">
         <v>1</v>
@@ -30562,7 +30562,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR138" t="n">
         <v>1.34</v>
@@ -30995,7 +30995,7 @@
         <v>0.8</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.11</v>
@@ -31213,7 +31213,7 @@
         <v>1.8</v>
       </c>
       <c r="AP141" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.33</v>
@@ -31431,7 +31431,7 @@
         <v>2.2</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ142" t="n">
         <v>1.78</v>
@@ -31652,7 +31652,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR143" t="n">
         <v>1.7</v>
@@ -31867,10 +31867,10 @@
         <v>1.5</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR144" t="n">
         <v>1.9</v>
@@ -32085,10 +32085,10 @@
         <v>1.33</v>
       </c>
       <c r="AP145" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR145" t="n">
         <v>1.58</v>
@@ -32303,7 +32303,7 @@
         <v>1.17</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ146" t="n">
         <v>1</v>
@@ -32521,10 +32521,10 @@
         <v>1.17</v>
       </c>
       <c r="AP147" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR147" t="n">
         <v>1.5</v>
@@ -32742,7 +32742,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR148" t="n">
         <v>1.87</v>
@@ -32957,10 +32957,10 @@
         <v>1.67</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR149" t="n">
         <v>1.26</v>
@@ -33175,10 +33175,10 @@
         <v>0.67</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR150" t="n">
         <v>1.23</v>
@@ -33396,7 +33396,7 @@
         <v>1</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR151" t="n">
         <v>1.87</v>
@@ -33611,10 +33611,10 @@
         <v>0.33</v>
       </c>
       <c r="AP152" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR152" t="n">
         <v>1.15</v>
@@ -33829,10 +33829,10 @@
         <v>2</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR153" t="n">
         <v>1.59</v>
@@ -34047,10 +34047,10 @@
         <v>1.17</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR154" t="n">
         <v>1.25</v>
@@ -34265,7 +34265,7 @@
         <v>1</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ155" t="n">
         <v>1.33</v>
@@ -34486,7 +34486,7 @@
         <v>2</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR156" t="n">
         <v>1.47</v>
@@ -37317,7 +37317,7 @@
         <v>1.33</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.33</v>
@@ -37753,10 +37753,10 @@
         <v>1.14</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR171" t="n">
         <v>1.8</v>
@@ -37971,7 +37971,7 @@
         <v>0.57</v>
       </c>
       <c r="AP172" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.67</v>
@@ -38407,10 +38407,10 @@
         <v>1.29</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR174" t="n">
         <v>1.23</v>
@@ -38628,7 +38628,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR175" t="n">
         <v>1.85</v>
@@ -39282,7 +39282,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR178" t="n">
         <v>1.52</v>
@@ -39497,7 +39497,7 @@
         <v>1.57</v>
       </c>
       <c r="AP179" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="AQ179" t="n">
         <v>1.89</v>
@@ -39715,7 +39715,7 @@
         <v>0.71</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ180" t="n">
         <v>1</v>
@@ -39936,7 +39936,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR181" t="n">
         <v>1.14</v>
@@ -40369,7 +40369,7 @@
         <v>1.43</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.11</v>
@@ -40587,7 +40587,7 @@
         <v>2</v>
       </c>
       <c r="AP184" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.78</v>
@@ -41023,7 +41023,7 @@
         <v>1.29</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.67</v>
@@ -41244,7 +41244,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR187" t="n">
         <v>1.72</v>
@@ -41459,7 +41459,7 @@
         <v>1.71</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.33</v>
@@ -41680,7 +41680,7 @@
         <v>2</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR189" t="n">
         <v>1.38</v>
@@ -41898,7 +41898,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR190" t="n">
         <v>1.72</v>
@@ -42113,7 +42113,7 @@
         <v>1</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ191" t="n">
         <v>0.78</v>
@@ -42334,7 +42334,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ192" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR192" t="n">
         <v>1.32</v>
@@ -42552,7 +42552,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR193" t="n">
         <v>1.81</v>
@@ -45462,6 +45462,2404 @@
       </c>
       <c r="BP206" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="n">
+        <v>8217283</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>45990.39583333334</v>
+      </c>
+      <c r="F207" t="n">
+        <v>18</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>1</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>1</v>
+      </c>
+      <c r="L207" t="n">
+        <v>2</v>
+      </c>
+      <c r="M207" t="n">
+        <v>1</v>
+      </c>
+      <c r="N207" t="n">
+        <v>3</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>['37', '68']</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R207" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S207" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="T207" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U207" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V207" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W207" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X207" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT207" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU207" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV207" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW207" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX207" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY207" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ207" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA207" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB207" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC207" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD207" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE207" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="BF207" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BG207" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH207" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI207" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ207" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BK207" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL207" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM207" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BN207" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO207" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP207" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="n">
+        <v>8217277</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>45990.39583333334</v>
+      </c>
+      <c r="F208" t="n">
+        <v>18</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>1</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>1</v>
+      </c>
+      <c r="L208" t="n">
+        <v>1</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>1</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R208" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S208" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T208" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U208" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V208" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="W208" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X208" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AI208" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK208" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN208" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO208" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP208" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ208" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR208" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS208" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT208" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV208" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW208" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX208" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY208" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA208" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB208" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC208" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD208" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BE208" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF208" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BG208" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH208" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI208" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ208" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BK208" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL208" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM208" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN208" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO208" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BP208" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="n">
+        <v>8217513</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>45990.5</v>
+      </c>
+      <c r="F209" t="n">
+        <v>18</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>3</v>
+      </c>
+      <c r="J209" t="n">
+        <v>1</v>
+      </c>
+      <c r="K209" t="n">
+        <v>4</v>
+      </c>
+      <c r="L209" t="n">
+        <v>3</v>
+      </c>
+      <c r="M209" t="n">
+        <v>3</v>
+      </c>
+      <c r="N209" t="n">
+        <v>6</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>['11', '22', '45+4']</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>['37', '66', '86']</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R209" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S209" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T209" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U209" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V209" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W209" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X209" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ209" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS209" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AT209" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AU209" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW209" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX209" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY209" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA209" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB209" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC209" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD209" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE209" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF209" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG209" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH209" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BI209" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ209" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BK209" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BL209" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM209" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BN209" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO209" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="BP209" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="n">
+        <v>8217452</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>45990.5</v>
+      </c>
+      <c r="F210" t="n">
+        <v>18</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>2</v>
+      </c>
+      <c r="M210" t="n">
+        <v>1</v>
+      </c>
+      <c r="N210" t="n">
+        <v>3</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>['82', '90+7']</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R210" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S210" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T210" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U210" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V210" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W210" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X210" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AQ210" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT210" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU210" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV210" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY210" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB210" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC210" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD210" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE210" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BF210" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG210" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH210" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BI210" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ210" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK210" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BL210" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM210" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BN210" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO210" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BP210" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="n">
+        <v>8217454</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>45990.5</v>
+      </c>
+      <c r="F211" t="n">
+        <v>18</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>1</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" t="n">
+        <v>2</v>
+      </c>
+      <c r="L211" t="n">
+        <v>4</v>
+      </c>
+      <c r="M211" t="n">
+        <v>3</v>
+      </c>
+      <c r="N211" t="n">
+        <v>7</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>['45+1', '53', '85', '86']</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>['33', '57', '72']</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R211" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S211" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="T211" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U211" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V211" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="W211" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X211" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ211" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT211" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU211" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV211" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB211" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC211" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD211" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BE211" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF211" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG211" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH211" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="BI211" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ211" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK211" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL211" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM211" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BN211" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO211" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP211" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="n">
+        <v>8217544</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>45990.5</v>
+      </c>
+      <c r="F212" t="n">
+        <v>18</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>1</v>
+      </c>
+      <c r="N212" t="n">
+        <v>1</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R212" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S212" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T212" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U212" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="V212" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W212" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X212" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AK212" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL212" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ212" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR212" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS212" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT212" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU212" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA212" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB212" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC212" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BE212" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="BF212" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BG212" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH212" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BI212" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ212" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK212" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL212" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM212" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN212" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO212" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP212" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>8217545</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>45990.5</v>
+      </c>
+      <c r="F213" t="n">
+        <v>18</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>1</v>
+      </c>
+      <c r="L213" t="n">
+        <v>2</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="n">
+        <v>2</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>['8', '50']</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R213" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S213" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="T213" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U213" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V213" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="W213" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X213" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ213" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR213" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS213" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT213" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU213" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW213" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX213" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY213" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ213" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA213" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB213" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC213" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD213" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BE213" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF213" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG213" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH213" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI213" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ213" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BK213" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BL213" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM213" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BN213" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO213" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BP213" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>8217475</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>45990.5</v>
+      </c>
+      <c r="F214" t="n">
+        <v>18</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>1</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" t="n">
+        <v>2</v>
+      </c>
+      <c r="L214" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" t="n">
+        <v>2</v>
+      </c>
+      <c r="N214" t="n">
+        <v>3</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>['8', '61']</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R214" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S214" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T214" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U214" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="V214" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W214" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X214" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AU214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW214" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY214" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB214" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE214" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BI214" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM214" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN214" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO214" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP214" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>8217474</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>45990.5</v>
+      </c>
+      <c r="F215" t="n">
+        <v>18</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="n">
+        <v>1</v>
+      </c>
+      <c r="N215" t="n">
+        <v>2</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R215" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S215" t="n">
+        <v>7</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U215" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="V215" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W215" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X215" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU215" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY215" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA215" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB215" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC215" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BE215" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF215" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH215" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI215" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ215" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK215" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL215" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM215" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN215" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO215" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP215" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>8217560</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>45990.5</v>
+      </c>
+      <c r="F216" t="n">
+        <v>18</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1</v>
+      </c>
+      <c r="K216" t="n">
+        <v>1</v>
+      </c>
+      <c r="L216" t="n">
+        <v>3</v>
+      </c>
+      <c r="M216" t="n">
+        <v>1</v>
+      </c>
+      <c r="N216" t="n">
+        <v>4</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>['64', '80', '90+10']</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>['18']</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R216" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S216" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T216" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U216" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V216" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W216" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X216" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU216" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV216" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW216" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY216" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA216" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB216" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC216" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BE216" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF216" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG216" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH216" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BI216" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ216" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK216" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL216" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM216" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BN216" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO216" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BP216" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>8217453</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>45990.5</v>
+      </c>
+      <c r="F217" t="n">
+        <v>18</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>1</v>
+      </c>
+      <c r="J217" t="n">
+        <v>1</v>
+      </c>
+      <c r="K217" t="n">
+        <v>2</v>
+      </c>
+      <c r="L217" t="n">
+        <v>2</v>
+      </c>
+      <c r="M217" t="n">
+        <v>2</v>
+      </c>
+      <c r="N217" t="n">
+        <v>4</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>['39', '63']</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>['45', '84']</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R217" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S217" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U217" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V217" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W217" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X217" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU217" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX217" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY217" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB217" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC217" t="n">
+  